--- a/reports/For Winter Ending (Prior Year)_Visits.xlsx
+++ b/reports/For Winter Ending (Prior Year)_Visits.xlsx
@@ -34,16 +34,16 @@
     <t>Purgatory Passes</t>
   </si>
   <si>
+    <t>Purgatory Comp Tickets</t>
+  </si>
+  <si>
+    <t>Purgatory Uplift Tickets</t>
+  </si>
+  <si>
     <t>Purgatory Tickets</t>
   </si>
   <si>
     <t>Purgatory Coaster</t>
-  </si>
-  <si>
-    <t>Purgatory Comp Tickets</t>
-  </si>
-  <si>
-    <t>Purgatory Uplift Tickets</t>
   </si>
 </sst>
 </file>
@@ -434,10 +434,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>45601</v>
+        <v>45612</v>
       </c>
       <c r="C2" s="2">
-        <v>1</v>
+        <v>987</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -448,10 +448,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>45604</v>
+        <v>45613</v>
       </c>
       <c r="C3" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>5</v>
@@ -462,13 +462,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>45605</v>
+        <v>45614</v>
       </c>
       <c r="C4" s="2">
-        <v>164</v>
+        <v>4</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -476,10 +476,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>45605</v>
+        <v>45615</v>
       </c>
       <c r="C5" s="2">
-        <v>8</v>
+        <v>167</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>5</v>
@@ -490,10 +490,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>45612</v>
+        <v>45616</v>
       </c>
       <c r="C6" s="2">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>5</v>
@@ -504,10 +504,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="2">
-        <v>45613</v>
+        <v>45616</v>
       </c>
       <c r="C7" s="2">
-        <v>769</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>5</v>
@@ -518,10 +518,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>45615</v>
+        <v>45617</v>
       </c>
       <c r="C8" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>5</v>
@@ -535,10 +535,10 @@
         <v>45618</v>
       </c>
       <c r="C9" s="2">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -546,10 +546,10 @@
         <v>4</v>
       </c>
       <c r="B10" s="2">
-        <v>45619</v>
+        <v>45618</v>
       </c>
       <c r="C10" s="2">
-        <v>2</v>
+        <v>343</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>5</v>
@@ -563,7 +563,7 @@
         <v>45619</v>
       </c>
       <c r="C11" s="2">
-        <v>4</v>
+        <v>85</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>5</v>
@@ -574,7 +574,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="2">
-        <v>45619</v>
+        <v>45620</v>
       </c>
       <c r="C12" s="2">
         <v>2</v>
@@ -591,10 +591,10 @@
         <v>45620</v>
       </c>
       <c r="C13" s="2">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -602,13 +602,13 @@
         <v>4</v>
       </c>
       <c r="B14" s="2">
-        <v>45622</v>
+        <v>45621</v>
       </c>
       <c r="C14" s="2">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -616,10 +616,10 @@
         <v>4</v>
       </c>
       <c r="B15" s="2">
-        <v>45623</v>
+        <v>45622</v>
       </c>
       <c r="C15" s="2">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>5</v>
@@ -630,13 +630,13 @@
         <v>4</v>
       </c>
       <c r="B16" s="2">
-        <v>45623</v>
+        <v>45624</v>
       </c>
       <c r="C16" s="2">
-        <v>125</v>
+        <v>6</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -647,10 +647,10 @@
         <v>45624</v>
       </c>
       <c r="C17" s="2">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -658,13 +658,13 @@
         <v>4</v>
       </c>
       <c r="B18" s="2">
-        <v>45625</v>
+        <v>45624</v>
       </c>
       <c r="C18" s="2">
+        <v>3</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -675,7 +675,7 @@
         <v>45625</v>
       </c>
       <c r="C19" s="2">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>5</v>
@@ -689,10 +689,10 @@
         <v>45626</v>
       </c>
       <c r="C20" s="2">
-        <v>1</v>
+        <v>410</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -700,13 +700,13 @@
         <v>4</v>
       </c>
       <c r="B21" s="2">
-        <v>45626</v>
+        <v>45627</v>
       </c>
       <c r="C21" s="2">
-        <v>297</v>
+        <v>3</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -714,13 +714,13 @@
         <v>4</v>
       </c>
       <c r="B22" s="2">
-        <v>45626</v>
+        <v>45611</v>
       </c>
       <c r="C22" s="2">
-        <v>115</v>
+        <v>3</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -728,10 +728,10 @@
         <v>4</v>
       </c>
       <c r="B23" s="2">
-        <v>45627</v>
+        <v>45612</v>
       </c>
       <c r="C23" s="2">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>5</v>
@@ -742,10 +742,10 @@
         <v>4</v>
       </c>
       <c r="B24" s="2">
-        <v>45628</v>
+        <v>45613</v>
       </c>
       <c r="C24" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>5</v>
@@ -756,13 +756,13 @@
         <v>4</v>
       </c>
       <c r="B25" s="2">
-        <v>45611</v>
+        <v>45614</v>
       </c>
       <c r="C25" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -770,10 +770,10 @@
         <v>4</v>
       </c>
       <c r="B26" s="2">
-        <v>45612</v>
+        <v>45614</v>
       </c>
       <c r="C26" s="2">
-        <v>129</v>
+        <v>200</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>5</v>
@@ -784,10 +784,10 @@
         <v>4</v>
       </c>
       <c r="B27" s="2">
-        <v>45613</v>
+        <v>45614</v>
       </c>
       <c r="C27" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>5</v>
@@ -798,13 +798,13 @@
         <v>4</v>
       </c>
       <c r="B28" s="2">
-        <v>45614</v>
+        <v>45615</v>
       </c>
       <c r="C28" s="2">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -812,10 +812,10 @@
         <v>4</v>
       </c>
       <c r="B29" s="2">
-        <v>45614</v>
+        <v>45616</v>
       </c>
       <c r="C29" s="2">
-        <v>200</v>
+        <v>3</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>5</v>
@@ -826,13 +826,13 @@
         <v>4</v>
       </c>
       <c r="B30" s="2">
-        <v>45614</v>
+        <v>45617</v>
       </c>
       <c r="C30" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -840,10 +840,10 @@
         <v>4</v>
       </c>
       <c r="B31" s="2">
-        <v>45615</v>
+        <v>45618</v>
       </c>
       <c r="C31" s="2">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>5</v>
@@ -854,7 +854,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="2">
-        <v>45616</v>
+        <v>45620</v>
       </c>
       <c r="C32" s="2">
         <v>3</v>
@@ -868,13 +868,13 @@
         <v>4</v>
       </c>
       <c r="B33" s="2">
-        <v>45617</v>
+        <v>45620</v>
       </c>
       <c r="C33" s="2">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -882,10 +882,10 @@
         <v>4</v>
       </c>
       <c r="B34" s="2">
-        <v>45618</v>
+        <v>45620</v>
       </c>
       <c r="C34" s="2">
-        <v>77</v>
+        <v>3</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>5</v>
@@ -896,10 +896,10 @@
         <v>4</v>
       </c>
       <c r="B35" s="2">
-        <v>45620</v>
+        <v>45621</v>
       </c>
       <c r="C35" s="2">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>5</v>
@@ -910,13 +910,13 @@
         <v>4</v>
       </c>
       <c r="B36" s="2">
-        <v>45620</v>
+        <v>45623</v>
       </c>
       <c r="C36" s="2">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -924,13 +924,13 @@
         <v>4</v>
       </c>
       <c r="B37" s="2">
-        <v>45620</v>
+        <v>45623</v>
       </c>
       <c r="C37" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -938,13 +938,13 @@
         <v>4</v>
       </c>
       <c r="B38" s="2">
-        <v>45621</v>
+        <v>45624</v>
       </c>
       <c r="C38" s="2">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -952,10 +952,10 @@
         <v>4</v>
       </c>
       <c r="B39" s="2">
-        <v>45623</v>
+        <v>45626</v>
       </c>
       <c r="C39" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>5</v>
@@ -966,13 +966,13 @@
         <v>4</v>
       </c>
       <c r="B40" s="2">
-        <v>45623</v>
+        <v>45627</v>
       </c>
       <c r="C40" s="2">
         <v>1</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -980,13 +980,13 @@
         <v>4</v>
       </c>
       <c r="B41" s="2">
-        <v>45624</v>
+        <v>45627</v>
       </c>
       <c r="C41" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -994,13 +994,13 @@
         <v>4</v>
       </c>
       <c r="B42" s="2">
-        <v>45626</v>
+        <v>45627</v>
       </c>
       <c r="C42" s="2">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1008,10 +1008,10 @@
         <v>4</v>
       </c>
       <c r="B43" s="2">
-        <v>45627</v>
+        <v>45606</v>
       </c>
       <c r="C43" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>5</v>
@@ -1022,13 +1022,13 @@
         <v>4</v>
       </c>
       <c r="B44" s="2">
-        <v>45627</v>
+        <v>45610</v>
       </c>
       <c r="C44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1036,13 +1036,13 @@
         <v>4</v>
       </c>
       <c r="B45" s="2">
-        <v>45627</v>
+        <v>45610</v>
       </c>
       <c r="C45" s="2">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1053,7 +1053,7 @@
         <v>45612</v>
       </c>
       <c r="C46" s="2">
-        <v>987</v>
+        <v>5</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>5</v>
@@ -1064,10 +1064,10 @@
         <v>4</v>
       </c>
       <c r="B47" s="2">
-        <v>45613</v>
+        <v>45612</v>
       </c>
       <c r="C47" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>5</v>
@@ -1078,13 +1078,13 @@
         <v>4</v>
       </c>
       <c r="B48" s="2">
-        <v>45614</v>
+        <v>45613</v>
       </c>
       <c r="C48" s="2">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1092,10 +1092,10 @@
         <v>4</v>
       </c>
       <c r="B49" s="2">
-        <v>45615</v>
+        <v>45614</v>
       </c>
       <c r="C49" s="2">
-        <v>167</v>
+        <v>75</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>5</v>
@@ -1109,10 +1109,10 @@
         <v>45616</v>
       </c>
       <c r="C50" s="2">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1123,7 +1123,7 @@
         <v>45616</v>
       </c>
       <c r="C51" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>5</v>
@@ -1137,7 +1137,7 @@
         <v>45617</v>
       </c>
       <c r="C52" s="2">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>5</v>
@@ -1148,13 +1148,13 @@
         <v>4</v>
       </c>
       <c r="B53" s="2">
-        <v>45618</v>
+        <v>45617</v>
       </c>
       <c r="C53" s="2">
-        <v>42</v>
+        <v>234</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1165,10 +1165,10 @@
         <v>45618</v>
       </c>
       <c r="C54" s="2">
-        <v>343</v>
+        <v>91</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1179,10 +1179,10 @@
         <v>45619</v>
       </c>
       <c r="C55" s="2">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1193,7 +1193,7 @@
         <v>45620</v>
       </c>
       <c r="C56" s="2">
-        <v>2</v>
+        <v>541</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>5</v>
@@ -1204,13 +1204,13 @@
         <v>4</v>
       </c>
       <c r="B57" s="2">
-        <v>45620</v>
+        <v>45621</v>
       </c>
       <c r="C57" s="2">
-        <v>1</v>
+        <v>224</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1221,10 +1221,10 @@
         <v>45621</v>
       </c>
       <c r="C58" s="2">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1235,10 +1235,10 @@
         <v>45622</v>
       </c>
       <c r="C59" s="2">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1246,10 +1246,10 @@
         <v>4</v>
       </c>
       <c r="B60" s="2">
-        <v>45624</v>
+        <v>45623</v>
       </c>
       <c r="C60" s="2">
-        <v>6</v>
+        <v>991</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>5</v>
@@ -1263,7 +1263,7 @@
         <v>45624</v>
       </c>
       <c r="C61" s="2">
-        <v>113</v>
+        <v>340</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>8</v>
@@ -1277,10 +1277,10 @@
         <v>45624</v>
       </c>
       <c r="C62" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1288,10 +1288,10 @@
         <v>4</v>
       </c>
       <c r="B63" s="2">
-        <v>45625</v>
+        <v>45624</v>
       </c>
       <c r="C63" s="2">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>5</v>
@@ -1302,13 +1302,13 @@
         <v>4</v>
       </c>
       <c r="B64" s="2">
-        <v>45626</v>
+        <v>45625</v>
       </c>
       <c r="C64" s="2">
-        <v>410</v>
+        <v>2</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1316,10 +1316,10 @@
         <v>4</v>
       </c>
       <c r="B65" s="2">
-        <v>45627</v>
+        <v>45626</v>
       </c>
       <c r="C65" s="2">
-        <v>3</v>
+        <v>1024</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>5</v>
@@ -1330,13 +1330,13 @@
         <v>4</v>
       </c>
       <c r="B66" s="2">
-        <v>45604</v>
+        <v>45627</v>
       </c>
       <c r="C66" s="2">
-        <v>3</v>
+        <v>173</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1344,10 +1344,10 @@
         <v>4</v>
       </c>
       <c r="B67" s="2">
-        <v>45605</v>
+        <v>45601</v>
       </c>
       <c r="C67" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>5</v>
@@ -1358,13 +1358,13 @@
         <v>4</v>
       </c>
       <c r="B68" s="2">
-        <v>45606</v>
+        <v>45604</v>
       </c>
       <c r="C68" s="2">
-        <v>127</v>
+        <v>15</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1372,13 +1372,13 @@
         <v>4</v>
       </c>
       <c r="B69" s="2">
-        <v>45612</v>
+        <v>45605</v>
       </c>
       <c r="C69" s="2">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1386,13 +1386,13 @@
         <v>4</v>
       </c>
       <c r="B70" s="2">
-        <v>45613</v>
+        <v>45607</v>
       </c>
       <c r="C70" s="2">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1400,13 +1400,13 @@
         <v>4</v>
       </c>
       <c r="B71" s="2">
-        <v>45615</v>
+        <v>45613</v>
       </c>
       <c r="C71" s="2">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1414,13 +1414,13 @@
         <v>4</v>
       </c>
       <c r="B72" s="2">
-        <v>45615</v>
+        <v>45613</v>
       </c>
       <c r="C72" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1428,13 +1428,13 @@
         <v>4</v>
       </c>
       <c r="B73" s="2">
-        <v>45616</v>
+        <v>45614</v>
       </c>
       <c r="C73" s="2">
-        <v>181</v>
+        <v>60</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1442,10 +1442,10 @@
         <v>4</v>
       </c>
       <c r="B74" s="2">
-        <v>45619</v>
+        <v>45615</v>
       </c>
       <c r="C74" s="2">
-        <v>623</v>
+        <v>4</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>5</v>
@@ -1456,13 +1456,13 @@
         <v>4</v>
       </c>
       <c r="B75" s="2">
-        <v>45619</v>
+        <v>45617</v>
       </c>
       <c r="C75" s="2">
+        <v>47</v>
+      </c>
+      <c r="D75" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1470,7 +1470,7 @@
         <v>4</v>
       </c>
       <c r="B76" s="2">
-        <v>45621</v>
+        <v>45619</v>
       </c>
       <c r="C76" s="2">
         <v>1</v>
@@ -1484,13 +1484,13 @@
         <v>4</v>
       </c>
       <c r="B77" s="2">
-        <v>45622</v>
+        <v>45620</v>
       </c>
       <c r="C77" s="2">
-        <v>454</v>
+        <v>245</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1498,13 +1498,13 @@
         <v>4</v>
       </c>
       <c r="B78" s="2">
-        <v>45622</v>
+        <v>45621</v>
       </c>
       <c r="C78" s="2">
-        <v>284</v>
+        <v>412</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1515,7 +1515,7 @@
         <v>45622</v>
       </c>
       <c r="C79" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>5</v>
@@ -1526,13 +1526,13 @@
         <v>4</v>
       </c>
       <c r="B80" s="2">
-        <v>45624</v>
+        <v>45623</v>
       </c>
       <c r="C80" s="2">
-        <v>1</v>
+        <v>349</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -1540,13 +1540,13 @@
         <v>4</v>
       </c>
       <c r="B81" s="2">
-        <v>45625</v>
+        <v>45623</v>
       </c>
       <c r="C81" s="2">
-        <v>426</v>
+        <v>1</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -1554,10 +1554,10 @@
         <v>4</v>
       </c>
       <c r="B82" s="2">
-        <v>45625</v>
+        <v>45624</v>
       </c>
       <c r="C82" s="2">
-        <v>1</v>
+        <v>957</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>5</v>
@@ -1571,7 +1571,7 @@
         <v>45625</v>
       </c>
       <c r="C83" s="2">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>5</v>
@@ -1582,10 +1582,10 @@
         <v>4</v>
       </c>
       <c r="B84" s="2">
-        <v>45627</v>
+        <v>45626</v>
       </c>
       <c r="C84" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>5</v>
@@ -1596,13 +1596,13 @@
         <v>4</v>
       </c>
       <c r="B85" s="2">
-        <v>45628</v>
+        <v>45627</v>
       </c>
       <c r="C85" s="2">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1610,13 +1610,13 @@
         <v>4</v>
       </c>
       <c r="B86" s="2">
-        <v>45628</v>
+        <v>45627</v>
       </c>
       <c r="C86" s="2">
-        <v>85</v>
+        <v>1018</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -1624,10 +1624,10 @@
         <v>4</v>
       </c>
       <c r="B87" s="2">
-        <v>45628</v>
+        <v>45627</v>
       </c>
       <c r="C87" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>5</v>
@@ -1638,10 +1638,10 @@
         <v>4</v>
       </c>
       <c r="B88" s="2">
-        <v>45601</v>
+        <v>45628</v>
       </c>
       <c r="C88" s="2">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>5</v>
@@ -1652,13 +1652,13 @@
         <v>4</v>
       </c>
       <c r="B89" s="2">
-        <v>45604</v>
+        <v>45601</v>
       </c>
       <c r="C89" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1666,10 +1666,10 @@
         <v>4</v>
       </c>
       <c r="B90" s="2">
-        <v>45605</v>
+        <v>45604</v>
       </c>
       <c r="C90" s="2">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>5</v>
@@ -1680,10 +1680,10 @@
         <v>4</v>
       </c>
       <c r="B91" s="2">
-        <v>45607</v>
+        <v>45605</v>
       </c>
       <c r="C91" s="2">
-        <v>1</v>
+        <v>164</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>8</v>
@@ -1694,10 +1694,10 @@
         <v>4</v>
       </c>
       <c r="B92" s="2">
-        <v>45613</v>
+        <v>45605</v>
       </c>
       <c r="C92" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>5</v>
@@ -1708,10 +1708,10 @@
         <v>4</v>
       </c>
       <c r="B93" s="2">
-        <v>45613</v>
+        <v>45612</v>
       </c>
       <c r="C93" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>5</v>
@@ -1722,13 +1722,13 @@
         <v>4</v>
       </c>
       <c r="B94" s="2">
-        <v>45614</v>
+        <v>45613</v>
       </c>
       <c r="C94" s="2">
-        <v>60</v>
+        <v>769</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -1739,7 +1739,7 @@
         <v>45615</v>
       </c>
       <c r="C95" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>5</v>
@@ -1750,13 +1750,13 @@
         <v>4</v>
       </c>
       <c r="B96" s="2">
-        <v>45617</v>
+        <v>45618</v>
       </c>
       <c r="C96" s="2">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -1767,7 +1767,7 @@
         <v>45619</v>
       </c>
       <c r="C97" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>5</v>
@@ -1778,13 +1778,13 @@
         <v>4</v>
       </c>
       <c r="B98" s="2">
-        <v>45620</v>
+        <v>45619</v>
       </c>
       <c r="C98" s="2">
-        <v>245</v>
+        <v>4</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -1792,10 +1792,10 @@
         <v>4</v>
       </c>
       <c r="B99" s="2">
-        <v>45621</v>
+        <v>45619</v>
       </c>
       <c r="C99" s="2">
-        <v>412</v>
+        <v>2</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>5</v>
@@ -1806,13 +1806,13 @@
         <v>4</v>
       </c>
       <c r="B100" s="2">
-        <v>45622</v>
+        <v>45620</v>
       </c>
       <c r="C100" s="2">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -1820,13 +1820,13 @@
         <v>4</v>
       </c>
       <c r="B101" s="2">
-        <v>45623</v>
+        <v>45622</v>
       </c>
       <c r="C101" s="2">
-        <v>349</v>
+        <v>1</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -1848,13 +1848,13 @@
         <v>4</v>
       </c>
       <c r="B103" s="2">
-        <v>45624</v>
+        <v>45623</v>
       </c>
       <c r="C103" s="2">
-        <v>957</v>
+        <v>125</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -1862,10 +1862,10 @@
         <v>4</v>
       </c>
       <c r="B104" s="2">
-        <v>45625</v>
+        <v>45624</v>
       </c>
       <c r="C104" s="2">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>5</v>
@@ -1876,7 +1876,7 @@
         <v>4</v>
       </c>
       <c r="B105" s="2">
-        <v>45626</v>
+        <v>45625</v>
       </c>
       <c r="C105" s="2">
         <v>7</v>
@@ -1890,13 +1890,13 @@
         <v>4</v>
       </c>
       <c r="B106" s="2">
-        <v>45627</v>
+        <v>45625</v>
       </c>
       <c r="C106" s="2">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -1904,10 +1904,10 @@
         <v>4</v>
       </c>
       <c r="B107" s="2">
-        <v>45627</v>
+        <v>45626</v>
       </c>
       <c r="C107" s="2">
-        <v>1018</v>
+        <v>1</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>5</v>
@@ -1918,13 +1918,13 @@
         <v>4</v>
       </c>
       <c r="B108" s="2">
-        <v>45627</v>
+        <v>45626</v>
       </c>
       <c r="C108" s="2">
+        <v>297</v>
+      </c>
+      <c r="D108" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -1932,13 +1932,13 @@
         <v>4</v>
       </c>
       <c r="B109" s="2">
-        <v>45628</v>
+        <v>45626</v>
       </c>
       <c r="C109" s="2">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -1946,13 +1946,13 @@
         <v>4</v>
       </c>
       <c r="B110" s="2">
-        <v>45602</v>
+        <v>45627</v>
       </c>
       <c r="C110" s="2">
-        <v>6</v>
+        <v>114</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -1960,13 +1960,13 @@
         <v>4</v>
       </c>
       <c r="B111" s="2">
-        <v>45605</v>
+        <v>45628</v>
       </c>
       <c r="C111" s="2">
-        <v>137</v>
+        <v>1</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -1974,10 +1974,10 @@
         <v>4</v>
       </c>
       <c r="B112" s="2">
-        <v>45605</v>
+        <v>45604</v>
       </c>
       <c r="C112" s="2">
-        <v>760</v>
+        <v>3</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>5</v>
@@ -1988,10 +1988,10 @@
         <v>4</v>
       </c>
       <c r="B113" s="2">
-        <v>45606</v>
+        <v>45605</v>
       </c>
       <c r="C113" s="2">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>5</v>
@@ -2002,13 +2002,13 @@
         <v>4</v>
       </c>
       <c r="B114" s="2">
-        <v>45611</v>
+        <v>45606</v>
       </c>
       <c r="C114" s="2">
-        <v>4</v>
+        <v>127</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2016,10 +2016,10 @@
         <v>4</v>
       </c>
       <c r="B115" s="2">
-        <v>45613</v>
+        <v>45612</v>
       </c>
       <c r="C115" s="2">
-        <v>153</v>
+        <v>47</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>6</v>
@@ -2030,10 +2030,10 @@
         <v>4</v>
       </c>
       <c r="B116" s="2">
-        <v>45614</v>
+        <v>45613</v>
       </c>
       <c r="C116" s="2">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>5</v>
@@ -2044,13 +2044,13 @@
         <v>4</v>
       </c>
       <c r="B117" s="2">
-        <v>45614</v>
+        <v>45615</v>
       </c>
       <c r="C117" s="2">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2058,13 +2058,13 @@
         <v>4</v>
       </c>
       <c r="B118" s="2">
-        <v>45616</v>
+        <v>45615</v>
       </c>
       <c r="C118" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2072,10 +2072,10 @@
         <v>4</v>
       </c>
       <c r="B119" s="2">
-        <v>45617</v>
+        <v>45616</v>
       </c>
       <c r="C119" s="2">
-        <v>4</v>
+        <v>181</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>5</v>
@@ -2089,10 +2089,10 @@
         <v>45619</v>
       </c>
       <c r="C120" s="2">
-        <v>224</v>
+        <v>623</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2100,10 +2100,10 @@
         <v>4</v>
       </c>
       <c r="B121" s="2">
-        <v>45620</v>
+        <v>45619</v>
       </c>
       <c r="C121" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>5</v>
@@ -2117,10 +2117,10 @@
         <v>45621</v>
       </c>
       <c r="C122" s="2">
-        <v>107</v>
+        <v>1</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2128,10 +2128,10 @@
         <v>4</v>
       </c>
       <c r="B123" s="2">
-        <v>45623</v>
+        <v>45622</v>
       </c>
       <c r="C123" s="2">
-        <v>3</v>
+        <v>454</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>5</v>
@@ -2142,13 +2142,13 @@
         <v>4</v>
       </c>
       <c r="B124" s="2">
-        <v>45623</v>
+        <v>45622</v>
       </c>
       <c r="C124" s="2">
-        <v>18</v>
+        <v>284</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2156,10 +2156,10 @@
         <v>4</v>
       </c>
       <c r="B125" s="2">
-        <v>45625</v>
+        <v>45622</v>
       </c>
       <c r="C125" s="2">
-        <v>707</v>
+        <v>3</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>5</v>
@@ -2170,7 +2170,7 @@
         <v>4</v>
       </c>
       <c r="B126" s="2">
-        <v>45626</v>
+        <v>45624</v>
       </c>
       <c r="C126" s="2">
         <v>1</v>
@@ -2184,13 +2184,13 @@
         <v>4</v>
       </c>
       <c r="B127" s="2">
-        <v>45626</v>
+        <v>45625</v>
       </c>
       <c r="C127" s="2">
-        <v>9</v>
+        <v>426</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2198,10 +2198,10 @@
         <v>4</v>
       </c>
       <c r="B128" s="2">
-        <v>45626</v>
+        <v>45625</v>
       </c>
       <c r="C128" s="2">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>5</v>
@@ -2212,10 +2212,10 @@
         <v>4</v>
       </c>
       <c r="B129" s="2">
-        <v>45627</v>
+        <v>45625</v>
       </c>
       <c r="C129" s="2">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>5</v>
@@ -2229,7 +2229,7 @@
         <v>45627</v>
       </c>
       <c r="C130" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>5</v>
@@ -2243,7 +2243,7 @@
         <v>45628</v>
       </c>
       <c r="C131" s="2">
-        <v>337</v>
+        <v>1</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>5</v>
@@ -2254,13 +2254,13 @@
         <v>4</v>
       </c>
       <c r="B132" s="2">
-        <v>45605</v>
+        <v>45628</v>
       </c>
       <c r="C132" s="2">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2268,10 +2268,10 @@
         <v>4</v>
       </c>
       <c r="B133" s="2">
-        <v>45606</v>
+        <v>45628</v>
       </c>
       <c r="C133" s="2">
-        <v>499</v>
+        <v>8</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>5</v>
@@ -2282,13 +2282,13 @@
         <v>4</v>
       </c>
       <c r="B134" s="2">
-        <v>45606</v>
+        <v>45605</v>
       </c>
       <c r="C134" s="2">
-        <v>117</v>
+        <v>1</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2299,7 +2299,7 @@
         <v>45606</v>
       </c>
       <c r="C135" s="2">
-        <v>6</v>
+        <v>499</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>5</v>
@@ -2310,13 +2310,13 @@
         <v>4</v>
       </c>
       <c r="B136" s="2">
-        <v>45612</v>
+        <v>45606</v>
       </c>
       <c r="C136" s="2">
-        <v>222</v>
+        <v>117</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -2324,10 +2324,10 @@
         <v>4</v>
       </c>
       <c r="B137" s="2">
-        <v>45612</v>
+        <v>45606</v>
       </c>
       <c r="C137" s="2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>5</v>
@@ -2338,13 +2338,13 @@
         <v>4</v>
       </c>
       <c r="B138" s="2">
-        <v>45614</v>
+        <v>45612</v>
       </c>
       <c r="C138" s="2">
-        <v>3</v>
+        <v>222</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -2352,10 +2352,10 @@
         <v>4</v>
       </c>
       <c r="B139" s="2">
-        <v>45615</v>
+        <v>45612</v>
       </c>
       <c r="C139" s="2">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>5</v>
@@ -2366,13 +2366,13 @@
         <v>4</v>
       </c>
       <c r="B140" s="2">
-        <v>45615</v>
+        <v>45614</v>
       </c>
       <c r="C140" s="2">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2394,13 +2394,13 @@
         <v>4</v>
       </c>
       <c r="B142" s="2">
-        <v>45618</v>
+        <v>45615</v>
       </c>
       <c r="C142" s="2">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2408,13 +2408,13 @@
         <v>4</v>
       </c>
       <c r="B143" s="2">
-        <v>45619</v>
+        <v>45615</v>
       </c>
       <c r="C143" s="2">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -2422,10 +2422,10 @@
         <v>4</v>
       </c>
       <c r="B144" s="2">
-        <v>45620</v>
+        <v>45618</v>
       </c>
       <c r="C144" s="2">
-        <v>93</v>
+        <v>2</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>5</v>
@@ -2436,13 +2436,13 @@
         <v>4</v>
       </c>
       <c r="B145" s="2">
-        <v>45621</v>
+        <v>45619</v>
       </c>
       <c r="C145" s="2">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -2450,10 +2450,10 @@
         <v>4</v>
       </c>
       <c r="B146" s="2">
-        <v>45621</v>
+        <v>45620</v>
       </c>
       <c r="C146" s="2">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>5</v>
@@ -2464,7 +2464,7 @@
         <v>4</v>
       </c>
       <c r="B147" s="2">
-        <v>45622</v>
+        <v>45621</v>
       </c>
       <c r="C147" s="2">
         <v>1</v>
@@ -2478,13 +2478,13 @@
         <v>4</v>
       </c>
       <c r="B148" s="2">
-        <v>45622</v>
+        <v>45621</v>
       </c>
       <c r="C148" s="2">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -2492,10 +2492,10 @@
         <v>4</v>
       </c>
       <c r="B149" s="2">
-        <v>45623</v>
+        <v>45622</v>
       </c>
       <c r="C149" s="2">
-        <v>124</v>
+        <v>1</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>5</v>
@@ -2506,13 +2506,13 @@
         <v>4</v>
       </c>
       <c r="B150" s="2">
-        <v>45624</v>
+        <v>45622</v>
       </c>
       <c r="C150" s="2">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -2520,10 +2520,10 @@
         <v>4</v>
       </c>
       <c r="B151" s="2">
-        <v>45624</v>
+        <v>45623</v>
       </c>
       <c r="C151" s="2">
-        <v>1</v>
+        <v>124</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>5</v>
@@ -2534,10 +2534,10 @@
         <v>4</v>
       </c>
       <c r="B152" s="2">
-        <v>45625</v>
+        <v>45624</v>
       </c>
       <c r="C152" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>5</v>
@@ -2548,13 +2548,13 @@
         <v>4</v>
       </c>
       <c r="B153" s="2">
-        <v>45625</v>
+        <v>45624</v>
       </c>
       <c r="C153" s="2">
-        <v>159</v>
+        <v>1</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -2565,10 +2565,10 @@
         <v>45625</v>
       </c>
       <c r="C154" s="2">
-        <v>132</v>
+        <v>1</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -2579,7 +2579,7 @@
         <v>45625</v>
       </c>
       <c r="C155" s="2">
-        <v>4</v>
+        <v>159</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>9</v>
@@ -2590,13 +2590,13 @@
         <v>4</v>
       </c>
       <c r="B156" s="2">
-        <v>45626</v>
+        <v>45625</v>
       </c>
       <c r="C156" s="2">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -2604,13 +2604,13 @@
         <v>4</v>
       </c>
       <c r="B157" s="2">
-        <v>45628</v>
+        <v>45625</v>
       </c>
       <c r="C157" s="2">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -2618,10 +2618,10 @@
         <v>4</v>
       </c>
       <c r="B158" s="2">
-        <v>45606</v>
+        <v>45626</v>
       </c>
       <c r="C158" s="2">
-        <v>5</v>
+        <v>98</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>5</v>
@@ -2632,13 +2632,13 @@
         <v>4</v>
       </c>
       <c r="B159" s="2">
-        <v>45610</v>
+        <v>45628</v>
       </c>
       <c r="C159" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -2646,13 +2646,13 @@
         <v>4</v>
       </c>
       <c r="B160" s="2">
-        <v>45610</v>
+        <v>45602</v>
       </c>
       <c r="C160" s="2">
         <v>6</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -2660,13 +2660,13 @@
         <v>4</v>
       </c>
       <c r="B161" s="2">
-        <v>45612</v>
+        <v>45605</v>
       </c>
       <c r="C161" s="2">
-        <v>5</v>
+        <v>137</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -2674,10 +2674,10 @@
         <v>4</v>
       </c>
       <c r="B162" s="2">
-        <v>45612</v>
+        <v>45605</v>
       </c>
       <c r="C162" s="2">
-        <v>12</v>
+        <v>760</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>5</v>
@@ -2688,13 +2688,13 @@
         <v>4</v>
       </c>
       <c r="B163" s="2">
-        <v>45613</v>
+        <v>45606</v>
       </c>
       <c r="C163" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B164" s="2">
-        <v>45614</v>
+        <v>45611</v>
       </c>
       <c r="C164" s="2">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -2716,10 +2716,10 @@
         <v>4</v>
       </c>
       <c r="B165" s="2">
-        <v>45616</v>
+        <v>45613</v>
       </c>
       <c r="C165" s="2">
-        <v>15</v>
+        <v>153</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>8</v>
@@ -2730,10 +2730,10 @@
         <v>4</v>
       </c>
       <c r="B166" s="2">
-        <v>45616</v>
+        <v>45614</v>
       </c>
       <c r="C166" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>5</v>
@@ -2744,10 +2744,10 @@
         <v>4</v>
       </c>
       <c r="B167" s="2">
-        <v>45617</v>
+        <v>45614</v>
       </c>
       <c r="C167" s="2">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>5</v>
@@ -2758,13 +2758,13 @@
         <v>4</v>
       </c>
       <c r="B168" s="2">
-        <v>45617</v>
+        <v>45616</v>
       </c>
       <c r="C168" s="2">
-        <v>234</v>
+        <v>46</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -2772,13 +2772,13 @@
         <v>4</v>
       </c>
       <c r="B169" s="2">
-        <v>45618</v>
+        <v>45617</v>
       </c>
       <c r="C169" s="2">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -2789,7 +2789,7 @@
         <v>45619</v>
       </c>
       <c r="C170" s="2">
-        <v>44</v>
+        <v>224</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>8</v>
@@ -2803,7 +2803,7 @@
         <v>45620</v>
       </c>
       <c r="C171" s="2">
-        <v>541</v>
+        <v>2</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>5</v>
@@ -2817,10 +2817,10 @@
         <v>45621</v>
       </c>
       <c r="C172" s="2">
-        <v>224</v>
+        <v>107</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -2828,10 +2828,10 @@
         <v>4</v>
       </c>
       <c r="B173" s="2">
-        <v>45621</v>
+        <v>45623</v>
       </c>
       <c r="C173" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>5</v>
@@ -2842,13 +2842,13 @@
         <v>4</v>
       </c>
       <c r="B174" s="2">
-        <v>45622</v>
+        <v>45623</v>
       </c>
       <c r="C174" s="2">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -2856,10 +2856,10 @@
         <v>4</v>
       </c>
       <c r="B175" s="2">
-        <v>45623</v>
+        <v>45625</v>
       </c>
       <c r="C175" s="2">
-        <v>991</v>
+        <v>707</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>5</v>
@@ -2870,13 +2870,13 @@
         <v>4</v>
       </c>
       <c r="B176" s="2">
-        <v>45624</v>
+        <v>45626</v>
       </c>
       <c r="C176" s="2">
-        <v>340</v>
+        <v>1</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -2884,10 +2884,10 @@
         <v>4</v>
       </c>
       <c r="B177" s="2">
-        <v>45624</v>
+        <v>45626</v>
       </c>
       <c r="C177" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>5</v>
@@ -2898,10 +2898,10 @@
         <v>4</v>
       </c>
       <c r="B178" s="2">
-        <v>45624</v>
+        <v>45626</v>
       </c>
       <c r="C178" s="2">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>5</v>
@@ -2912,10 +2912,10 @@
         <v>4</v>
       </c>
       <c r="B179" s="2">
-        <v>45625</v>
+        <v>45627</v>
       </c>
       <c r="C179" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>5</v>
@@ -2926,10 +2926,10 @@
         <v>4</v>
       </c>
       <c r="B180" s="2">
-        <v>45626</v>
+        <v>45627</v>
       </c>
       <c r="C180" s="2">
-        <v>1024</v>
+        <v>7</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>5</v>
@@ -2940,13 +2940,13 @@
         <v>4</v>
       </c>
       <c r="B181" s="2">
-        <v>45627</v>
+        <v>45628</v>
       </c>
       <c r="C181" s="2">
-        <v>173</v>
+        <v>337</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/reports/For Winter Ending (Prior Year)_Visits.xlsx
+++ b/reports/For Winter Ending (Prior Year)_Visits.xlsx
@@ -40,10 +40,10 @@
     <t>Purgatory Uplift Tickets</t>
   </si>
   <si>
-    <t>Purgatory Coaster</t>
+    <t>Purgatory Tickets</t>
   </si>
   <si>
-    <t>Purgatory Tickets</t>
+    <t>Purgatory Coaster</t>
   </si>
 </sst>
 </file>
@@ -434,10 +434,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>45611</v>
+        <v>45612</v>
       </c>
       <c r="C2" s="2">
-        <v>3</v>
+        <v>987</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -448,10 +448,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>45612</v>
+        <v>45613</v>
       </c>
       <c r="C3" s="2">
-        <v>129</v>
+        <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>5</v>
@@ -462,10 +462,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>45613</v>
+        <v>45614</v>
       </c>
       <c r="C4" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>5</v>
@@ -476,13 +476,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>45614</v>
+        <v>45615</v>
       </c>
       <c r="C5" s="2">
-        <v>11</v>
+        <v>167</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -490,10 +490,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>45614</v>
+        <v>45616</v>
       </c>
       <c r="C6" s="2">
-        <v>200</v>
+        <v>65</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>5</v>
@@ -504,7 +504,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="2">
-        <v>45614</v>
+        <v>45616</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
@@ -518,10 +518,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>45615</v>
+        <v>45617</v>
       </c>
       <c r="C8" s="2">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>5</v>
@@ -532,13 +532,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>45616</v>
+        <v>45618</v>
       </c>
       <c r="C9" s="2">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -546,13 +546,13 @@
         <v>4</v>
       </c>
       <c r="B10" s="2">
-        <v>45617</v>
+        <v>45618</v>
       </c>
       <c r="C10" s="2">
-        <v>10</v>
+        <v>343</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -560,10 +560,10 @@
         <v>4</v>
       </c>
       <c r="B11" s="2">
-        <v>45618</v>
+        <v>45619</v>
       </c>
       <c r="C11" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>5</v>
@@ -577,7 +577,7 @@
         <v>45620</v>
       </c>
       <c r="C12" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>5</v>
@@ -591,10 +591,10 @@
         <v>45620</v>
       </c>
       <c r="C13" s="2">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -602,13 +602,13 @@
         <v>4</v>
       </c>
       <c r="B14" s="2">
-        <v>45620</v>
+        <v>45621</v>
       </c>
       <c r="C14" s="2">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -616,10 +616,10 @@
         <v>4</v>
       </c>
       <c r="B15" s="2">
-        <v>45621</v>
+        <v>45622</v>
       </c>
       <c r="C15" s="2">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>5</v>
@@ -630,10 +630,10 @@
         <v>4</v>
       </c>
       <c r="B16" s="2">
-        <v>45623</v>
+        <v>45624</v>
       </c>
       <c r="C16" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>5</v>
@@ -644,13 +644,13 @@
         <v>4</v>
       </c>
       <c r="B17" s="2">
-        <v>45623</v>
+        <v>45624</v>
       </c>
       <c r="C17" s="2">
-        <v>1</v>
+        <v>113</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -664,7 +664,7 @@
         <v>3</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -672,10 +672,10 @@
         <v>4</v>
       </c>
       <c r="B19" s="2">
-        <v>45626</v>
+        <v>45625</v>
       </c>
       <c r="C19" s="2">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>5</v>
@@ -686,13 +686,13 @@
         <v>4</v>
       </c>
       <c r="B20" s="2">
-        <v>45627</v>
+        <v>45626</v>
       </c>
       <c r="C20" s="2">
-        <v>1</v>
+        <v>410</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -703,7 +703,7 @@
         <v>45627</v>
       </c>
       <c r="C21" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>5</v>
@@ -714,13 +714,13 @@
         <v>4</v>
       </c>
       <c r="B22" s="2">
-        <v>45627</v>
+        <v>45604</v>
       </c>
       <c r="C22" s="2">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -728,10 +728,10 @@
         <v>4</v>
       </c>
       <c r="B23" s="2">
-        <v>45601</v>
+        <v>45605</v>
       </c>
       <c r="C23" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>5</v>
@@ -742,13 +742,13 @@
         <v>4</v>
       </c>
       <c r="B24" s="2">
-        <v>45604</v>
+        <v>45606</v>
       </c>
       <c r="C24" s="2">
-        <v>1</v>
+        <v>127</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -756,13 +756,13 @@
         <v>4</v>
       </c>
       <c r="B25" s="2">
-        <v>45605</v>
+        <v>45612</v>
       </c>
       <c r="C25" s="2">
-        <v>164</v>
+        <v>47</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -770,10 +770,10 @@
         <v>4</v>
       </c>
       <c r="B26" s="2">
-        <v>45605</v>
+        <v>45613</v>
       </c>
       <c r="C26" s="2">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>5</v>
@@ -784,13 +784,13 @@
         <v>4</v>
       </c>
       <c r="B27" s="2">
-        <v>45612</v>
+        <v>45615</v>
       </c>
       <c r="C27" s="2">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -798,13 +798,13 @@
         <v>4</v>
       </c>
       <c r="B28" s="2">
-        <v>45613</v>
+        <v>45615</v>
       </c>
       <c r="C28" s="2">
-        <v>769</v>
+        <v>0</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -812,10 +812,10 @@
         <v>4</v>
       </c>
       <c r="B29" s="2">
-        <v>45615</v>
+        <v>45616</v>
       </c>
       <c r="C29" s="2">
-        <v>2</v>
+        <v>181</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>5</v>
@@ -826,10 +826,10 @@
         <v>4</v>
       </c>
       <c r="B30" s="2">
-        <v>45618</v>
+        <v>45619</v>
       </c>
       <c r="C30" s="2">
-        <v>2</v>
+        <v>623</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>5</v>
@@ -843,7 +843,7 @@
         <v>45619</v>
       </c>
       <c r="C31" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>5</v>
@@ -854,10 +854,10 @@
         <v>4</v>
       </c>
       <c r="B32" s="2">
-        <v>45619</v>
+        <v>45621</v>
       </c>
       <c r="C32" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>5</v>
@@ -868,10 +868,10 @@
         <v>4</v>
       </c>
       <c r="B33" s="2">
-        <v>45619</v>
+        <v>45622</v>
       </c>
       <c r="C33" s="2">
-        <v>2</v>
+        <v>454</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>5</v>
@@ -882,10 +882,10 @@
         <v>4</v>
       </c>
       <c r="B34" s="2">
-        <v>45620</v>
+        <v>45622</v>
       </c>
       <c r="C34" s="2">
-        <v>14</v>
+        <v>284</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>8</v>
@@ -899,7 +899,7 @@
         <v>45622</v>
       </c>
       <c r="C35" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>5</v>
@@ -910,7 +910,7 @@
         <v>4</v>
       </c>
       <c r="B36" s="2">
-        <v>45623</v>
+        <v>45624</v>
       </c>
       <c r="C36" s="2">
         <v>1</v>
@@ -924,13 +924,13 @@
         <v>4</v>
       </c>
       <c r="B37" s="2">
-        <v>45623</v>
+        <v>45625</v>
       </c>
       <c r="C37" s="2">
-        <v>125</v>
+        <v>426</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -938,10 +938,10 @@
         <v>4</v>
       </c>
       <c r="B38" s="2">
-        <v>45624</v>
+        <v>45625</v>
       </c>
       <c r="C38" s="2">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>5</v>
@@ -955,7 +955,7 @@
         <v>45625</v>
       </c>
       <c r="C39" s="2">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>5</v>
@@ -966,7 +966,7 @@
         <v>4</v>
       </c>
       <c r="B40" s="2">
-        <v>45625</v>
+        <v>45627</v>
       </c>
       <c r="C40" s="2">
         <v>4</v>
@@ -980,7 +980,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="2">
-        <v>45626</v>
+        <v>45628</v>
       </c>
       <c r="C41" s="2">
         <v>1</v>
@@ -994,10 +994,10 @@
         <v>4</v>
       </c>
       <c r="B42" s="2">
-        <v>45626</v>
+        <v>45628</v>
       </c>
       <c r="C42" s="2">
-        <v>297</v>
+        <v>85</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>8</v>
@@ -1008,13 +1008,13 @@
         <v>4</v>
       </c>
       <c r="B43" s="2">
-        <v>45626</v>
+        <v>45628</v>
       </c>
       <c r="C43" s="2">
-        <v>115</v>
+        <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1022,10 +1022,10 @@
         <v>4</v>
       </c>
       <c r="B44" s="2">
-        <v>45627</v>
+        <v>45601</v>
       </c>
       <c r="C44" s="2">
-        <v>114</v>
+        <v>1</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>5</v>
@@ -1036,7 +1036,7 @@
         <v>4</v>
       </c>
       <c r="B45" s="2">
-        <v>45628</v>
+        <v>45604</v>
       </c>
       <c r="C45" s="2">
         <v>1</v>
@@ -1050,13 +1050,13 @@
         <v>4</v>
       </c>
       <c r="B46" s="2">
-        <v>45612</v>
+        <v>45605</v>
       </c>
       <c r="C46" s="2">
-        <v>987</v>
+        <v>164</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1064,10 +1064,10 @@
         <v>4</v>
       </c>
       <c r="B47" s="2">
-        <v>45613</v>
+        <v>45605</v>
       </c>
       <c r="C47" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>5</v>
@@ -1078,10 +1078,10 @@
         <v>4</v>
       </c>
       <c r="B48" s="2">
-        <v>45614</v>
+        <v>45612</v>
       </c>
       <c r="C48" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>5</v>
@@ -1092,10 +1092,10 @@
         <v>4</v>
       </c>
       <c r="B49" s="2">
-        <v>45615</v>
+        <v>45613</v>
       </c>
       <c r="C49" s="2">
-        <v>167</v>
+        <v>769</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>5</v>
@@ -1106,10 +1106,10 @@
         <v>4</v>
       </c>
       <c r="B50" s="2">
-        <v>45616</v>
+        <v>45615</v>
       </c>
       <c r="C50" s="2">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>5</v>
@@ -1120,10 +1120,10 @@
         <v>4</v>
       </c>
       <c r="B51" s="2">
-        <v>45616</v>
+        <v>45618</v>
       </c>
       <c r="C51" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>5</v>
@@ -1134,10 +1134,10 @@
         <v>4</v>
       </c>
       <c r="B52" s="2">
-        <v>45617</v>
+        <v>45619</v>
       </c>
       <c r="C52" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>5</v>
@@ -1148,13 +1148,13 @@
         <v>4</v>
       </c>
       <c r="B53" s="2">
-        <v>45618</v>
+        <v>45619</v>
       </c>
       <c r="C53" s="2">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1162,10 +1162,10 @@
         <v>4</v>
       </c>
       <c r="B54" s="2">
-        <v>45618</v>
+        <v>45619</v>
       </c>
       <c r="C54" s="2">
-        <v>343</v>
+        <v>2</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>5</v>
@@ -1176,13 +1176,13 @@
         <v>4</v>
       </c>
       <c r="B55" s="2">
-        <v>45619</v>
+        <v>45620</v>
       </c>
       <c r="C55" s="2">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1190,10 +1190,10 @@
         <v>4</v>
       </c>
       <c r="B56" s="2">
-        <v>45620</v>
+        <v>45622</v>
       </c>
       <c r="C56" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>5</v>
@@ -1204,7 +1204,7 @@
         <v>4</v>
       </c>
       <c r="B57" s="2">
-        <v>45620</v>
+        <v>45623</v>
       </c>
       <c r="C57" s="2">
         <v>1</v>
@@ -1218,10 +1218,10 @@
         <v>4</v>
       </c>
       <c r="B58" s="2">
-        <v>45621</v>
+        <v>45623</v>
       </c>
       <c r="C58" s="2">
-        <v>78</v>
+        <v>125</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>6</v>
@@ -1232,10 +1232,10 @@
         <v>4</v>
       </c>
       <c r="B59" s="2">
-        <v>45622</v>
+        <v>45624</v>
       </c>
       <c r="C59" s="2">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>5</v>
@@ -1246,10 +1246,10 @@
         <v>4</v>
       </c>
       <c r="B60" s="2">
-        <v>45624</v>
+        <v>45625</v>
       </c>
       <c r="C60" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>5</v>
@@ -1260,13 +1260,13 @@
         <v>4</v>
       </c>
       <c r="B61" s="2">
-        <v>45624</v>
+        <v>45625</v>
       </c>
       <c r="C61" s="2">
-        <v>113</v>
+        <v>4</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1274,13 +1274,13 @@
         <v>4</v>
       </c>
       <c r="B62" s="2">
-        <v>45624</v>
+        <v>45626</v>
       </c>
       <c r="C62" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1288,13 +1288,13 @@
         <v>4</v>
       </c>
       <c r="B63" s="2">
-        <v>45625</v>
+        <v>45626</v>
       </c>
       <c r="C63" s="2">
-        <v>56</v>
+        <v>297</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1305,10 +1305,10 @@
         <v>45626</v>
       </c>
       <c r="C64" s="2">
-        <v>410</v>
+        <v>115</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1319,7 +1319,7 @@
         <v>45627</v>
       </c>
       <c r="C65" s="2">
-        <v>3</v>
+        <v>114</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>5</v>
@@ -1330,10 +1330,10 @@
         <v>4</v>
       </c>
       <c r="B66" s="2">
-        <v>45606</v>
+        <v>45628</v>
       </c>
       <c r="C66" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>5</v>
@@ -1344,13 +1344,13 @@
         <v>4</v>
       </c>
       <c r="B67" s="2">
-        <v>45610</v>
+        <v>45606</v>
       </c>
       <c r="C67" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1361,10 +1361,10 @@
         <v>45610</v>
       </c>
       <c r="C68" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1372,13 +1372,13 @@
         <v>4</v>
       </c>
       <c r="B69" s="2">
-        <v>45612</v>
+        <v>45610</v>
       </c>
       <c r="C69" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1389,7 +1389,7 @@
         <v>45612</v>
       </c>
       <c r="C70" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>5</v>
@@ -1400,13 +1400,13 @@
         <v>4</v>
       </c>
       <c r="B71" s="2">
-        <v>45613</v>
+        <v>45612</v>
       </c>
       <c r="C71" s="2">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1414,13 +1414,13 @@
         <v>4</v>
       </c>
       <c r="B72" s="2">
-        <v>45614</v>
+        <v>45613</v>
       </c>
       <c r="C72" s="2">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1428,13 +1428,13 @@
         <v>4</v>
       </c>
       <c r="B73" s="2">
-        <v>45616</v>
+        <v>45614</v>
       </c>
       <c r="C73" s="2">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1445,10 +1445,10 @@
         <v>45616</v>
       </c>
       <c r="C74" s="2">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1456,10 +1456,10 @@
         <v>4</v>
       </c>
       <c r="B75" s="2">
-        <v>45617</v>
+        <v>45616</v>
       </c>
       <c r="C75" s="2">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>5</v>
@@ -1473,7 +1473,7 @@
         <v>45617</v>
       </c>
       <c r="C76" s="2">
-        <v>234</v>
+        <v>91</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>5</v>
@@ -1484,13 +1484,13 @@
         <v>4</v>
       </c>
       <c r="B77" s="2">
-        <v>45618</v>
+        <v>45617</v>
       </c>
       <c r="C77" s="2">
-        <v>91</v>
+        <v>234</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1498,13 +1498,13 @@
         <v>4</v>
       </c>
       <c r="B78" s="2">
-        <v>45619</v>
+        <v>45618</v>
       </c>
       <c r="C78" s="2">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1512,13 +1512,13 @@
         <v>4</v>
       </c>
       <c r="B79" s="2">
-        <v>45620</v>
+        <v>45619</v>
       </c>
       <c r="C79" s="2">
-        <v>541</v>
+        <v>44</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -1526,13 +1526,13 @@
         <v>4</v>
       </c>
       <c r="B80" s="2">
-        <v>45621</v>
+        <v>45620</v>
       </c>
       <c r="C80" s="2">
-        <v>224</v>
+        <v>541</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -1543,10 +1543,10 @@
         <v>45621</v>
       </c>
       <c r="C81" s="2">
-        <v>1</v>
+        <v>224</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -1554,13 +1554,13 @@
         <v>4</v>
       </c>
       <c r="B82" s="2">
-        <v>45622</v>
+        <v>45621</v>
       </c>
       <c r="C82" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1568,13 +1568,13 @@
         <v>4</v>
       </c>
       <c r="B83" s="2">
-        <v>45623</v>
+        <v>45622</v>
       </c>
       <c r="C83" s="2">
-        <v>991</v>
+        <v>3</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -1582,13 +1582,13 @@
         <v>4</v>
       </c>
       <c r="B84" s="2">
-        <v>45624</v>
+        <v>45623</v>
       </c>
       <c r="C84" s="2">
-        <v>340</v>
+        <v>991</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -1599,10 +1599,10 @@
         <v>45624</v>
       </c>
       <c r="C85" s="2">
-        <v>1</v>
+        <v>340</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1613,7 +1613,7 @@
         <v>45624</v>
       </c>
       <c r="C86" s="2">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>5</v>
@@ -1624,10 +1624,10 @@
         <v>4</v>
       </c>
       <c r="B87" s="2">
-        <v>45625</v>
+        <v>45624</v>
       </c>
       <c r="C87" s="2">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>5</v>
@@ -1638,10 +1638,10 @@
         <v>4</v>
       </c>
       <c r="B88" s="2">
-        <v>45626</v>
+        <v>45625</v>
       </c>
       <c r="C88" s="2">
-        <v>1024</v>
+        <v>2</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>5</v>
@@ -1652,13 +1652,13 @@
         <v>4</v>
       </c>
       <c r="B89" s="2">
-        <v>45627</v>
+        <v>45626</v>
       </c>
       <c r="C89" s="2">
-        <v>173</v>
+        <v>1024</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1666,13 +1666,13 @@
         <v>4</v>
       </c>
       <c r="B90" s="2">
-        <v>45602</v>
+        <v>45627</v>
       </c>
       <c r="C90" s="2">
-        <v>6</v>
+        <v>173</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -1680,13 +1680,13 @@
         <v>4</v>
       </c>
       <c r="B91" s="2">
-        <v>45605</v>
+        <v>45601</v>
       </c>
       <c r="C91" s="2">
-        <v>137</v>
+        <v>1</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -1694,13 +1694,13 @@
         <v>4</v>
       </c>
       <c r="B92" s="2">
-        <v>45605</v>
+        <v>45604</v>
       </c>
       <c r="C92" s="2">
-        <v>760</v>
+        <v>15</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -1708,10 +1708,10 @@
         <v>4</v>
       </c>
       <c r="B93" s="2">
-        <v>45606</v>
+        <v>45605</v>
       </c>
       <c r="C93" s="2">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>5</v>
@@ -1722,10 +1722,10 @@
         <v>4</v>
       </c>
       <c r="B94" s="2">
-        <v>45611</v>
+        <v>45607</v>
       </c>
       <c r="C94" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>6</v>
@@ -1739,10 +1739,10 @@
         <v>45613</v>
       </c>
       <c r="C95" s="2">
-        <v>153</v>
+        <v>2</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -1750,10 +1750,10 @@
         <v>4</v>
       </c>
       <c r="B96" s="2">
-        <v>45614</v>
+        <v>45613</v>
       </c>
       <c r="C96" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>5</v>
@@ -1767,10 +1767,10 @@
         <v>45614</v>
       </c>
       <c r="C97" s="2">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -1778,13 +1778,13 @@
         <v>4</v>
       </c>
       <c r="B98" s="2">
-        <v>45616</v>
+        <v>45615</v>
       </c>
       <c r="C98" s="2">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -1795,10 +1795,10 @@
         <v>45617</v>
       </c>
       <c r="C99" s="2">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -1809,10 +1809,10 @@
         <v>45619</v>
       </c>
       <c r="C100" s="2">
-        <v>224</v>
+        <v>1</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -1823,10 +1823,10 @@
         <v>45620</v>
       </c>
       <c r="C101" s="2">
-        <v>2</v>
+        <v>245</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -1837,10 +1837,10 @@
         <v>45621</v>
       </c>
       <c r="C102" s="2">
-        <v>107</v>
+        <v>412</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -1848,10 +1848,10 @@
         <v>4</v>
       </c>
       <c r="B103" s="2">
-        <v>45623</v>
+        <v>45622</v>
       </c>
       <c r="C103" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>5</v>
@@ -1865,10 +1865,10 @@
         <v>45623</v>
       </c>
       <c r="C104" s="2">
-        <v>18</v>
+        <v>349</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -1876,10 +1876,10 @@
         <v>4</v>
       </c>
       <c r="B105" s="2">
-        <v>45625</v>
+        <v>45623</v>
       </c>
       <c r="C105" s="2">
-        <v>707</v>
+        <v>1</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>5</v>
@@ -1890,10 +1890,10 @@
         <v>4</v>
       </c>
       <c r="B106" s="2">
-        <v>45626</v>
+        <v>45624</v>
       </c>
       <c r="C106" s="2">
-        <v>1</v>
+        <v>957</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>5</v>
@@ -1904,10 +1904,10 @@
         <v>4</v>
       </c>
       <c r="B107" s="2">
-        <v>45626</v>
+        <v>45625</v>
       </c>
       <c r="C107" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>5</v>
@@ -1921,7 +1921,7 @@
         <v>45626</v>
       </c>
       <c r="C108" s="2">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>5</v>
@@ -1935,10 +1935,10 @@
         <v>45627</v>
       </c>
       <c r="C109" s="2">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -1949,7 +1949,7 @@
         <v>45627</v>
       </c>
       <c r="C110" s="2">
-        <v>7</v>
+        <v>1018</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>5</v>
@@ -1960,10 +1960,10 @@
         <v>4</v>
       </c>
       <c r="B111" s="2">
-        <v>45628</v>
+        <v>45627</v>
       </c>
       <c r="C111" s="2">
-        <v>337</v>
+        <v>9</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>5</v>
@@ -1974,10 +1974,10 @@
         <v>4</v>
       </c>
       <c r="B112" s="2">
-        <v>45605</v>
+        <v>45628</v>
       </c>
       <c r="C112" s="2">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>5</v>
@@ -1988,10 +1988,10 @@
         <v>4</v>
       </c>
       <c r="B113" s="2">
-        <v>45606</v>
+        <v>45605</v>
       </c>
       <c r="C113" s="2">
-        <v>499</v>
+        <v>1</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>5</v>
@@ -2005,10 +2005,10 @@
         <v>45606</v>
       </c>
       <c r="C114" s="2">
-        <v>117</v>
+        <v>499</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2019,10 +2019,10 @@
         <v>45606</v>
       </c>
       <c r="C115" s="2">
-        <v>6</v>
+        <v>117</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2030,13 +2030,13 @@
         <v>4</v>
       </c>
       <c r="B116" s="2">
-        <v>45612</v>
+        <v>45606</v>
       </c>
       <c r="C116" s="2">
-        <v>222</v>
+        <v>6</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2047,10 +2047,10 @@
         <v>45612</v>
       </c>
       <c r="C117" s="2">
-        <v>14</v>
+        <v>222</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2058,10 +2058,10 @@
         <v>4</v>
       </c>
       <c r="B118" s="2">
-        <v>45614</v>
+        <v>45612</v>
       </c>
       <c r="C118" s="2">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>5</v>
@@ -2072,10 +2072,10 @@
         <v>4</v>
       </c>
       <c r="B119" s="2">
-        <v>45615</v>
+        <v>45614</v>
       </c>
       <c r="C119" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>5</v>
@@ -2089,10 +2089,10 @@
         <v>45615</v>
       </c>
       <c r="C120" s="2">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2103,10 +2103,10 @@
         <v>45615</v>
       </c>
       <c r="C121" s="2">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2114,7 +2114,7 @@
         <v>4</v>
       </c>
       <c r="B122" s="2">
-        <v>45618</v>
+        <v>45615</v>
       </c>
       <c r="C122" s="2">
         <v>2</v>
@@ -2128,13 +2128,13 @@
         <v>4</v>
       </c>
       <c r="B123" s="2">
-        <v>45619</v>
+        <v>45618</v>
       </c>
       <c r="C123" s="2">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2142,13 +2142,13 @@
         <v>4</v>
       </c>
       <c r="B124" s="2">
-        <v>45620</v>
+        <v>45619</v>
       </c>
       <c r="C124" s="2">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2156,10 +2156,10 @@
         <v>4</v>
       </c>
       <c r="B125" s="2">
-        <v>45621</v>
+        <v>45620</v>
       </c>
       <c r="C125" s="2">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>5</v>
@@ -2184,7 +2184,7 @@
         <v>4</v>
       </c>
       <c r="B127" s="2">
-        <v>45622</v>
+        <v>45621</v>
       </c>
       <c r="C127" s="2">
         <v>1</v>
@@ -2201,10 +2201,10 @@
         <v>45622</v>
       </c>
       <c r="C128" s="2">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2212,13 +2212,13 @@
         <v>4</v>
       </c>
       <c r="B129" s="2">
-        <v>45623</v>
+        <v>45622</v>
       </c>
       <c r="C129" s="2">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2226,10 +2226,10 @@
         <v>4</v>
       </c>
       <c r="B130" s="2">
-        <v>45624</v>
+        <v>45623</v>
       </c>
       <c r="C130" s="2">
-        <v>3</v>
+        <v>124</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>5</v>
@@ -2243,7 +2243,7 @@
         <v>45624</v>
       </c>
       <c r="C131" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>5</v>
@@ -2254,7 +2254,7 @@
         <v>4</v>
       </c>
       <c r="B132" s="2">
-        <v>45625</v>
+        <v>45624</v>
       </c>
       <c r="C132" s="2">
         <v>1</v>
@@ -2271,10 +2271,10 @@
         <v>45625</v>
       </c>
       <c r="C133" s="2">
-        <v>159</v>
+        <v>1</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2285,10 +2285,10 @@
         <v>45625</v>
       </c>
       <c r="C134" s="2">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2299,10 +2299,10 @@
         <v>45625</v>
       </c>
       <c r="C135" s="2">
-        <v>4</v>
+        <v>132</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2310,13 +2310,13 @@
         <v>4</v>
       </c>
       <c r="B136" s="2">
-        <v>45626</v>
+        <v>45625</v>
       </c>
       <c r="C136" s="2">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -2324,13 +2324,13 @@
         <v>4</v>
       </c>
       <c r="B137" s="2">
-        <v>45628</v>
+        <v>45626</v>
       </c>
       <c r="C137" s="2">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -2338,13 +2338,13 @@
         <v>4</v>
       </c>
       <c r="B138" s="2">
-        <v>45604</v>
+        <v>45628</v>
       </c>
       <c r="C138" s="2">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -2352,13 +2352,13 @@
         <v>4</v>
       </c>
       <c r="B139" s="2">
-        <v>45605</v>
+        <v>45602</v>
       </c>
       <c r="C139" s="2">
         <v>6</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -2366,10 +2366,10 @@
         <v>4</v>
       </c>
       <c r="B140" s="2">
-        <v>45606</v>
+        <v>45605</v>
       </c>
       <c r="C140" s="2">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>6</v>
@@ -2380,13 +2380,13 @@
         <v>4</v>
       </c>
       <c r="B141" s="2">
-        <v>45612</v>
+        <v>45605</v>
       </c>
       <c r="C141" s="2">
-        <v>47</v>
+        <v>760</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -2394,10 +2394,10 @@
         <v>4</v>
       </c>
       <c r="B142" s="2">
-        <v>45613</v>
+        <v>45606</v>
       </c>
       <c r="C142" s="2">
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>5</v>
@@ -2408,10 +2408,10 @@
         <v>4</v>
       </c>
       <c r="B143" s="2">
-        <v>45615</v>
+        <v>45611</v>
       </c>
       <c r="C143" s="2">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>6</v>
@@ -2422,13 +2422,13 @@
         <v>4</v>
       </c>
       <c r="B144" s="2">
-        <v>45615</v>
+        <v>45613</v>
       </c>
       <c r="C144" s="2">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -2436,10 +2436,10 @@
         <v>4</v>
       </c>
       <c r="B145" s="2">
-        <v>45616</v>
+        <v>45614</v>
       </c>
       <c r="C145" s="2">
-        <v>181</v>
+        <v>2</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>5</v>
@@ -2450,10 +2450,10 @@
         <v>4</v>
       </c>
       <c r="B146" s="2">
-        <v>45619</v>
+        <v>45614</v>
       </c>
       <c r="C146" s="2">
-        <v>623</v>
+        <v>4</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>5</v>
@@ -2464,13 +2464,13 @@
         <v>4</v>
       </c>
       <c r="B147" s="2">
-        <v>45619</v>
+        <v>45616</v>
       </c>
       <c r="C147" s="2">
+        <v>46</v>
+      </c>
+      <c r="D147" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D147" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="B148" s="2">
-        <v>45621</v>
+        <v>45617</v>
       </c>
       <c r="C148" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>5</v>
@@ -2492,13 +2492,13 @@
         <v>4</v>
       </c>
       <c r="B149" s="2">
-        <v>45622</v>
+        <v>45619</v>
       </c>
       <c r="C149" s="2">
-        <v>454</v>
+        <v>224</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -2506,13 +2506,13 @@
         <v>4</v>
       </c>
       <c r="B150" s="2">
-        <v>45622</v>
+        <v>45620</v>
       </c>
       <c r="C150" s="2">
-        <v>284</v>
+        <v>2</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -2520,13 +2520,13 @@
         <v>4</v>
       </c>
       <c r="B151" s="2">
-        <v>45622</v>
+        <v>45621</v>
       </c>
       <c r="C151" s="2">
-        <v>3</v>
+        <v>107</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -2534,10 +2534,10 @@
         <v>4</v>
       </c>
       <c r="B152" s="2">
-        <v>45624</v>
+        <v>45623</v>
       </c>
       <c r="C152" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>5</v>
@@ -2548,13 +2548,13 @@
         <v>4</v>
       </c>
       <c r="B153" s="2">
-        <v>45625</v>
+        <v>45623</v>
       </c>
       <c r="C153" s="2">
-        <v>426</v>
+        <v>18</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -2565,7 +2565,7 @@
         <v>45625</v>
       </c>
       <c r="C154" s="2">
-        <v>1</v>
+        <v>707</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>5</v>
@@ -2576,10 +2576,10 @@
         <v>4</v>
       </c>
       <c r="B155" s="2">
-        <v>45625</v>
+        <v>45626</v>
       </c>
       <c r="C155" s="2">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>5</v>
@@ -2590,10 +2590,10 @@
         <v>4</v>
       </c>
       <c r="B156" s="2">
-        <v>45627</v>
+        <v>45626</v>
       </c>
       <c r="C156" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>5</v>
@@ -2604,10 +2604,10 @@
         <v>4</v>
       </c>
       <c r="B157" s="2">
-        <v>45628</v>
+        <v>45626</v>
       </c>
       <c r="C157" s="2">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>5</v>
@@ -2618,13 +2618,13 @@
         <v>4</v>
       </c>
       <c r="B158" s="2">
-        <v>45628</v>
+        <v>45627</v>
       </c>
       <c r="C158" s="2">
-        <v>85</v>
+        <v>1</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -2632,10 +2632,10 @@
         <v>4</v>
       </c>
       <c r="B159" s="2">
-        <v>45628</v>
+        <v>45627</v>
       </c>
       <c r="C159" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>5</v>
@@ -2646,10 +2646,10 @@
         <v>4</v>
       </c>
       <c r="B160" s="2">
-        <v>45601</v>
+        <v>45628</v>
       </c>
       <c r="C160" s="2">
-        <v>1</v>
+        <v>337</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>5</v>
@@ -2660,13 +2660,13 @@
         <v>4</v>
       </c>
       <c r="B161" s="2">
-        <v>45604</v>
+        <v>45611</v>
       </c>
       <c r="C161" s="2">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -2674,10 +2674,10 @@
         <v>4</v>
       </c>
       <c r="B162" s="2">
-        <v>45605</v>
+        <v>45612</v>
       </c>
       <c r="C162" s="2">
-        <v>58</v>
+        <v>129</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>5</v>
@@ -2688,13 +2688,13 @@
         <v>4</v>
       </c>
       <c r="B163" s="2">
-        <v>45607</v>
+        <v>45613</v>
       </c>
       <c r="C163" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B164" s="2">
-        <v>45613</v>
+        <v>45614</v>
       </c>
       <c r="C164" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -2716,10 +2716,10 @@
         <v>4</v>
       </c>
       <c r="B165" s="2">
-        <v>45613</v>
+        <v>45614</v>
       </c>
       <c r="C165" s="2">
-        <v>4</v>
+        <v>200</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>5</v>
@@ -2733,10 +2733,10 @@
         <v>45614</v>
       </c>
       <c r="C166" s="2">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -2747,7 +2747,7 @@
         <v>45615</v>
       </c>
       <c r="C167" s="2">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>5</v>
@@ -2758,13 +2758,13 @@
         <v>4</v>
       </c>
       <c r="B168" s="2">
-        <v>45617</v>
+        <v>45616</v>
       </c>
       <c r="C168" s="2">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -2772,13 +2772,13 @@
         <v>4</v>
       </c>
       <c r="B169" s="2">
-        <v>45619</v>
+        <v>45617</v>
       </c>
       <c r="C169" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -2786,13 +2786,13 @@
         <v>4</v>
       </c>
       <c r="B170" s="2">
-        <v>45620</v>
+        <v>45618</v>
       </c>
       <c r="C170" s="2">
-        <v>245</v>
+        <v>77</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -2800,10 +2800,10 @@
         <v>4</v>
       </c>
       <c r="B171" s="2">
-        <v>45621</v>
+        <v>45620</v>
       </c>
       <c r="C171" s="2">
-        <v>412</v>
+        <v>3</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>5</v>
@@ -2814,13 +2814,13 @@
         <v>4</v>
       </c>
       <c r="B172" s="2">
-        <v>45622</v>
+        <v>45620</v>
       </c>
       <c r="C172" s="2">
-        <v>2</v>
+        <v>81</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -2828,13 +2828,13 @@
         <v>4</v>
       </c>
       <c r="B173" s="2">
-        <v>45623</v>
+        <v>45620</v>
       </c>
       <c r="C173" s="2">
-        <v>349</v>
+        <v>3</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -2842,10 +2842,10 @@
         <v>4</v>
       </c>
       <c r="B174" s="2">
-        <v>45623</v>
+        <v>45621</v>
       </c>
       <c r="C174" s="2">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>5</v>
@@ -2856,10 +2856,10 @@
         <v>4</v>
       </c>
       <c r="B175" s="2">
-        <v>45624</v>
+        <v>45623</v>
       </c>
       <c r="C175" s="2">
-        <v>957</v>
+        <v>8</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>5</v>
@@ -2870,13 +2870,13 @@
         <v>4</v>
       </c>
       <c r="B176" s="2">
-        <v>45625</v>
+        <v>45623</v>
       </c>
       <c r="C176" s="2">
         <v>1</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -2884,13 +2884,13 @@
         <v>4</v>
       </c>
       <c r="B177" s="2">
-        <v>45626</v>
+        <v>45624</v>
       </c>
       <c r="C177" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -2898,13 +2898,13 @@
         <v>4</v>
       </c>
       <c r="B178" s="2">
-        <v>45627</v>
+        <v>45626</v>
       </c>
       <c r="C178" s="2">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -2915,7 +2915,7 @@
         <v>45627</v>
       </c>
       <c r="C179" s="2">
-        <v>1018</v>
+        <v>1</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>5</v>
@@ -2929,7 +2929,7 @@
         <v>45627</v>
       </c>
       <c r="C180" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>5</v>
@@ -2940,13 +2940,13 @@
         <v>4</v>
       </c>
       <c r="B181" s="2">
-        <v>45628</v>
+        <v>45627</v>
       </c>
       <c r="C181" s="2">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/reports/For Winter Ending (Prior Year)_Visits.xlsx
+++ b/reports/For Winter Ending (Prior Year)_Visits.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="10">
   <si>
     <t>Resort</t>
   </si>
@@ -37,13 +37,13 @@
     <t>Purgatory Comp Tickets</t>
   </si>
   <si>
-    <t>Purgatory Uplift Tickets</t>
-  </si>
-  <si>
     <t>Purgatory Tickets</t>
   </si>
   <si>
     <t>Purgatory Coaster</t>
+  </si>
+  <si>
+    <t>Purgatory Uplift Tickets</t>
   </si>
 </sst>
 </file>
@@ -406,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D181"/>
+  <dimension ref="A1:D237"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -434,10 +434,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>45612</v>
+        <v>45601</v>
       </c>
       <c r="C2" s="2">
-        <v>987</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -448,10 +448,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>45613</v>
+        <v>45601</v>
       </c>
       <c r="C3" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>5</v>
@@ -462,13 +462,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>45614</v>
+        <v>45602</v>
       </c>
       <c r="C4" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -476,13 +476,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>45615</v>
+        <v>45604</v>
       </c>
       <c r="C5" s="2">
-        <v>167</v>
+        <v>15</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -490,10 +490,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>45616</v>
+        <v>45604</v>
       </c>
       <c r="C6" s="2">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>5</v>
@@ -504,7 +504,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="2">
-        <v>45616</v>
+        <v>45604</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
@@ -518,13 +518,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>45617</v>
+        <v>45605</v>
       </c>
       <c r="C8" s="2">
-        <v>1</v>
+        <v>137</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -532,13 +532,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>45618</v>
+        <v>45605</v>
       </c>
       <c r="C9" s="2">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -546,10 +546,10 @@
         <v>4</v>
       </c>
       <c r="B10" s="2">
-        <v>45618</v>
+        <v>45605</v>
       </c>
       <c r="C10" s="2">
-        <v>343</v>
+        <v>760</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>5</v>
@@ -560,13 +560,13 @@
         <v>4</v>
       </c>
       <c r="B11" s="2">
-        <v>45619</v>
+        <v>45605</v>
       </c>
       <c r="C11" s="2">
-        <v>85</v>
+        <v>164</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -574,10 +574,10 @@
         <v>4</v>
       </c>
       <c r="B12" s="2">
-        <v>45620</v>
+        <v>45605</v>
       </c>
       <c r="C12" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>5</v>
@@ -588,10 +588,10 @@
         <v>4</v>
       </c>
       <c r="B13" s="2">
-        <v>45620</v>
+        <v>45605</v>
       </c>
       <c r="C13" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>5</v>
@@ -602,13 +602,13 @@
         <v>4</v>
       </c>
       <c r="B14" s="2">
-        <v>45621</v>
+        <v>45605</v>
       </c>
       <c r="C14" s="2">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -616,13 +616,13 @@
         <v>4</v>
       </c>
       <c r="B15" s="2">
-        <v>45622</v>
+        <v>45606</v>
       </c>
       <c r="C15" s="2">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -630,10 +630,10 @@
         <v>4</v>
       </c>
       <c r="B16" s="2">
-        <v>45624</v>
+        <v>45606</v>
       </c>
       <c r="C16" s="2">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>5</v>
@@ -644,13 +644,13 @@
         <v>4</v>
       </c>
       <c r="B17" s="2">
-        <v>45624</v>
+        <v>45606</v>
       </c>
       <c r="C17" s="2">
-        <v>113</v>
+        <v>499</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -658,10 +658,10 @@
         <v>4</v>
       </c>
       <c r="B18" s="2">
-        <v>45624</v>
+        <v>45606</v>
       </c>
       <c r="C18" s="2">
-        <v>3</v>
+        <v>117</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>7</v>
@@ -672,10 +672,10 @@
         <v>4</v>
       </c>
       <c r="B19" s="2">
-        <v>45625</v>
+        <v>45606</v>
       </c>
       <c r="C19" s="2">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>5</v>
@@ -686,13 +686,13 @@
         <v>4</v>
       </c>
       <c r="B20" s="2">
-        <v>45626</v>
+        <v>45606</v>
       </c>
       <c r="C20" s="2">
-        <v>410</v>
+        <v>6</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -700,13 +700,13 @@
         <v>4</v>
       </c>
       <c r="B21" s="2">
-        <v>45627</v>
+        <v>45607</v>
       </c>
       <c r="C21" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -714,13 +714,13 @@
         <v>4</v>
       </c>
       <c r="B22" s="2">
-        <v>45604</v>
+        <v>45610</v>
       </c>
       <c r="C22" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -728,13 +728,13 @@
         <v>4</v>
       </c>
       <c r="B23" s="2">
-        <v>45605</v>
+        <v>45610</v>
       </c>
       <c r="C23" s="2">
         <v>6</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -742,10 +742,10 @@
         <v>4</v>
       </c>
       <c r="B24" s="2">
-        <v>45606</v>
+        <v>45611</v>
       </c>
       <c r="C24" s="2">
-        <v>127</v>
+        <v>4</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>6</v>
@@ -756,13 +756,13 @@
         <v>4</v>
       </c>
       <c r="B25" s="2">
-        <v>45612</v>
+        <v>45611</v>
       </c>
       <c r="C25" s="2">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -770,10 +770,10 @@
         <v>4</v>
       </c>
       <c r="B26" s="2">
-        <v>45613</v>
+        <v>45612</v>
       </c>
       <c r="C26" s="2">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>5</v>
@@ -784,10 +784,10 @@
         <v>4</v>
       </c>
       <c r="B27" s="2">
-        <v>45615</v>
+        <v>45612</v>
       </c>
       <c r="C27" s="2">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>6</v>
@@ -798,13 +798,13 @@
         <v>4</v>
       </c>
       <c r="B28" s="2">
-        <v>45615</v>
+        <v>45612</v>
       </c>
       <c r="C28" s="2">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -812,10 +812,10 @@
         <v>4</v>
       </c>
       <c r="B29" s="2">
-        <v>45616</v>
+        <v>45612</v>
       </c>
       <c r="C29" s="2">
-        <v>181</v>
+        <v>987</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>5</v>
@@ -826,13 +826,13 @@
         <v>4</v>
       </c>
       <c r="B30" s="2">
-        <v>45619</v>
+        <v>45612</v>
       </c>
       <c r="C30" s="2">
-        <v>623</v>
+        <v>222</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -840,10 +840,10 @@
         <v>4</v>
       </c>
       <c r="B31" s="2">
-        <v>45619</v>
+        <v>45612</v>
       </c>
       <c r="C31" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>5</v>
@@ -854,10 +854,10 @@
         <v>4</v>
       </c>
       <c r="B32" s="2">
-        <v>45621</v>
+        <v>45612</v>
       </c>
       <c r="C32" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>5</v>
@@ -868,10 +868,10 @@
         <v>4</v>
       </c>
       <c r="B33" s="2">
-        <v>45622</v>
+        <v>45612</v>
       </c>
       <c r="C33" s="2">
-        <v>454</v>
+        <v>14</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>5</v>
@@ -882,13 +882,13 @@
         <v>4</v>
       </c>
       <c r="B34" s="2">
-        <v>45622</v>
+        <v>45613</v>
       </c>
       <c r="C34" s="2">
-        <v>284</v>
+        <v>2</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -896,13 +896,13 @@
         <v>4</v>
       </c>
       <c r="B35" s="2">
-        <v>45622</v>
+        <v>45613</v>
       </c>
       <c r="C35" s="2">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -910,10 +910,10 @@
         <v>4</v>
       </c>
       <c r="B36" s="2">
-        <v>45624</v>
+        <v>45613</v>
       </c>
       <c r="C36" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>5</v>
@@ -924,13 +924,13 @@
         <v>4</v>
       </c>
       <c r="B37" s="2">
-        <v>45625</v>
+        <v>45613</v>
       </c>
       <c r="C37" s="2">
-        <v>426</v>
+        <v>769</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -938,13 +938,13 @@
         <v>4</v>
       </c>
       <c r="B38" s="2">
-        <v>45625</v>
+        <v>45613</v>
       </c>
       <c r="C38" s="2">
-        <v>1</v>
+        <v>153</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -952,10 +952,10 @@
         <v>4</v>
       </c>
       <c r="B39" s="2">
-        <v>45625</v>
+        <v>45613</v>
       </c>
       <c r="C39" s="2">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>5</v>
@@ -966,10 +966,10 @@
         <v>4</v>
       </c>
       <c r="B40" s="2">
-        <v>45627</v>
+        <v>45613</v>
       </c>
       <c r="C40" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>5</v>
@@ -980,10 +980,10 @@
         <v>4</v>
       </c>
       <c r="B41" s="2">
-        <v>45628</v>
+        <v>45613</v>
       </c>
       <c r="C41" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>5</v>
@@ -994,13 +994,13 @@
         <v>4</v>
       </c>
       <c r="B42" s="2">
-        <v>45628</v>
+        <v>45614</v>
       </c>
       <c r="C42" s="2">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1008,13 +1008,13 @@
         <v>4</v>
       </c>
       <c r="B43" s="2">
-        <v>45628</v>
+        <v>45614</v>
       </c>
       <c r="C43" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1022,10 +1022,10 @@
         <v>4</v>
       </c>
       <c r="B44" s="2">
-        <v>45601</v>
+        <v>45614</v>
       </c>
       <c r="C44" s="2">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>5</v>
@@ -1036,10 +1036,10 @@
         <v>4</v>
       </c>
       <c r="B45" s="2">
-        <v>45604</v>
+        <v>45614</v>
       </c>
       <c r="C45" s="2">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>5</v>
@@ -1050,13 +1050,13 @@
         <v>4</v>
       </c>
       <c r="B46" s="2">
-        <v>45605</v>
+        <v>45614</v>
       </c>
       <c r="C46" s="2">
-        <v>164</v>
+        <v>60</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1064,10 +1064,10 @@
         <v>4</v>
       </c>
       <c r="B47" s="2">
-        <v>45605</v>
+        <v>45614</v>
       </c>
       <c r="C47" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>5</v>
@@ -1078,10 +1078,10 @@
         <v>4</v>
       </c>
       <c r="B48" s="2">
-        <v>45612</v>
+        <v>45614</v>
       </c>
       <c r="C48" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>5</v>
@@ -1092,10 +1092,10 @@
         <v>4</v>
       </c>
       <c r="B49" s="2">
-        <v>45613</v>
+        <v>45614</v>
       </c>
       <c r="C49" s="2">
-        <v>769</v>
+        <v>1</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>5</v>
@@ -1106,10 +1106,10 @@
         <v>4</v>
       </c>
       <c r="B50" s="2">
-        <v>45615</v>
+        <v>45614</v>
       </c>
       <c r="C50" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>5</v>
@@ -1120,7 +1120,7 @@
         <v>4</v>
       </c>
       <c r="B51" s="2">
-        <v>45618</v>
+        <v>45615</v>
       </c>
       <c r="C51" s="2">
         <v>2</v>
@@ -1134,13 +1134,13 @@
         <v>4</v>
       </c>
       <c r="B52" s="2">
-        <v>45619</v>
+        <v>45615</v>
       </c>
       <c r="C52" s="2">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1148,10 +1148,10 @@
         <v>4</v>
       </c>
       <c r="B53" s="2">
-        <v>45619</v>
+        <v>45615</v>
       </c>
       <c r="C53" s="2">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>5</v>
@@ -1162,10 +1162,10 @@
         <v>4</v>
       </c>
       <c r="B54" s="2">
-        <v>45619</v>
+        <v>45615</v>
       </c>
       <c r="C54" s="2">
-        <v>2</v>
+        <v>167</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>5</v>
@@ -1176,13 +1176,13 @@
         <v>4</v>
       </c>
       <c r="B55" s="2">
-        <v>45620</v>
+        <v>45615</v>
       </c>
       <c r="C55" s="2">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1190,13 +1190,13 @@
         <v>4</v>
       </c>
       <c r="B56" s="2">
-        <v>45622</v>
+        <v>45615</v>
       </c>
       <c r="C56" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1204,10 +1204,10 @@
         <v>4</v>
       </c>
       <c r="B57" s="2">
-        <v>45623</v>
+        <v>45615</v>
       </c>
       <c r="C57" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>5</v>
@@ -1218,13 +1218,13 @@
         <v>4</v>
       </c>
       <c r="B58" s="2">
-        <v>45623</v>
+        <v>45615</v>
       </c>
       <c r="C58" s="2">
-        <v>125</v>
+        <v>2</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1232,10 +1232,10 @@
         <v>4</v>
       </c>
       <c r="B59" s="2">
-        <v>45624</v>
+        <v>45615</v>
       </c>
       <c r="C59" s="2">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>5</v>
@@ -1246,13 +1246,13 @@
         <v>4</v>
       </c>
       <c r="B60" s="2">
-        <v>45625</v>
+        <v>45616</v>
       </c>
       <c r="C60" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1260,10 +1260,10 @@
         <v>4</v>
       </c>
       <c r="B61" s="2">
-        <v>45625</v>
+        <v>45616</v>
       </c>
       <c r="C61" s="2">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>5</v>
@@ -1274,10 +1274,10 @@
         <v>4</v>
       </c>
       <c r="B62" s="2">
-        <v>45626</v>
+        <v>45616</v>
       </c>
       <c r="C62" s="2">
-        <v>1</v>
+        <v>181</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>5</v>
@@ -1288,13 +1288,13 @@
         <v>4</v>
       </c>
       <c r="B63" s="2">
-        <v>45626</v>
+        <v>45616</v>
       </c>
       <c r="C63" s="2">
-        <v>297</v>
+        <v>46</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1302,13 +1302,13 @@
         <v>4</v>
       </c>
       <c r="B64" s="2">
-        <v>45626</v>
+        <v>45616</v>
       </c>
       <c r="C64" s="2">
-        <v>115</v>
+        <v>3</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1316,10 +1316,10 @@
         <v>4</v>
       </c>
       <c r="B65" s="2">
-        <v>45627</v>
+        <v>45616</v>
       </c>
       <c r="C65" s="2">
-        <v>114</v>
+        <v>1</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>5</v>
@@ -1330,10 +1330,10 @@
         <v>4</v>
       </c>
       <c r="B66" s="2">
-        <v>45628</v>
+        <v>45616</v>
       </c>
       <c r="C66" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>5</v>
@@ -1344,13 +1344,13 @@
         <v>4</v>
       </c>
       <c r="B67" s="2">
-        <v>45606</v>
+        <v>45617</v>
       </c>
       <c r="C67" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1358,13 +1358,13 @@
         <v>4</v>
       </c>
       <c r="B68" s="2">
-        <v>45610</v>
+        <v>45617</v>
       </c>
       <c r="C68" s="2">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1372,13 +1372,13 @@
         <v>4</v>
       </c>
       <c r="B69" s="2">
-        <v>45610</v>
+        <v>45617</v>
       </c>
       <c r="C69" s="2">
-        <v>6</v>
+        <v>234</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1386,13 +1386,13 @@
         <v>4</v>
       </c>
       <c r="B70" s="2">
-        <v>45612</v>
+        <v>45617</v>
       </c>
       <c r="C70" s="2">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1400,10 +1400,10 @@
         <v>4</v>
       </c>
       <c r="B71" s="2">
-        <v>45612</v>
+        <v>45617</v>
       </c>
       <c r="C71" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>5</v>
@@ -1414,13 +1414,13 @@
         <v>4</v>
       </c>
       <c r="B72" s="2">
-        <v>45613</v>
+        <v>45617</v>
       </c>
       <c r="C72" s="2">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1428,13 +1428,13 @@
         <v>4</v>
       </c>
       <c r="B73" s="2">
-        <v>45614</v>
+        <v>45618</v>
       </c>
       <c r="C73" s="2">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1442,13 +1442,13 @@
         <v>4</v>
       </c>
       <c r="B74" s="2">
-        <v>45616</v>
+        <v>45618</v>
       </c>
       <c r="C74" s="2">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1456,10 +1456,10 @@
         <v>4</v>
       </c>
       <c r="B75" s="2">
-        <v>45616</v>
+        <v>45618</v>
       </c>
       <c r="C75" s="2">
-        <v>4</v>
+        <v>343</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>5</v>
@@ -1470,13 +1470,13 @@
         <v>4</v>
       </c>
       <c r="B76" s="2">
-        <v>45617</v>
+        <v>45618</v>
       </c>
       <c r="C76" s="2">
         <v>91</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -1484,10 +1484,10 @@
         <v>4</v>
       </c>
       <c r="B77" s="2">
-        <v>45617</v>
+        <v>45618</v>
       </c>
       <c r="C77" s="2">
-        <v>234</v>
+        <v>2</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>5</v>
@@ -1501,10 +1501,10 @@
         <v>45618</v>
       </c>
       <c r="C78" s="2">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1515,10 +1515,10 @@
         <v>45619</v>
       </c>
       <c r="C79" s="2">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -1526,10 +1526,10 @@
         <v>4</v>
       </c>
       <c r="B80" s="2">
-        <v>45620</v>
+        <v>45619</v>
       </c>
       <c r="C80" s="2">
-        <v>541</v>
+        <v>4</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>5</v>
@@ -1540,10 +1540,10 @@
         <v>4</v>
       </c>
       <c r="B81" s="2">
-        <v>45621</v>
+        <v>45619</v>
       </c>
       <c r="C81" s="2">
-        <v>224</v>
+        <v>29</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>8</v>
@@ -1554,13 +1554,13 @@
         <v>4</v>
       </c>
       <c r="B82" s="2">
-        <v>45621</v>
+        <v>45619</v>
       </c>
       <c r="C82" s="2">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1568,13 +1568,13 @@
         <v>4</v>
       </c>
       <c r="B83" s="2">
-        <v>45622</v>
+        <v>45619</v>
       </c>
       <c r="C83" s="2">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -1582,10 +1582,10 @@
         <v>4</v>
       </c>
       <c r="B84" s="2">
-        <v>45623</v>
+        <v>45619</v>
       </c>
       <c r="C84" s="2">
-        <v>991</v>
+        <v>623</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>5</v>
@@ -1596,13 +1596,13 @@
         <v>4</v>
       </c>
       <c r="B85" s="2">
-        <v>45624</v>
+        <v>45619</v>
       </c>
       <c r="C85" s="2">
-        <v>340</v>
+        <v>224</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1610,7 +1610,7 @@
         <v>4</v>
       </c>
       <c r="B86" s="2">
-        <v>45624</v>
+        <v>45619</v>
       </c>
       <c r="C86" s="2">
         <v>1</v>
@@ -1624,10 +1624,10 @@
         <v>4</v>
       </c>
       <c r="B87" s="2">
-        <v>45624</v>
+        <v>45619</v>
       </c>
       <c r="C87" s="2">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>5</v>
@@ -1638,10 +1638,10 @@
         <v>4</v>
       </c>
       <c r="B88" s="2">
-        <v>45625</v>
+        <v>45619</v>
       </c>
       <c r="C88" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>5</v>
@@ -1652,10 +1652,10 @@
         <v>4</v>
       </c>
       <c r="B89" s="2">
-        <v>45626</v>
+        <v>45620</v>
       </c>
       <c r="C89" s="2">
-        <v>1024</v>
+        <v>2</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>5</v>
@@ -1666,13 +1666,13 @@
         <v>4</v>
       </c>
       <c r="B90" s="2">
-        <v>45627</v>
+        <v>45620</v>
       </c>
       <c r="C90" s="2">
-        <v>173</v>
+        <v>3</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -1680,13 +1680,13 @@
         <v>4</v>
       </c>
       <c r="B91" s="2">
-        <v>45601</v>
+        <v>45620</v>
       </c>
       <c r="C91" s="2">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -1694,10 +1694,10 @@
         <v>4</v>
       </c>
       <c r="B92" s="2">
-        <v>45604</v>
+        <v>45620</v>
       </c>
       <c r="C92" s="2">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>6</v>
@@ -1708,10 +1708,10 @@
         <v>4</v>
       </c>
       <c r="B93" s="2">
-        <v>45605</v>
+        <v>45620</v>
       </c>
       <c r="C93" s="2">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>5</v>
@@ -1722,13 +1722,13 @@
         <v>4</v>
       </c>
       <c r="B94" s="2">
-        <v>45607</v>
+        <v>45620</v>
       </c>
       <c r="C94" s="2">
-        <v>1</v>
+        <v>541</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -1736,13 +1736,13 @@
         <v>4</v>
       </c>
       <c r="B95" s="2">
-        <v>45613</v>
+        <v>45620</v>
       </c>
       <c r="C95" s="2">
-        <v>2</v>
+        <v>245</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -1750,10 +1750,10 @@
         <v>4</v>
       </c>
       <c r="B96" s="2">
-        <v>45613</v>
+        <v>45620</v>
       </c>
       <c r="C96" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>5</v>
@@ -1764,13 +1764,13 @@
         <v>4</v>
       </c>
       <c r="B97" s="2">
-        <v>45614</v>
+        <v>45620</v>
       </c>
       <c r="C97" s="2">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -1778,10 +1778,10 @@
         <v>4</v>
       </c>
       <c r="B98" s="2">
-        <v>45615</v>
+        <v>45620</v>
       </c>
       <c r="C98" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>5</v>
@@ -1792,13 +1792,13 @@
         <v>4</v>
       </c>
       <c r="B99" s="2">
-        <v>45617</v>
+        <v>45621</v>
       </c>
       <c r="C99" s="2">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -1806,13 +1806,13 @@
         <v>4</v>
       </c>
       <c r="B100" s="2">
-        <v>45619</v>
+        <v>45621</v>
       </c>
       <c r="C100" s="2">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -1820,13 +1820,13 @@
         <v>4</v>
       </c>
       <c r="B101" s="2">
-        <v>45620</v>
+        <v>45621</v>
       </c>
       <c r="C101" s="2">
-        <v>245</v>
+        <v>78</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -1837,7 +1837,7 @@
         <v>45621</v>
       </c>
       <c r="C102" s="2">
-        <v>412</v>
+        <v>75</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>5</v>
@@ -1848,10 +1848,10 @@
         <v>4</v>
       </c>
       <c r="B103" s="2">
-        <v>45622</v>
+        <v>45621</v>
       </c>
       <c r="C103" s="2">
-        <v>2</v>
+        <v>412</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>5</v>
@@ -1862,13 +1862,13 @@
         <v>4</v>
       </c>
       <c r="B104" s="2">
-        <v>45623</v>
+        <v>45621</v>
       </c>
       <c r="C104" s="2">
-        <v>349</v>
+        <v>224</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -1876,7 +1876,7 @@
         <v>4</v>
       </c>
       <c r="B105" s="2">
-        <v>45623</v>
+        <v>45621</v>
       </c>
       <c r="C105" s="2">
         <v>1</v>
@@ -1890,10 +1890,10 @@
         <v>4</v>
       </c>
       <c r="B106" s="2">
-        <v>45624</v>
+        <v>45621</v>
       </c>
       <c r="C106" s="2">
-        <v>957</v>
+        <v>1</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>5</v>
@@ -1904,7 +1904,7 @@
         <v>4</v>
       </c>
       <c r="B107" s="2">
-        <v>45625</v>
+        <v>45621</v>
       </c>
       <c r="C107" s="2">
         <v>1</v>
@@ -1918,10 +1918,10 @@
         <v>4</v>
       </c>
       <c r="B108" s="2">
-        <v>45626</v>
+        <v>45622</v>
       </c>
       <c r="C108" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>5</v>
@@ -1932,10 +1932,10 @@
         <v>4</v>
       </c>
       <c r="B109" s="2">
-        <v>45627</v>
+        <v>45622</v>
       </c>
       <c r="C109" s="2">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>6</v>
@@ -1946,10 +1946,10 @@
         <v>4</v>
       </c>
       <c r="B110" s="2">
-        <v>45627</v>
+        <v>45622</v>
       </c>
       <c r="C110" s="2">
-        <v>1018</v>
+        <v>71</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>5</v>
@@ -1960,10 +1960,10 @@
         <v>4</v>
       </c>
       <c r="B111" s="2">
-        <v>45627</v>
+        <v>45622</v>
       </c>
       <c r="C111" s="2">
-        <v>9</v>
+        <v>454</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>5</v>
@@ -1974,13 +1974,13 @@
         <v>4</v>
       </c>
       <c r="B112" s="2">
-        <v>45628</v>
+        <v>45622</v>
       </c>
       <c r="C112" s="2">
-        <v>88</v>
+        <v>284</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -1988,13 +1988,13 @@
         <v>4</v>
       </c>
       <c r="B113" s="2">
-        <v>45605</v>
+        <v>45622</v>
       </c>
       <c r="C113" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2002,10 +2002,10 @@
         <v>4</v>
       </c>
       <c r="B114" s="2">
-        <v>45606</v>
+        <v>45622</v>
       </c>
       <c r="C114" s="2">
-        <v>499</v>
+        <v>2</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>5</v>
@@ -2016,13 +2016,13 @@
         <v>4</v>
       </c>
       <c r="B115" s="2">
-        <v>45606</v>
+        <v>45622</v>
       </c>
       <c r="C115" s="2">
-        <v>117</v>
+        <v>1</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2030,10 +2030,10 @@
         <v>4</v>
       </c>
       <c r="B116" s="2">
-        <v>45606</v>
+        <v>45622</v>
       </c>
       <c r="C116" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>5</v>
@@ -2044,13 +2044,13 @@
         <v>4</v>
       </c>
       <c r="B117" s="2">
-        <v>45612</v>
+        <v>45623</v>
       </c>
       <c r="C117" s="2">
-        <v>222</v>
+        <v>1</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2058,10 +2058,10 @@
         <v>4</v>
       </c>
       <c r="B118" s="2">
-        <v>45612</v>
+        <v>45623</v>
       </c>
       <c r="C118" s="2">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>5</v>
@@ -2072,13 +2072,13 @@
         <v>4</v>
       </c>
       <c r="B119" s="2">
-        <v>45614</v>
+        <v>45623</v>
       </c>
       <c r="C119" s="2">
-        <v>3</v>
+        <v>125</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2086,10 +2086,10 @@
         <v>4</v>
       </c>
       <c r="B120" s="2">
-        <v>45615</v>
+        <v>45623</v>
       </c>
       <c r="C120" s="2">
-        <v>2</v>
+        <v>124</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>5</v>
@@ -2100,13 +2100,13 @@
         <v>4</v>
       </c>
       <c r="B121" s="2">
-        <v>45615</v>
+        <v>45623</v>
       </c>
       <c r="C121" s="2">
-        <v>36</v>
+        <v>991</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2114,13 +2114,13 @@
         <v>4</v>
       </c>
       <c r="B122" s="2">
-        <v>45615</v>
+        <v>45623</v>
       </c>
       <c r="C122" s="2">
-        <v>2</v>
+        <v>349</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2128,13 +2128,13 @@
         <v>4</v>
       </c>
       <c r="B123" s="2">
-        <v>45618</v>
+        <v>45623</v>
       </c>
       <c r="C123" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2142,13 +2142,13 @@
         <v>4</v>
       </c>
       <c r="B124" s="2">
-        <v>45619</v>
+        <v>45623</v>
       </c>
       <c r="C124" s="2">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2156,10 +2156,10 @@
         <v>4</v>
       </c>
       <c r="B125" s="2">
-        <v>45620</v>
+        <v>45623</v>
       </c>
       <c r="C125" s="2">
-        <v>93</v>
+        <v>1</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>5</v>
@@ -2170,10 +2170,10 @@
         <v>4</v>
       </c>
       <c r="B126" s="2">
-        <v>45621</v>
+        <v>45623</v>
       </c>
       <c r="C126" s="2">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>5</v>
@@ -2184,10 +2184,10 @@
         <v>4</v>
       </c>
       <c r="B127" s="2">
-        <v>45621</v>
+        <v>45624</v>
       </c>
       <c r="C127" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>5</v>
@@ -2198,13 +2198,13 @@
         <v>4</v>
       </c>
       <c r="B128" s="2">
-        <v>45622</v>
+        <v>45624</v>
       </c>
       <c r="C128" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2212,10 +2212,10 @@
         <v>4</v>
       </c>
       <c r="B129" s="2">
-        <v>45622</v>
+        <v>45624</v>
       </c>
       <c r="C129" s="2">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>6</v>
@@ -2226,10 +2226,10 @@
         <v>4</v>
       </c>
       <c r="B130" s="2">
-        <v>45623</v>
+        <v>45624</v>
       </c>
       <c r="C130" s="2">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>5</v>
@@ -2243,7 +2243,7 @@
         <v>45624</v>
       </c>
       <c r="C131" s="2">
-        <v>3</v>
+        <v>957</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>5</v>
@@ -2257,10 +2257,10 @@
         <v>45624</v>
       </c>
       <c r="C132" s="2">
-        <v>1</v>
+        <v>340</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2268,13 +2268,13 @@
         <v>4</v>
       </c>
       <c r="B133" s="2">
-        <v>45625</v>
+        <v>45624</v>
       </c>
       <c r="C133" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2282,13 +2282,13 @@
         <v>4</v>
       </c>
       <c r="B134" s="2">
-        <v>45625</v>
+        <v>45624</v>
       </c>
       <c r="C134" s="2">
-        <v>159</v>
+        <v>1</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2296,13 +2296,13 @@
         <v>4</v>
       </c>
       <c r="B135" s="2">
-        <v>45625</v>
+        <v>45624</v>
       </c>
       <c r="C135" s="2">
-        <v>132</v>
+        <v>1</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2310,13 +2310,13 @@
         <v>4</v>
       </c>
       <c r="B136" s="2">
-        <v>45625</v>
+        <v>45624</v>
       </c>
       <c r="C136" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -2324,10 +2324,10 @@
         <v>4</v>
       </c>
       <c r="B137" s="2">
-        <v>45626</v>
+        <v>45624</v>
       </c>
       <c r="C137" s="2">
-        <v>98</v>
+        <v>1</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>5</v>
@@ -2338,13 +2338,13 @@
         <v>4</v>
       </c>
       <c r="B138" s="2">
-        <v>45628</v>
+        <v>45624</v>
       </c>
       <c r="C138" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -2352,13 +2352,13 @@
         <v>4</v>
       </c>
       <c r="B139" s="2">
-        <v>45602</v>
+        <v>45625</v>
       </c>
       <c r="C139" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -2366,13 +2366,13 @@
         <v>4</v>
       </c>
       <c r="B140" s="2">
-        <v>45605</v>
+        <v>45625</v>
       </c>
       <c r="C140" s="2">
-        <v>137</v>
+        <v>7</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2380,13 +2380,13 @@
         <v>4</v>
       </c>
       <c r="B141" s="2">
-        <v>45605</v>
+        <v>45625</v>
       </c>
       <c r="C141" s="2">
-        <v>760</v>
+        <v>159</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -2394,13 +2394,13 @@
         <v>4</v>
       </c>
       <c r="B142" s="2">
-        <v>45606</v>
+        <v>45625</v>
       </c>
       <c r="C142" s="2">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2408,13 +2408,13 @@
         <v>4</v>
       </c>
       <c r="B143" s="2">
-        <v>45611</v>
+        <v>45625</v>
       </c>
       <c r="C143" s="2">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -2422,13 +2422,13 @@
         <v>4</v>
       </c>
       <c r="B144" s="2">
-        <v>45613</v>
+        <v>45625</v>
       </c>
       <c r="C144" s="2">
-        <v>153</v>
+        <v>707</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -2436,13 +2436,13 @@
         <v>4</v>
       </c>
       <c r="B145" s="2">
-        <v>45614</v>
+        <v>45625</v>
       </c>
       <c r="C145" s="2">
-        <v>2</v>
+        <v>426</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -2450,13 +2450,13 @@
         <v>4</v>
       </c>
       <c r="B146" s="2">
-        <v>45614</v>
+        <v>45625</v>
       </c>
       <c r="C146" s="2">
         <v>4</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -2464,13 +2464,13 @@
         <v>4</v>
       </c>
       <c r="B147" s="2">
-        <v>45616</v>
+        <v>45625</v>
       </c>
       <c r="C147" s="2">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="B148" s="2">
-        <v>45617</v>
+        <v>45625</v>
       </c>
       <c r="C148" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>5</v>
@@ -2492,13 +2492,13 @@
         <v>4</v>
       </c>
       <c r="B149" s="2">
-        <v>45619</v>
+        <v>45625</v>
       </c>
       <c r="C149" s="2">
-        <v>224</v>
+        <v>4</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -2506,10 +2506,10 @@
         <v>4</v>
       </c>
       <c r="B150" s="2">
-        <v>45620</v>
+        <v>45625</v>
       </c>
       <c r="C150" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>5</v>
@@ -2520,13 +2520,13 @@
         <v>4</v>
       </c>
       <c r="B151" s="2">
-        <v>45621</v>
+        <v>45625</v>
       </c>
       <c r="C151" s="2">
-        <v>107</v>
+        <v>28</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -2534,10 +2534,10 @@
         <v>4</v>
       </c>
       <c r="B152" s="2">
-        <v>45623</v>
+        <v>45626</v>
       </c>
       <c r="C152" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>5</v>
@@ -2548,10 +2548,10 @@
         <v>4</v>
       </c>
       <c r="B153" s="2">
-        <v>45623</v>
+        <v>45626</v>
       </c>
       <c r="C153" s="2">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>5</v>
@@ -2562,13 +2562,13 @@
         <v>4</v>
       </c>
       <c r="B154" s="2">
-        <v>45625</v>
+        <v>45626</v>
       </c>
       <c r="C154" s="2">
-        <v>707</v>
+        <v>297</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -2579,10 +2579,10 @@
         <v>45626</v>
       </c>
       <c r="C155" s="2">
-        <v>1</v>
+        <v>115</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -2593,7 +2593,7 @@
         <v>45626</v>
       </c>
       <c r="C156" s="2">
-        <v>9</v>
+        <v>98</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>5</v>
@@ -2607,7 +2607,7 @@
         <v>45626</v>
       </c>
       <c r="C157" s="2">
-        <v>37</v>
+        <v>1024</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>5</v>
@@ -2618,13 +2618,13 @@
         <v>4</v>
       </c>
       <c r="B158" s="2">
-        <v>45627</v>
+        <v>45626</v>
       </c>
       <c r="C158" s="2">
-        <v>1</v>
+        <v>410</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -2632,10 +2632,10 @@
         <v>4</v>
       </c>
       <c r="B159" s="2">
-        <v>45627</v>
+        <v>45626</v>
       </c>
       <c r="C159" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>5</v>
@@ -2646,10 +2646,10 @@
         <v>4</v>
       </c>
       <c r="B160" s="2">
-        <v>45628</v>
+        <v>45626</v>
       </c>
       <c r="C160" s="2">
-        <v>337</v>
+        <v>9</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>5</v>
@@ -2660,10 +2660,10 @@
         <v>4</v>
       </c>
       <c r="B161" s="2">
-        <v>45611</v>
+        <v>45626</v>
       </c>
       <c r="C161" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>5</v>
@@ -2674,10 +2674,10 @@
         <v>4</v>
       </c>
       <c r="B162" s="2">
-        <v>45612</v>
+        <v>45626</v>
       </c>
       <c r="C162" s="2">
-        <v>129</v>
+        <v>37</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>5</v>
@@ -2688,10 +2688,10 @@
         <v>4</v>
       </c>
       <c r="B163" s="2">
-        <v>45613</v>
+        <v>45627</v>
       </c>
       <c r="C163" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>5</v>
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B164" s="2">
-        <v>45614</v>
+        <v>45627</v>
       </c>
       <c r="C164" s="2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -2716,10 +2716,10 @@
         <v>4</v>
       </c>
       <c r="B165" s="2">
-        <v>45614</v>
+        <v>45627</v>
       </c>
       <c r="C165" s="2">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>5</v>
@@ -2730,10 +2730,10 @@
         <v>4</v>
       </c>
       <c r="B166" s="2">
-        <v>45614</v>
+        <v>45627</v>
       </c>
       <c r="C166" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>5</v>
@@ -2744,13 +2744,13 @@
         <v>4</v>
       </c>
       <c r="B167" s="2">
-        <v>45615</v>
+        <v>45627</v>
       </c>
       <c r="C167" s="2">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -2758,13 +2758,13 @@
         <v>4</v>
       </c>
       <c r="B168" s="2">
-        <v>45616</v>
+        <v>45627</v>
       </c>
       <c r="C168" s="2">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -2772,13 +2772,13 @@
         <v>4</v>
       </c>
       <c r="B169" s="2">
-        <v>45617</v>
+        <v>45627</v>
       </c>
       <c r="C169" s="2">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -2786,10 +2786,10 @@
         <v>4</v>
       </c>
       <c r="B170" s="2">
-        <v>45618</v>
+        <v>45627</v>
       </c>
       <c r="C170" s="2">
-        <v>77</v>
+        <v>1018</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>5</v>
@@ -2800,13 +2800,13 @@
         <v>4</v>
       </c>
       <c r="B171" s="2">
-        <v>45620</v>
+        <v>45627</v>
       </c>
       <c r="C171" s="2">
-        <v>3</v>
+        <v>173</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -2814,13 +2814,13 @@
         <v>4</v>
       </c>
       <c r="B172" s="2">
-        <v>45620</v>
+        <v>45627</v>
       </c>
       <c r="C172" s="2">
-        <v>81</v>
+        <v>4</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -2828,10 +2828,10 @@
         <v>4</v>
       </c>
       <c r="B173" s="2">
-        <v>45620</v>
+        <v>45627</v>
       </c>
       <c r="C173" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>5</v>
@@ -2842,10 +2842,10 @@
         <v>4</v>
       </c>
       <c r="B174" s="2">
-        <v>45621</v>
+        <v>45627</v>
       </c>
       <c r="C174" s="2">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>5</v>
@@ -2856,10 +2856,10 @@
         <v>4</v>
       </c>
       <c r="B175" s="2">
-        <v>45623</v>
+        <v>45628</v>
       </c>
       <c r="C175" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>5</v>
@@ -2870,13 +2870,13 @@
         <v>4</v>
       </c>
       <c r="B176" s="2">
-        <v>45623</v>
+        <v>45628</v>
       </c>
       <c r="C176" s="2">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -2884,13 +2884,13 @@
         <v>4</v>
       </c>
       <c r="B177" s="2">
-        <v>45624</v>
+        <v>45628</v>
       </c>
       <c r="C177" s="2">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -2898,10 +2898,10 @@
         <v>4</v>
       </c>
       <c r="B178" s="2">
-        <v>45626</v>
+        <v>45628</v>
       </c>
       <c r="C178" s="2">
-        <v>7</v>
+        <v>337</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>5</v>
@@ -2912,13 +2912,13 @@
         <v>4</v>
       </c>
       <c r="B179" s="2">
-        <v>45627</v>
+        <v>45628</v>
       </c>
       <c r="C179" s="2">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -2926,7 +2926,7 @@
         <v>4</v>
       </c>
       <c r="B180" s="2">
-        <v>45627</v>
+        <v>45628</v>
       </c>
       <c r="C180" s="2">
         <v>1</v>
@@ -2940,13 +2940,797 @@
         <v>4</v>
       </c>
       <c r="B181" s="2">
-        <v>45627</v>
+        <v>45628</v>
       </c>
       <c r="C181" s="2">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="D181" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4">
+      <c r="A182" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B182" s="2">
+        <v>45629</v>
+      </c>
+      <c r="C182" s="2">
+        <v>-3</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4">
+      <c r="A183" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B183" s="2">
+        <v>45629</v>
+      </c>
+      <c r="C183" s="2">
+        <v>21</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4">
+      <c r="A184" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B184" s="2">
+        <v>45629</v>
+      </c>
+      <c r="C184" s="2">
+        <v>99</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4">
+      <c r="A185" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B185" s="2">
+        <v>45629</v>
+      </c>
+      <c r="C185" s="2">
+        <v>368</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4">
+      <c r="A186" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B186" s="2">
+        <v>45629</v>
+      </c>
+      <c r="C186" s="2">
+        <v>85</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4">
+      <c r="A187" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B187" s="2">
+        <v>45629</v>
+      </c>
+      <c r="C187" s="2">
+        <v>1</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4">
+      <c r="A188" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B188" s="2">
+        <v>45629</v>
+      </c>
+      <c r="C188" s="2">
+        <v>5</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4">
+      <c r="A189" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B189" s="2">
+        <v>45630</v>
+      </c>
+      <c r="C189" s="2">
+        <v>20</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4">
+      <c r="A190" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B190" s="2">
+        <v>45630</v>
+      </c>
+      <c r="C190" s="2">
+        <v>117</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4">
+      <c r="A191" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B191" s="2">
+        <v>45630</v>
+      </c>
+      <c r="C191" s="2">
+        <v>392</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4">
+      <c r="A192" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B192" s="2">
+        <v>45630</v>
+      </c>
+      <c r="C192" s="2">
+        <v>90</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4">
+      <c r="A193" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B193" s="2">
+        <v>45630</v>
+      </c>
+      <c r="C193" s="2">
+        <v>2</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4">
+      <c r="A194" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B194" s="2">
+        <v>45630</v>
+      </c>
+      <c r="C194" s="2">
+        <v>3</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
+      <c r="A195" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B195" s="2">
+        <v>45630</v>
+      </c>
+      <c r="C195" s="2">
+        <v>2</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4">
+      <c r="A196" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B196" s="2">
+        <v>45631</v>
+      </c>
+      <c r="C196" s="2">
+        <v>1</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4">
+      <c r="A197" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B197" s="2">
+        <v>45631</v>
+      </c>
+      <c r="C197" s="2">
+        <v>16</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4">
+      <c r="A198" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B198" s="2">
+        <v>45631</v>
+      </c>
+      <c r="C198" s="2">
+        <v>86</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4">
+      <c r="A199" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B199" s="2">
+        <v>45631</v>
+      </c>
+      <c r="C199" s="2">
+        <v>417</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4">
+      <c r="A200" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B200" s="2">
+        <v>45631</v>
+      </c>
+      <c r="C200" s="2">
+        <v>89</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4">
+      <c r="A201" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B201" s="2">
+        <v>45631</v>
+      </c>
+      <c r="C201" s="2">
+        <v>2</v>
+      </c>
+      <c r="D201" s="2" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
+      <c r="A202" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B202" s="2">
+        <v>45631</v>
+      </c>
+      <c r="C202" s="2">
+        <v>7</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4">
+      <c r="A203" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B203" s="2">
+        <v>45632</v>
+      </c>
+      <c r="C203" s="2">
+        <v>1</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
+      <c r="A204" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B204" s="2">
+        <v>45632</v>
+      </c>
+      <c r="C204" s="2">
+        <v>1</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4">
+      <c r="A205" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B205" s="2">
+        <v>45632</v>
+      </c>
+      <c r="C205" s="2">
+        <v>27</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4">
+      <c r="A206" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B206" s="2">
+        <v>45632</v>
+      </c>
+      <c r="C206" s="2">
+        <v>114</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4">
+      <c r="A207" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B207" s="2">
+        <v>45632</v>
+      </c>
+      <c r="C207" s="2">
+        <v>580</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
+      <c r="A208" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B208" s="2">
+        <v>45632</v>
+      </c>
+      <c r="C208" s="2">
+        <v>113</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
+      <c r="A209" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B209" s="2">
+        <v>45632</v>
+      </c>
+      <c r="C209" s="2">
+        <v>5</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
+      <c r="A210" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B210" s="2">
+        <v>45633</v>
+      </c>
+      <c r="C210" s="2">
+        <v>3</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
+      <c r="A211" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B211" s="2">
+        <v>45633</v>
+      </c>
+      <c r="C211" s="2">
+        <v>60</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
+      <c r="A212" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B212" s="2">
+        <v>45633</v>
+      </c>
+      <c r="C212" s="2">
+        <v>62</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
+      <c r="A213" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B213" s="2">
+        <v>45633</v>
+      </c>
+      <c r="C213" s="2">
+        <v>149</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
+      <c r="A214" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B214" s="2">
+        <v>45633</v>
+      </c>
+      <c r="C214" s="2">
+        <v>1558</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
+      <c r="A215" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B215" s="2">
+        <v>45633</v>
+      </c>
+      <c r="C215" s="2">
+        <v>295</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
+      <c r="A216" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B216" s="2">
+        <v>45633</v>
+      </c>
+      <c r="C216" s="2">
+        <v>2</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
+      <c r="A217" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B217" s="2">
+        <v>45633</v>
+      </c>
+      <c r="C217" s="2">
+        <v>2</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4">
+      <c r="A218" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B218" s="2">
+        <v>45633</v>
+      </c>
+      <c r="C218" s="2">
+        <v>11</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
+      <c r="A219" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B219" s="2">
+        <v>45634</v>
+      </c>
+      <c r="C219" s="2">
+        <v>1</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
+      <c r="A220" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B220" s="2">
+        <v>45634</v>
+      </c>
+      <c r="C220" s="2">
+        <v>1</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4">
+      <c r="A221" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B221" s="2">
+        <v>45634</v>
+      </c>
+      <c r="C221" s="2">
+        <v>3</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4">
+      <c r="A222" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B222" s="2">
+        <v>45634</v>
+      </c>
+      <c r="C222" s="2">
+        <v>160</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
+      <c r="A223" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B223" s="2">
+        <v>45634</v>
+      </c>
+      <c r="C223" s="2">
+        <v>59</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
+      <c r="A224" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B224" s="2">
+        <v>45634</v>
+      </c>
+      <c r="C224" s="2">
+        <v>168</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
+      <c r="A225" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B225" s="2">
+        <v>45634</v>
+      </c>
+      <c r="C225" s="2">
+        <v>1260</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
+      <c r="A226" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B226" s="2">
+        <v>45634</v>
+      </c>
+      <c r="C226" s="2">
+        <v>160</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
+      <c r="A227" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B227" s="2">
+        <v>45634</v>
+      </c>
+      <c r="C227" s="2">
+        <v>5</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
+      <c r="A228" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B228" s="2">
+        <v>45634</v>
+      </c>
+      <c r="C228" s="2">
+        <v>2</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
+      <c r="A229" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B229" s="2">
+        <v>45634</v>
+      </c>
+      <c r="C229" s="2">
+        <v>13</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
+      <c r="A230" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B230" s="2">
+        <v>45635</v>
+      </c>
+      <c r="C230" s="2">
+        <v>25</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="A231" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B231" s="2">
+        <v>45635</v>
+      </c>
+      <c r="C231" s="2">
+        <v>84</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="A232" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B232" s="2">
+        <v>45635</v>
+      </c>
+      <c r="C232" s="2">
+        <v>360</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
+      <c r="A233" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B233" s="2">
+        <v>45635</v>
+      </c>
+      <c r="C233" s="2">
+        <v>135</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
+      <c r="A234" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B234" s="2">
+        <v>45635</v>
+      </c>
+      <c r="C234" s="2">
+        <v>2</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
+      <c r="A235" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B235" s="2">
+        <v>45635</v>
+      </c>
+      <c r="C235" s="2">
+        <v>2</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
+      <c r="A236" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B236" s="2">
+        <v>45635</v>
+      </c>
+      <c r="C236" s="2">
+        <v>1</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="A237" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B237" s="2">
+        <v>45635</v>
+      </c>
+      <c r="C237" s="2">
+        <v>10</v>
+      </c>
+      <c r="D237" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/reports/For Winter Ending (Prior Year)_Visits.xlsx
+++ b/reports/For Winter Ending (Prior Year)_Visits.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="9">
   <si>
     <t>Resort</t>
   </si>
@@ -28,22 +28,19 @@
     <t>Location</t>
   </si>
   <si>
-    <t>Purgatory</t>
+    <t>Snowbowl</t>
   </si>
   <si>
-    <t>Purgatory Passes</t>
+    <t>Snowbowl Passes</t>
   </si>
   <si>
-    <t>Purgatory Comp Tickets</t>
+    <t>Snowbowl Comp Tickets</t>
   </si>
   <si>
-    <t>Purgatory Tickets</t>
+    <t>Snowbowl Tickets</t>
   </si>
   <si>
-    <t>Purgatory Coaster</t>
-  </si>
-  <si>
-    <t>Purgatory Uplift Tickets</t>
+    <t>Snowbowl Uplift Tickets</t>
   </si>
 </sst>
 </file>
@@ -406,13 +403,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D237"/>
+  <dimension ref="A1:D238"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -434,7 +431,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>45601</v>
+        <v>45597</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
@@ -448,10 +445,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>45601</v>
+        <v>45604</v>
       </c>
       <c r="C3" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>5</v>
@@ -462,13 +459,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>45602</v>
+        <v>45604</v>
       </c>
       <c r="C4" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -479,10 +476,10 @@
         <v>45604</v>
       </c>
       <c r="C5" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -493,7 +490,7 @@
         <v>45604</v>
       </c>
       <c r="C6" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>5</v>
@@ -507,10 +504,10 @@
         <v>45604</v>
       </c>
       <c r="C7" s="2">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -518,13 +515,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>45605</v>
+        <v>45604</v>
       </c>
       <c r="C8" s="2">
-        <v>137</v>
+        <v>31</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -532,10 +529,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>45605</v>
+        <v>45604</v>
       </c>
       <c r="C9" s="2">
-        <v>58</v>
+        <v>789</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>5</v>
@@ -546,13 +543,13 @@
         <v>4</v>
       </c>
       <c r="B10" s="2">
-        <v>45605</v>
+        <v>45604</v>
       </c>
       <c r="C10" s="2">
-        <v>760</v>
+        <v>139</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -563,10 +560,10 @@
         <v>45605</v>
       </c>
       <c r="C11" s="2">
-        <v>164</v>
+        <v>2</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -577,7 +574,7 @@
         <v>45605</v>
       </c>
       <c r="C12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>5</v>
@@ -591,10 +588,10 @@
         <v>45605</v>
       </c>
       <c r="C13" s="2">
+        <v>18</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -605,7 +602,7 @@
         <v>45605</v>
       </c>
       <c r="C14" s="2">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>5</v>
@@ -616,13 +613,13 @@
         <v>4</v>
       </c>
       <c r="B15" s="2">
-        <v>45606</v>
+        <v>45605</v>
       </c>
       <c r="C15" s="2">
-        <v>127</v>
+        <v>512</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -630,13 +627,13 @@
         <v>4</v>
       </c>
       <c r="B16" s="2">
-        <v>45606</v>
+        <v>45605</v>
       </c>
       <c r="C16" s="2">
-        <v>43</v>
+        <v>237</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -644,13 +641,13 @@
         <v>4</v>
       </c>
       <c r="B17" s="2">
-        <v>45606</v>
+        <v>45605</v>
       </c>
       <c r="C17" s="2">
-        <v>499</v>
+        <v>187</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -661,10 +658,10 @@
         <v>45606</v>
       </c>
       <c r="C18" s="2">
-        <v>117</v>
+        <v>1</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -675,7 +672,7 @@
         <v>45606</v>
       </c>
       <c r="C19" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>5</v>
@@ -689,7 +686,7 @@
         <v>45606</v>
       </c>
       <c r="C20" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>5</v>
@@ -700,10 +697,10 @@
         <v>4</v>
       </c>
       <c r="B21" s="2">
-        <v>45607</v>
+        <v>45606</v>
       </c>
       <c r="C21" s="2">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>6</v>
@@ -714,13 +711,13 @@
         <v>4</v>
       </c>
       <c r="B22" s="2">
-        <v>45610</v>
+        <v>45606</v>
       </c>
       <c r="C22" s="2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -728,13 +725,13 @@
         <v>4</v>
       </c>
       <c r="B23" s="2">
-        <v>45610</v>
+        <v>45606</v>
       </c>
       <c r="C23" s="2">
-        <v>6</v>
+        <v>549</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -742,13 +739,13 @@
         <v>4</v>
       </c>
       <c r="B24" s="2">
-        <v>45611</v>
+        <v>45606</v>
       </c>
       <c r="C24" s="2">
-        <v>4</v>
+        <v>290</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -756,13 +753,13 @@
         <v>4</v>
       </c>
       <c r="B25" s="2">
-        <v>45611</v>
+        <v>45606</v>
       </c>
       <c r="C25" s="2">
-        <v>3</v>
+        <v>211</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -770,10 +767,10 @@
         <v>4</v>
       </c>
       <c r="B26" s="2">
-        <v>45612</v>
+        <v>45607</v>
       </c>
       <c r="C26" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>5</v>
@@ -784,13 +781,13 @@
         <v>4</v>
       </c>
       <c r="B27" s="2">
-        <v>45612</v>
+        <v>45607</v>
       </c>
       <c r="C27" s="2">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -798,10 +795,10 @@
         <v>4</v>
       </c>
       <c r="B28" s="2">
-        <v>45612</v>
+        <v>45607</v>
       </c>
       <c r="C28" s="2">
-        <v>129</v>
+        <v>6</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>5</v>
@@ -812,13 +809,13 @@
         <v>4</v>
       </c>
       <c r="B29" s="2">
-        <v>45612</v>
+        <v>45607</v>
       </c>
       <c r="C29" s="2">
-        <v>987</v>
+        <v>33</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -826,13 +823,13 @@
         <v>4</v>
       </c>
       <c r="B30" s="2">
-        <v>45612</v>
+        <v>45607</v>
       </c>
       <c r="C30" s="2">
-        <v>222</v>
+        <v>27</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -840,10 +837,10 @@
         <v>4</v>
       </c>
       <c r="B31" s="2">
-        <v>45612</v>
+        <v>45607</v>
       </c>
       <c r="C31" s="2">
-        <v>5</v>
+        <v>904</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>5</v>
@@ -854,13 +851,13 @@
         <v>4</v>
       </c>
       <c r="B32" s="2">
-        <v>45612</v>
+        <v>45607</v>
       </c>
       <c r="C32" s="2">
-        <v>12</v>
+        <v>473</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -868,13 +865,13 @@
         <v>4</v>
       </c>
       <c r="B33" s="2">
-        <v>45612</v>
+        <v>45607</v>
       </c>
       <c r="C33" s="2">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -882,10 +879,10 @@
         <v>4</v>
       </c>
       <c r="B34" s="2">
-        <v>45613</v>
+        <v>45608</v>
       </c>
       <c r="C34" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>5</v>
@@ -896,10 +893,10 @@
         <v>4</v>
       </c>
       <c r="B35" s="2">
-        <v>45613</v>
+        <v>45608</v>
       </c>
       <c r="C35" s="2">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>6</v>
@@ -910,10 +907,10 @@
         <v>4</v>
       </c>
       <c r="B36" s="2">
-        <v>45613</v>
+        <v>45608</v>
       </c>
       <c r="C36" s="2">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>5</v>
@@ -924,10 +921,10 @@
         <v>4</v>
       </c>
       <c r="B37" s="2">
-        <v>45613</v>
+        <v>45608</v>
       </c>
       <c r="C37" s="2">
-        <v>769</v>
+        <v>235</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>5</v>
@@ -938,10 +935,10 @@
         <v>4</v>
       </c>
       <c r="B38" s="2">
-        <v>45613</v>
+        <v>45608</v>
       </c>
       <c r="C38" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>7</v>
@@ -952,13 +949,13 @@
         <v>4</v>
       </c>
       <c r="B39" s="2">
-        <v>45613</v>
+        <v>45608</v>
       </c>
       <c r="C39" s="2">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -966,10 +963,10 @@
         <v>4</v>
       </c>
       <c r="B40" s="2">
-        <v>45613</v>
+        <v>45609</v>
       </c>
       <c r="C40" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>5</v>
@@ -980,13 +977,13 @@
         <v>4</v>
       </c>
       <c r="B41" s="2">
-        <v>45613</v>
+        <v>45609</v>
       </c>
       <c r="C41" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -994,10 +991,10 @@
         <v>4</v>
       </c>
       <c r="B42" s="2">
-        <v>45614</v>
+        <v>45609</v>
       </c>
       <c r="C42" s="2">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>5</v>
@@ -1008,13 +1005,13 @@
         <v>4</v>
       </c>
       <c r="B43" s="2">
-        <v>45614</v>
+        <v>45609</v>
       </c>
       <c r="C43" s="2">
-        <v>11</v>
+        <v>319</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1022,13 +1019,13 @@
         <v>4</v>
       </c>
       <c r="B44" s="2">
-        <v>45614</v>
+        <v>45609</v>
       </c>
       <c r="C44" s="2">
-        <v>75</v>
+        <v>186</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1036,13 +1033,13 @@
         <v>4</v>
       </c>
       <c r="B45" s="2">
-        <v>45614</v>
+        <v>45609</v>
       </c>
       <c r="C45" s="2">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1050,13 +1047,13 @@
         <v>4</v>
       </c>
       <c r="B46" s="2">
-        <v>45614</v>
+        <v>45610</v>
       </c>
       <c r="C46" s="2">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1064,13 +1061,13 @@
         <v>4</v>
       </c>
       <c r="B47" s="2">
-        <v>45614</v>
+        <v>45610</v>
       </c>
       <c r="C47" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1078,10 +1075,10 @@
         <v>4</v>
       </c>
       <c r="B48" s="2">
-        <v>45614</v>
+        <v>45610</v>
       </c>
       <c r="C48" s="2">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>5</v>
@@ -1092,10 +1089,10 @@
         <v>4</v>
       </c>
       <c r="B49" s="2">
-        <v>45614</v>
+        <v>45610</v>
       </c>
       <c r="C49" s="2">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>5</v>
@@ -1106,13 +1103,13 @@
         <v>4</v>
       </c>
       <c r="B50" s="2">
-        <v>45614</v>
+        <v>45610</v>
       </c>
       <c r="C50" s="2">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1120,13 +1117,13 @@
         <v>4</v>
       </c>
       <c r="B51" s="2">
-        <v>45615</v>
+        <v>45610</v>
       </c>
       <c r="C51" s="2">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1134,10 +1131,10 @@
         <v>4</v>
       </c>
       <c r="B52" s="2">
-        <v>45615</v>
+        <v>45611</v>
       </c>
       <c r="C52" s="2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>6</v>
@@ -1148,10 +1145,10 @@
         <v>4</v>
       </c>
       <c r="B53" s="2">
-        <v>45615</v>
+        <v>45611</v>
       </c>
       <c r="C53" s="2">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>5</v>
@@ -1162,13 +1159,13 @@
         <v>4</v>
       </c>
       <c r="B54" s="2">
-        <v>45615</v>
+        <v>45611</v>
       </c>
       <c r="C54" s="2">
-        <v>167</v>
+        <v>2</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1176,13 +1173,13 @@
         <v>4</v>
       </c>
       <c r="B55" s="2">
-        <v>45615</v>
+        <v>45611</v>
       </c>
       <c r="C55" s="2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1190,13 +1187,13 @@
         <v>4</v>
       </c>
       <c r="B56" s="2">
-        <v>45615</v>
+        <v>45612</v>
       </c>
       <c r="C56" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1204,10 +1201,10 @@
         <v>4</v>
       </c>
       <c r="B57" s="2">
-        <v>45615</v>
+        <v>45612</v>
       </c>
       <c r="C57" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>5</v>
@@ -1218,13 +1215,13 @@
         <v>4</v>
       </c>
       <c r="B58" s="2">
-        <v>45615</v>
+        <v>45612</v>
       </c>
       <c r="C58" s="2">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1232,10 +1229,10 @@
         <v>4</v>
       </c>
       <c r="B59" s="2">
-        <v>45615</v>
+        <v>45612</v>
       </c>
       <c r="C59" s="2">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>5</v>
@@ -1246,13 +1243,13 @@
         <v>4</v>
       </c>
       <c r="B60" s="2">
-        <v>45616</v>
+        <v>45612</v>
       </c>
       <c r="C60" s="2">
-        <v>15</v>
+        <v>614</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1260,13 +1257,13 @@
         <v>4</v>
       </c>
       <c r="B61" s="2">
-        <v>45616</v>
+        <v>45612</v>
       </c>
       <c r="C61" s="2">
-        <v>65</v>
+        <v>456</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1274,13 +1271,13 @@
         <v>4</v>
       </c>
       <c r="B62" s="2">
-        <v>45616</v>
+        <v>45612</v>
       </c>
       <c r="C62" s="2">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1288,13 +1285,13 @@
         <v>4</v>
       </c>
       <c r="B63" s="2">
-        <v>45616</v>
+        <v>45613</v>
       </c>
       <c r="C63" s="2">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1302,7 +1299,7 @@
         <v>4</v>
       </c>
       <c r="B64" s="2">
-        <v>45616</v>
+        <v>45613</v>
       </c>
       <c r="C64" s="2">
         <v>3</v>
@@ -1316,13 +1313,13 @@
         <v>4</v>
       </c>
       <c r="B65" s="2">
-        <v>45616</v>
+        <v>45613</v>
       </c>
       <c r="C65" s="2">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1330,10 +1327,10 @@
         <v>4</v>
       </c>
       <c r="B66" s="2">
-        <v>45616</v>
+        <v>45613</v>
       </c>
       <c r="C66" s="2">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>5</v>
@@ -1344,13 +1341,13 @@
         <v>4</v>
       </c>
       <c r="B67" s="2">
-        <v>45617</v>
+        <v>45613</v>
       </c>
       <c r="C67" s="2">
-        <v>10</v>
+        <v>606</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1358,13 +1355,13 @@
         <v>4</v>
       </c>
       <c r="B68" s="2">
-        <v>45617</v>
+        <v>45613</v>
       </c>
       <c r="C68" s="2">
-        <v>91</v>
+        <v>468</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1372,13 +1369,13 @@
         <v>4</v>
       </c>
       <c r="B69" s="2">
-        <v>45617</v>
+        <v>45613</v>
       </c>
       <c r="C69" s="2">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1386,13 +1383,13 @@
         <v>4</v>
       </c>
       <c r="B70" s="2">
-        <v>45617</v>
+        <v>45614</v>
       </c>
       <c r="C70" s="2">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1400,7 +1397,7 @@
         <v>4</v>
       </c>
       <c r="B71" s="2">
-        <v>45617</v>
+        <v>45614</v>
       </c>
       <c r="C71" s="2">
         <v>1</v>
@@ -1414,13 +1411,13 @@
         <v>4</v>
       </c>
       <c r="B72" s="2">
-        <v>45617</v>
+        <v>45614</v>
       </c>
       <c r="C72" s="2">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1428,13 +1425,13 @@
         <v>4</v>
       </c>
       <c r="B73" s="2">
-        <v>45618</v>
+        <v>45614</v>
       </c>
       <c r="C73" s="2">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1442,10 +1439,10 @@
         <v>4</v>
       </c>
       <c r="B74" s="2">
-        <v>45618</v>
+        <v>45614</v>
       </c>
       <c r="C74" s="2">
-        <v>77</v>
+        <v>320</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>5</v>
@@ -1456,13 +1453,13 @@
         <v>4</v>
       </c>
       <c r="B75" s="2">
-        <v>45618</v>
+        <v>45614</v>
       </c>
       <c r="C75" s="2">
-        <v>343</v>
+        <v>236</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1470,13 +1467,13 @@
         <v>4</v>
       </c>
       <c r="B76" s="2">
-        <v>45618</v>
+        <v>45614</v>
       </c>
       <c r="C76" s="2">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -1484,10 +1481,10 @@
         <v>4</v>
       </c>
       <c r="B77" s="2">
-        <v>45618</v>
+        <v>45615</v>
       </c>
       <c r="C77" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>5</v>
@@ -1498,13 +1495,13 @@
         <v>4</v>
       </c>
       <c r="B78" s="2">
-        <v>45618</v>
+        <v>45615</v>
       </c>
       <c r="C78" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1512,10 +1509,10 @@
         <v>4</v>
       </c>
       <c r="B79" s="2">
-        <v>45619</v>
+        <v>45615</v>
       </c>
       <c r="C79" s="2">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>5</v>
@@ -1526,10 +1523,10 @@
         <v>4</v>
       </c>
       <c r="B80" s="2">
-        <v>45619</v>
+        <v>45615</v>
       </c>
       <c r="C80" s="2">
-        <v>4</v>
+        <v>247</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>5</v>
@@ -1540,13 +1537,13 @@
         <v>4</v>
       </c>
       <c r="B81" s="2">
-        <v>45619</v>
+        <v>45615</v>
       </c>
       <c r="C81" s="2">
-        <v>29</v>
+        <v>194</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -1554,13 +1551,13 @@
         <v>4</v>
       </c>
       <c r="B82" s="2">
-        <v>45619</v>
+        <v>45615</v>
       </c>
       <c r="C82" s="2">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1568,10 +1565,10 @@
         <v>4</v>
       </c>
       <c r="B83" s="2">
-        <v>45619</v>
+        <v>45616</v>
       </c>
       <c r="C83" s="2">
-        <v>85</v>
+        <v>3</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>5</v>
@@ -1582,10 +1579,10 @@
         <v>4</v>
       </c>
       <c r="B84" s="2">
-        <v>45619</v>
+        <v>45616</v>
       </c>
       <c r="C84" s="2">
-        <v>623</v>
+        <v>1</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>5</v>
@@ -1596,13 +1593,13 @@
         <v>4</v>
       </c>
       <c r="B85" s="2">
-        <v>45619</v>
+        <v>45616</v>
       </c>
       <c r="C85" s="2">
-        <v>224</v>
+        <v>4</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1610,10 +1607,10 @@
         <v>4</v>
       </c>
       <c r="B86" s="2">
-        <v>45619</v>
+        <v>45616</v>
       </c>
       <c r="C86" s="2">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>5</v>
@@ -1624,10 +1621,10 @@
         <v>4</v>
       </c>
       <c r="B87" s="2">
-        <v>45619</v>
+        <v>45616</v>
       </c>
       <c r="C87" s="2">
-        <v>2</v>
+        <v>317</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>5</v>
@@ -1638,13 +1635,13 @@
         <v>4</v>
       </c>
       <c r="B88" s="2">
-        <v>45619</v>
+        <v>45616</v>
       </c>
       <c r="C88" s="2">
-        <v>8</v>
+        <v>202</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -1652,13 +1649,13 @@
         <v>4</v>
       </c>
       <c r="B89" s="2">
-        <v>45620</v>
+        <v>45616</v>
       </c>
       <c r="C89" s="2">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1666,7 +1663,7 @@
         <v>4</v>
       </c>
       <c r="B90" s="2">
-        <v>45620</v>
+        <v>45617</v>
       </c>
       <c r="C90" s="2">
         <v>3</v>
@@ -1680,13 +1677,13 @@
         <v>4</v>
       </c>
       <c r="B91" s="2">
-        <v>45620</v>
+        <v>45617</v>
       </c>
       <c r="C91" s="2">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -1694,10 +1691,10 @@
         <v>4</v>
       </c>
       <c r="B92" s="2">
-        <v>45620</v>
+        <v>45617</v>
       </c>
       <c r="C92" s="2">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>6</v>
@@ -1708,10 +1705,10 @@
         <v>4</v>
       </c>
       <c r="B93" s="2">
-        <v>45620</v>
+        <v>45617</v>
       </c>
       <c r="C93" s="2">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>5</v>
@@ -1722,10 +1719,10 @@
         <v>4</v>
       </c>
       <c r="B94" s="2">
-        <v>45620</v>
+        <v>45617</v>
       </c>
       <c r="C94" s="2">
-        <v>541</v>
+        <v>272</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>5</v>
@@ -1736,10 +1733,10 @@
         <v>4</v>
       </c>
       <c r="B95" s="2">
-        <v>45620</v>
+        <v>45617</v>
       </c>
       <c r="C95" s="2">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>7</v>
@@ -1750,13 +1747,13 @@
         <v>4</v>
       </c>
       <c r="B96" s="2">
-        <v>45620</v>
+        <v>45617</v>
       </c>
       <c r="C96" s="2">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -1764,10 +1761,10 @@
         <v>4</v>
       </c>
       <c r="B97" s="2">
-        <v>45620</v>
+        <v>45618</v>
       </c>
       <c r="C97" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>5</v>
@@ -1778,10 +1775,10 @@
         <v>4</v>
       </c>
       <c r="B98" s="2">
-        <v>45620</v>
+        <v>45618</v>
       </c>
       <c r="C98" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>5</v>
@@ -1792,13 +1789,13 @@
         <v>4</v>
       </c>
       <c r="B99" s="2">
-        <v>45621</v>
+        <v>45618</v>
       </c>
       <c r="C99" s="2">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -1806,13 +1803,13 @@
         <v>4</v>
       </c>
       <c r="B100" s="2">
-        <v>45621</v>
+        <v>45618</v>
       </c>
       <c r="C100" s="2">
-        <v>107</v>
+        <v>53</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -1820,13 +1817,13 @@
         <v>4</v>
       </c>
       <c r="B101" s="2">
-        <v>45621</v>
+        <v>45618</v>
       </c>
       <c r="C101" s="2">
-        <v>78</v>
+        <v>770</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -1834,13 +1831,13 @@
         <v>4</v>
       </c>
       <c r="B102" s="2">
-        <v>45621</v>
+        <v>45618</v>
       </c>
       <c r="C102" s="2">
-        <v>75</v>
+        <v>482</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -1848,13 +1845,13 @@
         <v>4</v>
       </c>
       <c r="B103" s="2">
-        <v>45621</v>
+        <v>45618</v>
       </c>
       <c r="C103" s="2">
-        <v>412</v>
+        <v>60</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -1862,13 +1859,13 @@
         <v>4</v>
       </c>
       <c r="B104" s="2">
-        <v>45621</v>
+        <v>45619</v>
       </c>
       <c r="C104" s="2">
-        <v>224</v>
+        <v>4</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -1876,10 +1873,10 @@
         <v>4</v>
       </c>
       <c r="B105" s="2">
-        <v>45621</v>
+        <v>45619</v>
       </c>
       <c r="C105" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>5</v>
@@ -1890,13 +1887,13 @@
         <v>4</v>
       </c>
       <c r="B106" s="2">
-        <v>45621</v>
+        <v>45619</v>
       </c>
       <c r="C106" s="2">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -1904,10 +1901,10 @@
         <v>4</v>
       </c>
       <c r="B107" s="2">
-        <v>45621</v>
+        <v>45619</v>
       </c>
       <c r="C107" s="2">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>5</v>
@@ -1918,10 +1915,10 @@
         <v>4</v>
       </c>
       <c r="B108" s="2">
-        <v>45622</v>
+        <v>45619</v>
       </c>
       <c r="C108" s="2">
-        <v>1</v>
+        <v>779</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>5</v>
@@ -1932,13 +1929,13 @@
         <v>4</v>
       </c>
       <c r="B109" s="2">
-        <v>45622</v>
+        <v>45619</v>
       </c>
       <c r="C109" s="2">
-        <v>88</v>
+        <v>719</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -1946,13 +1943,13 @@
         <v>4</v>
       </c>
       <c r="B110" s="2">
-        <v>45622</v>
+        <v>45619</v>
       </c>
       <c r="C110" s="2">
-        <v>71</v>
+        <v>163</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -1960,10 +1957,10 @@
         <v>4</v>
       </c>
       <c r="B111" s="2">
-        <v>45622</v>
+        <v>45620</v>
       </c>
       <c r="C111" s="2">
-        <v>454</v>
+        <v>7</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>5</v>
@@ -1974,13 +1971,13 @@
         <v>4</v>
       </c>
       <c r="B112" s="2">
-        <v>45622</v>
+        <v>45620</v>
       </c>
       <c r="C112" s="2">
-        <v>284</v>
+        <v>55</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -1988,13 +1985,13 @@
         <v>4</v>
       </c>
       <c r="B113" s="2">
-        <v>45622</v>
+        <v>45620</v>
       </c>
       <c r="C113" s="2">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2002,10 +1999,10 @@
         <v>4</v>
       </c>
       <c r="B114" s="2">
-        <v>45622</v>
+        <v>45620</v>
       </c>
       <c r="C114" s="2">
-        <v>2</v>
+        <v>670</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>5</v>
@@ -2016,13 +2013,13 @@
         <v>4</v>
       </c>
       <c r="B115" s="2">
-        <v>45622</v>
+        <v>45620</v>
       </c>
       <c r="C115" s="2">
-        <v>1</v>
+        <v>681</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2030,13 +2027,13 @@
         <v>4</v>
       </c>
       <c r="B116" s="2">
-        <v>45622</v>
+        <v>45620</v>
       </c>
       <c r="C116" s="2">
-        <v>3</v>
+        <v>298</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2044,7 +2041,7 @@
         <v>4</v>
       </c>
       <c r="B117" s="2">
-        <v>45623</v>
+        <v>45620</v>
       </c>
       <c r="C117" s="2">
         <v>1</v>
@@ -2058,10 +2055,10 @@
         <v>4</v>
       </c>
       <c r="B118" s="2">
-        <v>45623</v>
+        <v>45621</v>
       </c>
       <c r="C118" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>5</v>
@@ -2072,13 +2069,13 @@
         <v>4</v>
       </c>
       <c r="B119" s="2">
-        <v>45623</v>
+        <v>45621</v>
       </c>
       <c r="C119" s="2">
-        <v>125</v>
+        <v>5</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2086,10 +2083,10 @@
         <v>4</v>
       </c>
       <c r="B120" s="2">
-        <v>45623</v>
+        <v>45621</v>
       </c>
       <c r="C120" s="2">
-        <v>124</v>
+        <v>9</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>5</v>
@@ -2100,13 +2097,13 @@
         <v>4</v>
       </c>
       <c r="B121" s="2">
-        <v>45623</v>
+        <v>45621</v>
       </c>
       <c r="C121" s="2">
-        <v>991</v>
+        <v>77</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2114,13 +2111,13 @@
         <v>4</v>
       </c>
       <c r="B122" s="2">
-        <v>45623</v>
+        <v>45621</v>
       </c>
       <c r="C122" s="2">
-        <v>349</v>
+        <v>33</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2128,13 +2125,13 @@
         <v>4</v>
       </c>
       <c r="B123" s="2">
-        <v>45623</v>
+        <v>45621</v>
       </c>
       <c r="C123" s="2">
-        <v>1</v>
+        <v>480</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2142,13 +2139,13 @@
         <v>4</v>
       </c>
       <c r="B124" s="2">
-        <v>45623</v>
+        <v>45621</v>
       </c>
       <c r="C124" s="2">
-        <v>3</v>
+        <v>529</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2156,13 +2153,13 @@
         <v>4</v>
       </c>
       <c r="B125" s="2">
-        <v>45623</v>
+        <v>45621</v>
       </c>
       <c r="C125" s="2">
-        <v>1</v>
+        <v>158</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2170,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="B126" s="2">
-        <v>45623</v>
+        <v>45622</v>
       </c>
       <c r="C126" s="2">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>5</v>
@@ -2184,10 +2181,10 @@
         <v>4</v>
       </c>
       <c r="B127" s="2">
-        <v>45624</v>
+        <v>45622</v>
       </c>
       <c r="C127" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>5</v>
@@ -2198,13 +2195,13 @@
         <v>4</v>
       </c>
       <c r="B128" s="2">
-        <v>45624</v>
+        <v>45622</v>
       </c>
       <c r="C128" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2212,10 +2209,10 @@
         <v>4</v>
       </c>
       <c r="B129" s="2">
-        <v>45624</v>
+        <v>45622</v>
       </c>
       <c r="C129" s="2">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>6</v>
@@ -2226,10 +2223,10 @@
         <v>4</v>
       </c>
       <c r="B130" s="2">
-        <v>45624</v>
+        <v>45622</v>
       </c>
       <c r="C130" s="2">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>5</v>
@@ -2240,10 +2237,10 @@
         <v>4</v>
       </c>
       <c r="B131" s="2">
-        <v>45624</v>
+        <v>45622</v>
       </c>
       <c r="C131" s="2">
-        <v>957</v>
+        <v>415</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>5</v>
@@ -2254,10 +2251,10 @@
         <v>4</v>
       </c>
       <c r="B132" s="2">
-        <v>45624</v>
+        <v>45622</v>
       </c>
       <c r="C132" s="2">
-        <v>340</v>
+        <v>560</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>7</v>
@@ -2268,13 +2265,13 @@
         <v>4</v>
       </c>
       <c r="B133" s="2">
-        <v>45624</v>
+        <v>45622</v>
       </c>
       <c r="C133" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2282,10 +2279,10 @@
         <v>4</v>
       </c>
       <c r="B134" s="2">
-        <v>45624</v>
+        <v>45623</v>
       </c>
       <c r="C134" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>5</v>
@@ -2296,7 +2293,7 @@
         <v>4</v>
       </c>
       <c r="B135" s="2">
-        <v>45624</v>
+        <v>45623</v>
       </c>
       <c r="C135" s="2">
         <v>1</v>
@@ -2310,10 +2307,10 @@
         <v>4</v>
       </c>
       <c r="B136" s="2">
-        <v>45624</v>
+        <v>45623</v>
       </c>
       <c r="C136" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>5</v>
@@ -2324,10 +2321,10 @@
         <v>4</v>
       </c>
       <c r="B137" s="2">
-        <v>45624</v>
+        <v>45623</v>
       </c>
       <c r="C137" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>5</v>
@@ -2338,10 +2335,10 @@
         <v>4</v>
       </c>
       <c r="B138" s="2">
-        <v>45624</v>
+        <v>45623</v>
       </c>
       <c r="C138" s="2">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>5</v>
@@ -2352,13 +2349,13 @@
         <v>4</v>
       </c>
       <c r="B139" s="2">
-        <v>45625</v>
+        <v>45623</v>
       </c>
       <c r="C139" s="2">
-        <v>1</v>
+        <v>126</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -2366,10 +2363,10 @@
         <v>4</v>
       </c>
       <c r="B140" s="2">
-        <v>45625</v>
+        <v>45623</v>
       </c>
       <c r="C140" s="2">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>5</v>
@@ -2380,13 +2377,13 @@
         <v>4</v>
       </c>
       <c r="B141" s="2">
-        <v>45625</v>
+        <v>45623</v>
       </c>
       <c r="C141" s="2">
-        <v>159</v>
+        <v>608</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -2394,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B142" s="2">
-        <v>45625</v>
+        <v>45623</v>
       </c>
       <c r="C142" s="2">
-        <v>132</v>
+        <v>802</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2408,13 +2405,13 @@
         <v>4</v>
       </c>
       <c r="B143" s="2">
-        <v>45625</v>
+        <v>45623</v>
       </c>
       <c r="C143" s="2">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -2422,10 +2419,10 @@
         <v>4</v>
       </c>
       <c r="B144" s="2">
-        <v>45625</v>
+        <v>45624</v>
       </c>
       <c r="C144" s="2">
-        <v>707</v>
+        <v>3</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>5</v>
@@ -2436,13 +2433,13 @@
         <v>4</v>
       </c>
       <c r="B145" s="2">
-        <v>45625</v>
+        <v>45624</v>
       </c>
       <c r="C145" s="2">
-        <v>426</v>
+        <v>2</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -2450,13 +2447,13 @@
         <v>4</v>
       </c>
       <c r="B146" s="2">
-        <v>45625</v>
+        <v>45624</v>
       </c>
       <c r="C146" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -2464,13 +2461,13 @@
         <v>4</v>
       </c>
       <c r="B147" s="2">
-        <v>45625</v>
+        <v>45624</v>
       </c>
       <c r="C147" s="2">
-        <v>1</v>
+        <v>156</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -2478,10 +2475,10 @@
         <v>4</v>
       </c>
       <c r="B148" s="2">
-        <v>45625</v>
+        <v>45624</v>
       </c>
       <c r="C148" s="2">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>5</v>
@@ -2492,10 +2489,10 @@
         <v>4</v>
       </c>
       <c r="B149" s="2">
-        <v>45625</v>
+        <v>45624</v>
       </c>
       <c r="C149" s="2">
-        <v>4</v>
+        <v>583</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>5</v>
@@ -2506,13 +2503,13 @@
         <v>4</v>
       </c>
       <c r="B150" s="2">
-        <v>45625</v>
+        <v>45624</v>
       </c>
       <c r="C150" s="2">
-        <v>1</v>
+        <v>824</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -2520,13 +2517,13 @@
         <v>4</v>
       </c>
       <c r="B151" s="2">
-        <v>45625</v>
+        <v>45624</v>
       </c>
       <c r="C151" s="2">
-        <v>28</v>
+        <v>326</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -2534,10 +2531,10 @@
         <v>4</v>
       </c>
       <c r="B152" s="2">
-        <v>45626</v>
+        <v>45625</v>
       </c>
       <c r="C152" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>5</v>
@@ -2548,10 +2545,10 @@
         <v>4</v>
       </c>
       <c r="B153" s="2">
-        <v>45626</v>
+        <v>45625</v>
       </c>
       <c r="C153" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>5</v>
@@ -2562,13 +2559,13 @@
         <v>4</v>
       </c>
       <c r="B154" s="2">
-        <v>45626</v>
+        <v>45625</v>
       </c>
       <c r="C154" s="2">
-        <v>297</v>
+        <v>1</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -2576,13 +2573,13 @@
         <v>4</v>
       </c>
       <c r="B155" s="2">
-        <v>45626</v>
+        <v>45625</v>
       </c>
       <c r="C155" s="2">
-        <v>115</v>
+        <v>9</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -2590,10 +2587,10 @@
         <v>4</v>
       </c>
       <c r="B156" s="2">
-        <v>45626</v>
+        <v>45625</v>
       </c>
       <c r="C156" s="2">
-        <v>98</v>
+        <v>1</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>5</v>
@@ -2604,13 +2601,13 @@
         <v>4</v>
       </c>
       <c r="B157" s="2">
-        <v>45626</v>
+        <v>45625</v>
       </c>
       <c r="C157" s="2">
-        <v>1024</v>
+        <v>162</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -2618,13 +2615,13 @@
         <v>4</v>
       </c>
       <c r="B158" s="2">
-        <v>45626</v>
+        <v>45625</v>
       </c>
       <c r="C158" s="2">
-        <v>410</v>
+        <v>25</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -2632,10 +2629,10 @@
         <v>4</v>
       </c>
       <c r="B159" s="2">
-        <v>45626</v>
+        <v>45625</v>
       </c>
       <c r="C159" s="2">
-        <v>1</v>
+        <v>935</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>5</v>
@@ -2646,13 +2643,13 @@
         <v>4</v>
       </c>
       <c r="B160" s="2">
-        <v>45626</v>
+        <v>45625</v>
       </c>
       <c r="C160" s="2">
-        <v>9</v>
+        <v>1117</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -2660,13 +2657,13 @@
         <v>4</v>
       </c>
       <c r="B161" s="2">
-        <v>45626</v>
+        <v>45625</v>
       </c>
       <c r="C161" s="2">
-        <v>7</v>
+        <v>305</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -2674,10 +2671,10 @@
         <v>4</v>
       </c>
       <c r="B162" s="2">
-        <v>45626</v>
+        <v>45625</v>
       </c>
       <c r="C162" s="2">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>5</v>
@@ -2688,10 +2685,10 @@
         <v>4</v>
       </c>
       <c r="B163" s="2">
-        <v>45627</v>
+        <v>45626</v>
       </c>
       <c r="C163" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>5</v>
@@ -2702,10 +2699,10 @@
         <v>4</v>
       </c>
       <c r="B164" s="2">
-        <v>45627</v>
+        <v>45626</v>
       </c>
       <c r="C164" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>5</v>
@@ -2716,13 +2713,13 @@
         <v>4</v>
       </c>
       <c r="B165" s="2">
-        <v>45627</v>
+        <v>45626</v>
       </c>
       <c r="C165" s="2">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -2730,10 +2727,10 @@
         <v>4</v>
       </c>
       <c r="B166" s="2">
-        <v>45627</v>
+        <v>45626</v>
       </c>
       <c r="C166" s="2">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>5</v>
@@ -2744,13 +2741,13 @@
         <v>4</v>
       </c>
       <c r="B167" s="2">
-        <v>45627</v>
+        <v>45626</v>
       </c>
       <c r="C167" s="2">
-        <v>38</v>
+        <v>757</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -2758,13 +2755,13 @@
         <v>4</v>
       </c>
       <c r="B168" s="2">
-        <v>45627</v>
+        <v>45626</v>
       </c>
       <c r="C168" s="2">
-        <v>50</v>
+        <v>785</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -2772,13 +2769,13 @@
         <v>4</v>
       </c>
       <c r="B169" s="2">
-        <v>45627</v>
+        <v>45626</v>
       </c>
       <c r="C169" s="2">
-        <v>114</v>
+        <v>302</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -2786,10 +2783,10 @@
         <v>4</v>
       </c>
       <c r="B170" s="2">
-        <v>45627</v>
+        <v>45626</v>
       </c>
       <c r="C170" s="2">
-        <v>1018</v>
+        <v>4</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>5</v>
@@ -2803,10 +2800,10 @@
         <v>45627</v>
       </c>
       <c r="C171" s="2">
-        <v>173</v>
+        <v>3</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -2817,7 +2814,7 @@
         <v>45627</v>
       </c>
       <c r="C172" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>5</v>
@@ -2845,10 +2842,10 @@
         <v>45627</v>
       </c>
       <c r="C174" s="2">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -2856,10 +2853,10 @@
         <v>4</v>
       </c>
       <c r="B175" s="2">
-        <v>45628</v>
+        <v>45627</v>
       </c>
       <c r="C175" s="2">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>5</v>
@@ -2870,13 +2867,13 @@
         <v>4</v>
       </c>
       <c r="B176" s="2">
-        <v>45628</v>
+        <v>45627</v>
       </c>
       <c r="C176" s="2">
-        <v>15</v>
+        <v>637</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -2884,13 +2881,13 @@
         <v>4</v>
       </c>
       <c r="B177" s="2">
-        <v>45628</v>
+        <v>45627</v>
       </c>
       <c r="C177" s="2">
-        <v>88</v>
+        <v>786</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -2898,13 +2895,13 @@
         <v>4</v>
       </c>
       <c r="B178" s="2">
-        <v>45628</v>
+        <v>45627</v>
       </c>
       <c r="C178" s="2">
-        <v>337</v>
+        <v>160</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -2915,10 +2912,10 @@
         <v>45628</v>
       </c>
       <c r="C179" s="2">
-        <v>85</v>
+        <v>6</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -2929,7 +2926,7 @@
         <v>45628</v>
       </c>
       <c r="C180" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>5</v>
@@ -2943,7 +2940,7 @@
         <v>45628</v>
       </c>
       <c r="C181" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>5</v>
@@ -2954,13 +2951,13 @@
         <v>4</v>
       </c>
       <c r="B182" s="2">
-        <v>45629</v>
+        <v>45628</v>
       </c>
       <c r="C182" s="2">
-        <v>-3</v>
+        <v>53</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -2968,13 +2965,13 @@
         <v>4</v>
       </c>
       <c r="B183" s="2">
-        <v>45629</v>
+        <v>45628</v>
       </c>
       <c r="C183" s="2">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -2982,10 +2979,10 @@
         <v>4</v>
       </c>
       <c r="B184" s="2">
-        <v>45629</v>
+        <v>45628</v>
       </c>
       <c r="C184" s="2">
-        <v>99</v>
+        <v>388</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>5</v>
@@ -2996,13 +2993,13 @@
         <v>4</v>
       </c>
       <c r="B185" s="2">
-        <v>45629</v>
+        <v>45628</v>
       </c>
       <c r="C185" s="2">
-        <v>368</v>
+        <v>476</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -3010,13 +3007,13 @@
         <v>4</v>
       </c>
       <c r="B186" s="2">
-        <v>45629</v>
+        <v>45628</v>
       </c>
       <c r="C186" s="2">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -3027,7 +3024,7 @@
         <v>45629</v>
       </c>
       <c r="C187" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>5</v>
@@ -3041,7 +3038,7 @@
         <v>45629</v>
       </c>
       <c r="C188" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>5</v>
@@ -3052,13 +3049,13 @@
         <v>4</v>
       </c>
       <c r="B189" s="2">
-        <v>45630</v>
+        <v>45629</v>
       </c>
       <c r="C189" s="2">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3066,13 +3063,13 @@
         <v>4</v>
       </c>
       <c r="B190" s="2">
-        <v>45630</v>
+        <v>45629</v>
       </c>
       <c r="C190" s="2">
-        <v>117</v>
+        <v>31</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3080,10 +3077,10 @@
         <v>4</v>
       </c>
       <c r="B191" s="2">
-        <v>45630</v>
+        <v>45629</v>
       </c>
       <c r="C191" s="2">
-        <v>392</v>
+        <v>40</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>5</v>
@@ -3094,13 +3091,13 @@
         <v>4</v>
       </c>
       <c r="B192" s="2">
-        <v>45630</v>
+        <v>45629</v>
       </c>
       <c r="C192" s="2">
-        <v>90</v>
+        <v>384</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3108,13 +3105,13 @@
         <v>4</v>
       </c>
       <c r="B193" s="2">
-        <v>45630</v>
+        <v>45629</v>
       </c>
       <c r="C193" s="2">
-        <v>2</v>
+        <v>455</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3122,13 +3119,13 @@
         <v>4</v>
       </c>
       <c r="B194" s="2">
-        <v>45630</v>
+        <v>45629</v>
       </c>
       <c r="C194" s="2">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3139,7 +3136,7 @@
         <v>45630</v>
       </c>
       <c r="C195" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>5</v>
@@ -3150,10 +3147,10 @@
         <v>4</v>
       </c>
       <c r="B196" s="2">
-        <v>45631</v>
+        <v>45630</v>
       </c>
       <c r="C196" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>5</v>
@@ -3164,10 +3161,10 @@
         <v>4</v>
       </c>
       <c r="B197" s="2">
-        <v>45631</v>
+        <v>45630</v>
       </c>
       <c r="C197" s="2">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>6</v>
@@ -3178,10 +3175,10 @@
         <v>4</v>
       </c>
       <c r="B198" s="2">
-        <v>45631</v>
+        <v>45630</v>
       </c>
       <c r="C198" s="2">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>5</v>
@@ -3192,10 +3189,10 @@
         <v>4</v>
       </c>
       <c r="B199" s="2">
-        <v>45631</v>
+        <v>45630</v>
       </c>
       <c r="C199" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>5</v>
@@ -3206,10 +3203,10 @@
         <v>4</v>
       </c>
       <c r="B200" s="2">
-        <v>45631</v>
+        <v>45630</v>
       </c>
       <c r="C200" s="2">
-        <v>89</v>
+        <v>485</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>7</v>
@@ -3220,13 +3217,13 @@
         <v>4</v>
       </c>
       <c r="B201" s="2">
-        <v>45631</v>
+        <v>45630</v>
       </c>
       <c r="C201" s="2">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3237,7 +3234,7 @@
         <v>45631</v>
       </c>
       <c r="C202" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>5</v>
@@ -3248,10 +3245,10 @@
         <v>4</v>
       </c>
       <c r="B203" s="2">
-        <v>45632</v>
+        <v>45631</v>
       </c>
       <c r="C203" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>5</v>
@@ -3262,13 +3259,13 @@
         <v>4</v>
       </c>
       <c r="B204" s="2">
-        <v>45632</v>
+        <v>45631</v>
       </c>
       <c r="C204" s="2">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -3276,13 +3273,13 @@
         <v>4</v>
       </c>
       <c r="B205" s="2">
-        <v>45632</v>
+        <v>45631</v>
       </c>
       <c r="C205" s="2">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -3290,10 +3287,10 @@
         <v>4</v>
       </c>
       <c r="B206" s="2">
-        <v>45632</v>
+        <v>45631</v>
       </c>
       <c r="C206" s="2">
-        <v>114</v>
+        <v>376</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>5</v>
@@ -3304,13 +3301,13 @@
         <v>4</v>
       </c>
       <c r="B207" s="2">
-        <v>45632</v>
+        <v>45631</v>
       </c>
       <c r="C207" s="2">
-        <v>580</v>
+        <v>383</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -3318,13 +3315,13 @@
         <v>4</v>
       </c>
       <c r="B208" s="2">
-        <v>45632</v>
+        <v>45631</v>
       </c>
       <c r="C208" s="2">
-        <v>113</v>
+        <v>41</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -3335,7 +3332,7 @@
         <v>45632</v>
       </c>
       <c r="C209" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>5</v>
@@ -3346,13 +3343,13 @@
         <v>4</v>
       </c>
       <c r="B210" s="2">
-        <v>45633</v>
+        <v>45632</v>
       </c>
       <c r="C210" s="2">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -3360,13 +3357,13 @@
         <v>4</v>
       </c>
       <c r="B211" s="2">
-        <v>45633</v>
+        <v>45632</v>
       </c>
       <c r="C211" s="2">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -3374,13 +3371,13 @@
         <v>4</v>
       </c>
       <c r="B212" s="2">
-        <v>45633</v>
+        <v>45632</v>
       </c>
       <c r="C212" s="2">
-        <v>62</v>
+        <v>893</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -3388,13 +3385,13 @@
         <v>4</v>
       </c>
       <c r="B213" s="2">
-        <v>45633</v>
+        <v>45632</v>
       </c>
       <c r="C213" s="2">
-        <v>149</v>
+        <v>711</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -3402,13 +3399,13 @@
         <v>4</v>
       </c>
       <c r="B214" s="2">
-        <v>45633</v>
+        <v>45632</v>
       </c>
       <c r="C214" s="2">
-        <v>1558</v>
+        <v>50</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -3419,10 +3416,10 @@
         <v>45633</v>
       </c>
       <c r="C215" s="2">
-        <v>295</v>
+        <v>6</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -3433,7 +3430,7 @@
         <v>45633</v>
       </c>
       <c r="C216" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>5</v>
@@ -3447,7 +3444,7 @@
         <v>45633</v>
       </c>
       <c r="C217" s="2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>5</v>
@@ -3461,10 +3458,10 @@
         <v>45633</v>
       </c>
       <c r="C218" s="2">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -3472,10 +3469,10 @@
         <v>4</v>
       </c>
       <c r="B219" s="2">
-        <v>45634</v>
+        <v>45633</v>
       </c>
       <c r="C219" s="2">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>5</v>
@@ -3486,10 +3483,10 @@
         <v>4</v>
       </c>
       <c r="B220" s="2">
-        <v>45634</v>
+        <v>45633</v>
       </c>
       <c r="C220" s="2">
-        <v>1</v>
+        <v>881</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>5</v>
@@ -3500,13 +3497,13 @@
         <v>4</v>
       </c>
       <c r="B221" s="2">
-        <v>45634</v>
+        <v>45633</v>
       </c>
       <c r="C221" s="2">
-        <v>3</v>
+        <v>1404</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -3514,10 +3511,10 @@
         <v>4</v>
       </c>
       <c r="B222" s="2">
-        <v>45634</v>
+        <v>45633</v>
       </c>
       <c r="C222" s="2">
-        <v>160</v>
+        <v>118</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>8</v>
@@ -3531,10 +3528,10 @@
         <v>45634</v>
       </c>
       <c r="C223" s="2">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -3545,7 +3542,7 @@
         <v>45634</v>
       </c>
       <c r="C224" s="2">
-        <v>168</v>
+        <v>2</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>5</v>
@@ -3559,7 +3556,7 @@
         <v>45634</v>
       </c>
       <c r="C225" s="2">
-        <v>1260</v>
+        <v>1</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>5</v>
@@ -3573,10 +3570,10 @@
         <v>45634</v>
       </c>
       <c r="C226" s="2">
-        <v>160</v>
+        <v>10</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -3587,10 +3584,10 @@
         <v>45634</v>
       </c>
       <c r="C227" s="2">
-        <v>5</v>
+        <v>93</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -3601,7 +3598,7 @@
         <v>45634</v>
       </c>
       <c r="C228" s="2">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>5</v>
@@ -3615,7 +3612,7 @@
         <v>45634</v>
       </c>
       <c r="C229" s="2">
-        <v>13</v>
+        <v>854</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>5</v>
@@ -3626,13 +3623,13 @@
         <v>4</v>
       </c>
       <c r="B230" s="2">
-        <v>45635</v>
+        <v>45634</v>
       </c>
       <c r="C230" s="2">
-        <v>25</v>
+        <v>945</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -3640,13 +3637,13 @@
         <v>4</v>
       </c>
       <c r="B231" s="2">
-        <v>45635</v>
+        <v>45634</v>
       </c>
       <c r="C231" s="2">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -3657,7 +3654,7 @@
         <v>45635</v>
       </c>
       <c r="C232" s="2">
-        <v>360</v>
+        <v>4</v>
       </c>
       <c r="D232" s="2" t="s">
         <v>5</v>
@@ -3671,10 +3668,10 @@
         <v>45635</v>
       </c>
       <c r="C233" s="2">
-        <v>135</v>
+        <v>5</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -3685,10 +3682,10 @@
         <v>45635</v>
       </c>
       <c r="C234" s="2">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -3699,7 +3696,7 @@
         <v>45635</v>
       </c>
       <c r="C235" s="2">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>5</v>
@@ -3713,7 +3710,7 @@
         <v>45635</v>
       </c>
       <c r="C236" s="2">
-        <v>1</v>
+        <v>504</v>
       </c>
       <c r="D236" s="2" t="s">
         <v>5</v>
@@ -3727,10 +3724,24 @@
         <v>45635</v>
       </c>
       <c r="C237" s="2">
-        <v>10</v>
+        <v>735</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="A238" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B238" s="2">
+        <v>45635</v>
+      </c>
+      <c r="C238" s="2">
+        <v>2</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/reports/For Winter Ending (Prior Year)_Visits.xlsx
+++ b/reports/For Winter Ending (Prior Year)_Visits.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="10">
   <si>
     <t>Resort</t>
   </si>
@@ -28,19 +28,22 @@
     <t>Location</t>
   </si>
   <si>
-    <t>Snowbowl</t>
+    <t>Purgatory</t>
   </si>
   <si>
-    <t>Snowbowl Passes</t>
+    <t>Purgatory Passes</t>
   </si>
   <si>
-    <t>Snowbowl Comp Tickets</t>
+    <t>Purgatory Tickets</t>
   </si>
   <si>
-    <t>Snowbowl Tickets</t>
+    <t>Purgatory Coaster</t>
   </si>
   <si>
-    <t>Snowbowl Uplift Tickets</t>
+    <t>Purgatory Comp Tickets</t>
+  </si>
+  <si>
+    <t>Purgatory Uplift Tickets</t>
   </si>
 </sst>
 </file>
@@ -403,13 +406,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D238"/>
+  <dimension ref="A1:D237"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -431,7 +434,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>45597</v>
+        <v>45601</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
@@ -448,7 +451,7 @@
         <v>45604</v>
       </c>
       <c r="C3" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>5</v>
@@ -459,13 +462,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>45604</v>
+        <v>45605</v>
       </c>
       <c r="C4" s="2">
-        <v>1</v>
+        <v>164</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -473,10 +476,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>45604</v>
+        <v>45605</v>
       </c>
       <c r="C5" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>5</v>
@@ -487,10 +490,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>45604</v>
+        <v>45612</v>
       </c>
       <c r="C6" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>5</v>
@@ -501,13 +504,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="2">
-        <v>45604</v>
+        <v>45613</v>
       </c>
       <c r="C7" s="2">
-        <v>18</v>
+        <v>769</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -515,10 +518,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>45604</v>
+        <v>45615</v>
       </c>
       <c r="C8" s="2">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>5</v>
@@ -529,10 +532,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>45604</v>
+        <v>45618</v>
       </c>
       <c r="C9" s="2">
-        <v>789</v>
+        <v>2</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>5</v>
@@ -543,13 +546,13 @@
         <v>4</v>
       </c>
       <c r="B10" s="2">
-        <v>45604</v>
+        <v>45619</v>
       </c>
       <c r="C10" s="2">
-        <v>139</v>
+        <v>2</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -557,10 +560,10 @@
         <v>4</v>
       </c>
       <c r="B11" s="2">
-        <v>45605</v>
+        <v>45619</v>
       </c>
       <c r="C11" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>5</v>
@@ -571,7 +574,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="2">
-        <v>45605</v>
+        <v>45619</v>
       </c>
       <c r="C12" s="2">
         <v>2</v>
@@ -585,13 +588,13 @@
         <v>4</v>
       </c>
       <c r="B13" s="2">
-        <v>45605</v>
+        <v>45620</v>
       </c>
       <c r="C13" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -599,10 +602,10 @@
         <v>4</v>
       </c>
       <c r="B14" s="2">
-        <v>45605</v>
+        <v>45622</v>
       </c>
       <c r="C14" s="2">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>5</v>
@@ -613,10 +616,10 @@
         <v>4</v>
       </c>
       <c r="B15" s="2">
-        <v>45605</v>
+        <v>45623</v>
       </c>
       <c r="C15" s="2">
-        <v>512</v>
+        <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>5</v>
@@ -627,13 +630,13 @@
         <v>4</v>
       </c>
       <c r="B16" s="2">
-        <v>45605</v>
+        <v>45623</v>
       </c>
       <c r="C16" s="2">
-        <v>237</v>
+        <v>125</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -641,13 +644,13 @@
         <v>4</v>
       </c>
       <c r="B17" s="2">
-        <v>45605</v>
+        <v>45624</v>
       </c>
       <c r="C17" s="2">
-        <v>187</v>
+        <v>91</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -655,10 +658,10 @@
         <v>4</v>
       </c>
       <c r="B18" s="2">
-        <v>45606</v>
+        <v>45625</v>
       </c>
       <c r="C18" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>5</v>
@@ -669,10 +672,10 @@
         <v>4</v>
       </c>
       <c r="B19" s="2">
-        <v>45606</v>
+        <v>45625</v>
       </c>
       <c r="C19" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>5</v>
@@ -683,10 +686,10 @@
         <v>4</v>
       </c>
       <c r="B20" s="2">
-        <v>45606</v>
+        <v>45626</v>
       </c>
       <c r="C20" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>5</v>
@@ -697,13 +700,13 @@
         <v>4</v>
       </c>
       <c r="B21" s="2">
-        <v>45606</v>
+        <v>45626</v>
       </c>
       <c r="C21" s="2">
-        <v>26</v>
+        <v>297</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -711,13 +714,13 @@
         <v>4</v>
       </c>
       <c r="B22" s="2">
-        <v>45606</v>
+        <v>45626</v>
       </c>
       <c r="C22" s="2">
-        <v>29</v>
+        <v>115</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -725,10 +728,10 @@
         <v>4</v>
       </c>
       <c r="B23" s="2">
-        <v>45606</v>
+        <v>45627</v>
       </c>
       <c r="C23" s="2">
-        <v>549</v>
+        <v>114</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>5</v>
@@ -739,13 +742,13 @@
         <v>4</v>
       </c>
       <c r="B24" s="2">
-        <v>45606</v>
+        <v>45628</v>
       </c>
       <c r="C24" s="2">
-        <v>290</v>
+        <v>1</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -753,13 +756,13 @@
         <v>4</v>
       </c>
       <c r="B25" s="2">
-        <v>45606</v>
+        <v>45629</v>
       </c>
       <c r="C25" s="2">
-        <v>211</v>
+        <v>-3</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -767,13 +770,13 @@
         <v>4</v>
       </c>
       <c r="B26" s="2">
-        <v>45607</v>
+        <v>45629</v>
       </c>
       <c r="C26" s="2">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -781,10 +784,10 @@
         <v>4</v>
       </c>
       <c r="B27" s="2">
-        <v>45607</v>
+        <v>45630</v>
       </c>
       <c r="C27" s="2">
-        <v>1</v>
+        <v>117</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>5</v>
@@ -795,10 +798,10 @@
         <v>4</v>
       </c>
       <c r="B28" s="2">
-        <v>45607</v>
+        <v>45631</v>
       </c>
       <c r="C28" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>5</v>
@@ -809,13 +812,13 @@
         <v>4</v>
       </c>
       <c r="B29" s="2">
-        <v>45607</v>
+        <v>45632</v>
       </c>
       <c r="C29" s="2">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -823,10 +826,10 @@
         <v>4</v>
       </c>
       <c r="B30" s="2">
-        <v>45607</v>
+        <v>45633</v>
       </c>
       <c r="C30" s="2">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>5</v>
@@ -837,10 +840,10 @@
         <v>4</v>
       </c>
       <c r="B31" s="2">
-        <v>45607</v>
+        <v>45633</v>
       </c>
       <c r="C31" s="2">
-        <v>904</v>
+        <v>1558</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>5</v>
@@ -851,13 +854,13 @@
         <v>4</v>
       </c>
       <c r="B32" s="2">
-        <v>45607</v>
+        <v>45634</v>
       </c>
       <c r="C32" s="2">
-        <v>473</v>
+        <v>160</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -865,13 +868,13 @@
         <v>4</v>
       </c>
       <c r="B33" s="2">
-        <v>45607</v>
+        <v>45634</v>
       </c>
       <c r="C33" s="2">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -879,10 +882,10 @@
         <v>4</v>
       </c>
       <c r="B34" s="2">
-        <v>45608</v>
+        <v>45606</v>
       </c>
       <c r="C34" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>5</v>
@@ -893,13 +896,13 @@
         <v>4</v>
       </c>
       <c r="B35" s="2">
-        <v>45608</v>
+        <v>45610</v>
       </c>
       <c r="C35" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -907,13 +910,13 @@
         <v>4</v>
       </c>
       <c r="B36" s="2">
-        <v>45608</v>
+        <v>45610</v>
       </c>
       <c r="C36" s="2">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -921,10 +924,10 @@
         <v>4</v>
       </c>
       <c r="B37" s="2">
-        <v>45608</v>
+        <v>45612</v>
       </c>
       <c r="C37" s="2">
-        <v>235</v>
+        <v>5</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>5</v>
@@ -935,13 +938,13 @@
         <v>4</v>
       </c>
       <c r="B38" s="2">
-        <v>45608</v>
+        <v>45612</v>
       </c>
       <c r="C38" s="2">
-        <v>155</v>
+        <v>12</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -949,10 +952,10 @@
         <v>4</v>
       </c>
       <c r="B39" s="2">
-        <v>45608</v>
+        <v>45613</v>
       </c>
       <c r="C39" s="2">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>8</v>
@@ -963,10 +966,10 @@
         <v>4</v>
       </c>
       <c r="B40" s="2">
-        <v>45609</v>
+        <v>45614</v>
       </c>
       <c r="C40" s="2">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>5</v>
@@ -977,13 +980,13 @@
         <v>4</v>
       </c>
       <c r="B41" s="2">
-        <v>45609</v>
+        <v>45616</v>
       </c>
       <c r="C41" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -991,10 +994,10 @@
         <v>4</v>
       </c>
       <c r="B42" s="2">
-        <v>45609</v>
+        <v>45616</v>
       </c>
       <c r="C42" s="2">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>5</v>
@@ -1005,10 +1008,10 @@
         <v>4</v>
       </c>
       <c r="B43" s="2">
-        <v>45609</v>
+        <v>45617</v>
       </c>
       <c r="C43" s="2">
-        <v>319</v>
+        <v>91</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>5</v>
@@ -1019,13 +1022,13 @@
         <v>4</v>
       </c>
       <c r="B44" s="2">
-        <v>45609</v>
+        <v>45617</v>
       </c>
       <c r="C44" s="2">
-        <v>186</v>
+        <v>234</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1033,13 +1036,13 @@
         <v>4</v>
       </c>
       <c r="B45" s="2">
-        <v>45609</v>
+        <v>45618</v>
       </c>
       <c r="C45" s="2">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1047,13 +1050,13 @@
         <v>4</v>
       </c>
       <c r="B46" s="2">
-        <v>45610</v>
+        <v>45619</v>
       </c>
       <c r="C46" s="2">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1061,13 +1064,13 @@
         <v>4</v>
       </c>
       <c r="B47" s="2">
-        <v>45610</v>
+        <v>45620</v>
       </c>
       <c r="C47" s="2">
-        <v>8</v>
+        <v>541</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1075,13 +1078,13 @@
         <v>4</v>
       </c>
       <c r="B48" s="2">
-        <v>45610</v>
+        <v>45621</v>
       </c>
       <c r="C48" s="2">
-        <v>17</v>
+        <v>224</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1089,10 +1092,10 @@
         <v>4</v>
       </c>
       <c r="B49" s="2">
-        <v>45610</v>
+        <v>45621</v>
       </c>
       <c r="C49" s="2">
-        <v>237</v>
+        <v>1</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>5</v>
@@ -1103,13 +1106,13 @@
         <v>4</v>
       </c>
       <c r="B50" s="2">
-        <v>45610</v>
+        <v>45622</v>
       </c>
       <c r="C50" s="2">
-        <v>120</v>
+        <v>3</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1117,13 +1120,13 @@
         <v>4</v>
       </c>
       <c r="B51" s="2">
-        <v>45610</v>
+        <v>45623</v>
       </c>
       <c r="C51" s="2">
-        <v>28</v>
+        <v>991</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1131,10 +1134,10 @@
         <v>4</v>
       </c>
       <c r="B52" s="2">
-        <v>45611</v>
+        <v>45624</v>
       </c>
       <c r="C52" s="2">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>6</v>
@@ -1145,10 +1148,10 @@
         <v>4</v>
       </c>
       <c r="B53" s="2">
-        <v>45611</v>
+        <v>45624</v>
       </c>
       <c r="C53" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>5</v>
@@ -1159,13 +1162,13 @@
         <v>4</v>
       </c>
       <c r="B54" s="2">
-        <v>45611</v>
+        <v>45624</v>
       </c>
       <c r="C54" s="2">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1173,13 +1176,13 @@
         <v>4</v>
       </c>
       <c r="B55" s="2">
-        <v>45611</v>
+        <v>45625</v>
       </c>
       <c r="C55" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1187,10 +1190,10 @@
         <v>4</v>
       </c>
       <c r="B56" s="2">
-        <v>45612</v>
+        <v>45626</v>
       </c>
       <c r="C56" s="2">
-        <v>1</v>
+        <v>1024</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>5</v>
@@ -1201,13 +1204,13 @@
         <v>4</v>
       </c>
       <c r="B57" s="2">
-        <v>45612</v>
+        <v>45627</v>
       </c>
       <c r="C57" s="2">
-        <v>4</v>
+        <v>173</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1215,13 +1218,13 @@
         <v>4</v>
       </c>
       <c r="B58" s="2">
-        <v>45612</v>
+        <v>45634</v>
       </c>
       <c r="C58" s="2">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1229,10 +1232,10 @@
         <v>4</v>
       </c>
       <c r="B59" s="2">
-        <v>45612</v>
+        <v>45635</v>
       </c>
       <c r="C59" s="2">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>5</v>
@@ -1243,10 +1246,10 @@
         <v>4</v>
       </c>
       <c r="B60" s="2">
-        <v>45612</v>
+        <v>45611</v>
       </c>
       <c r="C60" s="2">
-        <v>614</v>
+        <v>3</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>5</v>
@@ -1260,10 +1263,10 @@
         <v>45612</v>
       </c>
       <c r="C61" s="2">
-        <v>456</v>
+        <v>129</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1271,13 +1274,13 @@
         <v>4</v>
       </c>
       <c r="B62" s="2">
-        <v>45612</v>
+        <v>45613</v>
       </c>
       <c r="C62" s="2">
-        <v>208</v>
+        <v>7</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1285,13 +1288,13 @@
         <v>4</v>
       </c>
       <c r="B63" s="2">
-        <v>45613</v>
+        <v>45614</v>
       </c>
       <c r="C63" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1299,10 +1302,10 @@
         <v>4</v>
       </c>
       <c r="B64" s="2">
-        <v>45613</v>
+        <v>45614</v>
       </c>
       <c r="C64" s="2">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>5</v>
@@ -1313,13 +1316,13 @@
         <v>4</v>
       </c>
       <c r="B65" s="2">
-        <v>45613</v>
+        <v>45614</v>
       </c>
       <c r="C65" s="2">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1327,10 +1330,10 @@
         <v>4</v>
       </c>
       <c r="B66" s="2">
-        <v>45613</v>
+        <v>45615</v>
       </c>
       <c r="C66" s="2">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>5</v>
@@ -1341,10 +1344,10 @@
         <v>4</v>
       </c>
       <c r="B67" s="2">
-        <v>45613</v>
+        <v>45616</v>
       </c>
       <c r="C67" s="2">
-        <v>606</v>
+        <v>3</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>5</v>
@@ -1355,13 +1358,13 @@
         <v>4</v>
       </c>
       <c r="B68" s="2">
-        <v>45613</v>
+        <v>45617</v>
       </c>
       <c r="C68" s="2">
-        <v>468</v>
+        <v>10</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1369,13 +1372,13 @@
         <v>4</v>
       </c>
       <c r="B69" s="2">
-        <v>45613</v>
+        <v>45618</v>
       </c>
       <c r="C69" s="2">
-        <v>217</v>
+        <v>77</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1383,10 +1386,10 @@
         <v>4</v>
       </c>
       <c r="B70" s="2">
-        <v>45614</v>
+        <v>45620</v>
       </c>
       <c r="C70" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>5</v>
@@ -1397,13 +1400,13 @@
         <v>4</v>
       </c>
       <c r="B71" s="2">
-        <v>45614</v>
+        <v>45620</v>
       </c>
       <c r="C71" s="2">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1411,13 +1414,13 @@
         <v>4</v>
       </c>
       <c r="B72" s="2">
-        <v>45614</v>
+        <v>45620</v>
       </c>
       <c r="C72" s="2">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1425,10 +1428,10 @@
         <v>4</v>
       </c>
       <c r="B73" s="2">
-        <v>45614</v>
+        <v>45621</v>
       </c>
       <c r="C73" s="2">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>5</v>
@@ -1439,10 +1442,10 @@
         <v>4</v>
       </c>
       <c r="B74" s="2">
-        <v>45614</v>
+        <v>45623</v>
       </c>
       <c r="C74" s="2">
-        <v>320</v>
+        <v>8</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>5</v>
@@ -1453,13 +1456,13 @@
         <v>4</v>
       </c>
       <c r="B75" s="2">
-        <v>45614</v>
+        <v>45623</v>
       </c>
       <c r="C75" s="2">
-        <v>236</v>
+        <v>1</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1467,13 +1470,13 @@
         <v>4</v>
       </c>
       <c r="B76" s="2">
-        <v>45614</v>
+        <v>45624</v>
       </c>
       <c r="C76" s="2">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -1481,10 +1484,10 @@
         <v>4</v>
       </c>
       <c r="B77" s="2">
-        <v>45615</v>
+        <v>45626</v>
       </c>
       <c r="C77" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>5</v>
@@ -1495,13 +1498,13 @@
         <v>4</v>
       </c>
       <c r="B78" s="2">
-        <v>45615</v>
+        <v>45627</v>
       </c>
       <c r="C78" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1509,10 +1512,10 @@
         <v>4</v>
       </c>
       <c r="B79" s="2">
-        <v>45615</v>
+        <v>45627</v>
       </c>
       <c r="C79" s="2">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>5</v>
@@ -1523,13 +1526,13 @@
         <v>4</v>
       </c>
       <c r="B80" s="2">
-        <v>45615</v>
+        <v>45627</v>
       </c>
       <c r="C80" s="2">
-        <v>247</v>
+        <v>38</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -1537,13 +1540,13 @@
         <v>4</v>
       </c>
       <c r="B81" s="2">
-        <v>45615</v>
+        <v>45630</v>
       </c>
       <c r="C81" s="2">
-        <v>194</v>
+        <v>90</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -1551,13 +1554,13 @@
         <v>4</v>
       </c>
       <c r="B82" s="2">
-        <v>45615</v>
+        <v>45633</v>
       </c>
       <c r="C82" s="2">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1565,13 +1568,13 @@
         <v>4</v>
       </c>
       <c r="B83" s="2">
-        <v>45616</v>
+        <v>45633</v>
       </c>
       <c r="C83" s="2">
-        <v>3</v>
+        <v>295</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -1579,10 +1582,10 @@
         <v>4</v>
       </c>
       <c r="B84" s="2">
-        <v>45616</v>
+        <v>45635</v>
       </c>
       <c r="C84" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>5</v>
@@ -1593,13 +1596,13 @@
         <v>4</v>
       </c>
       <c r="B85" s="2">
-        <v>45616</v>
+        <v>45602</v>
       </c>
       <c r="C85" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1607,13 +1610,13 @@
         <v>4</v>
       </c>
       <c r="B86" s="2">
-        <v>45616</v>
+        <v>45605</v>
       </c>
       <c r="C86" s="2">
-        <v>33</v>
+        <v>137</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -1621,10 +1624,10 @@
         <v>4</v>
       </c>
       <c r="B87" s="2">
-        <v>45616</v>
+        <v>45605</v>
       </c>
       <c r="C87" s="2">
-        <v>317</v>
+        <v>760</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>5</v>
@@ -1635,13 +1638,13 @@
         <v>4</v>
       </c>
       <c r="B88" s="2">
-        <v>45616</v>
+        <v>45606</v>
       </c>
       <c r="C88" s="2">
-        <v>202</v>
+        <v>43</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -1649,10 +1652,10 @@
         <v>4</v>
       </c>
       <c r="B89" s="2">
-        <v>45616</v>
+        <v>45611</v>
       </c>
       <c r="C89" s="2">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>8</v>
@@ -1663,13 +1666,13 @@
         <v>4</v>
       </c>
       <c r="B90" s="2">
-        <v>45617</v>
+        <v>45613</v>
       </c>
       <c r="C90" s="2">
-        <v>3</v>
+        <v>153</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -1677,10 +1680,10 @@
         <v>4</v>
       </c>
       <c r="B91" s="2">
-        <v>45617</v>
+        <v>45614</v>
       </c>
       <c r="C91" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>5</v>
@@ -1691,13 +1694,13 @@
         <v>4</v>
       </c>
       <c r="B92" s="2">
-        <v>45617</v>
+        <v>45614</v>
       </c>
       <c r="C92" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -1705,13 +1708,13 @@
         <v>4</v>
       </c>
       <c r="B93" s="2">
-        <v>45617</v>
+        <v>45616</v>
       </c>
       <c r="C93" s="2">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -1722,7 +1725,7 @@
         <v>45617</v>
       </c>
       <c r="C94" s="2">
-        <v>272</v>
+        <v>4</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>5</v>
@@ -1733,13 +1736,13 @@
         <v>4</v>
       </c>
       <c r="B95" s="2">
-        <v>45617</v>
+        <v>45619</v>
       </c>
       <c r="C95" s="2">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -1747,13 +1750,13 @@
         <v>4</v>
       </c>
       <c r="B96" s="2">
-        <v>45617</v>
+        <v>45620</v>
       </c>
       <c r="C96" s="2">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -1761,13 +1764,13 @@
         <v>4</v>
       </c>
       <c r="B97" s="2">
-        <v>45618</v>
+        <v>45621</v>
       </c>
       <c r="C97" s="2">
-        <v>2</v>
+        <v>107</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -1775,10 +1778,10 @@
         <v>4</v>
       </c>
       <c r="B98" s="2">
-        <v>45618</v>
+        <v>45623</v>
       </c>
       <c r="C98" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>5</v>
@@ -1789,13 +1792,13 @@
         <v>4</v>
       </c>
       <c r="B99" s="2">
-        <v>45618</v>
+        <v>45623</v>
       </c>
       <c r="C99" s="2">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -1803,10 +1806,10 @@
         <v>4</v>
       </c>
       <c r="B100" s="2">
-        <v>45618</v>
+        <v>45625</v>
       </c>
       <c r="C100" s="2">
-        <v>53</v>
+        <v>707</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>5</v>
@@ -1817,10 +1820,10 @@
         <v>4</v>
       </c>
       <c r="B101" s="2">
-        <v>45618</v>
+        <v>45626</v>
       </c>
       <c r="C101" s="2">
-        <v>770</v>
+        <v>1</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>5</v>
@@ -1831,13 +1834,13 @@
         <v>4</v>
       </c>
       <c r="B102" s="2">
-        <v>45618</v>
+        <v>45626</v>
       </c>
       <c r="C102" s="2">
-        <v>482</v>
+        <v>9</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -1845,13 +1848,13 @@
         <v>4</v>
       </c>
       <c r="B103" s="2">
-        <v>45618</v>
+        <v>45626</v>
       </c>
       <c r="C103" s="2">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -1859,10 +1862,10 @@
         <v>4</v>
       </c>
       <c r="B104" s="2">
-        <v>45619</v>
+        <v>45627</v>
       </c>
       <c r="C104" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>5</v>
@@ -1873,10 +1876,10 @@
         <v>4</v>
       </c>
       <c r="B105" s="2">
-        <v>45619</v>
+        <v>45627</v>
       </c>
       <c r="C105" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>5</v>
@@ -1887,13 +1890,13 @@
         <v>4</v>
       </c>
       <c r="B106" s="2">
-        <v>45619</v>
+        <v>45628</v>
       </c>
       <c r="C106" s="2">
-        <v>77</v>
+        <v>337</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -1901,10 +1904,10 @@
         <v>4</v>
       </c>
       <c r="B107" s="2">
-        <v>45619</v>
+        <v>45629</v>
       </c>
       <c r="C107" s="2">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>5</v>
@@ -1915,10 +1918,10 @@
         <v>4</v>
       </c>
       <c r="B108" s="2">
-        <v>45619</v>
+        <v>45630</v>
       </c>
       <c r="C108" s="2">
-        <v>779</v>
+        <v>3</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>5</v>
@@ -1929,13 +1932,13 @@
         <v>4</v>
       </c>
       <c r="B109" s="2">
-        <v>45619</v>
+        <v>45631</v>
       </c>
       <c r="C109" s="2">
-        <v>719</v>
+        <v>16</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -1943,13 +1946,13 @@
         <v>4</v>
       </c>
       <c r="B110" s="2">
-        <v>45619</v>
+        <v>45631</v>
       </c>
       <c r="C110" s="2">
-        <v>163</v>
+        <v>417</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -1957,10 +1960,10 @@
         <v>4</v>
       </c>
       <c r="B111" s="2">
-        <v>45620</v>
+        <v>45632</v>
       </c>
       <c r="C111" s="2">
-        <v>7</v>
+        <v>114</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>5</v>
@@ -1971,13 +1974,13 @@
         <v>4</v>
       </c>
       <c r="B112" s="2">
-        <v>45620</v>
+        <v>45632</v>
       </c>
       <c r="C112" s="2">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -1985,10 +1988,10 @@
         <v>4</v>
       </c>
       <c r="B113" s="2">
-        <v>45620</v>
+        <v>45633</v>
       </c>
       <c r="C113" s="2">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>5</v>
@@ -1999,13 +2002,13 @@
         <v>4</v>
       </c>
       <c r="B114" s="2">
-        <v>45620</v>
+        <v>45634</v>
       </c>
       <c r="C114" s="2">
-        <v>670</v>
+        <v>59</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2013,13 +2016,13 @@
         <v>4</v>
       </c>
       <c r="B115" s="2">
-        <v>45620</v>
+        <v>45634</v>
       </c>
       <c r="C115" s="2">
-        <v>681</v>
+        <v>1260</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2027,13 +2030,13 @@
         <v>4</v>
       </c>
       <c r="B116" s="2">
-        <v>45620</v>
+        <v>45635</v>
       </c>
       <c r="C116" s="2">
-        <v>298</v>
+        <v>84</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2041,10 +2044,10 @@
         <v>4</v>
       </c>
       <c r="B117" s="2">
-        <v>45620</v>
+        <v>45635</v>
       </c>
       <c r="C117" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>5</v>
@@ -2055,10 +2058,10 @@
         <v>4</v>
       </c>
       <c r="B118" s="2">
-        <v>45621</v>
+        <v>45601</v>
       </c>
       <c r="C118" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>5</v>
@@ -2069,13 +2072,13 @@
         <v>4</v>
       </c>
       <c r="B119" s="2">
-        <v>45621</v>
+        <v>45604</v>
       </c>
       <c r="C119" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2083,10 +2086,10 @@
         <v>4</v>
       </c>
       <c r="B120" s="2">
-        <v>45621</v>
+        <v>45605</v>
       </c>
       <c r="C120" s="2">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>5</v>
@@ -2097,13 +2100,13 @@
         <v>4</v>
       </c>
       <c r="B121" s="2">
-        <v>45621</v>
+        <v>45607</v>
       </c>
       <c r="C121" s="2">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2111,10 +2114,10 @@
         <v>4</v>
       </c>
       <c r="B122" s="2">
-        <v>45621</v>
+        <v>45613</v>
       </c>
       <c r="C122" s="2">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>5</v>
@@ -2125,10 +2128,10 @@
         <v>4</v>
       </c>
       <c r="B123" s="2">
-        <v>45621</v>
+        <v>45613</v>
       </c>
       <c r="C123" s="2">
-        <v>480</v>
+        <v>4</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>5</v>
@@ -2139,13 +2142,13 @@
         <v>4</v>
       </c>
       <c r="B124" s="2">
-        <v>45621</v>
+        <v>45614</v>
       </c>
       <c r="C124" s="2">
-        <v>529</v>
+        <v>60</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2153,13 +2156,13 @@
         <v>4</v>
       </c>
       <c r="B125" s="2">
-        <v>45621</v>
+        <v>45615</v>
       </c>
       <c r="C125" s="2">
-        <v>158</v>
+        <v>4</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2167,13 +2170,13 @@
         <v>4</v>
       </c>
       <c r="B126" s="2">
-        <v>45622</v>
+        <v>45617</v>
       </c>
       <c r="C126" s="2">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2181,10 +2184,10 @@
         <v>4</v>
       </c>
       <c r="B127" s="2">
-        <v>45622</v>
+        <v>45619</v>
       </c>
       <c r="C127" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>5</v>
@@ -2195,13 +2198,13 @@
         <v>4</v>
       </c>
       <c r="B128" s="2">
-        <v>45622</v>
+        <v>45620</v>
       </c>
       <c r="C128" s="2">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2209,13 +2212,13 @@
         <v>4</v>
       </c>
       <c r="B129" s="2">
-        <v>45622</v>
+        <v>45621</v>
       </c>
       <c r="C129" s="2">
-        <v>131</v>
+        <v>412</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2226,7 +2229,7 @@
         <v>45622</v>
       </c>
       <c r="C130" s="2">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>5</v>
@@ -2237,13 +2240,13 @@
         <v>4</v>
       </c>
       <c r="B131" s="2">
-        <v>45622</v>
+        <v>45623</v>
       </c>
       <c r="C131" s="2">
-        <v>415</v>
+        <v>349</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2251,13 +2254,13 @@
         <v>4</v>
       </c>
       <c r="B132" s="2">
-        <v>45622</v>
+        <v>45623</v>
       </c>
       <c r="C132" s="2">
-        <v>560</v>
+        <v>1</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2265,13 +2268,13 @@
         <v>4</v>
       </c>
       <c r="B133" s="2">
-        <v>45622</v>
+        <v>45624</v>
       </c>
       <c r="C133" s="2">
-        <v>0</v>
+        <v>957</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2279,10 +2282,10 @@
         <v>4</v>
       </c>
       <c r="B134" s="2">
-        <v>45623</v>
+        <v>45625</v>
       </c>
       <c r="C134" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>5</v>
@@ -2293,10 +2296,10 @@
         <v>4</v>
       </c>
       <c r="B135" s="2">
-        <v>45623</v>
+        <v>45626</v>
       </c>
       <c r="C135" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>5</v>
@@ -2307,13 +2310,13 @@
         <v>4</v>
       </c>
       <c r="B136" s="2">
-        <v>45623</v>
+        <v>45627</v>
       </c>
       <c r="C136" s="2">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -2321,10 +2324,10 @@
         <v>4</v>
       </c>
       <c r="B137" s="2">
-        <v>45623</v>
+        <v>45627</v>
       </c>
       <c r="C137" s="2">
-        <v>12</v>
+        <v>1018</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>5</v>
@@ -2335,10 +2338,10 @@
         <v>4</v>
       </c>
       <c r="B138" s="2">
-        <v>45623</v>
+        <v>45627</v>
       </c>
       <c r="C138" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>5</v>
@@ -2349,13 +2352,13 @@
         <v>4</v>
       </c>
       <c r="B139" s="2">
-        <v>45623</v>
+        <v>45628</v>
       </c>
       <c r="C139" s="2">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -2363,10 +2366,10 @@
         <v>4</v>
       </c>
       <c r="B140" s="2">
-        <v>45623</v>
+        <v>45629</v>
       </c>
       <c r="C140" s="2">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>5</v>
@@ -2377,13 +2380,13 @@
         <v>4</v>
       </c>
       <c r="B141" s="2">
-        <v>45623</v>
+        <v>45630</v>
       </c>
       <c r="C141" s="2">
-        <v>608</v>
+        <v>20</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -2391,13 +2394,13 @@
         <v>4</v>
       </c>
       <c r="B142" s="2">
-        <v>45623</v>
+        <v>45630</v>
       </c>
       <c r="C142" s="2">
-        <v>802</v>
+        <v>392</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2405,13 +2408,13 @@
         <v>4</v>
       </c>
       <c r="B143" s="2">
-        <v>45623</v>
+        <v>45630</v>
       </c>
       <c r="C143" s="2">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -2419,10 +2422,10 @@
         <v>4</v>
       </c>
       <c r="B144" s="2">
-        <v>45624</v>
+        <v>45630</v>
       </c>
       <c r="C144" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>5</v>
@@ -2433,10 +2436,10 @@
         <v>4</v>
       </c>
       <c r="B145" s="2">
-        <v>45624</v>
+        <v>45631</v>
       </c>
       <c r="C145" s="2">
-        <v>2</v>
+        <v>86</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>5</v>
@@ -2447,10 +2450,10 @@
         <v>4</v>
       </c>
       <c r="B146" s="2">
-        <v>45624</v>
+        <v>45632</v>
       </c>
       <c r="C146" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>5</v>
@@ -2461,13 +2464,13 @@
         <v>4</v>
       </c>
       <c r="B147" s="2">
-        <v>45624</v>
+        <v>45633</v>
       </c>
       <c r="C147" s="2">
-        <v>156</v>
+        <v>62</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -2475,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="B148" s="2">
-        <v>45624</v>
+        <v>45633</v>
       </c>
       <c r="C148" s="2">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>5</v>
@@ -2489,10 +2492,10 @@
         <v>4</v>
       </c>
       <c r="B149" s="2">
-        <v>45624</v>
+        <v>45634</v>
       </c>
       <c r="C149" s="2">
-        <v>583</v>
+        <v>168</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>5</v>
@@ -2503,13 +2506,13 @@
         <v>4</v>
       </c>
       <c r="B150" s="2">
-        <v>45624</v>
+        <v>45605</v>
       </c>
       <c r="C150" s="2">
-        <v>824</v>
+        <v>1</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -2517,13 +2520,13 @@
         <v>4</v>
       </c>
       <c r="B151" s="2">
-        <v>45624</v>
+        <v>45606</v>
       </c>
       <c r="C151" s="2">
-        <v>326</v>
+        <v>499</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -2531,13 +2534,13 @@
         <v>4</v>
       </c>
       <c r="B152" s="2">
-        <v>45625</v>
+        <v>45606</v>
       </c>
       <c r="C152" s="2">
-        <v>2</v>
+        <v>117</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -2545,10 +2548,10 @@
         <v>4</v>
       </c>
       <c r="B153" s="2">
-        <v>45625</v>
+        <v>45606</v>
       </c>
       <c r="C153" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>5</v>
@@ -2559,13 +2562,13 @@
         <v>4</v>
       </c>
       <c r="B154" s="2">
-        <v>45625</v>
+        <v>45612</v>
       </c>
       <c r="C154" s="2">
-        <v>1</v>
+        <v>222</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -2573,10 +2576,10 @@
         <v>4</v>
       </c>
       <c r="B155" s="2">
-        <v>45625</v>
+        <v>45612</v>
       </c>
       <c r="C155" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>5</v>
@@ -2587,10 +2590,10 @@
         <v>4</v>
       </c>
       <c r="B156" s="2">
-        <v>45625</v>
+        <v>45614</v>
       </c>
       <c r="C156" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>5</v>
@@ -2601,13 +2604,13 @@
         <v>4</v>
       </c>
       <c r="B157" s="2">
-        <v>45625</v>
+        <v>45615</v>
       </c>
       <c r="C157" s="2">
-        <v>162</v>
+        <v>2</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -2615,13 +2618,13 @@
         <v>4</v>
       </c>
       <c r="B158" s="2">
-        <v>45625</v>
+        <v>45615</v>
       </c>
       <c r="C158" s="2">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -2629,10 +2632,10 @@
         <v>4</v>
       </c>
       <c r="B159" s="2">
-        <v>45625</v>
+        <v>45615</v>
       </c>
       <c r="C159" s="2">
-        <v>935</v>
+        <v>2</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>5</v>
@@ -2643,13 +2646,13 @@
         <v>4</v>
       </c>
       <c r="B160" s="2">
-        <v>45625</v>
+        <v>45618</v>
       </c>
       <c r="C160" s="2">
-        <v>1117</v>
+        <v>2</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -2657,13 +2660,13 @@
         <v>4</v>
       </c>
       <c r="B161" s="2">
-        <v>45625</v>
+        <v>45619</v>
       </c>
       <c r="C161" s="2">
-        <v>305</v>
+        <v>29</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -2671,10 +2674,10 @@
         <v>4</v>
       </c>
       <c r="B162" s="2">
-        <v>45625</v>
+        <v>45620</v>
       </c>
       <c r="C162" s="2">
-        <v>4</v>
+        <v>93</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>5</v>
@@ -2685,10 +2688,10 @@
         <v>4</v>
       </c>
       <c r="B163" s="2">
-        <v>45626</v>
+        <v>45621</v>
       </c>
       <c r="C163" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>5</v>
@@ -2699,10 +2702,10 @@
         <v>4</v>
       </c>
       <c r="B164" s="2">
-        <v>45626</v>
+        <v>45621</v>
       </c>
       <c r="C164" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>5</v>
@@ -2713,13 +2716,13 @@
         <v>4</v>
       </c>
       <c r="B165" s="2">
-        <v>45626</v>
+        <v>45622</v>
       </c>
       <c r="C165" s="2">
-        <v>128</v>
+        <v>1</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -2727,13 +2730,13 @@
         <v>4</v>
       </c>
       <c r="B166" s="2">
-        <v>45626</v>
+        <v>45622</v>
       </c>
       <c r="C166" s="2">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -2741,10 +2744,10 @@
         <v>4</v>
       </c>
       <c r="B167" s="2">
-        <v>45626</v>
+        <v>45623</v>
       </c>
       <c r="C167" s="2">
-        <v>757</v>
+        <v>124</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>5</v>
@@ -2755,13 +2758,13 @@
         <v>4</v>
       </c>
       <c r="B168" s="2">
-        <v>45626</v>
+        <v>45624</v>
       </c>
       <c r="C168" s="2">
-        <v>785</v>
+        <v>3</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -2769,13 +2772,13 @@
         <v>4</v>
       </c>
       <c r="B169" s="2">
-        <v>45626</v>
+        <v>45624</v>
       </c>
       <c r="C169" s="2">
-        <v>302</v>
+        <v>1</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -2783,10 +2786,10 @@
         <v>4</v>
       </c>
       <c r="B170" s="2">
-        <v>45626</v>
+        <v>45625</v>
       </c>
       <c r="C170" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>5</v>
@@ -2797,13 +2800,13 @@
         <v>4</v>
       </c>
       <c r="B171" s="2">
-        <v>45627</v>
+        <v>45625</v>
       </c>
       <c r="C171" s="2">
-        <v>3</v>
+        <v>159</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -2811,13 +2814,13 @@
         <v>4</v>
       </c>
       <c r="B172" s="2">
-        <v>45627</v>
+        <v>45625</v>
       </c>
       <c r="C172" s="2">
-        <v>1</v>
+        <v>132</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -2825,13 +2828,13 @@
         <v>4</v>
       </c>
       <c r="B173" s="2">
-        <v>45627</v>
+        <v>45625</v>
       </c>
       <c r="C173" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -2839,13 +2842,13 @@
         <v>4</v>
       </c>
       <c r="B174" s="2">
-        <v>45627</v>
+        <v>45626</v>
       </c>
       <c r="C174" s="2">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -2853,13 +2856,13 @@
         <v>4</v>
       </c>
       <c r="B175" s="2">
-        <v>45627</v>
+        <v>45628</v>
       </c>
       <c r="C175" s="2">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -2867,10 +2870,10 @@
         <v>4</v>
       </c>
       <c r="B176" s="2">
-        <v>45627</v>
+        <v>45629</v>
       </c>
       <c r="C176" s="2">
-        <v>637</v>
+        <v>99</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>5</v>
@@ -2881,13 +2884,13 @@
         <v>4</v>
       </c>
       <c r="B177" s="2">
-        <v>45627</v>
+        <v>45629</v>
       </c>
       <c r="C177" s="2">
-        <v>786</v>
+        <v>368</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -2895,13 +2898,13 @@
         <v>4</v>
       </c>
       <c r="B178" s="2">
-        <v>45627</v>
+        <v>45631</v>
       </c>
       <c r="C178" s="2">
-        <v>160</v>
+        <v>2</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -2909,10 +2912,10 @@
         <v>4</v>
       </c>
       <c r="B179" s="2">
-        <v>45628</v>
+        <v>45632</v>
       </c>
       <c r="C179" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>5</v>
@@ -2923,10 +2926,10 @@
         <v>4</v>
       </c>
       <c r="B180" s="2">
-        <v>45628</v>
+        <v>45632</v>
       </c>
       <c r="C180" s="2">
-        <v>2</v>
+        <v>580</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>5</v>
@@ -2937,10 +2940,10 @@
         <v>4</v>
       </c>
       <c r="B181" s="2">
-        <v>45628</v>
+        <v>45635</v>
       </c>
       <c r="C181" s="2">
-        <v>1</v>
+        <v>360</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>5</v>
@@ -2951,13 +2954,13 @@
         <v>4</v>
       </c>
       <c r="B182" s="2">
-        <v>45628</v>
+        <v>45635</v>
       </c>
       <c r="C182" s="2">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -2965,10 +2968,10 @@
         <v>4</v>
       </c>
       <c r="B183" s="2">
-        <v>45628</v>
+        <v>45604</v>
       </c>
       <c r="C183" s="2">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>5</v>
@@ -2979,10 +2982,10 @@
         <v>4</v>
       </c>
       <c r="B184" s="2">
-        <v>45628</v>
+        <v>45605</v>
       </c>
       <c r="C184" s="2">
-        <v>388</v>
+        <v>6</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>5</v>
@@ -2993,13 +2996,13 @@
         <v>4</v>
       </c>
       <c r="B185" s="2">
-        <v>45628</v>
+        <v>45606</v>
       </c>
       <c r="C185" s="2">
-        <v>476</v>
+        <v>127</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -3007,10 +3010,10 @@
         <v>4</v>
       </c>
       <c r="B186" s="2">
-        <v>45628</v>
+        <v>45612</v>
       </c>
       <c r="C186" s="2">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>8</v>
@@ -3021,10 +3024,10 @@
         <v>4</v>
       </c>
       <c r="B187" s="2">
-        <v>45629</v>
+        <v>45613</v>
       </c>
       <c r="C187" s="2">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>5</v>
@@ -3035,13 +3038,13 @@
         <v>4</v>
       </c>
       <c r="B188" s="2">
-        <v>45629</v>
+        <v>45615</v>
       </c>
       <c r="C188" s="2">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3049,13 +3052,13 @@
         <v>4</v>
       </c>
       <c r="B189" s="2">
-        <v>45629</v>
+        <v>45615</v>
       </c>
       <c r="C189" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3063,13 +3066,13 @@
         <v>4</v>
       </c>
       <c r="B190" s="2">
-        <v>45629</v>
+        <v>45616</v>
       </c>
       <c r="C190" s="2">
-        <v>31</v>
+        <v>181</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3077,10 +3080,10 @@
         <v>4</v>
       </c>
       <c r="B191" s="2">
-        <v>45629</v>
+        <v>45619</v>
       </c>
       <c r="C191" s="2">
-        <v>40</v>
+        <v>623</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>5</v>
@@ -3091,10 +3094,10 @@
         <v>4</v>
       </c>
       <c r="B192" s="2">
-        <v>45629</v>
+        <v>45619</v>
       </c>
       <c r="C192" s="2">
-        <v>384</v>
+        <v>8</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>5</v>
@@ -3105,13 +3108,13 @@
         <v>4</v>
       </c>
       <c r="B193" s="2">
-        <v>45629</v>
+        <v>45621</v>
       </c>
       <c r="C193" s="2">
-        <v>455</v>
+        <v>1</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3119,13 +3122,13 @@
         <v>4</v>
       </c>
       <c r="B194" s="2">
-        <v>45629</v>
+        <v>45622</v>
       </c>
       <c r="C194" s="2">
-        <v>29</v>
+        <v>454</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3133,13 +3136,13 @@
         <v>4</v>
       </c>
       <c r="B195" s="2">
-        <v>45630</v>
+        <v>45622</v>
       </c>
       <c r="C195" s="2">
-        <v>1</v>
+        <v>284</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3147,10 +3150,10 @@
         <v>4</v>
       </c>
       <c r="B196" s="2">
-        <v>45630</v>
+        <v>45622</v>
       </c>
       <c r="C196" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>5</v>
@@ -3161,13 +3164,13 @@
         <v>4</v>
       </c>
       <c r="B197" s="2">
-        <v>45630</v>
+        <v>45624</v>
       </c>
       <c r="C197" s="2">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3175,13 +3178,13 @@
         <v>4</v>
       </c>
       <c r="B198" s="2">
-        <v>45630</v>
+        <v>45625</v>
       </c>
       <c r="C198" s="2">
-        <v>51</v>
+        <v>426</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3189,10 +3192,10 @@
         <v>4</v>
       </c>
       <c r="B199" s="2">
-        <v>45630</v>
+        <v>45625</v>
       </c>
       <c r="C199" s="2">
-        <v>416</v>
+        <v>1</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>5</v>
@@ -3203,13 +3206,13 @@
         <v>4</v>
       </c>
       <c r="B200" s="2">
-        <v>45630</v>
+        <v>45625</v>
       </c>
       <c r="C200" s="2">
-        <v>485</v>
+        <v>28</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3217,13 +3220,13 @@
         <v>4</v>
       </c>
       <c r="B201" s="2">
-        <v>45630</v>
+        <v>45627</v>
       </c>
       <c r="C201" s="2">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3231,10 +3234,10 @@
         <v>4</v>
       </c>
       <c r="B202" s="2">
-        <v>45631</v>
+        <v>45628</v>
       </c>
       <c r="C202" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>5</v>
@@ -3245,13 +3248,13 @@
         <v>4</v>
       </c>
       <c r="B203" s="2">
-        <v>45631</v>
+        <v>45628</v>
       </c>
       <c r="C203" s="2">
-        <v>4</v>
+        <v>85</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -3259,13 +3262,13 @@
         <v>4</v>
       </c>
       <c r="B204" s="2">
-        <v>45631</v>
+        <v>45628</v>
       </c>
       <c r="C204" s="2">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -3276,7 +3279,7 @@
         <v>45631</v>
       </c>
       <c r="C205" s="2">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>5</v>
@@ -3290,10 +3293,10 @@
         <v>45631</v>
       </c>
       <c r="C206" s="2">
-        <v>376</v>
+        <v>89</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -3301,13 +3304,13 @@
         <v>4</v>
       </c>
       <c r="B207" s="2">
-        <v>45631</v>
+        <v>45634</v>
       </c>
       <c r="C207" s="2">
-        <v>383</v>
+        <v>3</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -3315,13 +3318,13 @@
         <v>4</v>
       </c>
       <c r="B208" s="2">
-        <v>45631</v>
+        <v>45634</v>
       </c>
       <c r="C208" s="2">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -3329,13 +3332,13 @@
         <v>4</v>
       </c>
       <c r="B209" s="2">
-        <v>45632</v>
+        <v>45635</v>
       </c>
       <c r="C209" s="2">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -3343,13 +3346,13 @@
         <v>4</v>
       </c>
       <c r="B210" s="2">
-        <v>45632</v>
+        <v>45612</v>
       </c>
       <c r="C210" s="2">
-        <v>60</v>
+        <v>987</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -3357,10 +3360,10 @@
         <v>4</v>
       </c>
       <c r="B211" s="2">
-        <v>45632</v>
+        <v>45613</v>
       </c>
       <c r="C211" s="2">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>5</v>
@@ -3371,10 +3374,10 @@
         <v>4</v>
       </c>
       <c r="B212" s="2">
-        <v>45632</v>
+        <v>45614</v>
       </c>
       <c r="C212" s="2">
-        <v>893</v>
+        <v>4</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>5</v>
@@ -3385,13 +3388,13 @@
         <v>4</v>
       </c>
       <c r="B213" s="2">
-        <v>45632</v>
+        <v>45615</v>
       </c>
       <c r="C213" s="2">
-        <v>711</v>
+        <v>167</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -3399,13 +3402,13 @@
         <v>4</v>
       </c>
       <c r="B214" s="2">
-        <v>45632</v>
+        <v>45616</v>
       </c>
       <c r="C214" s="2">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -3413,10 +3416,10 @@
         <v>4</v>
       </c>
       <c r="B215" s="2">
-        <v>45633</v>
+        <v>45616</v>
       </c>
       <c r="C215" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>5</v>
@@ -3427,10 +3430,10 @@
         <v>4</v>
       </c>
       <c r="B216" s="2">
-        <v>45633</v>
+        <v>45617</v>
       </c>
       <c r="C216" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>5</v>
@@ -3441,13 +3444,13 @@
         <v>4</v>
       </c>
       <c r="B217" s="2">
-        <v>45633</v>
+        <v>45618</v>
       </c>
       <c r="C217" s="2">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -3455,13 +3458,13 @@
         <v>4</v>
       </c>
       <c r="B218" s="2">
-        <v>45633</v>
+        <v>45618</v>
       </c>
       <c r="C218" s="2">
-        <v>152</v>
+        <v>343</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -3469,10 +3472,10 @@
         <v>4</v>
       </c>
       <c r="B219" s="2">
-        <v>45633</v>
+        <v>45619</v>
       </c>
       <c r="C219" s="2">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>5</v>
@@ -3483,10 +3486,10 @@
         <v>4</v>
       </c>
       <c r="B220" s="2">
-        <v>45633</v>
+        <v>45620</v>
       </c>
       <c r="C220" s="2">
-        <v>881</v>
+        <v>2</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>5</v>
@@ -3497,13 +3500,13 @@
         <v>4</v>
       </c>
       <c r="B221" s="2">
-        <v>45633</v>
+        <v>45620</v>
       </c>
       <c r="C221" s="2">
-        <v>1404</v>
+        <v>1</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -3511,10 +3514,10 @@
         <v>4</v>
       </c>
       <c r="B222" s="2">
-        <v>45633</v>
+        <v>45621</v>
       </c>
       <c r="C222" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>8</v>
@@ -3525,10 +3528,10 @@
         <v>4</v>
       </c>
       <c r="B223" s="2">
-        <v>45634</v>
+        <v>45622</v>
       </c>
       <c r="C223" s="2">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>5</v>
@@ -3539,10 +3542,10 @@
         <v>4</v>
       </c>
       <c r="B224" s="2">
-        <v>45634</v>
+        <v>45624</v>
       </c>
       <c r="C224" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>5</v>
@@ -3553,13 +3556,13 @@
         <v>4</v>
       </c>
       <c r="B225" s="2">
-        <v>45634</v>
+        <v>45624</v>
       </c>
       <c r="C225" s="2">
-        <v>1</v>
+        <v>113</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -3567,13 +3570,13 @@
         <v>4</v>
       </c>
       <c r="B226" s="2">
-        <v>45634</v>
+        <v>45624</v>
       </c>
       <c r="C226" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -3581,13 +3584,13 @@
         <v>4</v>
       </c>
       <c r="B227" s="2">
-        <v>45634</v>
+        <v>45625</v>
       </c>
       <c r="C227" s="2">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -3595,13 +3598,13 @@
         <v>4</v>
       </c>
       <c r="B228" s="2">
-        <v>45634</v>
+        <v>45626</v>
       </c>
       <c r="C228" s="2">
-        <v>66</v>
+        <v>410</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -3609,10 +3612,10 @@
         <v>4</v>
       </c>
       <c r="B229" s="2">
-        <v>45634</v>
+        <v>45627</v>
       </c>
       <c r="C229" s="2">
-        <v>854</v>
+        <v>3</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>5</v>
@@ -3623,13 +3626,13 @@
         <v>4</v>
       </c>
       <c r="B230" s="2">
-        <v>45634</v>
+        <v>45629</v>
       </c>
       <c r="C230" s="2">
-        <v>945</v>
+        <v>85</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -3637,13 +3640,13 @@
         <v>4</v>
       </c>
       <c r="B231" s="2">
-        <v>45634</v>
+        <v>45632</v>
       </c>
       <c r="C231" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -3651,10 +3654,10 @@
         <v>4</v>
       </c>
       <c r="B232" s="2">
-        <v>45635</v>
+        <v>45633</v>
       </c>
       <c r="C232" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D232" s="2" t="s">
         <v>5</v>
@@ -3665,10 +3668,10 @@
         <v>4</v>
       </c>
       <c r="B233" s="2">
-        <v>45635</v>
+        <v>45633</v>
       </c>
       <c r="C233" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>5</v>
@@ -3679,13 +3682,13 @@
         <v>4</v>
       </c>
       <c r="B234" s="2">
-        <v>45635</v>
+        <v>45634</v>
       </c>
       <c r="C234" s="2">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -3693,10 +3696,10 @@
         <v>4</v>
       </c>
       <c r="B235" s="2">
-        <v>45635</v>
+        <v>45634</v>
       </c>
       <c r="C235" s="2">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>5</v>
@@ -3707,13 +3710,13 @@
         <v>4</v>
       </c>
       <c r="B236" s="2">
-        <v>45635</v>
+        <v>45634</v>
       </c>
       <c r="C236" s="2">
-        <v>504</v>
+        <v>160</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -3724,24 +3727,10 @@
         <v>45635</v>
       </c>
       <c r="C237" s="2">
-        <v>735</v>
+        <v>135</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="238" spans="1:4">
-      <c r="A238" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B238" s="2">
-        <v>45635</v>
-      </c>
-      <c r="C238" s="2">
-        <v>2</v>
-      </c>
-      <c r="D238" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/reports/For Winter Ending (Prior Year)_Visits.xlsx
+++ b/reports/For Winter Ending (Prior Year)_Visits.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="10">
   <si>
     <t>Resort</t>
   </si>
@@ -406,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D237"/>
+  <dimension ref="A1:D244"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -882,10 +882,10 @@
         <v>4</v>
       </c>
       <c r="B34" s="2">
-        <v>45606</v>
+        <v>45636</v>
       </c>
       <c r="C34" s="2">
-        <v>5</v>
+        <v>397</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>5</v>
@@ -896,13 +896,13 @@
         <v>4</v>
       </c>
       <c r="B35" s="2">
-        <v>45610</v>
+        <v>45612</v>
       </c>
       <c r="C35" s="2">
-        <v>0</v>
+        <v>987</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -910,13 +910,13 @@
         <v>4</v>
       </c>
       <c r="B36" s="2">
-        <v>45610</v>
+        <v>45613</v>
       </c>
       <c r="C36" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -924,10 +924,10 @@
         <v>4</v>
       </c>
       <c r="B37" s="2">
-        <v>45612</v>
+        <v>45614</v>
       </c>
       <c r="C37" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>5</v>
@@ -938,10 +938,10 @@
         <v>4</v>
       </c>
       <c r="B38" s="2">
-        <v>45612</v>
+        <v>45615</v>
       </c>
       <c r="C38" s="2">
-        <v>12</v>
+        <v>167</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>5</v>
@@ -952,13 +952,13 @@
         <v>4</v>
       </c>
       <c r="B39" s="2">
-        <v>45613</v>
+        <v>45616</v>
       </c>
       <c r="C39" s="2">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -966,10 +966,10 @@
         <v>4</v>
       </c>
       <c r="B40" s="2">
-        <v>45614</v>
+        <v>45616</v>
       </c>
       <c r="C40" s="2">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>5</v>
@@ -980,13 +980,13 @@
         <v>4</v>
       </c>
       <c r="B41" s="2">
-        <v>45616</v>
+        <v>45617</v>
       </c>
       <c r="C41" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -994,13 +994,13 @@
         <v>4</v>
       </c>
       <c r="B42" s="2">
-        <v>45616</v>
+        <v>45618</v>
       </c>
       <c r="C42" s="2">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1008,10 +1008,10 @@
         <v>4</v>
       </c>
       <c r="B43" s="2">
-        <v>45617</v>
+        <v>45618</v>
       </c>
       <c r="C43" s="2">
-        <v>91</v>
+        <v>343</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>5</v>
@@ -1022,10 +1022,10 @@
         <v>4</v>
       </c>
       <c r="B44" s="2">
-        <v>45617</v>
+        <v>45619</v>
       </c>
       <c r="C44" s="2">
-        <v>234</v>
+        <v>85</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>5</v>
@@ -1036,13 +1036,13 @@
         <v>4</v>
       </c>
       <c r="B45" s="2">
-        <v>45618</v>
+        <v>45620</v>
       </c>
       <c r="C45" s="2">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1050,13 +1050,13 @@
         <v>4</v>
       </c>
       <c r="B46" s="2">
-        <v>45619</v>
+        <v>45620</v>
       </c>
       <c r="C46" s="2">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1064,13 +1064,13 @@
         <v>4</v>
       </c>
       <c r="B47" s="2">
-        <v>45620</v>
+        <v>45621</v>
       </c>
       <c r="C47" s="2">
-        <v>541</v>
+        <v>78</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1078,13 +1078,13 @@
         <v>4</v>
       </c>
       <c r="B48" s="2">
-        <v>45621</v>
+        <v>45622</v>
       </c>
       <c r="C48" s="2">
-        <v>224</v>
+        <v>71</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1092,10 +1092,10 @@
         <v>4</v>
       </c>
       <c r="B49" s="2">
-        <v>45621</v>
+        <v>45624</v>
       </c>
       <c r="C49" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>5</v>
@@ -1106,13 +1106,13 @@
         <v>4</v>
       </c>
       <c r="B50" s="2">
-        <v>45622</v>
+        <v>45624</v>
       </c>
       <c r="C50" s="2">
-        <v>3</v>
+        <v>113</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1120,13 +1120,13 @@
         <v>4</v>
       </c>
       <c r="B51" s="2">
-        <v>45623</v>
+        <v>45624</v>
       </c>
       <c r="C51" s="2">
-        <v>991</v>
+        <v>3</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1134,13 +1134,13 @@
         <v>4</v>
       </c>
       <c r="B52" s="2">
-        <v>45624</v>
+        <v>45625</v>
       </c>
       <c r="C52" s="2">
-        <v>340</v>
+        <v>56</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1148,13 +1148,13 @@
         <v>4</v>
       </c>
       <c r="B53" s="2">
-        <v>45624</v>
+        <v>45626</v>
       </c>
       <c r="C53" s="2">
-        <v>1</v>
+        <v>410</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1162,10 +1162,10 @@
         <v>4</v>
       </c>
       <c r="B54" s="2">
-        <v>45624</v>
+        <v>45627</v>
       </c>
       <c r="C54" s="2">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>5</v>
@@ -1176,13 +1176,13 @@
         <v>4</v>
       </c>
       <c r="B55" s="2">
-        <v>45625</v>
+        <v>45629</v>
       </c>
       <c r="C55" s="2">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1190,13 +1190,13 @@
         <v>4</v>
       </c>
       <c r="B56" s="2">
-        <v>45626</v>
+        <v>45632</v>
       </c>
       <c r="C56" s="2">
-        <v>1024</v>
+        <v>113</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1204,13 +1204,13 @@
         <v>4</v>
       </c>
       <c r="B57" s="2">
-        <v>45627</v>
+        <v>45633</v>
       </c>
       <c r="C57" s="2">
-        <v>173</v>
+        <v>3</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1218,10 +1218,10 @@
         <v>4</v>
       </c>
       <c r="B58" s="2">
-        <v>45634</v>
+        <v>45633</v>
       </c>
       <c r="C58" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>5</v>
@@ -1232,7 +1232,7 @@
         <v>4</v>
       </c>
       <c r="B59" s="2">
-        <v>45635</v>
+        <v>45634</v>
       </c>
       <c r="C59" s="2">
         <v>1</v>
@@ -1246,10 +1246,10 @@
         <v>4</v>
       </c>
       <c r="B60" s="2">
-        <v>45611</v>
+        <v>45634</v>
       </c>
       <c r="C60" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>5</v>
@@ -1260,13 +1260,13 @@
         <v>4</v>
       </c>
       <c r="B61" s="2">
-        <v>45612</v>
+        <v>45634</v>
       </c>
       <c r="C61" s="2">
-        <v>129</v>
+        <v>160</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1274,13 +1274,13 @@
         <v>4</v>
       </c>
       <c r="B62" s="2">
-        <v>45613</v>
+        <v>45635</v>
       </c>
       <c r="C62" s="2">
-        <v>7</v>
+        <v>135</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1288,13 +1288,13 @@
         <v>4</v>
       </c>
       <c r="B63" s="2">
-        <v>45614</v>
+        <v>45604</v>
       </c>
       <c r="C63" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1302,10 +1302,10 @@
         <v>4</v>
       </c>
       <c r="B64" s="2">
-        <v>45614</v>
+        <v>45605</v>
       </c>
       <c r="C64" s="2">
-        <v>200</v>
+        <v>6</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>5</v>
@@ -1316,13 +1316,13 @@
         <v>4</v>
       </c>
       <c r="B65" s="2">
-        <v>45614</v>
+        <v>45606</v>
       </c>
       <c r="C65" s="2">
-        <v>1</v>
+        <v>127</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1330,13 +1330,13 @@
         <v>4</v>
       </c>
       <c r="B66" s="2">
-        <v>45615</v>
+        <v>45612</v>
       </c>
       <c r="C66" s="2">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1344,10 +1344,10 @@
         <v>4</v>
       </c>
       <c r="B67" s="2">
-        <v>45616</v>
+        <v>45613</v>
       </c>
       <c r="C67" s="2">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>5</v>
@@ -1358,10 +1358,10 @@
         <v>4</v>
       </c>
       <c r="B68" s="2">
-        <v>45617</v>
+        <v>45615</v>
       </c>
       <c r="C68" s="2">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>8</v>
@@ -1372,13 +1372,13 @@
         <v>4</v>
       </c>
       <c r="B69" s="2">
-        <v>45618</v>
+        <v>45615</v>
       </c>
       <c r="C69" s="2">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1386,10 +1386,10 @@
         <v>4</v>
       </c>
       <c r="B70" s="2">
-        <v>45620</v>
+        <v>45616</v>
       </c>
       <c r="C70" s="2">
-        <v>3</v>
+        <v>181</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>5</v>
@@ -1400,13 +1400,13 @@
         <v>4</v>
       </c>
       <c r="B71" s="2">
-        <v>45620</v>
+        <v>45619</v>
       </c>
       <c r="C71" s="2">
-        <v>81</v>
+        <v>623</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1414,10 +1414,10 @@
         <v>4</v>
       </c>
       <c r="B72" s="2">
-        <v>45620</v>
+        <v>45619</v>
       </c>
       <c r="C72" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>5</v>
@@ -1431,7 +1431,7 @@
         <v>45621</v>
       </c>
       <c r="C73" s="2">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>5</v>
@@ -1442,10 +1442,10 @@
         <v>4</v>
       </c>
       <c r="B74" s="2">
-        <v>45623</v>
+        <v>45622</v>
       </c>
       <c r="C74" s="2">
-        <v>8</v>
+        <v>454</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>5</v>
@@ -1456,13 +1456,13 @@
         <v>4</v>
       </c>
       <c r="B75" s="2">
-        <v>45623</v>
+        <v>45622</v>
       </c>
       <c r="C75" s="2">
-        <v>1</v>
+        <v>284</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1470,13 +1470,13 @@
         <v>4</v>
       </c>
       <c r="B76" s="2">
-        <v>45624</v>
+        <v>45622</v>
       </c>
       <c r="C76" s="2">
         <v>3</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -1484,10 +1484,10 @@
         <v>4</v>
       </c>
       <c r="B77" s="2">
-        <v>45626</v>
+        <v>45624</v>
       </c>
       <c r="C77" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>5</v>
@@ -1498,13 +1498,13 @@
         <v>4</v>
       </c>
       <c r="B78" s="2">
-        <v>45627</v>
+        <v>45625</v>
       </c>
       <c r="C78" s="2">
-        <v>1</v>
+        <v>426</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1512,7 +1512,7 @@
         <v>4</v>
       </c>
       <c r="B79" s="2">
-        <v>45627</v>
+        <v>45625</v>
       </c>
       <c r="C79" s="2">
         <v>1</v>
@@ -1526,13 +1526,13 @@
         <v>4</v>
       </c>
       <c r="B80" s="2">
-        <v>45627</v>
+        <v>45625</v>
       </c>
       <c r="C80" s="2">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -1540,13 +1540,13 @@
         <v>4</v>
       </c>
       <c r="B81" s="2">
-        <v>45630</v>
+        <v>45627</v>
       </c>
       <c r="C81" s="2">
-        <v>90</v>
+        <v>4</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -1554,13 +1554,13 @@
         <v>4</v>
       </c>
       <c r="B82" s="2">
-        <v>45633</v>
+        <v>45628</v>
       </c>
       <c r="C82" s="2">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1568,10 +1568,10 @@
         <v>4</v>
       </c>
       <c r="B83" s="2">
-        <v>45633</v>
+        <v>45628</v>
       </c>
       <c r="C83" s="2">
-        <v>295</v>
+        <v>85</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>6</v>
@@ -1582,10 +1582,10 @@
         <v>4</v>
       </c>
       <c r="B84" s="2">
-        <v>45635</v>
+        <v>45628</v>
       </c>
       <c r="C84" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>5</v>
@@ -1596,13 +1596,13 @@
         <v>4</v>
       </c>
       <c r="B85" s="2">
-        <v>45602</v>
+        <v>45631</v>
       </c>
       <c r="C85" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1610,13 +1610,13 @@
         <v>4</v>
       </c>
       <c r="B86" s="2">
-        <v>45605</v>
+        <v>45631</v>
       </c>
       <c r="C86" s="2">
-        <v>137</v>
+        <v>89</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -1624,10 +1624,10 @@
         <v>4</v>
       </c>
       <c r="B87" s="2">
-        <v>45605</v>
+        <v>45634</v>
       </c>
       <c r="C87" s="2">
-        <v>760</v>
+        <v>3</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>5</v>
@@ -1638,10 +1638,10 @@
         <v>4</v>
       </c>
       <c r="B88" s="2">
-        <v>45606</v>
+        <v>45634</v>
       </c>
       <c r="C88" s="2">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>5</v>
@@ -1652,10 +1652,10 @@
         <v>4</v>
       </c>
       <c r="B89" s="2">
-        <v>45611</v>
+        <v>45635</v>
       </c>
       <c r="C89" s="2">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>8</v>
@@ -1666,13 +1666,13 @@
         <v>4</v>
       </c>
       <c r="B90" s="2">
-        <v>45613</v>
+        <v>45636</v>
       </c>
       <c r="C90" s="2">
-        <v>153</v>
+        <v>98</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -1680,10 +1680,10 @@
         <v>4</v>
       </c>
       <c r="B91" s="2">
-        <v>45614</v>
+        <v>45606</v>
       </c>
       <c r="C91" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>5</v>
@@ -1694,13 +1694,13 @@
         <v>4</v>
       </c>
       <c r="B92" s="2">
-        <v>45614</v>
+        <v>45610</v>
       </c>
       <c r="C92" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -1708,13 +1708,13 @@
         <v>4</v>
       </c>
       <c r="B93" s="2">
-        <v>45616</v>
+        <v>45610</v>
       </c>
       <c r="C93" s="2">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -1722,10 +1722,10 @@
         <v>4</v>
       </c>
       <c r="B94" s="2">
-        <v>45617</v>
+        <v>45612</v>
       </c>
       <c r="C94" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>5</v>
@@ -1736,13 +1736,13 @@
         <v>4</v>
       </c>
       <c r="B95" s="2">
-        <v>45619</v>
+        <v>45612</v>
       </c>
       <c r="C95" s="2">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -1750,13 +1750,13 @@
         <v>4</v>
       </c>
       <c r="B96" s="2">
-        <v>45620</v>
+        <v>45613</v>
       </c>
       <c r="C96" s="2">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -1764,13 +1764,13 @@
         <v>4</v>
       </c>
       <c r="B97" s="2">
-        <v>45621</v>
+        <v>45614</v>
       </c>
       <c r="C97" s="2">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -1778,13 +1778,13 @@
         <v>4</v>
       </c>
       <c r="B98" s="2">
-        <v>45623</v>
+        <v>45616</v>
       </c>
       <c r="C98" s="2">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -1792,10 +1792,10 @@
         <v>4</v>
       </c>
       <c r="B99" s="2">
-        <v>45623</v>
+        <v>45616</v>
       </c>
       <c r="C99" s="2">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>5</v>
@@ -1806,10 +1806,10 @@
         <v>4</v>
       </c>
       <c r="B100" s="2">
-        <v>45625</v>
+        <v>45617</v>
       </c>
       <c r="C100" s="2">
-        <v>707</v>
+        <v>91</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>5</v>
@@ -1820,10 +1820,10 @@
         <v>4</v>
       </c>
       <c r="B101" s="2">
-        <v>45626</v>
+        <v>45617</v>
       </c>
       <c r="C101" s="2">
-        <v>1</v>
+        <v>234</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>5</v>
@@ -1834,13 +1834,13 @@
         <v>4</v>
       </c>
       <c r="B102" s="2">
-        <v>45626</v>
+        <v>45618</v>
       </c>
       <c r="C102" s="2">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -1848,13 +1848,13 @@
         <v>4</v>
       </c>
       <c r="B103" s="2">
-        <v>45626</v>
+        <v>45619</v>
       </c>
       <c r="C103" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -1862,10 +1862,10 @@
         <v>4</v>
       </c>
       <c r="B104" s="2">
-        <v>45627</v>
+        <v>45620</v>
       </c>
       <c r="C104" s="2">
-        <v>1</v>
+        <v>541</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>5</v>
@@ -1876,13 +1876,13 @@
         <v>4</v>
       </c>
       <c r="B105" s="2">
-        <v>45627</v>
+        <v>45621</v>
       </c>
       <c r="C105" s="2">
-        <v>7</v>
+        <v>224</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -1890,10 +1890,10 @@
         <v>4</v>
       </c>
       <c r="B106" s="2">
-        <v>45628</v>
+        <v>45621</v>
       </c>
       <c r="C106" s="2">
-        <v>337</v>
+        <v>1</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>5</v>
@@ -1904,13 +1904,13 @@
         <v>4</v>
       </c>
       <c r="B107" s="2">
-        <v>45629</v>
+        <v>45622</v>
       </c>
       <c r="C107" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -1918,10 +1918,10 @@
         <v>4</v>
       </c>
       <c r="B108" s="2">
-        <v>45630</v>
+        <v>45623</v>
       </c>
       <c r="C108" s="2">
-        <v>3</v>
+        <v>991</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>5</v>
@@ -1932,13 +1932,13 @@
         <v>4</v>
       </c>
       <c r="B109" s="2">
-        <v>45631</v>
+        <v>45624</v>
       </c>
       <c r="C109" s="2">
-        <v>16</v>
+        <v>340</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -1946,10 +1946,10 @@
         <v>4</v>
       </c>
       <c r="B110" s="2">
-        <v>45631</v>
+        <v>45624</v>
       </c>
       <c r="C110" s="2">
-        <v>417</v>
+        <v>1</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>5</v>
@@ -1960,10 +1960,10 @@
         <v>4</v>
       </c>
       <c r="B111" s="2">
-        <v>45632</v>
+        <v>45624</v>
       </c>
       <c r="C111" s="2">
-        <v>114</v>
+        <v>18</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>5</v>
@@ -1974,10 +1974,10 @@
         <v>4</v>
       </c>
       <c r="B112" s="2">
-        <v>45632</v>
+        <v>45625</v>
       </c>
       <c r="C112" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>5</v>
@@ -1988,10 +1988,10 @@
         <v>4</v>
       </c>
       <c r="B113" s="2">
-        <v>45633</v>
+        <v>45626</v>
       </c>
       <c r="C113" s="2">
-        <v>2</v>
+        <v>1024</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>5</v>
@@ -2002,13 +2002,13 @@
         <v>4</v>
       </c>
       <c r="B114" s="2">
-        <v>45634</v>
+        <v>45627</v>
       </c>
       <c r="C114" s="2">
-        <v>59</v>
+        <v>173</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2019,7 +2019,7 @@
         <v>45634</v>
       </c>
       <c r="C115" s="2">
-        <v>1260</v>
+        <v>5</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>5</v>
@@ -2033,7 +2033,7 @@
         <v>45635</v>
       </c>
       <c r="C116" s="2">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>5</v>
@@ -2044,7 +2044,7 @@
         <v>4</v>
       </c>
       <c r="B117" s="2">
-        <v>45635</v>
+        <v>45636</v>
       </c>
       <c r="C117" s="2">
         <v>2</v>
@@ -2506,13 +2506,13 @@
         <v>4</v>
       </c>
       <c r="B150" s="2">
-        <v>45605</v>
+        <v>45636</v>
       </c>
       <c r="C150" s="2">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -2520,10 +2520,10 @@
         <v>4</v>
       </c>
       <c r="B151" s="2">
-        <v>45606</v>
+        <v>45636</v>
       </c>
       <c r="C151" s="2">
-        <v>499</v>
+        <v>6</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>5</v>
@@ -2534,13 +2534,13 @@
         <v>4</v>
       </c>
       <c r="B152" s="2">
-        <v>45606</v>
+        <v>45602</v>
       </c>
       <c r="C152" s="2">
-        <v>117</v>
+        <v>6</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -2548,13 +2548,13 @@
         <v>4</v>
       </c>
       <c r="B153" s="2">
-        <v>45606</v>
+        <v>45605</v>
       </c>
       <c r="C153" s="2">
-        <v>6</v>
+        <v>137</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -2562,13 +2562,13 @@
         <v>4</v>
       </c>
       <c r="B154" s="2">
-        <v>45612</v>
+        <v>45605</v>
       </c>
       <c r="C154" s="2">
-        <v>222</v>
+        <v>760</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -2576,10 +2576,10 @@
         <v>4</v>
       </c>
       <c r="B155" s="2">
-        <v>45612</v>
+        <v>45606</v>
       </c>
       <c r="C155" s="2">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>5</v>
@@ -2590,13 +2590,13 @@
         <v>4</v>
       </c>
       <c r="B156" s="2">
-        <v>45614</v>
+        <v>45611</v>
       </c>
       <c r="C156" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -2604,13 +2604,13 @@
         <v>4</v>
       </c>
       <c r="B157" s="2">
-        <v>45615</v>
+        <v>45613</v>
       </c>
       <c r="C157" s="2">
-        <v>2</v>
+        <v>153</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -2618,13 +2618,13 @@
         <v>4</v>
       </c>
       <c r="B158" s="2">
-        <v>45615</v>
+        <v>45614</v>
       </c>
       <c r="C158" s="2">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -2632,10 +2632,10 @@
         <v>4</v>
       </c>
       <c r="B159" s="2">
-        <v>45615</v>
+        <v>45614</v>
       </c>
       <c r="C159" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>5</v>
@@ -2646,13 +2646,13 @@
         <v>4</v>
       </c>
       <c r="B160" s="2">
-        <v>45618</v>
+        <v>45616</v>
       </c>
       <c r="C160" s="2">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -2660,13 +2660,13 @@
         <v>4</v>
       </c>
       <c r="B161" s="2">
-        <v>45619</v>
+        <v>45617</v>
       </c>
       <c r="C161" s="2">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -2674,13 +2674,13 @@
         <v>4</v>
       </c>
       <c r="B162" s="2">
-        <v>45620</v>
+        <v>45619</v>
       </c>
       <c r="C162" s="2">
-        <v>93</v>
+        <v>224</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -2688,10 +2688,10 @@
         <v>4</v>
       </c>
       <c r="B163" s="2">
-        <v>45621</v>
+        <v>45620</v>
       </c>
       <c r="C163" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>5</v>
@@ -2705,10 +2705,10 @@
         <v>45621</v>
       </c>
       <c r="C164" s="2">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -2716,10 +2716,10 @@
         <v>4</v>
       </c>
       <c r="B165" s="2">
-        <v>45622</v>
+        <v>45623</v>
       </c>
       <c r="C165" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>5</v>
@@ -2730,13 +2730,13 @@
         <v>4</v>
       </c>
       <c r="B166" s="2">
-        <v>45622</v>
+        <v>45623</v>
       </c>
       <c r="C166" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -2744,10 +2744,10 @@
         <v>4</v>
       </c>
       <c r="B167" s="2">
-        <v>45623</v>
+        <v>45625</v>
       </c>
       <c r="C167" s="2">
-        <v>124</v>
+        <v>707</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>5</v>
@@ -2758,10 +2758,10 @@
         <v>4</v>
       </c>
       <c r="B168" s="2">
-        <v>45624</v>
+        <v>45626</v>
       </c>
       <c r="C168" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>5</v>
@@ -2772,10 +2772,10 @@
         <v>4</v>
       </c>
       <c r="B169" s="2">
-        <v>45624</v>
+        <v>45626</v>
       </c>
       <c r="C169" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>5</v>
@@ -2786,10 +2786,10 @@
         <v>4</v>
       </c>
       <c r="B170" s="2">
-        <v>45625</v>
+        <v>45626</v>
       </c>
       <c r="C170" s="2">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>5</v>
@@ -2800,13 +2800,13 @@
         <v>4</v>
       </c>
       <c r="B171" s="2">
-        <v>45625</v>
+        <v>45627</v>
       </c>
       <c r="C171" s="2">
-        <v>159</v>
+        <v>1</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -2814,13 +2814,13 @@
         <v>4</v>
       </c>
       <c r="B172" s="2">
-        <v>45625</v>
+        <v>45627</v>
       </c>
       <c r="C172" s="2">
-        <v>132</v>
+        <v>7</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -2828,13 +2828,13 @@
         <v>4</v>
       </c>
       <c r="B173" s="2">
-        <v>45625</v>
+        <v>45628</v>
       </c>
       <c r="C173" s="2">
-        <v>4</v>
+        <v>337</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -2842,10 +2842,10 @@
         <v>4</v>
       </c>
       <c r="B174" s="2">
-        <v>45626</v>
+        <v>45629</v>
       </c>
       <c r="C174" s="2">
-        <v>98</v>
+        <v>5</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>5</v>
@@ -2856,13 +2856,13 @@
         <v>4</v>
       </c>
       <c r="B175" s="2">
-        <v>45628</v>
+        <v>45630</v>
       </c>
       <c r="C175" s="2">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -2870,13 +2870,13 @@
         <v>4</v>
       </c>
       <c r="B176" s="2">
-        <v>45629</v>
+        <v>45631</v>
       </c>
       <c r="C176" s="2">
-        <v>99</v>
+        <v>16</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -2884,10 +2884,10 @@
         <v>4</v>
       </c>
       <c r="B177" s="2">
-        <v>45629</v>
+        <v>45631</v>
       </c>
       <c r="C177" s="2">
-        <v>368</v>
+        <v>417</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>5</v>
@@ -2898,13 +2898,13 @@
         <v>4</v>
       </c>
       <c r="B178" s="2">
-        <v>45631</v>
+        <v>45632</v>
       </c>
       <c r="C178" s="2">
-        <v>2</v>
+        <v>114</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -2915,7 +2915,7 @@
         <v>45632</v>
       </c>
       <c r="C179" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>5</v>
@@ -2926,10 +2926,10 @@
         <v>4</v>
       </c>
       <c r="B180" s="2">
-        <v>45632</v>
+        <v>45633</v>
       </c>
       <c r="C180" s="2">
-        <v>580</v>
+        <v>2</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>5</v>
@@ -2940,13 +2940,13 @@
         <v>4</v>
       </c>
       <c r="B181" s="2">
-        <v>45635</v>
+        <v>45634</v>
       </c>
       <c r="C181" s="2">
-        <v>360</v>
+        <v>59</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -2954,10 +2954,10 @@
         <v>4</v>
       </c>
       <c r="B182" s="2">
-        <v>45635</v>
+        <v>45634</v>
       </c>
       <c r="C182" s="2">
-        <v>10</v>
+        <v>1260</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>5</v>
@@ -2968,10 +2968,10 @@
         <v>4</v>
       </c>
       <c r="B183" s="2">
-        <v>45604</v>
+        <v>45635</v>
       </c>
       <c r="C183" s="2">
-        <v>3</v>
+        <v>84</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>5</v>
@@ -2982,10 +2982,10 @@
         <v>4</v>
       </c>
       <c r="B184" s="2">
-        <v>45605</v>
+        <v>45635</v>
       </c>
       <c r="C184" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>5</v>
@@ -2996,13 +2996,13 @@
         <v>4</v>
       </c>
       <c r="B185" s="2">
-        <v>45606</v>
+        <v>45636</v>
       </c>
       <c r="C185" s="2">
-        <v>127</v>
+        <v>3</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -3010,13 +3010,13 @@
         <v>4</v>
       </c>
       <c r="B186" s="2">
-        <v>45612</v>
+        <v>45611</v>
       </c>
       <c r="C186" s="2">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -3024,10 +3024,10 @@
         <v>4</v>
       </c>
       <c r="B187" s="2">
-        <v>45613</v>
+        <v>45612</v>
       </c>
       <c r="C187" s="2">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>5</v>
@@ -3038,13 +3038,13 @@
         <v>4</v>
       </c>
       <c r="B188" s="2">
-        <v>45615</v>
+        <v>45613</v>
       </c>
       <c r="C188" s="2">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3052,13 +3052,13 @@
         <v>4</v>
       </c>
       <c r="B189" s="2">
-        <v>45615</v>
+        <v>45614</v>
       </c>
       <c r="C189" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3066,10 +3066,10 @@
         <v>4</v>
       </c>
       <c r="B190" s="2">
-        <v>45616</v>
+        <v>45614</v>
       </c>
       <c r="C190" s="2">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>5</v>
@@ -3080,10 +3080,10 @@
         <v>4</v>
       </c>
       <c r="B191" s="2">
-        <v>45619</v>
+        <v>45614</v>
       </c>
       <c r="C191" s="2">
-        <v>623</v>
+        <v>1</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>5</v>
@@ -3094,10 +3094,10 @@
         <v>4</v>
       </c>
       <c r="B192" s="2">
-        <v>45619</v>
+        <v>45615</v>
       </c>
       <c r="C192" s="2">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>5</v>
@@ -3108,10 +3108,10 @@
         <v>4</v>
       </c>
       <c r="B193" s="2">
-        <v>45621</v>
+        <v>45616</v>
       </c>
       <c r="C193" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>5</v>
@@ -3122,13 +3122,13 @@
         <v>4</v>
       </c>
       <c r="B194" s="2">
-        <v>45622</v>
+        <v>45617</v>
       </c>
       <c r="C194" s="2">
-        <v>454</v>
+        <v>10</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3136,13 +3136,13 @@
         <v>4</v>
       </c>
       <c r="B195" s="2">
-        <v>45622</v>
+        <v>45618</v>
       </c>
       <c r="C195" s="2">
-        <v>284</v>
+        <v>77</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3150,7 +3150,7 @@
         <v>4</v>
       </c>
       <c r="B196" s="2">
-        <v>45622</v>
+        <v>45620</v>
       </c>
       <c r="C196" s="2">
         <v>3</v>
@@ -3164,13 +3164,13 @@
         <v>4</v>
       </c>
       <c r="B197" s="2">
-        <v>45624</v>
+        <v>45620</v>
       </c>
       <c r="C197" s="2">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3178,13 +3178,13 @@
         <v>4</v>
       </c>
       <c r="B198" s="2">
-        <v>45625</v>
+        <v>45620</v>
       </c>
       <c r="C198" s="2">
-        <v>426</v>
+        <v>3</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3192,10 +3192,10 @@
         <v>4</v>
       </c>
       <c r="B199" s="2">
-        <v>45625</v>
+        <v>45621</v>
       </c>
       <c r="C199" s="2">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>5</v>
@@ -3206,10 +3206,10 @@
         <v>4</v>
       </c>
       <c r="B200" s="2">
-        <v>45625</v>
+        <v>45623</v>
       </c>
       <c r="C200" s="2">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>5</v>
@@ -3220,13 +3220,13 @@
         <v>4</v>
       </c>
       <c r="B201" s="2">
-        <v>45627</v>
+        <v>45623</v>
       </c>
       <c r="C201" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3234,13 +3234,13 @@
         <v>4</v>
       </c>
       <c r="B202" s="2">
-        <v>45628</v>
+        <v>45624</v>
       </c>
       <c r="C202" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3248,13 +3248,13 @@
         <v>4</v>
       </c>
       <c r="B203" s="2">
-        <v>45628</v>
+        <v>45626</v>
       </c>
       <c r="C203" s="2">
-        <v>85</v>
+        <v>7</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -3262,10 +3262,10 @@
         <v>4</v>
       </c>
       <c r="B204" s="2">
-        <v>45628</v>
+        <v>45627</v>
       </c>
       <c r="C204" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>5</v>
@@ -3276,7 +3276,7 @@
         <v>4</v>
       </c>
       <c r="B205" s="2">
-        <v>45631</v>
+        <v>45627</v>
       </c>
       <c r="C205" s="2">
         <v>1</v>
@@ -3290,13 +3290,13 @@
         <v>4</v>
       </c>
       <c r="B206" s="2">
-        <v>45631</v>
+        <v>45627</v>
       </c>
       <c r="C206" s="2">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -3304,13 +3304,13 @@
         <v>4</v>
       </c>
       <c r="B207" s="2">
-        <v>45634</v>
+        <v>45630</v>
       </c>
       <c r="C207" s="2">
-        <v>3</v>
+        <v>90</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -3318,13 +3318,13 @@
         <v>4</v>
       </c>
       <c r="B208" s="2">
-        <v>45634</v>
+        <v>45633</v>
       </c>
       <c r="C208" s="2">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -3332,13 +3332,13 @@
         <v>4</v>
       </c>
       <c r="B209" s="2">
-        <v>45635</v>
+        <v>45633</v>
       </c>
       <c r="C209" s="2">
-        <v>25</v>
+        <v>295</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -3346,10 +3346,10 @@
         <v>4</v>
       </c>
       <c r="B210" s="2">
-        <v>45612</v>
+        <v>45635</v>
       </c>
       <c r="C210" s="2">
-        <v>987</v>
+        <v>2</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>5</v>
@@ -3360,13 +3360,13 @@
         <v>4</v>
       </c>
       <c r="B211" s="2">
-        <v>45613</v>
+        <v>45636</v>
       </c>
       <c r="C211" s="2">
-        <v>7</v>
+        <v>135</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -3374,10 +3374,10 @@
         <v>4</v>
       </c>
       <c r="B212" s="2">
-        <v>45614</v>
+        <v>45605</v>
       </c>
       <c r="C212" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>5</v>
@@ -3388,10 +3388,10 @@
         <v>4</v>
       </c>
       <c r="B213" s="2">
-        <v>45615</v>
+        <v>45606</v>
       </c>
       <c r="C213" s="2">
-        <v>167</v>
+        <v>499</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>5</v>
@@ -3402,13 +3402,13 @@
         <v>4</v>
       </c>
       <c r="B214" s="2">
-        <v>45616</v>
+        <v>45606</v>
       </c>
       <c r="C214" s="2">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -3416,10 +3416,10 @@
         <v>4</v>
       </c>
       <c r="B215" s="2">
-        <v>45616</v>
+        <v>45606</v>
       </c>
       <c r="C215" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>5</v>
@@ -3430,13 +3430,13 @@
         <v>4</v>
       </c>
       <c r="B216" s="2">
-        <v>45617</v>
+        <v>45612</v>
       </c>
       <c r="C216" s="2">
-        <v>1</v>
+        <v>222</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -3444,13 +3444,13 @@
         <v>4</v>
       </c>
       <c r="B217" s="2">
-        <v>45618</v>
+        <v>45612</v>
       </c>
       <c r="C217" s="2">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -3458,10 +3458,10 @@
         <v>4</v>
       </c>
       <c r="B218" s="2">
-        <v>45618</v>
+        <v>45614</v>
       </c>
       <c r="C218" s="2">
-        <v>343</v>
+        <v>3</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>5</v>
@@ -3472,10 +3472,10 @@
         <v>4</v>
       </c>
       <c r="B219" s="2">
-        <v>45619</v>
+        <v>45615</v>
       </c>
       <c r="C219" s="2">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>5</v>
@@ -3486,13 +3486,13 @@
         <v>4</v>
       </c>
       <c r="B220" s="2">
-        <v>45620</v>
+        <v>45615</v>
       </c>
       <c r="C220" s="2">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -3500,10 +3500,10 @@
         <v>4</v>
       </c>
       <c r="B221" s="2">
-        <v>45620</v>
+        <v>45615</v>
       </c>
       <c r="C221" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>5</v>
@@ -3514,13 +3514,13 @@
         <v>4</v>
       </c>
       <c r="B222" s="2">
-        <v>45621</v>
+        <v>45618</v>
       </c>
       <c r="C222" s="2">
-        <v>78</v>
+        <v>2</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -3528,13 +3528,13 @@
         <v>4</v>
       </c>
       <c r="B223" s="2">
-        <v>45622</v>
+        <v>45619</v>
       </c>
       <c r="C223" s="2">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -3542,10 +3542,10 @@
         <v>4</v>
       </c>
       <c r="B224" s="2">
-        <v>45624</v>
+        <v>45620</v>
       </c>
       <c r="C224" s="2">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>5</v>
@@ -3556,13 +3556,13 @@
         <v>4</v>
       </c>
       <c r="B225" s="2">
-        <v>45624</v>
+        <v>45621</v>
       </c>
       <c r="C225" s="2">
-        <v>113</v>
+        <v>1</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -3570,13 +3570,13 @@
         <v>4</v>
       </c>
       <c r="B226" s="2">
-        <v>45624</v>
+        <v>45621</v>
       </c>
       <c r="C226" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -3584,10 +3584,10 @@
         <v>4</v>
       </c>
       <c r="B227" s="2">
-        <v>45625</v>
+        <v>45622</v>
       </c>
       <c r="C227" s="2">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>5</v>
@@ -3598,13 +3598,13 @@
         <v>4</v>
       </c>
       <c r="B228" s="2">
-        <v>45626</v>
+        <v>45622</v>
       </c>
       <c r="C228" s="2">
-        <v>410</v>
+        <v>88</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -3612,10 +3612,10 @@
         <v>4</v>
       </c>
       <c r="B229" s="2">
-        <v>45627</v>
+        <v>45623</v>
       </c>
       <c r="C229" s="2">
-        <v>3</v>
+        <v>124</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>5</v>
@@ -3626,13 +3626,13 @@
         <v>4</v>
       </c>
       <c r="B230" s="2">
-        <v>45629</v>
+        <v>45624</v>
       </c>
       <c r="C230" s="2">
-        <v>85</v>
+        <v>3</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -3640,13 +3640,13 @@
         <v>4</v>
       </c>
       <c r="B231" s="2">
-        <v>45632</v>
+        <v>45624</v>
       </c>
       <c r="C231" s="2">
-        <v>113</v>
+        <v>1</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -3654,10 +3654,10 @@
         <v>4</v>
       </c>
       <c r="B232" s="2">
-        <v>45633</v>
+        <v>45625</v>
       </c>
       <c r="C232" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D232" s="2" t="s">
         <v>5</v>
@@ -3668,13 +3668,13 @@
         <v>4</v>
       </c>
       <c r="B233" s="2">
-        <v>45633</v>
+        <v>45625</v>
       </c>
       <c r="C233" s="2">
-        <v>2</v>
+        <v>159</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -3682,13 +3682,13 @@
         <v>4</v>
       </c>
       <c r="B234" s="2">
-        <v>45634</v>
+        <v>45625</v>
       </c>
       <c r="C234" s="2">
-        <v>1</v>
+        <v>132</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -3696,13 +3696,13 @@
         <v>4</v>
       </c>
       <c r="B235" s="2">
-        <v>45634</v>
+        <v>45625</v>
       </c>
       <c r="C235" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -3710,13 +3710,13 @@
         <v>4</v>
       </c>
       <c r="B236" s="2">
-        <v>45634</v>
+        <v>45626</v>
       </c>
       <c r="C236" s="2">
-        <v>160</v>
+        <v>98</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -3724,13 +3724,111 @@
         <v>4</v>
       </c>
       <c r="B237" s="2">
+        <v>45628</v>
+      </c>
+      <c r="C237" s="2">
+        <v>15</v>
+      </c>
+      <c r="D237" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="A238" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B238" s="2">
+        <v>45629</v>
+      </c>
+      <c r="C238" s="2">
+        <v>99</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B239" s="2">
+        <v>45629</v>
+      </c>
+      <c r="C239" s="2">
+        <v>368</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="A240" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B240" s="2">
+        <v>45631</v>
+      </c>
+      <c r="C240" s="2">
+        <v>2</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
+      <c r="A241" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B241" s="2">
+        <v>45632</v>
+      </c>
+      <c r="C241" s="2">
+        <v>1</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
+      <c r="A242" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B242" s="2">
+        <v>45632</v>
+      </c>
+      <c r="C242" s="2">
+        <v>580</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
+      <c r="A243" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B243" s="2">
         <v>45635</v>
       </c>
-      <c r="C237" s="2">
-        <v>135</v>
-      </c>
-      <c r="D237" s="2" t="s">
-        <v>6</v>
+      <c r="C243" s="2">
+        <v>360</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
+      <c r="A244" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B244" s="2">
+        <v>45635</v>
+      </c>
+      <c r="C244" s="2">
+        <v>10</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/reports/For Winter Ending (Prior Year)_Visits.xlsx
+++ b/reports/For Winter Ending (Prior Year)_Visits.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="9">
   <si>
     <t>Resort</t>
   </si>
@@ -28,22 +28,19 @@
     <t>Location</t>
   </si>
   <si>
-    <t>Purgatory</t>
+    <t>Snowbowl</t>
   </si>
   <si>
-    <t>Purgatory Passes</t>
+    <t>Snowbowl Passes</t>
   </si>
   <si>
-    <t>Purgatory Tickets</t>
+    <t>Snowbowl Uplift Tickets</t>
   </si>
   <si>
-    <t>Purgatory Coaster</t>
+    <t>Snowbowl Comp Tickets</t>
   </si>
   <si>
-    <t>Purgatory Comp Tickets</t>
-  </si>
-  <si>
-    <t>Purgatory Uplift Tickets</t>
+    <t>Snowbowl Tickets</t>
   </si>
 </sst>
 </file>
@@ -406,13 +403,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D244"/>
+  <dimension ref="A1:D246"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -434,10 +431,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>45601</v>
+        <v>45604</v>
       </c>
       <c r="C2" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -448,10 +445,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>45604</v>
+        <v>45605</v>
       </c>
       <c r="C3" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>5</v>
@@ -465,10 +462,10 @@
         <v>45605</v>
       </c>
       <c r="C4" s="2">
-        <v>164</v>
+        <v>512</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -476,10 +473,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>45605</v>
+        <v>45607</v>
       </c>
       <c r="C5" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>5</v>
@@ -490,13 +487,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>45612</v>
+        <v>45607</v>
       </c>
       <c r="C6" s="2">
-        <v>5</v>
+        <v>103</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -504,10 +501,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="2">
-        <v>45613</v>
+        <v>45608</v>
       </c>
       <c r="C7" s="2">
-        <v>769</v>
+        <v>235</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>5</v>
@@ -518,10 +515,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>45615</v>
+        <v>45611</v>
       </c>
       <c r="C8" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>5</v>
@@ -532,13 +529,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>45618</v>
+        <v>45612</v>
       </c>
       <c r="C9" s="2">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -546,13 +543,13 @@
         <v>4</v>
       </c>
       <c r="B10" s="2">
-        <v>45619</v>
+        <v>45615</v>
       </c>
       <c r="C10" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -560,13 +557,13 @@
         <v>4</v>
       </c>
       <c r="B11" s="2">
-        <v>45619</v>
+        <v>45618</v>
       </c>
       <c r="C11" s="2">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -574,7 +571,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="2">
-        <v>45619</v>
+        <v>45621</v>
       </c>
       <c r="C12" s="2">
         <v>2</v>
@@ -588,10 +585,10 @@
         <v>4</v>
       </c>
       <c r="B13" s="2">
-        <v>45620</v>
+        <v>45621</v>
       </c>
       <c r="C13" s="2">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>7</v>
@@ -602,10 +599,10 @@
         <v>4</v>
       </c>
       <c r="B14" s="2">
-        <v>45622</v>
+        <v>45623</v>
       </c>
       <c r="C14" s="2">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>5</v>
@@ -616,10 +613,10 @@
         <v>4</v>
       </c>
       <c r="B15" s="2">
-        <v>45623</v>
+        <v>45624</v>
       </c>
       <c r="C15" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>5</v>
@@ -630,10 +627,10 @@
         <v>4</v>
       </c>
       <c r="B16" s="2">
-        <v>45623</v>
+        <v>45624</v>
       </c>
       <c r="C16" s="2">
-        <v>125</v>
+        <v>824</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>8</v>
@@ -644,10 +641,10 @@
         <v>4</v>
       </c>
       <c r="B17" s="2">
-        <v>45624</v>
+        <v>45626</v>
       </c>
       <c r="C17" s="2">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>5</v>
@@ -658,10 +655,10 @@
         <v>4</v>
       </c>
       <c r="B18" s="2">
-        <v>45625</v>
+        <v>45626</v>
       </c>
       <c r="C18" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>5</v>
@@ -672,13 +669,13 @@
         <v>4</v>
       </c>
       <c r="B19" s="2">
-        <v>45625</v>
+        <v>45627</v>
       </c>
       <c r="C19" s="2">
-        <v>4</v>
+        <v>786</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -686,13 +683,13 @@
         <v>4</v>
       </c>
       <c r="B20" s="2">
-        <v>45626</v>
+        <v>45627</v>
       </c>
       <c r="C20" s="2">
-        <v>1</v>
+        <v>160</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -700,13 +697,13 @@
         <v>4</v>
       </c>
       <c r="B21" s="2">
-        <v>45626</v>
+        <v>45628</v>
       </c>
       <c r="C21" s="2">
-        <v>297</v>
+        <v>1</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -714,13 +711,13 @@
         <v>4</v>
       </c>
       <c r="B22" s="2">
-        <v>45626</v>
+        <v>45629</v>
       </c>
       <c r="C22" s="2">
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -728,13 +725,13 @@
         <v>4</v>
       </c>
       <c r="B23" s="2">
-        <v>45627</v>
+        <v>45630</v>
       </c>
       <c r="C23" s="2">
-        <v>114</v>
+        <v>485</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -742,13 +739,13 @@
         <v>4</v>
       </c>
       <c r="B24" s="2">
-        <v>45628</v>
+        <v>45630</v>
       </c>
       <c r="C24" s="2">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -756,13 +753,13 @@
         <v>4</v>
       </c>
       <c r="B25" s="2">
-        <v>45629</v>
+        <v>45631</v>
       </c>
       <c r="C25" s="2">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -770,13 +767,13 @@
         <v>4</v>
       </c>
       <c r="B26" s="2">
-        <v>45629</v>
+        <v>45633</v>
       </c>
       <c r="C26" s="2">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -784,13 +781,13 @@
         <v>4</v>
       </c>
       <c r="B27" s="2">
-        <v>45630</v>
+        <v>45633</v>
       </c>
       <c r="C27" s="2">
-        <v>117</v>
+        <v>1404</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -798,13 +795,13 @@
         <v>4</v>
       </c>
       <c r="B28" s="2">
-        <v>45631</v>
+        <v>45633</v>
       </c>
       <c r="C28" s="2">
-        <v>7</v>
+        <v>118</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -812,13 +809,13 @@
         <v>4</v>
       </c>
       <c r="B29" s="2">
-        <v>45632</v>
+        <v>45634</v>
       </c>
       <c r="C29" s="2">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -826,10 +823,10 @@
         <v>4</v>
       </c>
       <c r="B30" s="2">
-        <v>45633</v>
+        <v>45634</v>
       </c>
       <c r="C30" s="2">
-        <v>149</v>
+        <v>854</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>5</v>
@@ -840,10 +837,10 @@
         <v>4</v>
       </c>
       <c r="B31" s="2">
-        <v>45633</v>
+        <v>45636</v>
       </c>
       <c r="C31" s="2">
-        <v>1558</v>
+        <v>2</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>5</v>
@@ -854,10 +851,10 @@
         <v>4</v>
       </c>
       <c r="B32" s="2">
-        <v>45634</v>
+        <v>45636</v>
       </c>
       <c r="C32" s="2">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>6</v>
@@ -868,10 +865,10 @@
         <v>4</v>
       </c>
       <c r="B33" s="2">
-        <v>45634</v>
+        <v>45604</v>
       </c>
       <c r="C33" s="2">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>5</v>
@@ -882,10 +879,10 @@
         <v>4</v>
       </c>
       <c r="B34" s="2">
-        <v>45636</v>
+        <v>45604</v>
       </c>
       <c r="C34" s="2">
-        <v>397</v>
+        <v>789</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>5</v>
@@ -896,13 +893,13 @@
         <v>4</v>
       </c>
       <c r="B35" s="2">
-        <v>45612</v>
+        <v>45605</v>
       </c>
       <c r="C35" s="2">
-        <v>987</v>
+        <v>237</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -910,10 +907,10 @@
         <v>4</v>
       </c>
       <c r="B36" s="2">
-        <v>45613</v>
+        <v>45606</v>
       </c>
       <c r="C36" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>5</v>
@@ -924,10 +921,10 @@
         <v>4</v>
       </c>
       <c r="B37" s="2">
-        <v>45614</v>
+        <v>45607</v>
       </c>
       <c r="C37" s="2">
-        <v>4</v>
+        <v>904</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>5</v>
@@ -938,10 +935,10 @@
         <v>4</v>
       </c>
       <c r="B38" s="2">
-        <v>45615</v>
+        <v>45609</v>
       </c>
       <c r="C38" s="2">
-        <v>167</v>
+        <v>1</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>5</v>
@@ -955,10 +952,10 @@
         <v>45616</v>
       </c>
       <c r="C39" s="2">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -966,13 +963,13 @@
         <v>4</v>
       </c>
       <c r="B40" s="2">
-        <v>45616</v>
+        <v>45619</v>
       </c>
       <c r="C40" s="2">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -980,7 +977,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="2">
-        <v>45617</v>
+        <v>45622</v>
       </c>
       <c r="C41" s="2">
         <v>1</v>
@@ -994,13 +991,13 @@
         <v>4</v>
       </c>
       <c r="B42" s="2">
-        <v>45618</v>
+        <v>45622</v>
       </c>
       <c r="C42" s="2">
-        <v>42</v>
+        <v>131</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1008,13 +1005,13 @@
         <v>4</v>
       </c>
       <c r="B43" s="2">
-        <v>45618</v>
+        <v>45623</v>
       </c>
       <c r="C43" s="2">
-        <v>343</v>
+        <v>61</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1022,10 +1019,10 @@
         <v>4</v>
       </c>
       <c r="B44" s="2">
-        <v>45619</v>
+        <v>45625</v>
       </c>
       <c r="C44" s="2">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>5</v>
@@ -1036,13 +1033,13 @@
         <v>4</v>
       </c>
       <c r="B45" s="2">
-        <v>45620</v>
+        <v>45625</v>
       </c>
       <c r="C45" s="2">
-        <v>2</v>
+        <v>162</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1050,10 +1047,10 @@
         <v>4</v>
       </c>
       <c r="B46" s="2">
-        <v>45620</v>
+        <v>45625</v>
       </c>
       <c r="C46" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>5</v>
@@ -1064,13 +1061,13 @@
         <v>4</v>
       </c>
       <c r="B47" s="2">
-        <v>45621</v>
+        <v>45626</v>
       </c>
       <c r="C47" s="2">
-        <v>78</v>
+        <v>302</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1078,10 +1075,10 @@
         <v>4</v>
       </c>
       <c r="B48" s="2">
-        <v>45622</v>
+        <v>45627</v>
       </c>
       <c r="C48" s="2">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>5</v>
@@ -1092,7 +1089,7 @@
         <v>4</v>
       </c>
       <c r="B49" s="2">
-        <v>45624</v>
+        <v>45628</v>
       </c>
       <c r="C49" s="2">
         <v>6</v>
@@ -1106,10 +1103,10 @@
         <v>4</v>
       </c>
       <c r="B50" s="2">
-        <v>45624</v>
+        <v>45628</v>
       </c>
       <c r="C50" s="2">
-        <v>113</v>
+        <v>476</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>8</v>
@@ -1120,13 +1117,13 @@
         <v>4</v>
       </c>
       <c r="B51" s="2">
-        <v>45624</v>
+        <v>45629</v>
       </c>
       <c r="C51" s="2">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1134,10 +1131,10 @@
         <v>4</v>
       </c>
       <c r="B52" s="2">
-        <v>45625</v>
+        <v>45630</v>
       </c>
       <c r="C52" s="2">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>5</v>
@@ -1148,13 +1145,13 @@
         <v>4</v>
       </c>
       <c r="B53" s="2">
-        <v>45626</v>
+        <v>45630</v>
       </c>
       <c r="C53" s="2">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1162,13 +1159,13 @@
         <v>4</v>
       </c>
       <c r="B54" s="2">
-        <v>45627</v>
+        <v>45631</v>
       </c>
       <c r="C54" s="2">
-        <v>3</v>
+        <v>383</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1176,13 +1173,13 @@
         <v>4</v>
       </c>
       <c r="B55" s="2">
-        <v>45629</v>
+        <v>45632</v>
       </c>
       <c r="C55" s="2">
-        <v>85</v>
+        <v>7</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1193,7 +1190,7 @@
         <v>45632</v>
       </c>
       <c r="C56" s="2">
-        <v>113</v>
+        <v>50</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>6</v>
@@ -1207,7 +1204,7 @@
         <v>45633</v>
       </c>
       <c r="C57" s="2">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>5</v>
@@ -1221,7 +1218,7 @@
         <v>45633</v>
       </c>
       <c r="C58" s="2">
-        <v>2</v>
+        <v>881</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>5</v>
@@ -1235,7 +1232,7 @@
         <v>45634</v>
       </c>
       <c r="C59" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>5</v>
@@ -1249,10 +1246,10 @@
         <v>45634</v>
       </c>
       <c r="C60" s="2">
-        <v>1</v>
+        <v>945</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1260,13 +1257,13 @@
         <v>4</v>
       </c>
       <c r="B61" s="2">
-        <v>45634</v>
+        <v>45635</v>
       </c>
       <c r="C61" s="2">
-        <v>160</v>
+        <v>5</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1274,13 +1271,13 @@
         <v>4</v>
       </c>
       <c r="B62" s="2">
-        <v>45635</v>
+        <v>45636</v>
       </c>
       <c r="C62" s="2">
-        <v>135</v>
+        <v>338</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1288,10 +1285,10 @@
         <v>4</v>
       </c>
       <c r="B63" s="2">
-        <v>45604</v>
+        <v>45597</v>
       </c>
       <c r="C63" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>5</v>
@@ -1302,13 +1299,13 @@
         <v>4</v>
       </c>
       <c r="B64" s="2">
-        <v>45605</v>
+        <v>45604</v>
       </c>
       <c r="C64" s="2">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1319,10 +1316,10 @@
         <v>45606</v>
       </c>
       <c r="C65" s="2">
-        <v>127</v>
+        <v>3</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1330,13 +1327,13 @@
         <v>4</v>
       </c>
       <c r="B66" s="2">
-        <v>45612</v>
+        <v>45606</v>
       </c>
       <c r="C66" s="2">
-        <v>47</v>
+        <v>549</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1344,13 +1341,13 @@
         <v>4</v>
       </c>
       <c r="B67" s="2">
-        <v>45613</v>
+        <v>45606</v>
       </c>
       <c r="C67" s="2">
-        <v>100</v>
+        <v>290</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1358,13 +1355,13 @@
         <v>4</v>
       </c>
       <c r="B68" s="2">
-        <v>45615</v>
+        <v>45607</v>
       </c>
       <c r="C68" s="2">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1372,13 +1369,13 @@
         <v>4</v>
       </c>
       <c r="B69" s="2">
-        <v>45615</v>
+        <v>45609</v>
       </c>
       <c r="C69" s="2">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1386,13 +1383,13 @@
         <v>4</v>
       </c>
       <c r="B70" s="2">
-        <v>45616</v>
+        <v>45610</v>
       </c>
       <c r="C70" s="2">
-        <v>181</v>
+        <v>8</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1400,10 +1397,10 @@
         <v>4</v>
       </c>
       <c r="B71" s="2">
-        <v>45619</v>
+        <v>45612</v>
       </c>
       <c r="C71" s="2">
-        <v>623</v>
+        <v>1</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>5</v>
@@ -1414,10 +1411,10 @@
         <v>4</v>
       </c>
       <c r="B72" s="2">
-        <v>45619</v>
+        <v>45613</v>
       </c>
       <c r="C72" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>5</v>
@@ -1428,13 +1425,13 @@
         <v>4</v>
       </c>
       <c r="B73" s="2">
-        <v>45621</v>
+        <v>45613</v>
       </c>
       <c r="C73" s="2">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1442,10 +1439,10 @@
         <v>4</v>
       </c>
       <c r="B74" s="2">
-        <v>45622</v>
+        <v>45615</v>
       </c>
       <c r="C74" s="2">
-        <v>454</v>
+        <v>3</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>5</v>
@@ -1456,13 +1453,13 @@
         <v>4</v>
       </c>
       <c r="B75" s="2">
-        <v>45622</v>
+        <v>45615</v>
       </c>
       <c r="C75" s="2">
-        <v>284</v>
+        <v>24</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1470,10 +1467,10 @@
         <v>4</v>
       </c>
       <c r="B76" s="2">
-        <v>45622</v>
+        <v>45618</v>
       </c>
       <c r="C76" s="2">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>5</v>
@@ -1484,10 +1481,10 @@
         <v>4</v>
       </c>
       <c r="B77" s="2">
-        <v>45624</v>
+        <v>45619</v>
       </c>
       <c r="C77" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>5</v>
@@ -1498,10 +1495,10 @@
         <v>4</v>
       </c>
       <c r="B78" s="2">
-        <v>45625</v>
+        <v>45619</v>
       </c>
       <c r="C78" s="2">
-        <v>426</v>
+        <v>163</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>6</v>
@@ -1512,10 +1509,10 @@
         <v>4</v>
       </c>
       <c r="B79" s="2">
-        <v>45625</v>
+        <v>45620</v>
       </c>
       <c r="C79" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>5</v>
@@ -1526,10 +1523,10 @@
         <v>4</v>
       </c>
       <c r="B80" s="2">
-        <v>45625</v>
+        <v>45621</v>
       </c>
       <c r="C80" s="2">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>5</v>
@@ -1540,13 +1537,13 @@
         <v>4</v>
       </c>
       <c r="B81" s="2">
-        <v>45627</v>
+        <v>45622</v>
       </c>
       <c r="C81" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -1554,10 +1551,10 @@
         <v>4</v>
       </c>
       <c r="B82" s="2">
-        <v>45628</v>
+        <v>45623</v>
       </c>
       <c r="C82" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>5</v>
@@ -1568,13 +1565,13 @@
         <v>4</v>
       </c>
       <c r="B83" s="2">
-        <v>45628</v>
+        <v>45624</v>
       </c>
       <c r="C83" s="2">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -1582,13 +1579,13 @@
         <v>4</v>
       </c>
       <c r="B84" s="2">
-        <v>45628</v>
+        <v>45625</v>
       </c>
       <c r="C84" s="2">
-        <v>8</v>
+        <v>305</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -1596,10 +1593,10 @@
         <v>4</v>
       </c>
       <c r="B85" s="2">
-        <v>45631</v>
+        <v>45626</v>
       </c>
       <c r="C85" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>5</v>
@@ -1610,13 +1607,13 @@
         <v>4</v>
       </c>
       <c r="B86" s="2">
-        <v>45631</v>
+        <v>45626</v>
       </c>
       <c r="C86" s="2">
-        <v>89</v>
+        <v>757</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -1624,13 +1621,13 @@
         <v>4</v>
       </c>
       <c r="B87" s="2">
-        <v>45634</v>
+        <v>45628</v>
       </c>
       <c r="C87" s="2">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -1638,10 +1635,10 @@
         <v>4</v>
       </c>
       <c r="B88" s="2">
-        <v>45634</v>
+        <v>45629</v>
       </c>
       <c r="C88" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>5</v>
@@ -1652,13 +1649,13 @@
         <v>4</v>
       </c>
       <c r="B89" s="2">
-        <v>45635</v>
+        <v>45629</v>
       </c>
       <c r="C89" s="2">
-        <v>25</v>
+        <v>384</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1666,10 +1663,10 @@
         <v>4</v>
       </c>
       <c r="B90" s="2">
-        <v>45636</v>
+        <v>45632</v>
       </c>
       <c r="C90" s="2">
-        <v>98</v>
+        <v>893</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>5</v>
@@ -1680,13 +1677,13 @@
         <v>4</v>
       </c>
       <c r="B91" s="2">
-        <v>45606</v>
+        <v>45632</v>
       </c>
       <c r="C91" s="2">
-        <v>5</v>
+        <v>711</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -1694,10 +1691,10 @@
         <v>4</v>
       </c>
       <c r="B92" s="2">
-        <v>45610</v>
+        <v>45633</v>
       </c>
       <c r="C92" s="2">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>7</v>
@@ -1708,13 +1705,13 @@
         <v>4</v>
       </c>
       <c r="B93" s="2">
-        <v>45610</v>
+        <v>45635</v>
       </c>
       <c r="C93" s="2">
-        <v>6</v>
+        <v>504</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -1722,13 +1719,13 @@
         <v>4</v>
       </c>
       <c r="B94" s="2">
-        <v>45612</v>
+        <v>45635</v>
       </c>
       <c r="C94" s="2">
-        <v>5</v>
+        <v>735</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -1736,13 +1733,13 @@
         <v>4</v>
       </c>
       <c r="B95" s="2">
-        <v>45612</v>
+        <v>45636</v>
       </c>
       <c r="C95" s="2">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -1750,13 +1747,13 @@
         <v>4</v>
       </c>
       <c r="B96" s="2">
-        <v>45613</v>
+        <v>45604</v>
       </c>
       <c r="C96" s="2">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -1764,10 +1761,10 @@
         <v>4</v>
       </c>
       <c r="B97" s="2">
-        <v>45614</v>
+        <v>45604</v>
       </c>
       <c r="C97" s="2">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>5</v>
@@ -1778,10 +1775,10 @@
         <v>4</v>
       </c>
       <c r="B98" s="2">
-        <v>45616</v>
+        <v>45604</v>
       </c>
       <c r="C98" s="2">
-        <v>15</v>
+        <v>139</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>8</v>
@@ -1792,13 +1789,13 @@
         <v>4</v>
       </c>
       <c r="B99" s="2">
-        <v>45616</v>
+        <v>45607</v>
       </c>
       <c r="C99" s="2">
-        <v>4</v>
+        <v>473</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -1806,13 +1803,13 @@
         <v>4</v>
       </c>
       <c r="B100" s="2">
-        <v>45617</v>
+        <v>45608</v>
       </c>
       <c r="C100" s="2">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -1820,13 +1817,13 @@
         <v>4</v>
       </c>
       <c r="B101" s="2">
-        <v>45617</v>
+        <v>45610</v>
       </c>
       <c r="C101" s="2">
-        <v>234</v>
+        <v>120</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -1834,13 +1831,13 @@
         <v>4</v>
       </c>
       <c r="B102" s="2">
-        <v>45618</v>
+        <v>45611</v>
       </c>
       <c r="C102" s="2">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -1848,10 +1845,10 @@
         <v>4</v>
       </c>
       <c r="B103" s="2">
-        <v>45619</v>
+        <v>45613</v>
       </c>
       <c r="C103" s="2">
-        <v>44</v>
+        <v>468</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>8</v>
@@ -1862,13 +1859,13 @@
         <v>4</v>
       </c>
       <c r="B104" s="2">
-        <v>45620</v>
+        <v>45614</v>
       </c>
       <c r="C104" s="2">
-        <v>541</v>
+        <v>18</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -1876,13 +1873,13 @@
         <v>4</v>
       </c>
       <c r="B105" s="2">
-        <v>45621</v>
+        <v>45616</v>
       </c>
       <c r="C105" s="2">
-        <v>224</v>
+        <v>3</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -1890,13 +1887,13 @@
         <v>4</v>
       </c>
       <c r="B106" s="2">
-        <v>45621</v>
+        <v>45617</v>
       </c>
       <c r="C106" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -1904,13 +1901,13 @@
         <v>4</v>
       </c>
       <c r="B107" s="2">
-        <v>45622</v>
+        <v>45618</v>
       </c>
       <c r="C107" s="2">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -1918,10 +1915,10 @@
         <v>4</v>
       </c>
       <c r="B108" s="2">
-        <v>45623</v>
+        <v>45619</v>
       </c>
       <c r="C108" s="2">
-        <v>991</v>
+        <v>49</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>5</v>
@@ -1932,10 +1929,10 @@
         <v>4</v>
       </c>
       <c r="B109" s="2">
-        <v>45624</v>
+        <v>45621</v>
       </c>
       <c r="C109" s="2">
-        <v>340</v>
+        <v>158</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>6</v>
@@ -1946,10 +1943,10 @@
         <v>4</v>
       </c>
       <c r="B110" s="2">
-        <v>45624</v>
+        <v>45622</v>
       </c>
       <c r="C110" s="2">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>5</v>
@@ -1960,10 +1957,10 @@
         <v>4</v>
       </c>
       <c r="B111" s="2">
-        <v>45624</v>
+        <v>45622</v>
       </c>
       <c r="C111" s="2">
-        <v>18</v>
+        <v>415</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>5</v>
@@ -1974,10 +1971,10 @@
         <v>4</v>
       </c>
       <c r="B112" s="2">
-        <v>45625</v>
+        <v>45623</v>
       </c>
       <c r="C112" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>5</v>
@@ -1988,10 +1985,10 @@
         <v>4</v>
       </c>
       <c r="B113" s="2">
-        <v>45626</v>
+        <v>45623</v>
       </c>
       <c r="C113" s="2">
-        <v>1024</v>
+        <v>1</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>5</v>
@@ -2002,13 +1999,13 @@
         <v>4</v>
       </c>
       <c r="B114" s="2">
-        <v>45627</v>
+        <v>45624</v>
       </c>
       <c r="C114" s="2">
-        <v>173</v>
+        <v>7</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2016,13 +2013,13 @@
         <v>4</v>
       </c>
       <c r="B115" s="2">
-        <v>45634</v>
+        <v>45624</v>
       </c>
       <c r="C115" s="2">
-        <v>5</v>
+        <v>326</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2030,7 +2027,7 @@
         <v>4</v>
       </c>
       <c r="B116" s="2">
-        <v>45635</v>
+        <v>45625</v>
       </c>
       <c r="C116" s="2">
         <v>1</v>
@@ -2044,10 +2041,10 @@
         <v>4</v>
       </c>
       <c r="B117" s="2">
-        <v>45636</v>
+        <v>45625</v>
       </c>
       <c r="C117" s="2">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>5</v>
@@ -2058,10 +2055,10 @@
         <v>4</v>
       </c>
       <c r="B118" s="2">
-        <v>45601</v>
+        <v>45625</v>
       </c>
       <c r="C118" s="2">
-        <v>1</v>
+        <v>935</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>5</v>
@@ -2072,13 +2069,13 @@
         <v>4</v>
       </c>
       <c r="B119" s="2">
-        <v>45604</v>
+        <v>45627</v>
       </c>
       <c r="C119" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2086,10 +2083,10 @@
         <v>4</v>
       </c>
       <c r="B120" s="2">
-        <v>45605</v>
+        <v>45628</v>
       </c>
       <c r="C120" s="2">
-        <v>58</v>
+        <v>388</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>5</v>
@@ -2100,13 +2097,13 @@
         <v>4</v>
       </c>
       <c r="B121" s="2">
-        <v>45607</v>
+        <v>45630</v>
       </c>
       <c r="C121" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2114,10 +2111,10 @@
         <v>4</v>
       </c>
       <c r="B122" s="2">
-        <v>45613</v>
+        <v>45631</v>
       </c>
       <c r="C122" s="2">
-        <v>2</v>
+        <v>376</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>5</v>
@@ -2128,10 +2125,10 @@
         <v>4</v>
       </c>
       <c r="B123" s="2">
-        <v>45613</v>
+        <v>45633</v>
       </c>
       <c r="C123" s="2">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>5</v>
@@ -2142,13 +2139,13 @@
         <v>4</v>
       </c>
       <c r="B124" s="2">
-        <v>45614</v>
+        <v>45636</v>
       </c>
       <c r="C124" s="2">
-        <v>60</v>
+        <v>642</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2156,10 +2153,10 @@
         <v>4</v>
       </c>
       <c r="B125" s="2">
-        <v>45615</v>
+        <v>45605</v>
       </c>
       <c r="C125" s="2">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>5</v>
@@ -2170,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="B126" s="2">
-        <v>45617</v>
+        <v>45606</v>
       </c>
       <c r="C126" s="2">
-        <v>47</v>
+        <v>211</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>6</v>
@@ -2184,10 +2181,10 @@
         <v>4</v>
       </c>
       <c r="B127" s="2">
-        <v>45619</v>
+        <v>45607</v>
       </c>
       <c r="C127" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>5</v>
@@ -2198,13 +2195,13 @@
         <v>4</v>
       </c>
       <c r="B128" s="2">
-        <v>45620</v>
+        <v>45608</v>
       </c>
       <c r="C128" s="2">
-        <v>245</v>
+        <v>16</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2212,13 +2209,13 @@
         <v>4</v>
       </c>
       <c r="B129" s="2">
-        <v>45621</v>
+        <v>45609</v>
       </c>
       <c r="C129" s="2">
-        <v>412</v>
+        <v>40</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2226,10 +2223,10 @@
         <v>4</v>
       </c>
       <c r="B130" s="2">
-        <v>45622</v>
+        <v>45610</v>
       </c>
       <c r="C130" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>5</v>
@@ -2240,13 +2237,13 @@
         <v>4</v>
       </c>
       <c r="B131" s="2">
-        <v>45623</v>
+        <v>45610</v>
       </c>
       <c r="C131" s="2">
-        <v>349</v>
+        <v>237</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2254,13 +2251,13 @@
         <v>4</v>
       </c>
       <c r="B132" s="2">
-        <v>45623</v>
+        <v>45612</v>
       </c>
       <c r="C132" s="2">
-        <v>1</v>
+        <v>208</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2268,10 +2265,10 @@
         <v>4</v>
       </c>
       <c r="B133" s="2">
-        <v>45624</v>
+        <v>45613</v>
       </c>
       <c r="C133" s="2">
-        <v>957</v>
+        <v>3</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>5</v>
@@ -2282,10 +2279,10 @@
         <v>4</v>
       </c>
       <c r="B134" s="2">
-        <v>45625</v>
+        <v>45613</v>
       </c>
       <c r="C134" s="2">
-        <v>1</v>
+        <v>606</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>5</v>
@@ -2296,13 +2293,13 @@
         <v>4</v>
       </c>
       <c r="B135" s="2">
-        <v>45626</v>
+        <v>45615</v>
       </c>
       <c r="C135" s="2">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2310,13 +2307,13 @@
         <v>4</v>
       </c>
       <c r="B136" s="2">
-        <v>45627</v>
+        <v>45616</v>
       </c>
       <c r="C136" s="2">
-        <v>50</v>
+        <v>317</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -2324,13 +2321,13 @@
         <v>4</v>
       </c>
       <c r="B137" s="2">
-        <v>45627</v>
+        <v>45616</v>
       </c>
       <c r="C137" s="2">
-        <v>1018</v>
+        <v>202</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -2338,10 +2335,10 @@
         <v>4</v>
       </c>
       <c r="B138" s="2">
-        <v>45627</v>
+        <v>45619</v>
       </c>
       <c r="C138" s="2">
-        <v>9</v>
+        <v>779</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>5</v>
@@ -2352,13 +2349,13 @@
         <v>4</v>
       </c>
       <c r="B139" s="2">
-        <v>45628</v>
+        <v>45619</v>
       </c>
       <c r="C139" s="2">
-        <v>88</v>
+        <v>719</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -2366,13 +2363,13 @@
         <v>4</v>
       </c>
       <c r="B140" s="2">
-        <v>45629</v>
+        <v>45620</v>
       </c>
       <c r="C140" s="2">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2380,13 +2377,13 @@
         <v>4</v>
       </c>
       <c r="B141" s="2">
-        <v>45630</v>
+        <v>45622</v>
       </c>
       <c r="C141" s="2">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -2394,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B142" s="2">
-        <v>45630</v>
+        <v>45622</v>
       </c>
       <c r="C142" s="2">
-        <v>392</v>
+        <v>560</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2408,10 +2405,10 @@
         <v>4</v>
       </c>
       <c r="B143" s="2">
-        <v>45630</v>
+        <v>45623</v>
       </c>
       <c r="C143" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>5</v>
@@ -2422,13 +2419,13 @@
         <v>4</v>
       </c>
       <c r="B144" s="2">
-        <v>45630</v>
+        <v>45623</v>
       </c>
       <c r="C144" s="2">
-        <v>2</v>
+        <v>126</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -2436,10 +2433,10 @@
         <v>4</v>
       </c>
       <c r="B145" s="2">
-        <v>45631</v>
+        <v>45625</v>
       </c>
       <c r="C145" s="2">
-        <v>86</v>
+        <v>3</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>5</v>
@@ -2450,13 +2447,13 @@
         <v>4</v>
       </c>
       <c r="B146" s="2">
-        <v>45632</v>
+        <v>45625</v>
       </c>
       <c r="C146" s="2">
-        <v>1</v>
+        <v>1117</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -2464,13 +2461,13 @@
         <v>4</v>
       </c>
       <c r="B147" s="2">
-        <v>45633</v>
+        <v>45626</v>
       </c>
       <c r="C147" s="2">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -2478,13 +2475,13 @@
         <v>4</v>
       </c>
       <c r="B148" s="2">
-        <v>45633</v>
+        <v>45626</v>
       </c>
       <c r="C148" s="2">
-        <v>11</v>
+        <v>128</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -2492,10 +2489,10 @@
         <v>4</v>
       </c>
       <c r="B149" s="2">
-        <v>45634</v>
+        <v>45628</v>
       </c>
       <c r="C149" s="2">
-        <v>168</v>
+        <v>2</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>5</v>
@@ -2506,13 +2503,13 @@
         <v>4</v>
       </c>
       <c r="B150" s="2">
-        <v>45636</v>
+        <v>45628</v>
       </c>
       <c r="C150" s="2">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -2520,10 +2517,10 @@
         <v>4</v>
       </c>
       <c r="B151" s="2">
-        <v>45636</v>
+        <v>45629</v>
       </c>
       <c r="C151" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>5</v>
@@ -2534,13 +2531,13 @@
         <v>4</v>
       </c>
       <c r="B152" s="2">
-        <v>45602</v>
+        <v>45631</v>
       </c>
       <c r="C152" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -2548,13 +2545,13 @@
         <v>4</v>
       </c>
       <c r="B153" s="2">
-        <v>45605</v>
+        <v>45631</v>
       </c>
       <c r="C153" s="2">
-        <v>137</v>
+        <v>48</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -2562,10 +2559,10 @@
         <v>4</v>
       </c>
       <c r="B154" s="2">
-        <v>45605</v>
+        <v>45634</v>
       </c>
       <c r="C154" s="2">
-        <v>760</v>
+        <v>1</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>5</v>
@@ -2576,10 +2573,10 @@
         <v>4</v>
       </c>
       <c r="B155" s="2">
-        <v>45606</v>
+        <v>45634</v>
       </c>
       <c r="C155" s="2">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>5</v>
@@ -2590,13 +2587,13 @@
         <v>4</v>
       </c>
       <c r="B156" s="2">
-        <v>45611</v>
+        <v>45635</v>
       </c>
       <c r="C156" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -2604,13 +2601,13 @@
         <v>4</v>
       </c>
       <c r="B157" s="2">
-        <v>45613</v>
+        <v>45636</v>
       </c>
       <c r="C157" s="2">
-        <v>153</v>
+        <v>6</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -2618,13 +2615,13 @@
         <v>4</v>
       </c>
       <c r="B158" s="2">
-        <v>45614</v>
+        <v>45605</v>
       </c>
       <c r="C158" s="2">
-        <v>2</v>
+        <v>187</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -2632,10 +2629,10 @@
         <v>4</v>
       </c>
       <c r="B159" s="2">
-        <v>45614</v>
+        <v>45606</v>
       </c>
       <c r="C159" s="2">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>5</v>
@@ -2646,13 +2643,13 @@
         <v>4</v>
       </c>
       <c r="B160" s="2">
-        <v>45616</v>
+        <v>45607</v>
       </c>
       <c r="C160" s="2">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -2660,13 +2657,13 @@
         <v>4</v>
       </c>
       <c r="B161" s="2">
-        <v>45617</v>
+        <v>45608</v>
       </c>
       <c r="C161" s="2">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -2674,13 +2671,13 @@
         <v>4</v>
       </c>
       <c r="B162" s="2">
-        <v>45619</v>
+        <v>45609</v>
       </c>
       <c r="C162" s="2">
-        <v>224</v>
+        <v>23</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -2688,10 +2685,10 @@
         <v>4</v>
       </c>
       <c r="B163" s="2">
-        <v>45620</v>
+        <v>45609</v>
       </c>
       <c r="C163" s="2">
-        <v>2</v>
+        <v>319</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>5</v>
@@ -2702,13 +2699,13 @@
         <v>4</v>
       </c>
       <c r="B164" s="2">
-        <v>45621</v>
+        <v>45611</v>
       </c>
       <c r="C164" s="2">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -2716,10 +2713,10 @@
         <v>4</v>
       </c>
       <c r="B165" s="2">
-        <v>45623</v>
+        <v>45612</v>
       </c>
       <c r="C165" s="2">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>5</v>
@@ -2730,10 +2727,10 @@
         <v>4</v>
       </c>
       <c r="B166" s="2">
-        <v>45623</v>
+        <v>45612</v>
       </c>
       <c r="C166" s="2">
-        <v>18</v>
+        <v>614</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>5</v>
@@ -2744,10 +2741,10 @@
         <v>4</v>
       </c>
       <c r="B167" s="2">
-        <v>45625</v>
+        <v>45614</v>
       </c>
       <c r="C167" s="2">
-        <v>707</v>
+        <v>1</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>5</v>
@@ -2758,10 +2755,10 @@
         <v>4</v>
       </c>
       <c r="B168" s="2">
-        <v>45626</v>
+        <v>45615</v>
       </c>
       <c r="C168" s="2">
-        <v>1</v>
+        <v>247</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>5</v>
@@ -2772,10 +2769,10 @@
         <v>4</v>
       </c>
       <c r="B169" s="2">
-        <v>45626</v>
+        <v>45617</v>
       </c>
       <c r="C169" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>5</v>
@@ -2786,13 +2783,13 @@
         <v>4</v>
       </c>
       <c r="B170" s="2">
-        <v>45626</v>
+        <v>45620</v>
       </c>
       <c r="C170" s="2">
-        <v>37</v>
+        <v>681</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -2800,7 +2797,7 @@
         <v>4</v>
       </c>
       <c r="B171" s="2">
-        <v>45627</v>
+        <v>45620</v>
       </c>
       <c r="C171" s="2">
         <v>1</v>
@@ -2814,13 +2811,13 @@
         <v>4</v>
       </c>
       <c r="B172" s="2">
-        <v>45627</v>
+        <v>45623</v>
       </c>
       <c r="C172" s="2">
-        <v>7</v>
+        <v>802</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -2828,13 +2825,13 @@
         <v>4</v>
       </c>
       <c r="B173" s="2">
-        <v>45628</v>
+        <v>45624</v>
       </c>
       <c r="C173" s="2">
-        <v>337</v>
+        <v>156</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -2842,13 +2839,13 @@
         <v>4</v>
       </c>
       <c r="B174" s="2">
-        <v>45629</v>
+        <v>45626</v>
       </c>
       <c r="C174" s="2">
-        <v>5</v>
+        <v>785</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -2856,7 +2853,7 @@
         <v>4</v>
       </c>
       <c r="B175" s="2">
-        <v>45630</v>
+        <v>45627</v>
       </c>
       <c r="C175" s="2">
         <v>3</v>
@@ -2870,13 +2867,13 @@
         <v>4</v>
       </c>
       <c r="B176" s="2">
-        <v>45631</v>
+        <v>45627</v>
       </c>
       <c r="C176" s="2">
-        <v>16</v>
+        <v>109</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -2884,10 +2881,10 @@
         <v>4</v>
       </c>
       <c r="B177" s="2">
-        <v>45631</v>
+        <v>45629</v>
       </c>
       <c r="C177" s="2">
-        <v>417</v>
+        <v>1</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>5</v>
@@ -2898,13 +2895,13 @@
         <v>4</v>
       </c>
       <c r="B178" s="2">
-        <v>45632</v>
+        <v>45629</v>
       </c>
       <c r="C178" s="2">
-        <v>114</v>
+        <v>455</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -2912,10 +2909,10 @@
         <v>4</v>
       </c>
       <c r="B179" s="2">
-        <v>45632</v>
+        <v>45630</v>
       </c>
       <c r="C179" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>5</v>
@@ -2926,13 +2923,13 @@
         <v>4</v>
       </c>
       <c r="B180" s="2">
-        <v>45633</v>
+        <v>45630</v>
       </c>
       <c r="C180" s="2">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -2940,13 +2937,13 @@
         <v>4</v>
       </c>
       <c r="B181" s="2">
-        <v>45634</v>
+        <v>45631</v>
       </c>
       <c r="C181" s="2">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -2954,10 +2951,10 @@
         <v>4</v>
       </c>
       <c r="B182" s="2">
-        <v>45634</v>
+        <v>45632</v>
       </c>
       <c r="C182" s="2">
-        <v>1260</v>
+        <v>68</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>5</v>
@@ -2968,10 +2965,10 @@
         <v>4</v>
       </c>
       <c r="B183" s="2">
-        <v>45635</v>
+        <v>45633</v>
       </c>
       <c r="C183" s="2">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>5</v>
@@ -2982,13 +2979,13 @@
         <v>4</v>
       </c>
       <c r="B184" s="2">
-        <v>45635</v>
+        <v>45634</v>
       </c>
       <c r="C184" s="2">
-        <v>2</v>
+        <v>108</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -2996,10 +2993,10 @@
         <v>4</v>
       </c>
       <c r="B185" s="2">
-        <v>45636</v>
+        <v>45635</v>
       </c>
       <c r="C185" s="2">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>5</v>
@@ -3010,10 +3007,10 @@
         <v>4</v>
       </c>
       <c r="B186" s="2">
-        <v>45611</v>
+        <v>45636</v>
       </c>
       <c r="C186" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>5</v>
@@ -3024,10 +3021,10 @@
         <v>4</v>
       </c>
       <c r="B187" s="2">
-        <v>45612</v>
+        <v>45604</v>
       </c>
       <c r="C187" s="2">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>5</v>
@@ -3038,10 +3035,10 @@
         <v>4</v>
       </c>
       <c r="B188" s="2">
-        <v>45613</v>
+        <v>45606</v>
       </c>
       <c r="C188" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>5</v>
@@ -3052,13 +3049,13 @@
         <v>4</v>
       </c>
       <c r="B189" s="2">
-        <v>45614</v>
+        <v>45606</v>
       </c>
       <c r="C189" s="2">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3066,13 +3063,13 @@
         <v>4</v>
       </c>
       <c r="B190" s="2">
-        <v>45614</v>
+        <v>45609</v>
       </c>
       <c r="C190" s="2">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3080,13 +3077,13 @@
         <v>4</v>
       </c>
       <c r="B191" s="2">
-        <v>45614</v>
+        <v>45610</v>
       </c>
       <c r="C191" s="2">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -3094,13 +3091,13 @@
         <v>4</v>
       </c>
       <c r="B192" s="2">
-        <v>45615</v>
+        <v>45612</v>
       </c>
       <c r="C192" s="2">
-        <v>67</v>
+        <v>456</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3108,13 +3105,13 @@
         <v>4</v>
       </c>
       <c r="B193" s="2">
-        <v>45616</v>
+        <v>45613</v>
       </c>
       <c r="C193" s="2">
-        <v>3</v>
+        <v>217</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3122,13 +3119,13 @@
         <v>4</v>
       </c>
       <c r="B194" s="2">
-        <v>45617</v>
+        <v>45614</v>
       </c>
       <c r="C194" s="2">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3136,10 +3133,10 @@
         <v>4</v>
       </c>
       <c r="B195" s="2">
-        <v>45618</v>
+        <v>45614</v>
       </c>
       <c r="C195" s="2">
-        <v>77</v>
+        <v>320</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>5</v>
@@ -3150,13 +3147,13 @@
         <v>4</v>
       </c>
       <c r="B196" s="2">
-        <v>45620</v>
+        <v>45615</v>
       </c>
       <c r="C196" s="2">
-        <v>3</v>
+        <v>194</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3164,13 +3161,13 @@
         <v>4</v>
       </c>
       <c r="B197" s="2">
-        <v>45620</v>
+        <v>45616</v>
       </c>
       <c r="C197" s="2">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3178,13 +3175,13 @@
         <v>4</v>
       </c>
       <c r="B198" s="2">
-        <v>45620</v>
+        <v>45616</v>
       </c>
       <c r="C198" s="2">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3192,10 +3189,10 @@
         <v>4</v>
       </c>
       <c r="B199" s="2">
-        <v>45621</v>
+        <v>45617</v>
       </c>
       <c r="C199" s="2">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>5</v>
@@ -3206,10 +3203,10 @@
         <v>4</v>
       </c>
       <c r="B200" s="2">
-        <v>45623</v>
+        <v>45617</v>
       </c>
       <c r="C200" s="2">
-        <v>8</v>
+        <v>272</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>5</v>
@@ -3220,13 +3217,13 @@
         <v>4</v>
       </c>
       <c r="B201" s="2">
-        <v>45623</v>
+        <v>45618</v>
       </c>
       <c r="C201" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3234,13 +3231,13 @@
         <v>4</v>
       </c>
       <c r="B202" s="2">
-        <v>45624</v>
+        <v>45618</v>
       </c>
       <c r="C202" s="2">
-        <v>3</v>
+        <v>482</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3248,10 +3245,10 @@
         <v>4</v>
       </c>
       <c r="B203" s="2">
-        <v>45626</v>
+        <v>45619</v>
       </c>
       <c r="C203" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>5</v>
@@ -3262,10 +3259,10 @@
         <v>4</v>
       </c>
       <c r="B204" s="2">
-        <v>45627</v>
+        <v>45620</v>
       </c>
       <c r="C204" s="2">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>5</v>
@@ -3276,10 +3273,10 @@
         <v>4</v>
       </c>
       <c r="B205" s="2">
-        <v>45627</v>
+        <v>45620</v>
       </c>
       <c r="C205" s="2">
-        <v>1</v>
+        <v>670</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>5</v>
@@ -3290,13 +3287,13 @@
         <v>4</v>
       </c>
       <c r="B206" s="2">
-        <v>45627</v>
+        <v>45621</v>
       </c>
       <c r="C206" s="2">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -3304,13 +3301,13 @@
         <v>4</v>
       </c>
       <c r="B207" s="2">
-        <v>45630</v>
+        <v>45621</v>
       </c>
       <c r="C207" s="2">
-        <v>90</v>
+        <v>529</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -3318,13 +3315,13 @@
         <v>4</v>
       </c>
       <c r="B208" s="2">
-        <v>45633</v>
+        <v>45622</v>
       </c>
       <c r="C208" s="2">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -3332,13 +3329,13 @@
         <v>4</v>
       </c>
       <c r="B209" s="2">
-        <v>45633</v>
+        <v>45623</v>
       </c>
       <c r="C209" s="2">
-        <v>295</v>
+        <v>608</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -3346,10 +3343,10 @@
         <v>4</v>
       </c>
       <c r="B210" s="2">
-        <v>45635</v>
+        <v>45624</v>
       </c>
       <c r="C210" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>5</v>
@@ -3360,13 +3357,13 @@
         <v>4</v>
       </c>
       <c r="B211" s="2">
-        <v>45636</v>
+        <v>45625</v>
       </c>
       <c r="C211" s="2">
-        <v>135</v>
+        <v>9</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -3374,7 +3371,7 @@
         <v>4</v>
       </c>
       <c r="B212" s="2">
-        <v>45605</v>
+        <v>45625</v>
       </c>
       <c r="C212" s="2">
         <v>1</v>
@@ -3388,10 +3385,10 @@
         <v>4</v>
       </c>
       <c r="B213" s="2">
-        <v>45606</v>
+        <v>45627</v>
       </c>
       <c r="C213" s="2">
-        <v>499</v>
+        <v>1</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>5</v>
@@ -3402,13 +3399,13 @@
         <v>4</v>
       </c>
       <c r="B214" s="2">
-        <v>45606</v>
+        <v>45629</v>
       </c>
       <c r="C214" s="2">
-        <v>117</v>
+        <v>31</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -3416,13 +3413,13 @@
         <v>4</v>
       </c>
       <c r="B215" s="2">
-        <v>45606</v>
+        <v>45632</v>
       </c>
       <c r="C215" s="2">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -3430,13 +3427,13 @@
         <v>4</v>
       </c>
       <c r="B216" s="2">
-        <v>45612</v>
+        <v>45635</v>
       </c>
       <c r="C216" s="2">
-        <v>222</v>
+        <v>4</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -3444,13 +3441,13 @@
         <v>4</v>
       </c>
       <c r="B217" s="2">
-        <v>45612</v>
+        <v>45635</v>
       </c>
       <c r="C217" s="2">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -3458,10 +3455,10 @@
         <v>4</v>
       </c>
       <c r="B218" s="2">
-        <v>45614</v>
+        <v>45605</v>
       </c>
       <c r="C218" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>5</v>
@@ -3472,13 +3469,13 @@
         <v>4</v>
       </c>
       <c r="B219" s="2">
-        <v>45615</v>
+        <v>45605</v>
       </c>
       <c r="C219" s="2">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -3486,13 +3483,13 @@
         <v>4</v>
       </c>
       <c r="B220" s="2">
-        <v>45615</v>
+        <v>45607</v>
       </c>
       <c r="C220" s="2">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -3500,10 +3497,10 @@
         <v>4</v>
       </c>
       <c r="B221" s="2">
-        <v>45615</v>
+        <v>45608</v>
       </c>
       <c r="C221" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>5</v>
@@ -3514,13 +3511,13 @@
         <v>4</v>
       </c>
       <c r="B222" s="2">
-        <v>45618</v>
+        <v>45608</v>
       </c>
       <c r="C222" s="2">
-        <v>2</v>
+        <v>155</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -3528,13 +3525,13 @@
         <v>4</v>
       </c>
       <c r="B223" s="2">
-        <v>45619</v>
+        <v>45610</v>
       </c>
       <c r="C223" s="2">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -3542,13 +3539,13 @@
         <v>4</v>
       </c>
       <c r="B224" s="2">
-        <v>45620</v>
+        <v>45611</v>
       </c>
       <c r="C224" s="2">
-        <v>93</v>
+        <v>2</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -3556,10 +3553,10 @@
         <v>4</v>
       </c>
       <c r="B225" s="2">
-        <v>45621</v>
+        <v>45612</v>
       </c>
       <c r="C225" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>5</v>
@@ -3570,10 +3567,10 @@
         <v>4</v>
       </c>
       <c r="B226" s="2">
-        <v>45621</v>
+        <v>45613</v>
       </c>
       <c r="C226" s="2">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>5</v>
@@ -3584,10 +3581,10 @@
         <v>4</v>
       </c>
       <c r="B227" s="2">
-        <v>45622</v>
+        <v>45614</v>
       </c>
       <c r="C227" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>5</v>
@@ -3598,10 +3595,10 @@
         <v>4</v>
       </c>
       <c r="B228" s="2">
-        <v>45622</v>
+        <v>45614</v>
       </c>
       <c r="C228" s="2">
-        <v>88</v>
+        <v>236</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>8</v>
@@ -3612,13 +3609,13 @@
         <v>4</v>
       </c>
       <c r="B229" s="2">
-        <v>45623</v>
+        <v>45614</v>
       </c>
       <c r="C229" s="2">
-        <v>124</v>
+        <v>45</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -3626,10 +3623,10 @@
         <v>4</v>
       </c>
       <c r="B230" s="2">
-        <v>45624</v>
+        <v>45616</v>
       </c>
       <c r="C230" s="2">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="D230" s="2" t="s">
         <v>5</v>
@@ -3640,10 +3637,10 @@
         <v>4</v>
       </c>
       <c r="B231" s="2">
-        <v>45624</v>
+        <v>45617</v>
       </c>
       <c r="C231" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D231" s="2" t="s">
         <v>5</v>
@@ -3654,13 +3651,13 @@
         <v>4</v>
       </c>
       <c r="B232" s="2">
-        <v>45625</v>
+        <v>45617</v>
       </c>
       <c r="C232" s="2">
-        <v>1</v>
+        <v>209</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -3668,13 +3665,13 @@
         <v>4</v>
       </c>
       <c r="B233" s="2">
-        <v>45625</v>
+        <v>45617</v>
       </c>
       <c r="C233" s="2">
-        <v>159</v>
+        <v>46</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -3682,13 +3679,13 @@
         <v>4</v>
       </c>
       <c r="B234" s="2">
-        <v>45625</v>
+        <v>45618</v>
       </c>
       <c r="C234" s="2">
-        <v>132</v>
+        <v>8</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -3696,13 +3693,13 @@
         <v>4</v>
       </c>
       <c r="B235" s="2">
-        <v>45625</v>
+        <v>45618</v>
       </c>
       <c r="C235" s="2">
-        <v>4</v>
+        <v>770</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -3710,13 +3707,13 @@
         <v>4</v>
       </c>
       <c r="B236" s="2">
-        <v>45626</v>
+        <v>45620</v>
       </c>
       <c r="C236" s="2">
-        <v>98</v>
+        <v>298</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -3724,13 +3721,13 @@
         <v>4</v>
       </c>
       <c r="B237" s="2">
-        <v>45628</v>
+        <v>45621</v>
       </c>
       <c r="C237" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -3738,10 +3735,10 @@
         <v>4</v>
       </c>
       <c r="B238" s="2">
-        <v>45629</v>
+        <v>45621</v>
       </c>
       <c r="C238" s="2">
-        <v>99</v>
+        <v>480</v>
       </c>
       <c r="D238" s="2" t="s">
         <v>5</v>
@@ -3752,10 +3749,10 @@
         <v>4</v>
       </c>
       <c r="B239" s="2">
-        <v>45629</v>
+        <v>45623</v>
       </c>
       <c r="C239" s="2">
-        <v>368</v>
+        <v>1</v>
       </c>
       <c r="D239" s="2" t="s">
         <v>5</v>
@@ -3766,13 +3763,13 @@
         <v>4</v>
       </c>
       <c r="B240" s="2">
-        <v>45631</v>
+        <v>45624</v>
       </c>
       <c r="C240" s="2">
-        <v>2</v>
+        <v>583</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -3780,10 +3777,10 @@
         <v>4</v>
       </c>
       <c r="B241" s="2">
-        <v>45632</v>
+        <v>45627</v>
       </c>
       <c r="C241" s="2">
-        <v>1</v>
+        <v>637</v>
       </c>
       <c r="D241" s="2" t="s">
         <v>5</v>
@@ -3794,13 +3791,13 @@
         <v>4</v>
       </c>
       <c r="B242" s="2">
-        <v>45632</v>
+        <v>45628</v>
       </c>
       <c r="C242" s="2">
-        <v>580</v>
+        <v>53</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -3808,13 +3805,13 @@
         <v>4</v>
       </c>
       <c r="B243" s="2">
-        <v>45635</v>
+        <v>45631</v>
       </c>
       <c r="C243" s="2">
-        <v>360</v>
+        <v>28</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -3822,12 +3819,40 @@
         <v>4</v>
       </c>
       <c r="B244" s="2">
-        <v>45635</v>
+        <v>45634</v>
       </c>
       <c r="C244" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D244" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
+      <c r="A245" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B245" s="2">
+        <v>45634</v>
+      </c>
+      <c r="C245" s="2">
+        <v>93</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
+      <c r="A246" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B246" s="2">
+        <v>45636</v>
+      </c>
+      <c r="C246" s="2">
+        <v>39</v>
+      </c>
+      <c r="D246" s="2" t="s">
         <v>5</v>
       </c>
     </row>

--- a/reports/For Winter Ending (Prior Year)_Visits.xlsx
+++ b/reports/For Winter Ending (Prior Year)_Visits.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="9">
   <si>
     <t>Resort</t>
   </si>
@@ -28,22 +28,19 @@
     <t>Location</t>
   </si>
   <si>
-    <t>Purgatory</t>
+    <t>Snowbowl</t>
   </si>
   <si>
-    <t>Purgatory Passes</t>
+    <t>Snowbowl Passes</t>
   </si>
   <si>
-    <t>Purgatory Comp Tickets</t>
+    <t>Snowbowl Uplift Tickets</t>
   </si>
   <si>
-    <t>Purgatory Uplift Tickets</t>
+    <t>Snowbowl Comp Tickets</t>
   </si>
   <si>
-    <t>Purgatory Coaster</t>
-  </si>
-  <si>
-    <t>Purgatory Tickets</t>
+    <t>Snowbowl Tickets</t>
   </si>
 </sst>
 </file>
@@ -406,13 +403,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D251"/>
+  <dimension ref="A1:D253"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -434,10 +431,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>45611</v>
+        <v>45604</v>
       </c>
       <c r="C2" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -448,10 +445,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>45612</v>
+        <v>45605</v>
       </c>
       <c r="C3" s="2">
-        <v>129</v>
+        <v>2</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>5</v>
@@ -462,10 +459,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>45613</v>
+        <v>45605</v>
       </c>
       <c r="C4" s="2">
-        <v>7</v>
+        <v>512</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>5</v>
@@ -476,13 +473,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>45614</v>
+        <v>45607</v>
       </c>
       <c r="C5" s="2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -490,13 +487,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>45614</v>
+        <v>45607</v>
       </c>
       <c r="C6" s="2">
-        <v>200</v>
+        <v>103</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -504,10 +501,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="2">
-        <v>45614</v>
+        <v>45608</v>
       </c>
       <c r="C7" s="2">
-        <v>1</v>
+        <v>235</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>5</v>
@@ -518,10 +515,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>45615</v>
+        <v>45611</v>
       </c>
       <c r="C8" s="2">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>5</v>
@@ -532,13 +529,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>45616</v>
+        <v>45612</v>
       </c>
       <c r="C9" s="2">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -546,13 +543,13 @@
         <v>4</v>
       </c>
       <c r="B10" s="2">
-        <v>45617</v>
+        <v>45615</v>
       </c>
       <c r="C10" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -563,10 +560,10 @@
         <v>45618</v>
       </c>
       <c r="C11" s="2">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -574,10 +571,10 @@
         <v>4</v>
       </c>
       <c r="B12" s="2">
-        <v>45620</v>
+        <v>45621</v>
       </c>
       <c r="C12" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>5</v>
@@ -588,13 +585,13 @@
         <v>4</v>
       </c>
       <c r="B13" s="2">
-        <v>45620</v>
+        <v>45621</v>
       </c>
       <c r="C13" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -602,10 +599,10 @@
         <v>4</v>
       </c>
       <c r="B14" s="2">
-        <v>45620</v>
+        <v>45623</v>
       </c>
       <c r="C14" s="2">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>5</v>
@@ -616,10 +613,10 @@
         <v>4</v>
       </c>
       <c r="B15" s="2">
-        <v>45621</v>
+        <v>45624</v>
       </c>
       <c r="C15" s="2">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>5</v>
@@ -630,13 +627,13 @@
         <v>4</v>
       </c>
       <c r="B16" s="2">
-        <v>45623</v>
+        <v>45624</v>
       </c>
       <c r="C16" s="2">
+        <v>824</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -644,13 +641,13 @@
         <v>4</v>
       </c>
       <c r="B17" s="2">
-        <v>45623</v>
+        <v>45626</v>
       </c>
       <c r="C17" s="2">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -658,13 +655,13 @@
         <v>4</v>
       </c>
       <c r="B18" s="2">
-        <v>45624</v>
+        <v>45626</v>
       </c>
       <c r="C18" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -672,13 +669,13 @@
         <v>4</v>
       </c>
       <c r="B19" s="2">
-        <v>45626</v>
+        <v>45627</v>
       </c>
       <c r="C19" s="2">
-        <v>7</v>
+        <v>786</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -689,10 +686,10 @@
         <v>45627</v>
       </c>
       <c r="C20" s="2">
-        <v>1</v>
+        <v>160</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -700,7 +697,7 @@
         <v>4</v>
       </c>
       <c r="B21" s="2">
-        <v>45627</v>
+        <v>45628</v>
       </c>
       <c r="C21" s="2">
         <v>1</v>
@@ -714,13 +711,13 @@
         <v>4</v>
       </c>
       <c r="B22" s="2">
-        <v>45627</v>
+        <v>45629</v>
       </c>
       <c r="C22" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -731,10 +728,10 @@
         <v>45630</v>
       </c>
       <c r="C23" s="2">
-        <v>90</v>
+        <v>485</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -742,13 +739,13 @@
         <v>4</v>
       </c>
       <c r="B24" s="2">
-        <v>45633</v>
+        <v>45630</v>
       </c>
       <c r="C24" s="2">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -756,13 +753,13 @@
         <v>4</v>
       </c>
       <c r="B25" s="2">
-        <v>45633</v>
+        <v>45631</v>
       </c>
       <c r="C25" s="2">
-        <v>295</v>
+        <v>4</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -770,10 +767,10 @@
         <v>4</v>
       </c>
       <c r="B26" s="2">
-        <v>45635</v>
+        <v>45633</v>
       </c>
       <c r="C26" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>5</v>
@@ -784,13 +781,13 @@
         <v>4</v>
       </c>
       <c r="B27" s="2">
-        <v>45636</v>
+        <v>45633</v>
       </c>
       <c r="C27" s="2">
-        <v>135</v>
+        <v>1404</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -798,13 +795,13 @@
         <v>4</v>
       </c>
       <c r="B28" s="2">
-        <v>45637</v>
+        <v>45633</v>
       </c>
       <c r="C28" s="2">
-        <v>514</v>
+        <v>118</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -812,10 +809,10 @@
         <v>4</v>
       </c>
       <c r="B29" s="2">
-        <v>45604</v>
+        <v>45634</v>
       </c>
       <c r="C29" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>5</v>
@@ -826,10 +823,10 @@
         <v>4</v>
       </c>
       <c r="B30" s="2">
-        <v>45605</v>
+        <v>45634</v>
       </c>
       <c r="C30" s="2">
-        <v>6</v>
+        <v>854</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>5</v>
@@ -840,13 +837,13 @@
         <v>4</v>
       </c>
       <c r="B31" s="2">
-        <v>45606</v>
+        <v>45636</v>
       </c>
       <c r="C31" s="2">
-        <v>127</v>
+        <v>2</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -854,10 +851,10 @@
         <v>4</v>
       </c>
       <c r="B32" s="2">
-        <v>45612</v>
+        <v>45636</v>
       </c>
       <c r="C32" s="2">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>6</v>
@@ -868,10 +865,10 @@
         <v>4</v>
       </c>
       <c r="B33" s="2">
-        <v>45613</v>
+        <v>45637</v>
       </c>
       <c r="C33" s="2">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>5</v>
@@ -882,13 +879,13 @@
         <v>4</v>
       </c>
       <c r="B34" s="2">
-        <v>45615</v>
+        <v>45637</v>
       </c>
       <c r="C34" s="2">
-        <v>19</v>
+        <v>535</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -896,13 +893,13 @@
         <v>4</v>
       </c>
       <c r="B35" s="2">
-        <v>45615</v>
+        <v>45604</v>
       </c>
       <c r="C35" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -910,10 +907,10 @@
         <v>4</v>
       </c>
       <c r="B36" s="2">
-        <v>45616</v>
+        <v>45606</v>
       </c>
       <c r="C36" s="2">
-        <v>181</v>
+        <v>1</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>5</v>
@@ -924,13 +921,13 @@
         <v>4</v>
       </c>
       <c r="B37" s="2">
-        <v>45619</v>
+        <v>45606</v>
       </c>
       <c r="C37" s="2">
-        <v>623</v>
+        <v>26</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -938,13 +935,13 @@
         <v>4</v>
       </c>
       <c r="B38" s="2">
-        <v>45619</v>
+        <v>45609</v>
       </c>
       <c r="C38" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -952,13 +949,13 @@
         <v>4</v>
       </c>
       <c r="B39" s="2">
-        <v>45621</v>
+        <v>45610</v>
       </c>
       <c r="C39" s="2">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -966,13 +963,13 @@
         <v>4</v>
       </c>
       <c r="B40" s="2">
-        <v>45622</v>
+        <v>45612</v>
       </c>
       <c r="C40" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -980,13 +977,13 @@
         <v>4</v>
       </c>
       <c r="B41" s="2">
-        <v>45622</v>
+        <v>45613</v>
       </c>
       <c r="C41" s="2">
-        <v>284</v>
+        <v>217</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -994,10 +991,10 @@
         <v>4</v>
       </c>
       <c r="B42" s="2">
-        <v>45622</v>
+        <v>45614</v>
       </c>
       <c r="C42" s="2">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>5</v>
@@ -1008,10 +1005,10 @@
         <v>4</v>
       </c>
       <c r="B43" s="2">
-        <v>45624</v>
+        <v>45614</v>
       </c>
       <c r="C43" s="2">
-        <v>1</v>
+        <v>320</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>5</v>
@@ -1022,13 +1019,13 @@
         <v>4</v>
       </c>
       <c r="B44" s="2">
-        <v>45625</v>
+        <v>45615</v>
       </c>
       <c r="C44" s="2">
-        <v>426</v>
+        <v>194</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1036,7 +1033,7 @@
         <v>4</v>
       </c>
       <c r="B45" s="2">
-        <v>45625</v>
+        <v>45616</v>
       </c>
       <c r="C45" s="2">
         <v>1</v>
@@ -1050,13 +1047,13 @@
         <v>4</v>
       </c>
       <c r="B46" s="2">
-        <v>45625</v>
+        <v>45616</v>
       </c>
       <c r="C46" s="2">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1064,10 +1061,10 @@
         <v>4</v>
       </c>
       <c r="B47" s="2">
-        <v>45627</v>
+        <v>45617</v>
       </c>
       <c r="C47" s="2">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>5</v>
@@ -1078,10 +1075,10 @@
         <v>4</v>
       </c>
       <c r="B48" s="2">
-        <v>45628</v>
+        <v>45617</v>
       </c>
       <c r="C48" s="2">
-        <v>1</v>
+        <v>272</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>5</v>
@@ -1092,13 +1089,13 @@
         <v>4</v>
       </c>
       <c r="B49" s="2">
-        <v>45628</v>
+        <v>45618</v>
       </c>
       <c r="C49" s="2">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1106,13 +1103,13 @@
         <v>4</v>
       </c>
       <c r="B50" s="2">
-        <v>45628</v>
+        <v>45618</v>
       </c>
       <c r="C50" s="2">
+        <v>482</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1120,10 +1117,10 @@
         <v>4</v>
       </c>
       <c r="B51" s="2">
-        <v>45631</v>
+        <v>45619</v>
       </c>
       <c r="C51" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>5</v>
@@ -1134,13 +1131,13 @@
         <v>4</v>
       </c>
       <c r="B52" s="2">
-        <v>45631</v>
+        <v>45620</v>
       </c>
       <c r="C52" s="2">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1148,10 +1145,10 @@
         <v>4</v>
       </c>
       <c r="B53" s="2">
-        <v>45634</v>
+        <v>45620</v>
       </c>
       <c r="C53" s="2">
-        <v>3</v>
+        <v>670</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>5</v>
@@ -1162,10 +1159,10 @@
         <v>4</v>
       </c>
       <c r="B54" s="2">
-        <v>45634</v>
+        <v>45621</v>
       </c>
       <c r="C54" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>5</v>
@@ -1176,13 +1173,13 @@
         <v>4</v>
       </c>
       <c r="B55" s="2">
-        <v>45635</v>
+        <v>45621</v>
       </c>
       <c r="C55" s="2">
-        <v>25</v>
+        <v>529</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1190,10 +1187,10 @@
         <v>4</v>
       </c>
       <c r="B56" s="2">
-        <v>45636</v>
+        <v>45622</v>
       </c>
       <c r="C56" s="2">
-        <v>98</v>
+        <v>9</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>5</v>
@@ -1204,10 +1201,10 @@
         <v>4</v>
       </c>
       <c r="B57" s="2">
-        <v>45637</v>
+        <v>45623</v>
       </c>
       <c r="C57" s="2">
-        <v>1</v>
+        <v>608</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>5</v>
@@ -1218,10 +1215,10 @@
         <v>4</v>
       </c>
       <c r="B58" s="2">
-        <v>45637</v>
+        <v>45624</v>
       </c>
       <c r="C58" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>5</v>
@@ -1232,10 +1229,10 @@
         <v>4</v>
       </c>
       <c r="B59" s="2">
-        <v>45606</v>
+        <v>45625</v>
       </c>
       <c r="C59" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>5</v>
@@ -1246,13 +1243,13 @@
         <v>4</v>
       </c>
       <c r="B60" s="2">
-        <v>45610</v>
+        <v>45625</v>
       </c>
       <c r="C60" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1260,13 +1257,13 @@
         <v>4</v>
       </c>
       <c r="B61" s="2">
-        <v>45610</v>
+        <v>45627</v>
       </c>
       <c r="C61" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1274,13 +1271,13 @@
         <v>4</v>
       </c>
       <c r="B62" s="2">
-        <v>45612</v>
+        <v>45629</v>
       </c>
       <c r="C62" s="2">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1288,13 +1285,13 @@
         <v>4</v>
       </c>
       <c r="B63" s="2">
-        <v>45612</v>
+        <v>45632</v>
       </c>
       <c r="C63" s="2">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1302,13 +1299,13 @@
         <v>4</v>
       </c>
       <c r="B64" s="2">
-        <v>45613</v>
+        <v>45635</v>
       </c>
       <c r="C64" s="2">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1316,13 +1313,13 @@
         <v>4</v>
       </c>
       <c r="B65" s="2">
-        <v>45614</v>
+        <v>45635</v>
       </c>
       <c r="C65" s="2">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1330,10 +1327,10 @@
         <v>4</v>
       </c>
       <c r="B66" s="2">
-        <v>45616</v>
+        <v>45605</v>
       </c>
       <c r="C66" s="2">
-        <v>15</v>
+        <v>187</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>6</v>
@@ -1344,10 +1341,10 @@
         <v>4</v>
       </c>
       <c r="B67" s="2">
-        <v>45616</v>
+        <v>45606</v>
       </c>
       <c r="C67" s="2">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>5</v>
@@ -1358,10 +1355,10 @@
         <v>4</v>
       </c>
       <c r="B68" s="2">
-        <v>45617</v>
+        <v>45607</v>
       </c>
       <c r="C68" s="2">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>5</v>
@@ -1372,13 +1369,13 @@
         <v>4</v>
       </c>
       <c r="B69" s="2">
-        <v>45617</v>
+        <v>45608</v>
       </c>
       <c r="C69" s="2">
-        <v>234</v>
+        <v>32</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1386,13 +1383,13 @@
         <v>4</v>
       </c>
       <c r="B70" s="2">
-        <v>45618</v>
+        <v>45609</v>
       </c>
       <c r="C70" s="2">
-        <v>91</v>
+        <v>23</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1400,13 +1397,13 @@
         <v>4</v>
       </c>
       <c r="B71" s="2">
-        <v>45619</v>
+        <v>45609</v>
       </c>
       <c r="C71" s="2">
-        <v>44</v>
+        <v>319</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1414,13 +1411,13 @@
         <v>4</v>
       </c>
       <c r="B72" s="2">
-        <v>45620</v>
+        <v>45611</v>
       </c>
       <c r="C72" s="2">
-        <v>541</v>
+        <v>0</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1428,13 +1425,13 @@
         <v>4</v>
       </c>
       <c r="B73" s="2">
-        <v>45621</v>
+        <v>45612</v>
       </c>
       <c r="C73" s="2">
-        <v>224</v>
+        <v>37</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1442,10 +1439,10 @@
         <v>4</v>
       </c>
       <c r="B74" s="2">
-        <v>45621</v>
+        <v>45612</v>
       </c>
       <c r="C74" s="2">
-        <v>1</v>
+        <v>614</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>5</v>
@@ -1456,13 +1453,13 @@
         <v>4</v>
       </c>
       <c r="B75" s="2">
-        <v>45622</v>
+        <v>45614</v>
       </c>
       <c r="C75" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1470,10 +1467,10 @@
         <v>4</v>
       </c>
       <c r="B76" s="2">
-        <v>45623</v>
+        <v>45615</v>
       </c>
       <c r="C76" s="2">
-        <v>991</v>
+        <v>247</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>5</v>
@@ -1484,13 +1481,13 @@
         <v>4</v>
       </c>
       <c r="B77" s="2">
-        <v>45624</v>
+        <v>45617</v>
       </c>
       <c r="C77" s="2">
-        <v>340</v>
+        <v>4</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1498,13 +1495,13 @@
         <v>4</v>
       </c>
       <c r="B78" s="2">
-        <v>45624</v>
+        <v>45620</v>
       </c>
       <c r="C78" s="2">
-        <v>1</v>
+        <v>681</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1512,10 +1509,10 @@
         <v>4</v>
       </c>
       <c r="B79" s="2">
-        <v>45624</v>
+        <v>45620</v>
       </c>
       <c r="C79" s="2">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>5</v>
@@ -1526,13 +1523,13 @@
         <v>4</v>
       </c>
       <c r="B80" s="2">
-        <v>45625</v>
+        <v>45623</v>
       </c>
       <c r="C80" s="2">
-        <v>2</v>
+        <v>802</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -1540,13 +1537,13 @@
         <v>4</v>
       </c>
       <c r="B81" s="2">
-        <v>45626</v>
+        <v>45624</v>
       </c>
       <c r="C81" s="2">
-        <v>1024</v>
+        <v>156</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -1554,13 +1551,13 @@
         <v>4</v>
       </c>
       <c r="B82" s="2">
-        <v>45627</v>
+        <v>45626</v>
       </c>
       <c r="C82" s="2">
-        <v>173</v>
+        <v>785</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1568,10 +1565,10 @@
         <v>4</v>
       </c>
       <c r="B83" s="2">
-        <v>45634</v>
+        <v>45627</v>
       </c>
       <c r="C83" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>5</v>
@@ -1582,13 +1579,13 @@
         <v>4</v>
       </c>
       <c r="B84" s="2">
-        <v>45635</v>
+        <v>45627</v>
       </c>
       <c r="C84" s="2">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -1596,10 +1593,10 @@
         <v>4</v>
       </c>
       <c r="B85" s="2">
-        <v>45636</v>
+        <v>45629</v>
       </c>
       <c r="C85" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>5</v>
@@ -1610,13 +1607,13 @@
         <v>4</v>
       </c>
       <c r="B86" s="2">
-        <v>45601</v>
+        <v>45629</v>
       </c>
       <c r="C86" s="2">
-        <v>1</v>
+        <v>455</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -1624,7 +1621,7 @@
         <v>4</v>
       </c>
       <c r="B87" s="2">
-        <v>45604</v>
+        <v>45630</v>
       </c>
       <c r="C87" s="2">
         <v>1</v>
@@ -1638,13 +1635,13 @@
         <v>4</v>
       </c>
       <c r="B88" s="2">
-        <v>45605</v>
+        <v>45630</v>
       </c>
       <c r="C88" s="2">
-        <v>164</v>
+        <v>34</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -1652,13 +1649,13 @@
         <v>4</v>
       </c>
       <c r="B89" s="2">
-        <v>45605</v>
+        <v>45631</v>
       </c>
       <c r="C89" s="2">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1666,10 +1663,10 @@
         <v>4</v>
       </c>
       <c r="B90" s="2">
-        <v>45612</v>
+        <v>45632</v>
       </c>
       <c r="C90" s="2">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>5</v>
@@ -1680,10 +1677,10 @@
         <v>4</v>
       </c>
       <c r="B91" s="2">
-        <v>45613</v>
+        <v>45633</v>
       </c>
       <c r="C91" s="2">
-        <v>769</v>
+        <v>6</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>5</v>
@@ -1694,13 +1691,13 @@
         <v>4</v>
       </c>
       <c r="B92" s="2">
-        <v>45615</v>
+        <v>45634</v>
       </c>
       <c r="C92" s="2">
-        <v>2</v>
+        <v>108</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -1708,10 +1705,10 @@
         <v>4</v>
       </c>
       <c r="B93" s="2">
-        <v>45618</v>
+        <v>45635</v>
       </c>
       <c r="C93" s="2">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>5</v>
@@ -1722,10 +1719,10 @@
         <v>4</v>
       </c>
       <c r="B94" s="2">
-        <v>45619</v>
+        <v>45636</v>
       </c>
       <c r="C94" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>5</v>
@@ -1736,13 +1733,13 @@
         <v>4</v>
       </c>
       <c r="B95" s="2">
-        <v>45619</v>
+        <v>45637</v>
       </c>
       <c r="C95" s="2">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -1750,7 +1747,7 @@
         <v>4</v>
       </c>
       <c r="B96" s="2">
-        <v>45619</v>
+        <v>45605</v>
       </c>
       <c r="C96" s="2">
         <v>2</v>
@@ -1764,13 +1761,13 @@
         <v>4</v>
       </c>
       <c r="B97" s="2">
-        <v>45620</v>
+        <v>45605</v>
       </c>
       <c r="C97" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -1778,10 +1775,10 @@
         <v>4</v>
       </c>
       <c r="B98" s="2">
-        <v>45622</v>
+        <v>45607</v>
       </c>
       <c r="C98" s="2">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>5</v>
@@ -1792,10 +1789,10 @@
         <v>4</v>
       </c>
       <c r="B99" s="2">
-        <v>45623</v>
+        <v>45608</v>
       </c>
       <c r="C99" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>5</v>
@@ -1806,13 +1803,13 @@
         <v>4</v>
       </c>
       <c r="B100" s="2">
-        <v>45623</v>
+        <v>45608</v>
       </c>
       <c r="C100" s="2">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -1820,10 +1817,10 @@
         <v>4</v>
       </c>
       <c r="B101" s="2">
-        <v>45624</v>
+        <v>45610</v>
       </c>
       <c r="C101" s="2">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>5</v>
@@ -1834,13 +1831,13 @@
         <v>4</v>
       </c>
       <c r="B102" s="2">
-        <v>45625</v>
+        <v>45611</v>
       </c>
       <c r="C102" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -1848,7 +1845,7 @@
         <v>4</v>
       </c>
       <c r="B103" s="2">
-        <v>45625</v>
+        <v>45612</v>
       </c>
       <c r="C103" s="2">
         <v>4</v>
@@ -1862,10 +1859,10 @@
         <v>4</v>
       </c>
       <c r="B104" s="2">
-        <v>45626</v>
+        <v>45613</v>
       </c>
       <c r="C104" s="2">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>5</v>
@@ -1876,13 +1873,13 @@
         <v>4</v>
       </c>
       <c r="B105" s="2">
-        <v>45626</v>
+        <v>45614</v>
       </c>
       <c r="C105" s="2">
-        <v>297</v>
+        <v>2</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -1890,13 +1887,13 @@
         <v>4</v>
       </c>
       <c r="B106" s="2">
-        <v>45626</v>
+        <v>45614</v>
       </c>
       <c r="C106" s="2">
-        <v>115</v>
+        <v>236</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -1904,13 +1901,13 @@
         <v>4</v>
       </c>
       <c r="B107" s="2">
-        <v>45627</v>
+        <v>45614</v>
       </c>
       <c r="C107" s="2">
-        <v>114</v>
+        <v>45</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -1918,10 +1915,10 @@
         <v>4</v>
       </c>
       <c r="B108" s="2">
-        <v>45628</v>
+        <v>45616</v>
       </c>
       <c r="C108" s="2">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>5</v>
@@ -1932,13 +1929,13 @@
         <v>4</v>
       </c>
       <c r="B109" s="2">
-        <v>45629</v>
+        <v>45617</v>
       </c>
       <c r="C109" s="2">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -1946,13 +1943,13 @@
         <v>4</v>
       </c>
       <c r="B110" s="2">
-        <v>45629</v>
+        <v>45617</v>
       </c>
       <c r="C110" s="2">
-        <v>21</v>
+        <v>209</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -1960,13 +1957,13 @@
         <v>4</v>
       </c>
       <c r="B111" s="2">
-        <v>45630</v>
+        <v>45617</v>
       </c>
       <c r="C111" s="2">
-        <v>117</v>
+        <v>46</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -1974,10 +1971,10 @@
         <v>4</v>
       </c>
       <c r="B112" s="2">
-        <v>45631</v>
+        <v>45618</v>
       </c>
       <c r="C112" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>5</v>
@@ -1988,13 +1985,13 @@
         <v>4</v>
       </c>
       <c r="B113" s="2">
-        <v>45632</v>
+        <v>45618</v>
       </c>
       <c r="C113" s="2">
-        <v>27</v>
+        <v>770</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2002,13 +1999,13 @@
         <v>4</v>
       </c>
       <c r="B114" s="2">
-        <v>45633</v>
+        <v>45620</v>
       </c>
       <c r="C114" s="2">
-        <v>149</v>
+        <v>298</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2016,10 +2013,10 @@
         <v>4</v>
       </c>
       <c r="B115" s="2">
-        <v>45633</v>
+        <v>45621</v>
       </c>
       <c r="C115" s="2">
-        <v>1558</v>
+        <v>9</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>5</v>
@@ -2030,13 +2027,13 @@
         <v>4</v>
       </c>
       <c r="B116" s="2">
-        <v>45634</v>
+        <v>45621</v>
       </c>
       <c r="C116" s="2">
-        <v>160</v>
+        <v>480</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2044,10 +2041,10 @@
         <v>4</v>
       </c>
       <c r="B117" s="2">
-        <v>45634</v>
+        <v>45623</v>
       </c>
       <c r="C117" s="2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>5</v>
@@ -2058,10 +2055,10 @@
         <v>4</v>
       </c>
       <c r="B118" s="2">
-        <v>45636</v>
+        <v>45624</v>
       </c>
       <c r="C118" s="2">
-        <v>397</v>
+        <v>583</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>5</v>
@@ -2072,13 +2069,13 @@
         <v>4</v>
       </c>
       <c r="B119" s="2">
-        <v>45637</v>
+        <v>45627</v>
       </c>
       <c r="C119" s="2">
-        <v>151</v>
+        <v>637</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2086,13 +2083,13 @@
         <v>4</v>
       </c>
       <c r="B120" s="2">
-        <v>45637</v>
+        <v>45628</v>
       </c>
       <c r="C120" s="2">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2100,13 +2097,13 @@
         <v>4</v>
       </c>
       <c r="B121" s="2">
-        <v>45602</v>
+        <v>45631</v>
       </c>
       <c r="C121" s="2">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2114,13 +2111,13 @@
         <v>4</v>
       </c>
       <c r="B122" s="2">
-        <v>45605</v>
+        <v>45634</v>
       </c>
       <c r="C122" s="2">
-        <v>137</v>
+        <v>2</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2128,13 +2125,13 @@
         <v>4</v>
       </c>
       <c r="B123" s="2">
-        <v>45605</v>
+        <v>45634</v>
       </c>
       <c r="C123" s="2">
-        <v>760</v>
+        <v>93</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2142,10 +2139,10 @@
         <v>4</v>
       </c>
       <c r="B124" s="2">
-        <v>45606</v>
+        <v>45636</v>
       </c>
       <c r="C124" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>5</v>
@@ -2156,13 +2153,13 @@
         <v>4</v>
       </c>
       <c r="B125" s="2">
-        <v>45611</v>
+        <v>45637</v>
       </c>
       <c r="C125" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2170,13 +2167,13 @@
         <v>4</v>
       </c>
       <c r="B126" s="2">
-        <v>45613</v>
+        <v>45637</v>
       </c>
       <c r="C126" s="2">
-        <v>153</v>
+        <v>778</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2184,10 +2181,10 @@
         <v>4</v>
       </c>
       <c r="B127" s="2">
-        <v>45614</v>
+        <v>45604</v>
       </c>
       <c r="C127" s="2">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>5</v>
@@ -2198,10 +2195,10 @@
         <v>4</v>
       </c>
       <c r="B128" s="2">
-        <v>45614</v>
+        <v>45604</v>
       </c>
       <c r="C128" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>5</v>
@@ -2212,13 +2209,13 @@
         <v>4</v>
       </c>
       <c r="B129" s="2">
-        <v>45616</v>
+        <v>45604</v>
       </c>
       <c r="C129" s="2">
-        <v>46</v>
+        <v>139</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2226,13 +2223,13 @@
         <v>4</v>
       </c>
       <c r="B130" s="2">
-        <v>45617</v>
+        <v>45607</v>
       </c>
       <c r="C130" s="2">
-        <v>4</v>
+        <v>473</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2240,13 +2237,13 @@
         <v>4</v>
       </c>
       <c r="B131" s="2">
-        <v>45619</v>
+        <v>45608</v>
       </c>
       <c r="C131" s="2">
-        <v>224</v>
+        <v>3</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2254,13 +2251,13 @@
         <v>4</v>
       </c>
       <c r="B132" s="2">
-        <v>45620</v>
+        <v>45610</v>
       </c>
       <c r="C132" s="2">
-        <v>2</v>
+        <v>120</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2268,13 +2265,13 @@
         <v>4</v>
       </c>
       <c r="B133" s="2">
-        <v>45621</v>
+        <v>45611</v>
       </c>
       <c r="C133" s="2">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2282,13 +2279,13 @@
         <v>4</v>
       </c>
       <c r="B134" s="2">
-        <v>45623</v>
+        <v>45613</v>
       </c>
       <c r="C134" s="2">
-        <v>3</v>
+        <v>468</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2296,13 +2293,13 @@
         <v>4</v>
       </c>
       <c r="B135" s="2">
-        <v>45623</v>
+        <v>45614</v>
       </c>
       <c r="C135" s="2">
         <v>18</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2310,10 +2307,10 @@
         <v>4</v>
       </c>
       <c r="B136" s="2">
-        <v>45625</v>
+        <v>45616</v>
       </c>
       <c r="C136" s="2">
-        <v>707</v>
+        <v>3</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>5</v>
@@ -2324,13 +2321,13 @@
         <v>4</v>
       </c>
       <c r="B137" s="2">
-        <v>45626</v>
+        <v>45617</v>
       </c>
       <c r="C137" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -2338,13 +2335,13 @@
         <v>4</v>
       </c>
       <c r="B138" s="2">
-        <v>45626</v>
+        <v>45618</v>
       </c>
       <c r="C138" s="2">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -2352,10 +2349,10 @@
         <v>4</v>
       </c>
       <c r="B139" s="2">
-        <v>45626</v>
+        <v>45619</v>
       </c>
       <c r="C139" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>5</v>
@@ -2366,13 +2363,13 @@
         <v>4</v>
       </c>
       <c r="B140" s="2">
-        <v>45627</v>
+        <v>45621</v>
       </c>
       <c r="C140" s="2">
-        <v>1</v>
+        <v>158</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2380,10 +2377,10 @@
         <v>4</v>
       </c>
       <c r="B141" s="2">
-        <v>45627</v>
+        <v>45622</v>
       </c>
       <c r="C141" s="2">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>5</v>
@@ -2394,10 +2391,10 @@
         <v>4</v>
       </c>
       <c r="B142" s="2">
-        <v>45628</v>
+        <v>45622</v>
       </c>
       <c r="C142" s="2">
-        <v>337</v>
+        <v>415</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>5</v>
@@ -2408,10 +2405,10 @@
         <v>4</v>
       </c>
       <c r="B143" s="2">
-        <v>45629</v>
+        <v>45623</v>
       </c>
       <c r="C143" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>5</v>
@@ -2422,10 +2419,10 @@
         <v>4</v>
       </c>
       <c r="B144" s="2">
-        <v>45630</v>
+        <v>45623</v>
       </c>
       <c r="C144" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>5</v>
@@ -2436,13 +2433,13 @@
         <v>4</v>
       </c>
       <c r="B145" s="2">
-        <v>45631</v>
+        <v>45624</v>
       </c>
       <c r="C145" s="2">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -2450,13 +2447,13 @@
         <v>4</v>
       </c>
       <c r="B146" s="2">
-        <v>45631</v>
+        <v>45624</v>
       </c>
       <c r="C146" s="2">
-        <v>417</v>
+        <v>326</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -2464,10 +2461,10 @@
         <v>4</v>
       </c>
       <c r="B147" s="2">
-        <v>45632</v>
+        <v>45625</v>
       </c>
       <c r="C147" s="2">
-        <v>114</v>
+        <v>1</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>5</v>
@@ -2478,10 +2475,10 @@
         <v>4</v>
       </c>
       <c r="B148" s="2">
-        <v>45632</v>
+        <v>45625</v>
       </c>
       <c r="C148" s="2">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>5</v>
@@ -2492,10 +2489,10 @@
         <v>4</v>
       </c>
       <c r="B149" s="2">
-        <v>45633</v>
+        <v>45625</v>
       </c>
       <c r="C149" s="2">
-        <v>2</v>
+        <v>935</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>5</v>
@@ -2506,13 +2503,13 @@
         <v>4</v>
       </c>
       <c r="B150" s="2">
-        <v>45634</v>
+        <v>45627</v>
       </c>
       <c r="C150" s="2">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -2520,10 +2517,10 @@
         <v>4</v>
       </c>
       <c r="B151" s="2">
-        <v>45634</v>
+        <v>45628</v>
       </c>
       <c r="C151" s="2">
-        <v>1260</v>
+        <v>388</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>5</v>
@@ -2534,10 +2531,10 @@
         <v>4</v>
       </c>
       <c r="B152" s="2">
-        <v>45635</v>
+        <v>45630</v>
       </c>
       <c r="C152" s="2">
-        <v>84</v>
+        <v>5</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>5</v>
@@ -2548,10 +2545,10 @@
         <v>4</v>
       </c>
       <c r="B153" s="2">
-        <v>45635</v>
+        <v>45631</v>
       </c>
       <c r="C153" s="2">
-        <v>2</v>
+        <v>376</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>5</v>
@@ -2562,10 +2559,10 @@
         <v>4</v>
       </c>
       <c r="B154" s="2">
-        <v>45636</v>
+        <v>45633</v>
       </c>
       <c r="C154" s="2">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>5</v>
@@ -2576,13 +2573,13 @@
         <v>4</v>
       </c>
       <c r="B155" s="2">
-        <v>45637</v>
+        <v>45636</v>
       </c>
       <c r="C155" s="2">
-        <v>36</v>
+        <v>642</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -2590,13 +2587,13 @@
         <v>4</v>
       </c>
       <c r="B156" s="2">
-        <v>45605</v>
+        <v>45637</v>
       </c>
       <c r="C156" s="2">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -2604,10 +2601,10 @@
         <v>4</v>
       </c>
       <c r="B157" s="2">
-        <v>45606</v>
+        <v>45597</v>
       </c>
       <c r="C157" s="2">
-        <v>499</v>
+        <v>1</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>5</v>
@@ -2618,13 +2615,13 @@
         <v>4</v>
       </c>
       <c r="B158" s="2">
-        <v>45606</v>
+        <v>45604</v>
       </c>
       <c r="C158" s="2">
-        <v>117</v>
+        <v>18</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -2635,7 +2632,7 @@
         <v>45606</v>
       </c>
       <c r="C159" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>5</v>
@@ -2646,13 +2643,13 @@
         <v>4</v>
       </c>
       <c r="B160" s="2">
-        <v>45612</v>
+        <v>45606</v>
       </c>
       <c r="C160" s="2">
-        <v>222</v>
+        <v>549</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -2660,13 +2657,13 @@
         <v>4</v>
       </c>
       <c r="B161" s="2">
-        <v>45612</v>
+        <v>45606</v>
       </c>
       <c r="C161" s="2">
-        <v>14</v>
+        <v>290</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -2674,13 +2671,13 @@
         <v>4</v>
       </c>
       <c r="B162" s="2">
-        <v>45614</v>
+        <v>45607</v>
       </c>
       <c r="C162" s="2">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -2688,13 +2685,13 @@
         <v>4</v>
       </c>
       <c r="B163" s="2">
-        <v>45615</v>
+        <v>45609</v>
       </c>
       <c r="C163" s="2">
-        <v>2</v>
+        <v>186</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -2702,13 +2699,13 @@
         <v>4</v>
       </c>
       <c r="B164" s="2">
-        <v>45615</v>
+        <v>45610</v>
       </c>
       <c r="C164" s="2">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -2716,10 +2713,10 @@
         <v>4</v>
       </c>
       <c r="B165" s="2">
-        <v>45615</v>
+        <v>45612</v>
       </c>
       <c r="C165" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>5</v>
@@ -2730,10 +2727,10 @@
         <v>4</v>
       </c>
       <c r="B166" s="2">
-        <v>45618</v>
+        <v>45613</v>
       </c>
       <c r="C166" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>5</v>
@@ -2744,13 +2741,13 @@
         <v>4</v>
       </c>
       <c r="B167" s="2">
-        <v>45619</v>
+        <v>45613</v>
       </c>
       <c r="C167" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -2758,10 +2755,10 @@
         <v>4</v>
       </c>
       <c r="B168" s="2">
-        <v>45620</v>
+        <v>45615</v>
       </c>
       <c r="C168" s="2">
-        <v>93</v>
+        <v>3</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>5</v>
@@ -2772,10 +2769,10 @@
         <v>4</v>
       </c>
       <c r="B169" s="2">
-        <v>45621</v>
+        <v>45615</v>
       </c>
       <c r="C169" s="2">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>5</v>
@@ -2786,10 +2783,10 @@
         <v>4</v>
       </c>
       <c r="B170" s="2">
-        <v>45621</v>
+        <v>45618</v>
       </c>
       <c r="C170" s="2">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>5</v>
@@ -2800,10 +2797,10 @@
         <v>4</v>
       </c>
       <c r="B171" s="2">
-        <v>45622</v>
+        <v>45619</v>
       </c>
       <c r="C171" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>5</v>
@@ -2814,10 +2811,10 @@
         <v>4</v>
       </c>
       <c r="B172" s="2">
-        <v>45622</v>
+        <v>45619</v>
       </c>
       <c r="C172" s="2">
-        <v>88</v>
+        <v>163</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>6</v>
@@ -2828,10 +2825,10 @@
         <v>4</v>
       </c>
       <c r="B173" s="2">
-        <v>45623</v>
+        <v>45620</v>
       </c>
       <c r="C173" s="2">
-        <v>124</v>
+        <v>7</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>5</v>
@@ -2842,10 +2839,10 @@
         <v>4</v>
       </c>
       <c r="B174" s="2">
-        <v>45624</v>
+        <v>45621</v>
       </c>
       <c r="C174" s="2">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>5</v>
@@ -2856,13 +2853,13 @@
         <v>4</v>
       </c>
       <c r="B175" s="2">
-        <v>45624</v>
+        <v>45622</v>
       </c>
       <c r="C175" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -2870,10 +2867,10 @@
         <v>4</v>
       </c>
       <c r="B176" s="2">
-        <v>45625</v>
+        <v>45623</v>
       </c>
       <c r="C176" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>5</v>
@@ -2884,13 +2881,13 @@
         <v>4</v>
       </c>
       <c r="B177" s="2">
-        <v>45625</v>
+        <v>45624</v>
       </c>
       <c r="C177" s="2">
-        <v>159</v>
+        <v>36</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -2901,7 +2898,7 @@
         <v>45625</v>
       </c>
       <c r="C178" s="2">
-        <v>132</v>
+        <v>305</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>6</v>
@@ -2912,13 +2909,13 @@
         <v>4</v>
       </c>
       <c r="B179" s="2">
-        <v>45625</v>
+        <v>45626</v>
       </c>
       <c r="C179" s="2">
         <v>4</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -2929,7 +2926,7 @@
         <v>45626</v>
       </c>
       <c r="C180" s="2">
-        <v>98</v>
+        <v>757</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>5</v>
@@ -2943,7 +2940,7 @@
         <v>45628</v>
       </c>
       <c r="C181" s="2">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>6</v>
@@ -2957,7 +2954,7 @@
         <v>45629</v>
       </c>
       <c r="C182" s="2">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>5</v>
@@ -2971,7 +2968,7 @@
         <v>45629</v>
       </c>
       <c r="C183" s="2">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>5</v>
@@ -2982,13 +2979,13 @@
         <v>4</v>
       </c>
       <c r="B184" s="2">
-        <v>45631</v>
+        <v>45632</v>
       </c>
       <c r="C184" s="2">
-        <v>2</v>
+        <v>893</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -2999,10 +2996,10 @@
         <v>45632</v>
       </c>
       <c r="C185" s="2">
-        <v>1</v>
+        <v>711</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -3010,13 +3007,13 @@
         <v>4</v>
       </c>
       <c r="B186" s="2">
-        <v>45632</v>
+        <v>45633</v>
       </c>
       <c r="C186" s="2">
-        <v>580</v>
+        <v>152</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -3027,7 +3024,7 @@
         <v>45635</v>
       </c>
       <c r="C187" s="2">
-        <v>360</v>
+        <v>504</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>5</v>
@@ -3041,10 +3038,10 @@
         <v>45635</v>
       </c>
       <c r="C188" s="2">
-        <v>10</v>
+        <v>735</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3052,13 +3049,13 @@
         <v>4</v>
       </c>
       <c r="B189" s="2">
-        <v>45601</v>
+        <v>45636</v>
       </c>
       <c r="C189" s="2">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3066,13 +3063,13 @@
         <v>4</v>
       </c>
       <c r="B190" s="2">
-        <v>45604</v>
+        <v>45605</v>
       </c>
       <c r="C190" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3080,13 +3077,13 @@
         <v>4</v>
       </c>
       <c r="B191" s="2">
-        <v>45605</v>
+        <v>45606</v>
       </c>
       <c r="C191" s="2">
-        <v>58</v>
+        <v>211</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -3097,10 +3094,10 @@
         <v>45607</v>
       </c>
       <c r="C192" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3108,10 +3105,10 @@
         <v>4</v>
       </c>
       <c r="B193" s="2">
-        <v>45613</v>
+        <v>45608</v>
       </c>
       <c r="C193" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>5</v>
@@ -3122,13 +3119,13 @@
         <v>4</v>
       </c>
       <c r="B194" s="2">
-        <v>45613</v>
+        <v>45609</v>
       </c>
       <c r="C194" s="2">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3136,13 +3133,13 @@
         <v>4</v>
       </c>
       <c r="B195" s="2">
-        <v>45614</v>
+        <v>45610</v>
       </c>
       <c r="C195" s="2">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3150,10 +3147,10 @@
         <v>4</v>
       </c>
       <c r="B196" s="2">
-        <v>45615</v>
+        <v>45610</v>
       </c>
       <c r="C196" s="2">
-        <v>4</v>
+        <v>237</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>5</v>
@@ -3164,13 +3161,13 @@
         <v>4</v>
       </c>
       <c r="B197" s="2">
-        <v>45617</v>
+        <v>45612</v>
       </c>
       <c r="C197" s="2">
-        <v>47</v>
+        <v>208</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3178,10 +3175,10 @@
         <v>4</v>
       </c>
       <c r="B198" s="2">
-        <v>45619</v>
+        <v>45613</v>
       </c>
       <c r="C198" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>5</v>
@@ -3192,13 +3189,13 @@
         <v>4</v>
       </c>
       <c r="B199" s="2">
-        <v>45620</v>
+        <v>45613</v>
       </c>
       <c r="C199" s="2">
-        <v>245</v>
+        <v>606</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -3206,13 +3203,13 @@
         <v>4</v>
       </c>
       <c r="B200" s="2">
-        <v>45621</v>
+        <v>45615</v>
       </c>
       <c r="C200" s="2">
-        <v>412</v>
+        <v>17</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3220,10 +3217,10 @@
         <v>4</v>
       </c>
       <c r="B201" s="2">
-        <v>45622</v>
+        <v>45616</v>
       </c>
       <c r="C201" s="2">
-        <v>2</v>
+        <v>317</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>5</v>
@@ -3234,13 +3231,13 @@
         <v>4</v>
       </c>
       <c r="B202" s="2">
-        <v>45623</v>
+        <v>45616</v>
       </c>
       <c r="C202" s="2">
-        <v>349</v>
+        <v>202</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3248,10 +3245,10 @@
         <v>4</v>
       </c>
       <c r="B203" s="2">
-        <v>45623</v>
+        <v>45619</v>
       </c>
       <c r="C203" s="2">
-        <v>1</v>
+        <v>779</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>5</v>
@@ -3262,13 +3259,13 @@
         <v>4</v>
       </c>
       <c r="B204" s="2">
-        <v>45624</v>
+        <v>45619</v>
       </c>
       <c r="C204" s="2">
-        <v>957</v>
+        <v>719</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -3276,13 +3273,13 @@
         <v>4</v>
       </c>
       <c r="B205" s="2">
-        <v>45625</v>
+        <v>45620</v>
       </c>
       <c r="C205" s="2">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -3290,10 +3287,10 @@
         <v>4</v>
       </c>
       <c r="B206" s="2">
-        <v>45626</v>
+        <v>45622</v>
       </c>
       <c r="C206" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>5</v>
@@ -3304,13 +3301,13 @@
         <v>4</v>
       </c>
       <c r="B207" s="2">
-        <v>45627</v>
+        <v>45622</v>
       </c>
       <c r="C207" s="2">
-        <v>50</v>
+        <v>560</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -3318,10 +3315,10 @@
         <v>4</v>
       </c>
       <c r="B208" s="2">
-        <v>45627</v>
+        <v>45623</v>
       </c>
       <c r="C208" s="2">
-        <v>1018</v>
+        <v>1</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>5</v>
@@ -3332,13 +3329,13 @@
         <v>4</v>
       </c>
       <c r="B209" s="2">
-        <v>45627</v>
+        <v>45623</v>
       </c>
       <c r="C209" s="2">
-        <v>9</v>
+        <v>126</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -3346,10 +3343,10 @@
         <v>4</v>
       </c>
       <c r="B210" s="2">
-        <v>45628</v>
+        <v>45625</v>
       </c>
       <c r="C210" s="2">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>5</v>
@@ -3360,13 +3357,13 @@
         <v>4</v>
       </c>
       <c r="B211" s="2">
-        <v>45629</v>
+        <v>45625</v>
       </c>
       <c r="C211" s="2">
-        <v>1</v>
+        <v>1117</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -3374,13 +3371,13 @@
         <v>4</v>
       </c>
       <c r="B212" s="2">
-        <v>45630</v>
+        <v>45626</v>
       </c>
       <c r="C212" s="2">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -3388,13 +3385,13 @@
         <v>4</v>
       </c>
       <c r="B213" s="2">
-        <v>45630</v>
+        <v>45626</v>
       </c>
       <c r="C213" s="2">
-        <v>392</v>
+        <v>128</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -3402,7 +3399,7 @@
         <v>4</v>
       </c>
       <c r="B214" s="2">
-        <v>45630</v>
+        <v>45628</v>
       </c>
       <c r="C214" s="2">
         <v>2</v>
@@ -3416,10 +3413,10 @@
         <v>4</v>
       </c>
       <c r="B215" s="2">
-        <v>45630</v>
+        <v>45628</v>
       </c>
       <c r="C215" s="2">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>5</v>
@@ -3430,10 +3427,10 @@
         <v>4</v>
       </c>
       <c r="B216" s="2">
-        <v>45631</v>
+        <v>45629</v>
       </c>
       <c r="C216" s="2">
-        <v>86</v>
+        <v>4</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>5</v>
@@ -3444,10 +3441,10 @@
         <v>4</v>
       </c>
       <c r="B217" s="2">
-        <v>45632</v>
+        <v>45631</v>
       </c>
       <c r="C217" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>5</v>
@@ -3458,13 +3455,13 @@
         <v>4</v>
       </c>
       <c r="B218" s="2">
-        <v>45633</v>
+        <v>45631</v>
       </c>
       <c r="C218" s="2">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -3472,10 +3469,10 @@
         <v>4</v>
       </c>
       <c r="B219" s="2">
-        <v>45633</v>
+        <v>45634</v>
       </c>
       <c r="C219" s="2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>5</v>
@@ -3489,7 +3486,7 @@
         <v>45634</v>
       </c>
       <c r="C220" s="2">
-        <v>168</v>
+        <v>66</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>5</v>
@@ -3500,10 +3497,10 @@
         <v>4</v>
       </c>
       <c r="B221" s="2">
-        <v>45636</v>
+        <v>45635</v>
       </c>
       <c r="C221" s="2">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>6</v>
@@ -3531,7 +3528,7 @@
         <v>45637</v>
       </c>
       <c r="C223" s="2">
-        <v>133</v>
+        <v>64</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>5</v>
@@ -3542,10 +3539,10 @@
         <v>4</v>
       </c>
       <c r="B224" s="2">
-        <v>45612</v>
+        <v>45604</v>
       </c>
       <c r="C224" s="2">
-        <v>987</v>
+        <v>31</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>5</v>
@@ -3556,10 +3553,10 @@
         <v>4</v>
       </c>
       <c r="B225" s="2">
-        <v>45613</v>
+        <v>45604</v>
       </c>
       <c r="C225" s="2">
-        <v>7</v>
+        <v>789</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>5</v>
@@ -3570,13 +3567,13 @@
         <v>4</v>
       </c>
       <c r="B226" s="2">
-        <v>45614</v>
+        <v>45605</v>
       </c>
       <c r="C226" s="2">
-        <v>4</v>
+        <v>237</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -3584,10 +3581,10 @@
         <v>4</v>
       </c>
       <c r="B227" s="2">
-        <v>45615</v>
+        <v>45606</v>
       </c>
       <c r="C227" s="2">
-        <v>167</v>
+        <v>4</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>5</v>
@@ -3598,10 +3595,10 @@
         <v>4</v>
       </c>
       <c r="B228" s="2">
-        <v>45616</v>
+        <v>45607</v>
       </c>
       <c r="C228" s="2">
-        <v>65</v>
+        <v>904</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>5</v>
@@ -3612,7 +3609,7 @@
         <v>4</v>
       </c>
       <c r="B229" s="2">
-        <v>45616</v>
+        <v>45609</v>
       </c>
       <c r="C229" s="2">
         <v>1</v>
@@ -3626,13 +3623,13 @@
         <v>4</v>
       </c>
       <c r="B230" s="2">
-        <v>45617</v>
+        <v>45616</v>
       </c>
       <c r="C230" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -3640,13 +3637,13 @@
         <v>4</v>
       </c>
       <c r="B231" s="2">
-        <v>45618</v>
+        <v>45619</v>
       </c>
       <c r="C231" s="2">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -3654,10 +3651,10 @@
         <v>4</v>
       </c>
       <c r="B232" s="2">
-        <v>45618</v>
+        <v>45622</v>
       </c>
       <c r="C232" s="2">
-        <v>343</v>
+        <v>1</v>
       </c>
       <c r="D232" s="2" t="s">
         <v>5</v>
@@ -3668,13 +3665,13 @@
         <v>4</v>
       </c>
       <c r="B233" s="2">
-        <v>45619</v>
+        <v>45622</v>
       </c>
       <c r="C233" s="2">
-        <v>85</v>
+        <v>131</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -3682,13 +3679,13 @@
         <v>4</v>
       </c>
       <c r="B234" s="2">
-        <v>45620</v>
+        <v>45623</v>
       </c>
       <c r="C234" s="2">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -3696,10 +3693,10 @@
         <v>4</v>
       </c>
       <c r="B235" s="2">
-        <v>45620</v>
+        <v>45625</v>
       </c>
       <c r="C235" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>5</v>
@@ -3710,13 +3707,13 @@
         <v>4</v>
       </c>
       <c r="B236" s="2">
-        <v>45621</v>
+        <v>45625</v>
       </c>
       <c r="C236" s="2">
-        <v>78</v>
+        <v>162</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -3724,10 +3721,10 @@
         <v>4</v>
       </c>
       <c r="B237" s="2">
-        <v>45622</v>
+        <v>45625</v>
       </c>
       <c r="C237" s="2">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="D237" s="2" t="s">
         <v>5</v>
@@ -3738,13 +3735,13 @@
         <v>4</v>
       </c>
       <c r="B238" s="2">
-        <v>45624</v>
+        <v>45626</v>
       </c>
       <c r="C238" s="2">
+        <v>302</v>
+      </c>
+      <c r="D238" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D238" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -3752,13 +3749,13 @@
         <v>4</v>
       </c>
       <c r="B239" s="2">
-        <v>45624</v>
+        <v>45627</v>
       </c>
       <c r="C239" s="2">
-        <v>113</v>
+        <v>61</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -3766,13 +3763,13 @@
         <v>4</v>
       </c>
       <c r="B240" s="2">
-        <v>45624</v>
+        <v>45628</v>
       </c>
       <c r="C240" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -3780,13 +3777,13 @@
         <v>4</v>
       </c>
       <c r="B241" s="2">
-        <v>45625</v>
+        <v>45628</v>
       </c>
       <c r="C241" s="2">
-        <v>56</v>
+        <v>476</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -3794,13 +3791,13 @@
         <v>4</v>
       </c>
       <c r="B242" s="2">
-        <v>45626</v>
+        <v>45629</v>
       </c>
       <c r="C242" s="2">
-        <v>410</v>
+        <v>29</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -3808,10 +3805,10 @@
         <v>4</v>
       </c>
       <c r="B243" s="2">
-        <v>45627</v>
+        <v>45630</v>
       </c>
       <c r="C243" s="2">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="D243" s="2" t="s">
         <v>5</v>
@@ -3822,13 +3819,13 @@
         <v>4</v>
       </c>
       <c r="B244" s="2">
-        <v>45629</v>
+        <v>45630</v>
       </c>
       <c r="C244" s="2">
-        <v>85</v>
+        <v>416</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -3836,13 +3833,13 @@
         <v>4</v>
       </c>
       <c r="B245" s="2">
-        <v>45632</v>
+        <v>45631</v>
       </c>
       <c r="C245" s="2">
-        <v>113</v>
+        <v>383</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -3850,10 +3847,10 @@
         <v>4</v>
       </c>
       <c r="B246" s="2">
-        <v>45633</v>
+        <v>45632</v>
       </c>
       <c r="C246" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D246" s="2" t="s">
         <v>5</v>
@@ -3864,13 +3861,13 @@
         <v>4</v>
       </c>
       <c r="B247" s="2">
-        <v>45633</v>
+        <v>45632</v>
       </c>
       <c r="C247" s="2">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -3878,10 +3875,10 @@
         <v>4</v>
       </c>
       <c r="B248" s="2">
-        <v>45634</v>
+        <v>45633</v>
       </c>
       <c r="C248" s="2">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="D248" s="2" t="s">
         <v>5</v>
@@ -3892,10 +3889,10 @@
         <v>4</v>
       </c>
       <c r="B249" s="2">
-        <v>45634</v>
+        <v>45633</v>
       </c>
       <c r="C249" s="2">
-        <v>1</v>
+        <v>881</v>
       </c>
       <c r="D249" s="2" t="s">
         <v>5</v>
@@ -3909,10 +3906,10 @@
         <v>45634</v>
       </c>
       <c r="C250" s="2">
-        <v>160</v>
+        <v>2</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -3920,13 +3917,41 @@
         <v>4</v>
       </c>
       <c r="B251" s="2">
+        <v>45634</v>
+      </c>
+      <c r="C251" s="2">
+        <v>945</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
+      <c r="A252" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B252" s="2">
         <v>45635</v>
       </c>
-      <c r="C251" s="2">
-        <v>135</v>
-      </c>
-      <c r="D251" s="2" t="s">
-        <v>9</v>
+      <c r="C252" s="2">
+        <v>5</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4">
+      <c r="A253" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B253" s="2">
+        <v>45636</v>
+      </c>
+      <c r="C253" s="2">
+        <v>338</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/reports/For Winter Ending (Prior Year)_Visits.xlsx
+++ b/reports/For Winter Ending (Prior Year)_Visits.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="10">
   <si>
     <t>Resort</t>
   </si>
@@ -28,19 +28,22 @@
     <t>Location</t>
   </si>
   <si>
-    <t>Snowbowl</t>
+    <t>Purgatory</t>
   </si>
   <si>
-    <t>Snowbowl Passes</t>
+    <t>Purgatory Passes</t>
   </si>
   <si>
-    <t>Snowbowl Uplift Tickets</t>
+    <t>Purgatory Comp Tickets</t>
   </si>
   <si>
-    <t>Snowbowl Comp Tickets</t>
+    <t>Purgatory Uplift Tickets</t>
   </si>
   <si>
-    <t>Snowbowl Tickets</t>
+    <t>Purgatory Coaster</t>
+  </si>
+  <si>
+    <t>Purgatory Tickets</t>
   </si>
 </sst>
 </file>
@@ -403,13 +406,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D253"/>
+  <dimension ref="A1:D283"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -431,10 +434,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>45604</v>
+        <v>45611</v>
       </c>
       <c r="C2" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -445,10 +448,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>45605</v>
+        <v>45612</v>
       </c>
       <c r="C3" s="2">
-        <v>2</v>
+        <v>129</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>5</v>
@@ -459,10 +462,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>45605</v>
+        <v>45613</v>
       </c>
       <c r="C4" s="2">
-        <v>512</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>5</v>
@@ -473,13 +476,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>45607</v>
+        <v>45614</v>
       </c>
       <c r="C5" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -487,13 +490,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>45607</v>
+        <v>45614</v>
       </c>
       <c r="C6" s="2">
-        <v>103</v>
+        <v>200</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -501,10 +504,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="2">
-        <v>45608</v>
+        <v>45614</v>
       </c>
       <c r="C7" s="2">
-        <v>235</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>5</v>
@@ -515,10 +518,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>45611</v>
+        <v>45615</v>
       </c>
       <c r="C8" s="2">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>5</v>
@@ -529,13 +532,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>45612</v>
+        <v>45616</v>
       </c>
       <c r="C9" s="2">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -543,13 +546,13 @@
         <v>4</v>
       </c>
       <c r="B10" s="2">
-        <v>45615</v>
+        <v>45617</v>
       </c>
       <c r="C10" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -560,10 +563,10 @@
         <v>45618</v>
       </c>
       <c r="C11" s="2">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -571,10 +574,10 @@
         <v>4</v>
       </c>
       <c r="B12" s="2">
-        <v>45621</v>
+        <v>45620</v>
       </c>
       <c r="C12" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>5</v>
@@ -585,13 +588,13 @@
         <v>4</v>
       </c>
       <c r="B13" s="2">
-        <v>45621</v>
+        <v>45620</v>
       </c>
       <c r="C13" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -599,10 +602,10 @@
         <v>4</v>
       </c>
       <c r="B14" s="2">
-        <v>45623</v>
+        <v>45620</v>
       </c>
       <c r="C14" s="2">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>5</v>
@@ -613,10 +616,10 @@
         <v>4</v>
       </c>
       <c r="B15" s="2">
-        <v>45624</v>
+        <v>45621</v>
       </c>
       <c r="C15" s="2">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>5</v>
@@ -627,13 +630,13 @@
         <v>4</v>
       </c>
       <c r="B16" s="2">
-        <v>45624</v>
+        <v>45623</v>
       </c>
       <c r="C16" s="2">
-        <v>824</v>
+        <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -641,13 +644,13 @@
         <v>4</v>
       </c>
       <c r="B17" s="2">
-        <v>45626</v>
+        <v>45623</v>
       </c>
       <c r="C17" s="2">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -655,13 +658,13 @@
         <v>4</v>
       </c>
       <c r="B18" s="2">
-        <v>45626</v>
+        <v>45624</v>
       </c>
       <c r="C18" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -669,13 +672,13 @@
         <v>4</v>
       </c>
       <c r="B19" s="2">
-        <v>45627</v>
+        <v>45626</v>
       </c>
       <c r="C19" s="2">
-        <v>786</v>
+        <v>7</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -686,10 +689,10 @@
         <v>45627</v>
       </c>
       <c r="C20" s="2">
-        <v>160</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -697,7 +700,7 @@
         <v>4</v>
       </c>
       <c r="B21" s="2">
-        <v>45628</v>
+        <v>45627</v>
       </c>
       <c r="C21" s="2">
         <v>1</v>
@@ -711,13 +714,13 @@
         <v>4</v>
       </c>
       <c r="B22" s="2">
-        <v>45629</v>
+        <v>45627</v>
       </c>
       <c r="C22" s="2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -728,10 +731,10 @@
         <v>45630</v>
       </c>
       <c r="C23" s="2">
-        <v>485</v>
+        <v>90</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -739,13 +742,13 @@
         <v>4</v>
       </c>
       <c r="B24" s="2">
-        <v>45630</v>
+        <v>45633</v>
       </c>
       <c r="C24" s="2">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -753,13 +756,13 @@
         <v>4</v>
       </c>
       <c r="B25" s="2">
-        <v>45631</v>
+        <v>45633</v>
       </c>
       <c r="C25" s="2">
-        <v>4</v>
+        <v>295</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -767,10 +770,10 @@
         <v>4</v>
       </c>
       <c r="B26" s="2">
-        <v>45633</v>
+        <v>45635</v>
       </c>
       <c r="C26" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>5</v>
@@ -781,13 +784,13 @@
         <v>4</v>
       </c>
       <c r="B27" s="2">
-        <v>45633</v>
+        <v>45636</v>
       </c>
       <c r="C27" s="2">
-        <v>1404</v>
+        <v>135</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -795,13 +798,13 @@
         <v>4</v>
       </c>
       <c r="B28" s="2">
-        <v>45633</v>
+        <v>45637</v>
       </c>
       <c r="C28" s="2">
-        <v>118</v>
+        <v>514</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -809,10 +812,10 @@
         <v>4</v>
       </c>
       <c r="B29" s="2">
-        <v>45634</v>
+        <v>45638</v>
       </c>
       <c r="C29" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>5</v>
@@ -823,10 +826,10 @@
         <v>4</v>
       </c>
       <c r="B30" s="2">
-        <v>45634</v>
+        <v>45638</v>
       </c>
       <c r="C30" s="2">
-        <v>854</v>
+        <v>1</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>5</v>
@@ -837,13 +840,13 @@
         <v>4</v>
       </c>
       <c r="B31" s="2">
-        <v>45636</v>
+        <v>45639</v>
       </c>
       <c r="C31" s="2">
-        <v>2</v>
+        <v>265</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -851,13 +854,13 @@
         <v>4</v>
       </c>
       <c r="B32" s="2">
-        <v>45636</v>
+        <v>45640</v>
       </c>
       <c r="C32" s="2">
-        <v>0</v>
+        <v>1413</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -865,10 +868,10 @@
         <v>4</v>
       </c>
       <c r="B33" s="2">
-        <v>45637</v>
+        <v>45612</v>
       </c>
       <c r="C33" s="2">
-        <v>2</v>
+        <v>987</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>5</v>
@@ -879,10 +882,10 @@
         <v>4</v>
       </c>
       <c r="B34" s="2">
-        <v>45637</v>
+        <v>45613</v>
       </c>
       <c r="C34" s="2">
-        <v>535</v>
+        <v>7</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>5</v>
@@ -893,10 +896,10 @@
         <v>4</v>
       </c>
       <c r="B35" s="2">
-        <v>45604</v>
+        <v>45614</v>
       </c>
       <c r="C35" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>5</v>
@@ -907,10 +910,10 @@
         <v>4</v>
       </c>
       <c r="B36" s="2">
-        <v>45606</v>
+        <v>45615</v>
       </c>
       <c r="C36" s="2">
-        <v>1</v>
+        <v>167</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>5</v>
@@ -921,13 +924,13 @@
         <v>4</v>
       </c>
       <c r="B37" s="2">
-        <v>45606</v>
+        <v>45616</v>
       </c>
       <c r="C37" s="2">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -935,13 +938,13 @@
         <v>4</v>
       </c>
       <c r="B38" s="2">
-        <v>45609</v>
+        <v>45616</v>
       </c>
       <c r="C38" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -949,13 +952,13 @@
         <v>4</v>
       </c>
       <c r="B39" s="2">
-        <v>45610</v>
+        <v>45617</v>
       </c>
       <c r="C39" s="2">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -963,13 +966,13 @@
         <v>4</v>
       </c>
       <c r="B40" s="2">
-        <v>45612</v>
+        <v>45618</v>
       </c>
       <c r="C40" s="2">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -977,13 +980,13 @@
         <v>4</v>
       </c>
       <c r="B41" s="2">
-        <v>45613</v>
+        <v>45618</v>
       </c>
       <c r="C41" s="2">
-        <v>217</v>
+        <v>343</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -991,10 +994,10 @@
         <v>4</v>
       </c>
       <c r="B42" s="2">
-        <v>45614</v>
+        <v>45619</v>
       </c>
       <c r="C42" s="2">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>5</v>
@@ -1005,10 +1008,10 @@
         <v>4</v>
       </c>
       <c r="B43" s="2">
-        <v>45614</v>
+        <v>45620</v>
       </c>
       <c r="C43" s="2">
-        <v>320</v>
+        <v>2</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>5</v>
@@ -1019,13 +1022,13 @@
         <v>4</v>
       </c>
       <c r="B44" s="2">
-        <v>45615</v>
+        <v>45620</v>
       </c>
       <c r="C44" s="2">
-        <v>194</v>
+        <v>1</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1033,13 +1036,13 @@
         <v>4</v>
       </c>
       <c r="B45" s="2">
-        <v>45616</v>
+        <v>45621</v>
       </c>
       <c r="C45" s="2">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1047,13 +1050,13 @@
         <v>4</v>
       </c>
       <c r="B46" s="2">
-        <v>45616</v>
+        <v>45622</v>
       </c>
       <c r="C46" s="2">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1061,10 +1064,10 @@
         <v>4</v>
       </c>
       <c r="B47" s="2">
-        <v>45617</v>
+        <v>45624</v>
       </c>
       <c r="C47" s="2">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>5</v>
@@ -1075,13 +1078,13 @@
         <v>4</v>
       </c>
       <c r="B48" s="2">
-        <v>45617</v>
+        <v>45624</v>
       </c>
       <c r="C48" s="2">
-        <v>272</v>
+        <v>113</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1089,13 +1092,13 @@
         <v>4</v>
       </c>
       <c r="B49" s="2">
-        <v>45618</v>
+        <v>45624</v>
       </c>
       <c r="C49" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1103,13 +1106,13 @@
         <v>4</v>
       </c>
       <c r="B50" s="2">
-        <v>45618</v>
+        <v>45625</v>
       </c>
       <c r="C50" s="2">
-        <v>482</v>
+        <v>56</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1117,13 +1120,13 @@
         <v>4</v>
       </c>
       <c r="B51" s="2">
-        <v>45619</v>
+        <v>45626</v>
       </c>
       <c r="C51" s="2">
-        <v>10</v>
+        <v>410</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1131,10 +1134,10 @@
         <v>4</v>
       </c>
       <c r="B52" s="2">
-        <v>45620</v>
+        <v>45627</v>
       </c>
       <c r="C52" s="2">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>5</v>
@@ -1145,13 +1148,13 @@
         <v>4</v>
       </c>
       <c r="B53" s="2">
-        <v>45620</v>
+        <v>45629</v>
       </c>
       <c r="C53" s="2">
-        <v>670</v>
+        <v>85</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1159,13 +1162,13 @@
         <v>4</v>
       </c>
       <c r="B54" s="2">
-        <v>45621</v>
+        <v>45632</v>
       </c>
       <c r="C54" s="2">
-        <v>5</v>
+        <v>113</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1173,13 +1176,13 @@
         <v>4</v>
       </c>
       <c r="B55" s="2">
-        <v>45621</v>
+        <v>45633</v>
       </c>
       <c r="C55" s="2">
-        <v>529</v>
+        <v>3</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1187,10 +1190,10 @@
         <v>4</v>
       </c>
       <c r="B56" s="2">
-        <v>45622</v>
+        <v>45633</v>
       </c>
       <c r="C56" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>5</v>
@@ -1201,10 +1204,10 @@
         <v>4</v>
       </c>
       <c r="B57" s="2">
-        <v>45623</v>
+        <v>45634</v>
       </c>
       <c r="C57" s="2">
-        <v>608</v>
+        <v>1</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>5</v>
@@ -1215,10 +1218,10 @@
         <v>4</v>
       </c>
       <c r="B58" s="2">
-        <v>45624</v>
+        <v>45634</v>
       </c>
       <c r="C58" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>5</v>
@@ -1229,13 +1232,13 @@
         <v>4</v>
       </c>
       <c r="B59" s="2">
-        <v>45625</v>
+        <v>45634</v>
       </c>
       <c r="C59" s="2">
-        <v>9</v>
+        <v>160</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1243,13 +1246,13 @@
         <v>4</v>
       </c>
       <c r="B60" s="2">
-        <v>45625</v>
+        <v>45635</v>
       </c>
       <c r="C60" s="2">
-        <v>1</v>
+        <v>135</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1257,7 +1260,7 @@
         <v>4</v>
       </c>
       <c r="B61" s="2">
-        <v>45627</v>
+        <v>45639</v>
       </c>
       <c r="C61" s="2">
         <v>1</v>
@@ -1271,13 +1274,13 @@
         <v>4</v>
       </c>
       <c r="B62" s="2">
-        <v>45629</v>
+        <v>45639</v>
       </c>
       <c r="C62" s="2">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1285,13 +1288,13 @@
         <v>4</v>
       </c>
       <c r="B63" s="2">
-        <v>45632</v>
+        <v>45639</v>
       </c>
       <c r="C63" s="2">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1299,10 +1302,10 @@
         <v>4</v>
       </c>
       <c r="B64" s="2">
-        <v>45635</v>
+        <v>45640</v>
       </c>
       <c r="C64" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>5</v>
@@ -1313,13 +1316,13 @@
         <v>4</v>
       </c>
       <c r="B65" s="2">
-        <v>45635</v>
+        <v>45604</v>
       </c>
       <c r="C65" s="2">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1330,10 +1333,10 @@
         <v>45605</v>
       </c>
       <c r="C66" s="2">
-        <v>187</v>
+        <v>6</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1344,10 +1347,10 @@
         <v>45606</v>
       </c>
       <c r="C67" s="2">
-        <v>29</v>
+        <v>127</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1355,13 +1358,13 @@
         <v>4</v>
       </c>
       <c r="B68" s="2">
-        <v>45607</v>
+        <v>45612</v>
       </c>
       <c r="C68" s="2">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1369,13 +1372,13 @@
         <v>4</v>
       </c>
       <c r="B69" s="2">
-        <v>45608</v>
+        <v>45613</v>
       </c>
       <c r="C69" s="2">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1383,13 +1386,13 @@
         <v>4</v>
       </c>
       <c r="B70" s="2">
-        <v>45609</v>
+        <v>45615</v>
       </c>
       <c r="C70" s="2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1397,13 +1400,13 @@
         <v>4</v>
       </c>
       <c r="B71" s="2">
-        <v>45609</v>
+        <v>45615</v>
       </c>
       <c r="C71" s="2">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1411,13 +1414,13 @@
         <v>4</v>
       </c>
       <c r="B72" s="2">
-        <v>45611</v>
+        <v>45616</v>
       </c>
       <c r="C72" s="2">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1425,10 +1428,10 @@
         <v>4</v>
       </c>
       <c r="B73" s="2">
-        <v>45612</v>
+        <v>45619</v>
       </c>
       <c r="C73" s="2">
-        <v>37</v>
+        <v>623</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>5</v>
@@ -1439,10 +1442,10 @@
         <v>4</v>
       </c>
       <c r="B74" s="2">
-        <v>45612</v>
+        <v>45619</v>
       </c>
       <c r="C74" s="2">
-        <v>614</v>
+        <v>8</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>5</v>
@@ -1453,7 +1456,7 @@
         <v>4</v>
       </c>
       <c r="B75" s="2">
-        <v>45614</v>
+        <v>45621</v>
       </c>
       <c r="C75" s="2">
         <v>1</v>
@@ -1467,10 +1470,10 @@
         <v>4</v>
       </c>
       <c r="B76" s="2">
-        <v>45615</v>
+        <v>45622</v>
       </c>
       <c r="C76" s="2">
-        <v>247</v>
+        <v>454</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>5</v>
@@ -1481,13 +1484,13 @@
         <v>4</v>
       </c>
       <c r="B77" s="2">
-        <v>45617</v>
+        <v>45622</v>
       </c>
       <c r="C77" s="2">
-        <v>4</v>
+        <v>284</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1495,13 +1498,13 @@
         <v>4</v>
       </c>
       <c r="B78" s="2">
-        <v>45620</v>
+        <v>45622</v>
       </c>
       <c r="C78" s="2">
-        <v>681</v>
+        <v>3</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1509,7 +1512,7 @@
         <v>4</v>
       </c>
       <c r="B79" s="2">
-        <v>45620</v>
+        <v>45624</v>
       </c>
       <c r="C79" s="2">
         <v>1</v>
@@ -1523,13 +1526,13 @@
         <v>4</v>
       </c>
       <c r="B80" s="2">
-        <v>45623</v>
+        <v>45625</v>
       </c>
       <c r="C80" s="2">
-        <v>802</v>
+        <v>426</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -1537,13 +1540,13 @@
         <v>4</v>
       </c>
       <c r="B81" s="2">
-        <v>45624</v>
+        <v>45625</v>
       </c>
       <c r="C81" s="2">
-        <v>156</v>
+        <v>1</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -1551,13 +1554,13 @@
         <v>4</v>
       </c>
       <c r="B82" s="2">
-        <v>45626</v>
+        <v>45625</v>
       </c>
       <c r="C82" s="2">
-        <v>785</v>
+        <v>28</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1568,7 +1571,7 @@
         <v>45627</v>
       </c>
       <c r="C83" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>5</v>
@@ -1579,13 +1582,13 @@
         <v>4</v>
       </c>
       <c r="B84" s="2">
-        <v>45627</v>
+        <v>45628</v>
       </c>
       <c r="C84" s="2">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -1593,13 +1596,13 @@
         <v>4</v>
       </c>
       <c r="B85" s="2">
-        <v>45629</v>
+        <v>45628</v>
       </c>
       <c r="C85" s="2">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1607,13 +1610,13 @@
         <v>4</v>
       </c>
       <c r="B86" s="2">
-        <v>45629</v>
+        <v>45628</v>
       </c>
       <c r="C86" s="2">
-        <v>455</v>
+        <v>8</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -1621,7 +1624,7 @@
         <v>4</v>
       </c>
       <c r="B87" s="2">
-        <v>45630</v>
+        <v>45631</v>
       </c>
       <c r="C87" s="2">
         <v>1</v>
@@ -1635,13 +1638,13 @@
         <v>4</v>
       </c>
       <c r="B88" s="2">
-        <v>45630</v>
+        <v>45631</v>
       </c>
       <c r="C88" s="2">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -1649,13 +1652,13 @@
         <v>4</v>
       </c>
       <c r="B89" s="2">
-        <v>45631</v>
+        <v>45634</v>
       </c>
       <c r="C89" s="2">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1663,10 +1666,10 @@
         <v>4</v>
       </c>
       <c r="B90" s="2">
-        <v>45632</v>
+        <v>45634</v>
       </c>
       <c r="C90" s="2">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>5</v>
@@ -1677,13 +1680,13 @@
         <v>4</v>
       </c>
       <c r="B91" s="2">
-        <v>45633</v>
+        <v>45635</v>
       </c>
       <c r="C91" s="2">
+        <v>25</v>
+      </c>
+      <c r="D91" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -1691,13 +1694,13 @@
         <v>4</v>
       </c>
       <c r="B92" s="2">
-        <v>45634</v>
+        <v>45636</v>
       </c>
       <c r="C92" s="2">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -1705,10 +1708,10 @@
         <v>4</v>
       </c>
       <c r="B93" s="2">
-        <v>45635</v>
+        <v>45637</v>
       </c>
       <c r="C93" s="2">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>5</v>
@@ -1719,10 +1722,10 @@
         <v>4</v>
       </c>
       <c r="B94" s="2">
-        <v>45636</v>
+        <v>45637</v>
       </c>
       <c r="C94" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>5</v>
@@ -1733,13 +1736,13 @@
         <v>4</v>
       </c>
       <c r="B95" s="2">
-        <v>45637</v>
+        <v>45638</v>
       </c>
       <c r="C95" s="2">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -1747,13 +1750,13 @@
         <v>4</v>
       </c>
       <c r="B96" s="2">
-        <v>45605</v>
+        <v>45638</v>
       </c>
       <c r="C96" s="2">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -1761,13 +1764,13 @@
         <v>4</v>
       </c>
       <c r="B97" s="2">
-        <v>45605</v>
+        <v>45639</v>
       </c>
       <c r="C97" s="2">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -1775,10 +1778,10 @@
         <v>4</v>
       </c>
       <c r="B98" s="2">
-        <v>45607</v>
+        <v>45640</v>
       </c>
       <c r="C98" s="2">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>5</v>
@@ -1789,10 +1792,10 @@
         <v>4</v>
       </c>
       <c r="B99" s="2">
-        <v>45608</v>
+        <v>45606</v>
       </c>
       <c r="C99" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>5</v>
@@ -1803,10 +1806,10 @@
         <v>4</v>
       </c>
       <c r="B100" s="2">
-        <v>45608</v>
+        <v>45610</v>
       </c>
       <c r="C100" s="2">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>8</v>
@@ -1820,10 +1823,10 @@
         <v>45610</v>
       </c>
       <c r="C101" s="2">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -1831,13 +1834,13 @@
         <v>4</v>
       </c>
       <c r="B102" s="2">
-        <v>45611</v>
+        <v>45612</v>
       </c>
       <c r="C102" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -1848,7 +1851,7 @@
         <v>45612</v>
       </c>
       <c r="C103" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>5</v>
@@ -1862,10 +1865,10 @@
         <v>45613</v>
       </c>
       <c r="C104" s="2">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -1876,7 +1879,7 @@
         <v>45614</v>
       </c>
       <c r="C105" s="2">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>5</v>
@@ -1887,13 +1890,13 @@
         <v>4</v>
       </c>
       <c r="B106" s="2">
-        <v>45614</v>
+        <v>45616</v>
       </c>
       <c r="C106" s="2">
-        <v>236</v>
+        <v>15</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -1901,13 +1904,13 @@
         <v>4</v>
       </c>
       <c r="B107" s="2">
-        <v>45614</v>
+        <v>45616</v>
       </c>
       <c r="C107" s="2">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -1915,10 +1918,10 @@
         <v>4</v>
       </c>
       <c r="B108" s="2">
-        <v>45616</v>
+        <v>45617</v>
       </c>
       <c r="C108" s="2">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>5</v>
@@ -1932,7 +1935,7 @@
         <v>45617</v>
       </c>
       <c r="C109" s="2">
-        <v>3</v>
+        <v>234</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>5</v>
@@ -1943,13 +1946,13 @@
         <v>4</v>
       </c>
       <c r="B110" s="2">
-        <v>45617</v>
+        <v>45618</v>
       </c>
       <c r="C110" s="2">
-        <v>209</v>
+        <v>91</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -1957,10 +1960,10 @@
         <v>4</v>
       </c>
       <c r="B111" s="2">
-        <v>45617</v>
+        <v>45619</v>
       </c>
       <c r="C111" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>6</v>
@@ -1971,10 +1974,10 @@
         <v>4</v>
       </c>
       <c r="B112" s="2">
-        <v>45618</v>
+        <v>45620</v>
       </c>
       <c r="C112" s="2">
-        <v>8</v>
+        <v>541</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>5</v>
@@ -1985,13 +1988,13 @@
         <v>4</v>
       </c>
       <c r="B113" s="2">
-        <v>45618</v>
+        <v>45621</v>
       </c>
       <c r="C113" s="2">
-        <v>770</v>
+        <v>224</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -1999,13 +2002,13 @@
         <v>4</v>
       </c>
       <c r="B114" s="2">
-        <v>45620</v>
+        <v>45621</v>
       </c>
       <c r="C114" s="2">
-        <v>298</v>
+        <v>1</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2013,13 +2016,13 @@
         <v>4</v>
       </c>
       <c r="B115" s="2">
-        <v>45621</v>
+        <v>45622</v>
       </c>
       <c r="C115" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2027,10 +2030,10 @@
         <v>4</v>
       </c>
       <c r="B116" s="2">
-        <v>45621</v>
+        <v>45623</v>
       </c>
       <c r="C116" s="2">
-        <v>480</v>
+        <v>991</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>5</v>
@@ -2041,13 +2044,13 @@
         <v>4</v>
       </c>
       <c r="B117" s="2">
-        <v>45623</v>
+        <v>45624</v>
       </c>
       <c r="C117" s="2">
-        <v>1</v>
+        <v>340</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2058,7 +2061,7 @@
         <v>45624</v>
       </c>
       <c r="C118" s="2">
-        <v>583</v>
+        <v>1</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>5</v>
@@ -2069,10 +2072,10 @@
         <v>4</v>
       </c>
       <c r="B119" s="2">
-        <v>45627</v>
+        <v>45624</v>
       </c>
       <c r="C119" s="2">
-        <v>637</v>
+        <v>18</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>5</v>
@@ -2083,13 +2086,13 @@
         <v>4</v>
       </c>
       <c r="B120" s="2">
-        <v>45628</v>
+        <v>45625</v>
       </c>
       <c r="C120" s="2">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2097,13 +2100,13 @@
         <v>4</v>
       </c>
       <c r="B121" s="2">
-        <v>45631</v>
+        <v>45626</v>
       </c>
       <c r="C121" s="2">
-        <v>28</v>
+        <v>1024</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2111,13 +2114,13 @@
         <v>4</v>
       </c>
       <c r="B122" s="2">
-        <v>45634</v>
+        <v>45627</v>
       </c>
       <c r="C122" s="2">
-        <v>2</v>
+        <v>173</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2128,10 +2131,10 @@
         <v>45634</v>
       </c>
       <c r="C123" s="2">
-        <v>93</v>
+        <v>5</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2139,10 +2142,10 @@
         <v>4</v>
       </c>
       <c r="B124" s="2">
-        <v>45636</v>
+        <v>45635</v>
       </c>
       <c r="C124" s="2">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>5</v>
@@ -2153,10 +2156,10 @@
         <v>4</v>
       </c>
       <c r="B125" s="2">
-        <v>45637</v>
+        <v>45636</v>
       </c>
       <c r="C125" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>5</v>
@@ -2167,13 +2170,13 @@
         <v>4</v>
       </c>
       <c r="B126" s="2">
-        <v>45637</v>
+        <v>45638</v>
       </c>
       <c r="C126" s="2">
-        <v>778</v>
+        <v>1</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2181,10 +2184,10 @@
         <v>4</v>
       </c>
       <c r="B127" s="2">
-        <v>45604</v>
+        <v>45638</v>
       </c>
       <c r="C127" s="2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>5</v>
@@ -2195,7 +2198,7 @@
         <v>4</v>
       </c>
       <c r="B128" s="2">
-        <v>45604</v>
+        <v>45639</v>
       </c>
       <c r="C128" s="2">
         <v>1</v>
@@ -2209,13 +2212,13 @@
         <v>4</v>
       </c>
       <c r="B129" s="2">
-        <v>45604</v>
+        <v>45639</v>
       </c>
       <c r="C129" s="2">
-        <v>139</v>
+        <v>63</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2223,13 +2226,13 @@
         <v>4</v>
       </c>
       <c r="B130" s="2">
-        <v>45607</v>
+        <v>45640</v>
       </c>
       <c r="C130" s="2">
-        <v>473</v>
+        <v>145</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2237,13 +2240,13 @@
         <v>4</v>
       </c>
       <c r="B131" s="2">
-        <v>45608</v>
+        <v>45601</v>
       </c>
       <c r="C131" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2251,13 +2254,13 @@
         <v>4</v>
       </c>
       <c r="B132" s="2">
-        <v>45610</v>
+        <v>45604</v>
       </c>
       <c r="C132" s="2">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2265,13 +2268,13 @@
         <v>4</v>
       </c>
       <c r="B133" s="2">
-        <v>45611</v>
+        <v>45605</v>
       </c>
       <c r="C133" s="2">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2279,13 +2282,13 @@
         <v>4</v>
       </c>
       <c r="B134" s="2">
-        <v>45613</v>
+        <v>45605</v>
       </c>
       <c r="C134" s="2">
-        <v>468</v>
+        <v>8</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2293,13 +2296,13 @@
         <v>4</v>
       </c>
       <c r="B135" s="2">
-        <v>45614</v>
+        <v>45612</v>
       </c>
       <c r="C135" s="2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2307,10 +2310,10 @@
         <v>4</v>
       </c>
       <c r="B136" s="2">
-        <v>45616</v>
+        <v>45613</v>
       </c>
       <c r="C136" s="2">
-        <v>3</v>
+        <v>769</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>5</v>
@@ -2321,13 +2324,13 @@
         <v>4</v>
       </c>
       <c r="B137" s="2">
-        <v>45617</v>
+        <v>45615</v>
       </c>
       <c r="C137" s="2">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -2338,10 +2341,10 @@
         <v>45618</v>
       </c>
       <c r="C138" s="2">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -2352,7 +2355,7 @@
         <v>45619</v>
       </c>
       <c r="C139" s="2">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>5</v>
@@ -2363,13 +2366,13 @@
         <v>4</v>
       </c>
       <c r="B140" s="2">
-        <v>45621</v>
+        <v>45619</v>
       </c>
       <c r="C140" s="2">
-        <v>158</v>
+        <v>4</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2377,10 +2380,10 @@
         <v>4</v>
       </c>
       <c r="B141" s="2">
-        <v>45622</v>
+        <v>45619</v>
       </c>
       <c r="C141" s="2">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>5</v>
@@ -2391,13 +2394,13 @@
         <v>4</v>
       </c>
       <c r="B142" s="2">
-        <v>45622</v>
+        <v>45620</v>
       </c>
       <c r="C142" s="2">
-        <v>415</v>
+        <v>14</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2405,10 +2408,10 @@
         <v>4</v>
       </c>
       <c r="B143" s="2">
-        <v>45623</v>
+        <v>45622</v>
       </c>
       <c r="C143" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>5</v>
@@ -2433,13 +2436,13 @@
         <v>4</v>
       </c>
       <c r="B145" s="2">
-        <v>45624</v>
+        <v>45623</v>
       </c>
       <c r="C145" s="2">
-        <v>7</v>
+        <v>125</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -2450,10 +2453,10 @@
         <v>45624</v>
       </c>
       <c r="C146" s="2">
-        <v>326</v>
+        <v>91</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -2464,7 +2467,7 @@
         <v>45625</v>
       </c>
       <c r="C147" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>5</v>
@@ -2478,7 +2481,7 @@
         <v>45625</v>
       </c>
       <c r="C148" s="2">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>5</v>
@@ -2489,10 +2492,10 @@
         <v>4</v>
       </c>
       <c r="B149" s="2">
-        <v>45625</v>
+        <v>45626</v>
       </c>
       <c r="C149" s="2">
-        <v>935</v>
+        <v>1</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>5</v>
@@ -2503,13 +2506,13 @@
         <v>4</v>
       </c>
       <c r="B150" s="2">
-        <v>45627</v>
+        <v>45626</v>
       </c>
       <c r="C150" s="2">
-        <v>7</v>
+        <v>297</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -2517,13 +2520,13 @@
         <v>4</v>
       </c>
       <c r="B151" s="2">
-        <v>45628</v>
+        <v>45626</v>
       </c>
       <c r="C151" s="2">
-        <v>388</v>
+        <v>115</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -2531,10 +2534,10 @@
         <v>4</v>
       </c>
       <c r="B152" s="2">
-        <v>45630</v>
+        <v>45627</v>
       </c>
       <c r="C152" s="2">
-        <v>5</v>
+        <v>114</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>5</v>
@@ -2545,10 +2548,10 @@
         <v>4</v>
       </c>
       <c r="B153" s="2">
-        <v>45631</v>
+        <v>45628</v>
       </c>
       <c r="C153" s="2">
-        <v>376</v>
+        <v>1</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>5</v>
@@ -2559,13 +2562,13 @@
         <v>4</v>
       </c>
       <c r="B154" s="2">
-        <v>45633</v>
+        <v>45629</v>
       </c>
       <c r="C154" s="2">
-        <v>15</v>
+        <v>-3</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -2573,13 +2576,13 @@
         <v>4</v>
       </c>
       <c r="B155" s="2">
-        <v>45636</v>
+        <v>45629</v>
       </c>
       <c r="C155" s="2">
-        <v>642</v>
+        <v>21</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -2587,13 +2590,13 @@
         <v>4</v>
       </c>
       <c r="B156" s="2">
-        <v>45637</v>
+        <v>45630</v>
       </c>
       <c r="C156" s="2">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -2601,10 +2604,10 @@
         <v>4</v>
       </c>
       <c r="B157" s="2">
-        <v>45597</v>
+        <v>45631</v>
       </c>
       <c r="C157" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>5</v>
@@ -2615,13 +2618,13 @@
         <v>4</v>
       </c>
       <c r="B158" s="2">
-        <v>45604</v>
+        <v>45632</v>
       </c>
       <c r="C158" s="2">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -2629,10 +2632,10 @@
         <v>4</v>
       </c>
       <c r="B159" s="2">
-        <v>45606</v>
+        <v>45633</v>
       </c>
       <c r="C159" s="2">
-        <v>3</v>
+        <v>149</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>5</v>
@@ -2643,10 +2646,10 @@
         <v>4</v>
       </c>
       <c r="B160" s="2">
-        <v>45606</v>
+        <v>45633</v>
       </c>
       <c r="C160" s="2">
-        <v>549</v>
+        <v>1558</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>5</v>
@@ -2657,13 +2660,13 @@
         <v>4</v>
       </c>
       <c r="B161" s="2">
-        <v>45606</v>
+        <v>45634</v>
       </c>
       <c r="C161" s="2">
-        <v>290</v>
+        <v>160</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -2671,13 +2674,13 @@
         <v>4</v>
       </c>
       <c r="B162" s="2">
-        <v>45607</v>
+        <v>45634</v>
       </c>
       <c r="C162" s="2">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -2685,13 +2688,13 @@
         <v>4</v>
       </c>
       <c r="B163" s="2">
-        <v>45609</v>
+        <v>45636</v>
       </c>
       <c r="C163" s="2">
-        <v>186</v>
+        <v>397</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -2699,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B164" s="2">
-        <v>45610</v>
+        <v>45637</v>
       </c>
       <c r="C164" s="2">
-        <v>8</v>
+        <v>151</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -2713,10 +2716,10 @@
         <v>4</v>
       </c>
       <c r="B165" s="2">
-        <v>45612</v>
+        <v>45637</v>
       </c>
       <c r="C165" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>5</v>
@@ -2727,13 +2730,13 @@
         <v>4</v>
       </c>
       <c r="B166" s="2">
-        <v>45613</v>
+        <v>45638</v>
       </c>
       <c r="C166" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -2741,13 +2744,13 @@
         <v>4</v>
       </c>
       <c r="B167" s="2">
-        <v>45613</v>
+        <v>45639</v>
       </c>
       <c r="C167" s="2">
-        <v>31</v>
+        <v>573</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -2755,13 +2758,13 @@
         <v>4</v>
       </c>
       <c r="B168" s="2">
-        <v>45615</v>
+        <v>45640</v>
       </c>
       <c r="C168" s="2">
-        <v>3</v>
+        <v>570</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -2769,10 +2772,10 @@
         <v>4</v>
       </c>
       <c r="B169" s="2">
-        <v>45615</v>
+        <v>45640</v>
       </c>
       <c r="C169" s="2">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>5</v>
@@ -2783,10 +2786,10 @@
         <v>4</v>
       </c>
       <c r="B170" s="2">
-        <v>45618</v>
+        <v>45601</v>
       </c>
       <c r="C170" s="2">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>5</v>
@@ -2797,13 +2800,13 @@
         <v>4</v>
       </c>
       <c r="B171" s="2">
-        <v>45619</v>
+        <v>45604</v>
       </c>
       <c r="C171" s="2">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -2811,13 +2814,13 @@
         <v>4</v>
       </c>
       <c r="B172" s="2">
-        <v>45619</v>
+        <v>45605</v>
       </c>
       <c r="C172" s="2">
-        <v>163</v>
+        <v>58</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -2825,13 +2828,13 @@
         <v>4</v>
       </c>
       <c r="B173" s="2">
-        <v>45620</v>
+        <v>45607</v>
       </c>
       <c r="C173" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -2839,10 +2842,10 @@
         <v>4</v>
       </c>
       <c r="B174" s="2">
-        <v>45621</v>
+        <v>45613</v>
       </c>
       <c r="C174" s="2">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>5</v>
@@ -2853,13 +2856,13 @@
         <v>4</v>
       </c>
       <c r="B175" s="2">
-        <v>45622</v>
+        <v>45613</v>
       </c>
       <c r="C175" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -2867,13 +2870,13 @@
         <v>4</v>
       </c>
       <c r="B176" s="2">
-        <v>45623</v>
+        <v>45614</v>
       </c>
       <c r="C176" s="2">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -2881,10 +2884,10 @@
         <v>4</v>
       </c>
       <c r="B177" s="2">
-        <v>45624</v>
+        <v>45615</v>
       </c>
       <c r="C177" s="2">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>5</v>
@@ -2895,13 +2898,13 @@
         <v>4</v>
       </c>
       <c r="B178" s="2">
-        <v>45625</v>
+        <v>45617</v>
       </c>
       <c r="C178" s="2">
-        <v>305</v>
+        <v>47</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -2909,10 +2912,10 @@
         <v>4</v>
       </c>
       <c r="B179" s="2">
-        <v>45626</v>
+        <v>45619</v>
       </c>
       <c r="C179" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>5</v>
@@ -2923,13 +2926,13 @@
         <v>4</v>
       </c>
       <c r="B180" s="2">
-        <v>45626</v>
+        <v>45620</v>
       </c>
       <c r="C180" s="2">
-        <v>757</v>
+        <v>245</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -2937,13 +2940,13 @@
         <v>4</v>
       </c>
       <c r="B181" s="2">
-        <v>45628</v>
+        <v>45621</v>
       </c>
       <c r="C181" s="2">
-        <v>70</v>
+        <v>412</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -2951,10 +2954,10 @@
         <v>4</v>
       </c>
       <c r="B182" s="2">
-        <v>45629</v>
+        <v>45622</v>
       </c>
       <c r="C182" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>5</v>
@@ -2965,13 +2968,13 @@
         <v>4</v>
       </c>
       <c r="B183" s="2">
-        <v>45629</v>
+        <v>45623</v>
       </c>
       <c r="C183" s="2">
-        <v>384</v>
+        <v>349</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -2979,10 +2982,10 @@
         <v>4</v>
       </c>
       <c r="B184" s="2">
-        <v>45632</v>
+        <v>45623</v>
       </c>
       <c r="C184" s="2">
-        <v>893</v>
+        <v>1</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>5</v>
@@ -2993,13 +2996,13 @@
         <v>4</v>
       </c>
       <c r="B185" s="2">
-        <v>45632</v>
+        <v>45624</v>
       </c>
       <c r="C185" s="2">
-        <v>711</v>
+        <v>957</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -3007,13 +3010,13 @@
         <v>4</v>
       </c>
       <c r="B186" s="2">
-        <v>45633</v>
+        <v>45625</v>
       </c>
       <c r="C186" s="2">
-        <v>152</v>
+        <v>1</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -3021,10 +3024,10 @@
         <v>4</v>
       </c>
       <c r="B187" s="2">
-        <v>45635</v>
+        <v>45626</v>
       </c>
       <c r="C187" s="2">
-        <v>504</v>
+        <v>7</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>5</v>
@@ -3035,13 +3038,13 @@
         <v>4</v>
       </c>
       <c r="B188" s="2">
-        <v>45635</v>
+        <v>45627</v>
       </c>
       <c r="C188" s="2">
-        <v>735</v>
+        <v>50</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3049,13 +3052,13 @@
         <v>4</v>
       </c>
       <c r="B189" s="2">
-        <v>45636</v>
+        <v>45627</v>
       </c>
       <c r="C189" s="2">
-        <v>63</v>
+        <v>1018</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3063,10 +3066,10 @@
         <v>4</v>
       </c>
       <c r="B190" s="2">
-        <v>45605</v>
+        <v>45627</v>
       </c>
       <c r="C190" s="2">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>5</v>
@@ -3077,13 +3080,13 @@
         <v>4</v>
       </c>
       <c r="B191" s="2">
-        <v>45606</v>
+        <v>45628</v>
       </c>
       <c r="C191" s="2">
-        <v>211</v>
+        <v>88</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -3091,10 +3094,10 @@
         <v>4</v>
       </c>
       <c r="B192" s="2">
-        <v>45607</v>
+        <v>45629</v>
       </c>
       <c r="C192" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>5</v>
@@ -3105,13 +3108,13 @@
         <v>4</v>
       </c>
       <c r="B193" s="2">
-        <v>45608</v>
+        <v>45630</v>
       </c>
       <c r="C193" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3119,13 +3122,13 @@
         <v>4</v>
       </c>
       <c r="B194" s="2">
-        <v>45609</v>
+        <v>45630</v>
       </c>
       <c r="C194" s="2">
-        <v>40</v>
+        <v>392</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3133,10 +3136,10 @@
         <v>4</v>
       </c>
       <c r="B195" s="2">
-        <v>45610</v>
+        <v>45630</v>
       </c>
       <c r="C195" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>5</v>
@@ -3147,10 +3150,10 @@
         <v>4</v>
       </c>
       <c r="B196" s="2">
-        <v>45610</v>
+        <v>45630</v>
       </c>
       <c r="C196" s="2">
-        <v>237</v>
+        <v>2</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>5</v>
@@ -3161,13 +3164,13 @@
         <v>4</v>
       </c>
       <c r="B197" s="2">
-        <v>45612</v>
+        <v>45631</v>
       </c>
       <c r="C197" s="2">
-        <v>208</v>
+        <v>86</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3175,10 +3178,10 @@
         <v>4</v>
       </c>
       <c r="B198" s="2">
-        <v>45613</v>
+        <v>45632</v>
       </c>
       <c r="C198" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>5</v>
@@ -3189,13 +3192,13 @@
         <v>4</v>
       </c>
       <c r="B199" s="2">
-        <v>45613</v>
+        <v>45633</v>
       </c>
       <c r="C199" s="2">
-        <v>606</v>
+        <v>62</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -3203,13 +3206,13 @@
         <v>4</v>
       </c>
       <c r="B200" s="2">
-        <v>45615</v>
+        <v>45633</v>
       </c>
       <c r="C200" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3217,10 +3220,10 @@
         <v>4</v>
       </c>
       <c r="B201" s="2">
-        <v>45616</v>
+        <v>45634</v>
       </c>
       <c r="C201" s="2">
-        <v>317</v>
+        <v>168</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>5</v>
@@ -3231,13 +3234,13 @@
         <v>4</v>
       </c>
       <c r="B202" s="2">
-        <v>45616</v>
+        <v>45636</v>
       </c>
       <c r="C202" s="2">
-        <v>202</v>
+        <v>51</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3245,10 +3248,10 @@
         <v>4</v>
       </c>
       <c r="B203" s="2">
-        <v>45619</v>
+        <v>45636</v>
       </c>
       <c r="C203" s="2">
-        <v>779</v>
+        <v>6</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>5</v>
@@ -3259,13 +3262,13 @@
         <v>4</v>
       </c>
       <c r="B204" s="2">
-        <v>45619</v>
+        <v>45637</v>
       </c>
       <c r="C204" s="2">
-        <v>719</v>
+        <v>133</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -3273,13 +3276,13 @@
         <v>4</v>
       </c>
       <c r="B205" s="2">
-        <v>45620</v>
+        <v>45639</v>
       </c>
       <c r="C205" s="2">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -3287,10 +3290,10 @@
         <v>4</v>
       </c>
       <c r="B206" s="2">
-        <v>45622</v>
+        <v>45640</v>
       </c>
       <c r="C206" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>5</v>
@@ -3301,10 +3304,10 @@
         <v>4</v>
       </c>
       <c r="B207" s="2">
-        <v>45622</v>
+        <v>45640</v>
       </c>
       <c r="C207" s="2">
-        <v>560</v>
+        <v>88</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>8</v>
@@ -3315,13 +3318,13 @@
         <v>4</v>
       </c>
       <c r="B208" s="2">
-        <v>45623</v>
+        <v>45602</v>
       </c>
       <c r="C208" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -3329,13 +3332,13 @@
         <v>4</v>
       </c>
       <c r="B209" s="2">
-        <v>45623</v>
+        <v>45605</v>
       </c>
       <c r="C209" s="2">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -3343,10 +3346,10 @@
         <v>4</v>
       </c>
       <c r="B210" s="2">
-        <v>45625</v>
+        <v>45605</v>
       </c>
       <c r="C210" s="2">
-        <v>3</v>
+        <v>760</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>5</v>
@@ -3357,13 +3360,13 @@
         <v>4</v>
       </c>
       <c r="B211" s="2">
-        <v>45625</v>
+        <v>45606</v>
       </c>
       <c r="C211" s="2">
-        <v>1117</v>
+        <v>43</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -3371,13 +3374,13 @@
         <v>4</v>
       </c>
       <c r="B212" s="2">
-        <v>45626</v>
+        <v>45611</v>
       </c>
       <c r="C212" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -3385,13 +3388,13 @@
         <v>4</v>
       </c>
       <c r="B213" s="2">
-        <v>45626</v>
+        <v>45613</v>
       </c>
       <c r="C213" s="2">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -3399,7 +3402,7 @@
         <v>4</v>
       </c>
       <c r="B214" s="2">
-        <v>45628</v>
+        <v>45614</v>
       </c>
       <c r="C214" s="2">
         <v>2</v>
@@ -3413,10 +3416,10 @@
         <v>4</v>
       </c>
       <c r="B215" s="2">
-        <v>45628</v>
+        <v>45614</v>
       </c>
       <c r="C215" s="2">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>5</v>
@@ -3427,13 +3430,13 @@
         <v>4</v>
       </c>
       <c r="B216" s="2">
-        <v>45629</v>
+        <v>45616</v>
       </c>
       <c r="C216" s="2">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -3441,10 +3444,10 @@
         <v>4</v>
       </c>
       <c r="B217" s="2">
-        <v>45631</v>
+        <v>45617</v>
       </c>
       <c r="C217" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>5</v>
@@ -3455,13 +3458,13 @@
         <v>4</v>
       </c>
       <c r="B218" s="2">
-        <v>45631</v>
+        <v>45619</v>
       </c>
       <c r="C218" s="2">
-        <v>48</v>
+        <v>224</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -3469,10 +3472,10 @@
         <v>4</v>
       </c>
       <c r="B219" s="2">
-        <v>45634</v>
+        <v>45620</v>
       </c>
       <c r="C219" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>5</v>
@@ -3483,13 +3486,13 @@
         <v>4</v>
       </c>
       <c r="B220" s="2">
-        <v>45634</v>
+        <v>45621</v>
       </c>
       <c r="C220" s="2">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -3497,13 +3500,13 @@
         <v>4</v>
       </c>
       <c r="B221" s="2">
-        <v>45635</v>
+        <v>45623</v>
       </c>
       <c r="C221" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -3511,10 +3514,10 @@
         <v>4</v>
       </c>
       <c r="B222" s="2">
-        <v>45636</v>
+        <v>45623</v>
       </c>
       <c r="C222" s="2">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>5</v>
@@ -3525,10 +3528,10 @@
         <v>4</v>
       </c>
       <c r="B223" s="2">
-        <v>45637</v>
+        <v>45625</v>
       </c>
       <c r="C223" s="2">
-        <v>64</v>
+        <v>707</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>5</v>
@@ -3539,10 +3542,10 @@
         <v>4</v>
       </c>
       <c r="B224" s="2">
-        <v>45604</v>
+        <v>45626</v>
       </c>
       <c r="C224" s="2">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>5</v>
@@ -3553,10 +3556,10 @@
         <v>4</v>
       </c>
       <c r="B225" s="2">
-        <v>45604</v>
+        <v>45626</v>
       </c>
       <c r="C225" s="2">
-        <v>789</v>
+        <v>9</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>5</v>
@@ -3567,13 +3570,13 @@
         <v>4</v>
       </c>
       <c r="B226" s="2">
-        <v>45605</v>
+        <v>45626</v>
       </c>
       <c r="C226" s="2">
-        <v>237</v>
+        <v>37</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -3581,10 +3584,10 @@
         <v>4</v>
       </c>
       <c r="B227" s="2">
-        <v>45606</v>
+        <v>45627</v>
       </c>
       <c r="C227" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>5</v>
@@ -3595,10 +3598,10 @@
         <v>4</v>
       </c>
       <c r="B228" s="2">
-        <v>45607</v>
+        <v>45627</v>
       </c>
       <c r="C228" s="2">
-        <v>904</v>
+        <v>7</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>5</v>
@@ -3609,10 +3612,10 @@
         <v>4</v>
       </c>
       <c r="B229" s="2">
-        <v>45609</v>
+        <v>45628</v>
       </c>
       <c r="C229" s="2">
-        <v>1</v>
+        <v>337</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>5</v>
@@ -3623,13 +3626,13 @@
         <v>4</v>
       </c>
       <c r="B230" s="2">
-        <v>45616</v>
+        <v>45629</v>
       </c>
       <c r="C230" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -3637,13 +3640,13 @@
         <v>4</v>
       </c>
       <c r="B231" s="2">
-        <v>45619</v>
+        <v>45630</v>
       </c>
       <c r="C231" s="2">
-        <v>77</v>
+        <v>3</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -3651,13 +3654,13 @@
         <v>4</v>
       </c>
       <c r="B232" s="2">
-        <v>45622</v>
+        <v>45631</v>
       </c>
       <c r="C232" s="2">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -3665,13 +3668,13 @@
         <v>4</v>
       </c>
       <c r="B233" s="2">
-        <v>45622</v>
+        <v>45631</v>
       </c>
       <c r="C233" s="2">
-        <v>131</v>
+        <v>417</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -3679,13 +3682,13 @@
         <v>4</v>
       </c>
       <c r="B234" s="2">
-        <v>45623</v>
+        <v>45632</v>
       </c>
       <c r="C234" s="2">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -3693,10 +3696,10 @@
         <v>4</v>
       </c>
       <c r="B235" s="2">
-        <v>45625</v>
+        <v>45632</v>
       </c>
       <c r="C235" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>5</v>
@@ -3707,13 +3710,13 @@
         <v>4</v>
       </c>
       <c r="B236" s="2">
-        <v>45625</v>
+        <v>45633</v>
       </c>
       <c r="C236" s="2">
-        <v>162</v>
+        <v>2</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -3721,13 +3724,13 @@
         <v>4</v>
       </c>
       <c r="B237" s="2">
-        <v>45625</v>
+        <v>45634</v>
       </c>
       <c r="C237" s="2">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -3735,13 +3738,13 @@
         <v>4</v>
       </c>
       <c r="B238" s="2">
-        <v>45626</v>
+        <v>45634</v>
       </c>
       <c r="C238" s="2">
-        <v>302</v>
+        <v>1260</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -3749,10 +3752,10 @@
         <v>4</v>
       </c>
       <c r="B239" s="2">
-        <v>45627</v>
+        <v>45635</v>
       </c>
       <c r="C239" s="2">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="D239" s="2" t="s">
         <v>5</v>
@@ -3763,10 +3766,10 @@
         <v>4</v>
       </c>
       <c r="B240" s="2">
-        <v>45628</v>
+        <v>45635</v>
       </c>
       <c r="C240" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>5</v>
@@ -3777,13 +3780,13 @@
         <v>4</v>
       </c>
       <c r="B241" s="2">
-        <v>45628</v>
+        <v>45636</v>
       </c>
       <c r="C241" s="2">
-        <v>476</v>
+        <v>3</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -3791,10 +3794,10 @@
         <v>4</v>
       </c>
       <c r="B242" s="2">
-        <v>45629</v>
+        <v>45637</v>
       </c>
       <c r="C242" s="2">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D242" s="2" t="s">
         <v>6</v>
@@ -3805,10 +3808,10 @@
         <v>4</v>
       </c>
       <c r="B243" s="2">
-        <v>45630</v>
+        <v>45638</v>
       </c>
       <c r="C243" s="2">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="D243" s="2" t="s">
         <v>5</v>
@@ -3819,10 +3822,10 @@
         <v>4</v>
       </c>
       <c r="B244" s="2">
-        <v>45630</v>
+        <v>45640</v>
       </c>
       <c r="C244" s="2">
-        <v>416</v>
+        <v>5</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>5</v>
@@ -3833,13 +3836,13 @@
         <v>4</v>
       </c>
       <c r="B245" s="2">
-        <v>45631</v>
+        <v>45640</v>
       </c>
       <c r="C245" s="2">
-        <v>383</v>
+        <v>129</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -3847,10 +3850,10 @@
         <v>4</v>
       </c>
       <c r="B246" s="2">
-        <v>45632</v>
+        <v>45605</v>
       </c>
       <c r="C246" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D246" s="2" t="s">
         <v>5</v>
@@ -3861,13 +3864,13 @@
         <v>4</v>
       </c>
       <c r="B247" s="2">
-        <v>45632</v>
+        <v>45606</v>
       </c>
       <c r="C247" s="2">
-        <v>50</v>
+        <v>499</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -3875,13 +3878,13 @@
         <v>4</v>
       </c>
       <c r="B248" s="2">
-        <v>45633</v>
+        <v>45606</v>
       </c>
       <c r="C248" s="2">
-        <v>67</v>
+        <v>117</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -3889,10 +3892,10 @@
         <v>4</v>
       </c>
       <c r="B249" s="2">
-        <v>45633</v>
+        <v>45606</v>
       </c>
       <c r="C249" s="2">
-        <v>881</v>
+        <v>6</v>
       </c>
       <c r="D249" s="2" t="s">
         <v>5</v>
@@ -3903,13 +3906,13 @@
         <v>4</v>
       </c>
       <c r="B250" s="2">
-        <v>45634</v>
+        <v>45612</v>
       </c>
       <c r="C250" s="2">
-        <v>2</v>
+        <v>222</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -3917,13 +3920,13 @@
         <v>4</v>
       </c>
       <c r="B251" s="2">
-        <v>45634</v>
+        <v>45612</v>
       </c>
       <c r="C251" s="2">
-        <v>945</v>
+        <v>14</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -3931,10 +3934,10 @@
         <v>4</v>
       </c>
       <c r="B252" s="2">
-        <v>45635</v>
+        <v>45614</v>
       </c>
       <c r="C252" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D252" s="2" t="s">
         <v>5</v>
@@ -3945,12 +3948,432 @@
         <v>4</v>
       </c>
       <c r="B253" s="2">
-        <v>45636</v>
+        <v>45615</v>
       </c>
       <c r="C253" s="2">
-        <v>338</v>
+        <v>2</v>
       </c>
       <c r="D253" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4">
+      <c r="A254" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B254" s="2">
+        <v>45615</v>
+      </c>
+      <c r="C254" s="2">
+        <v>36</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
+      <c r="A255" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B255" s="2">
+        <v>45615</v>
+      </c>
+      <c r="C255" s="2">
+        <v>2</v>
+      </c>
+      <c r="D255" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
+      <c r="A256" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B256" s="2">
+        <v>45618</v>
+      </c>
+      <c r="C256" s="2">
+        <v>2</v>
+      </c>
+      <c r="D256" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
+      <c r="A257" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B257" s="2">
+        <v>45619</v>
+      </c>
+      <c r="C257" s="2">
+        <v>29</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
+      <c r="A258" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B258" s="2">
+        <v>45620</v>
+      </c>
+      <c r="C258" s="2">
+        <v>93</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4">
+      <c r="A259" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B259" s="2">
+        <v>45621</v>
+      </c>
+      <c r="C259" s="2">
+        <v>1</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4">
+      <c r="A260" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B260" s="2">
+        <v>45621</v>
+      </c>
+      <c r="C260" s="2">
+        <v>1</v>
+      </c>
+      <c r="D260" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4">
+      <c r="A261" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B261" s="2">
+        <v>45622</v>
+      </c>
+      <c r="C261" s="2">
+        <v>1</v>
+      </c>
+      <c r="D261" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4">
+      <c r="A262" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B262" s="2">
+        <v>45622</v>
+      </c>
+      <c r="C262" s="2">
+        <v>88</v>
+      </c>
+      <c r="D262" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4">
+      <c r="A263" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B263" s="2">
+        <v>45623</v>
+      </c>
+      <c r="C263" s="2">
+        <v>124</v>
+      </c>
+      <c r="D263" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4">
+      <c r="A264" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B264" s="2">
+        <v>45624</v>
+      </c>
+      <c r="C264" s="2">
+        <v>3</v>
+      </c>
+      <c r="D264" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4">
+      <c r="A265" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B265" s="2">
+        <v>45624</v>
+      </c>
+      <c r="C265" s="2">
+        <v>1</v>
+      </c>
+      <c r="D265" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4">
+      <c r="A266" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B266" s="2">
+        <v>45625</v>
+      </c>
+      <c r="C266" s="2">
+        <v>1</v>
+      </c>
+      <c r="D266" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4">
+      <c r="A267" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B267" s="2">
+        <v>45625</v>
+      </c>
+      <c r="C267" s="2">
+        <v>159</v>
+      </c>
+      <c r="D267" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4">
+      <c r="A268" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B268" s="2">
+        <v>45625</v>
+      </c>
+      <c r="C268" s="2">
+        <v>132</v>
+      </c>
+      <c r="D268" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4">
+      <c r="A269" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B269" s="2">
+        <v>45625</v>
+      </c>
+      <c r="C269" s="2">
+        <v>4</v>
+      </c>
+      <c r="D269" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4">
+      <c r="A270" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B270" s="2">
+        <v>45626</v>
+      </c>
+      <c r="C270" s="2">
+        <v>98</v>
+      </c>
+      <c r="D270" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4">
+      <c r="A271" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B271" s="2">
+        <v>45628</v>
+      </c>
+      <c r="C271" s="2">
+        <v>15</v>
+      </c>
+      <c r="D271" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4">
+      <c r="A272" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B272" s="2">
+        <v>45629</v>
+      </c>
+      <c r="C272" s="2">
+        <v>99</v>
+      </c>
+      <c r="D272" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4">
+      <c r="A273" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B273" s="2">
+        <v>45629</v>
+      </c>
+      <c r="C273" s="2">
+        <v>368</v>
+      </c>
+      <c r="D273" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
+      <c r="A274" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B274" s="2">
+        <v>45631</v>
+      </c>
+      <c r="C274" s="2">
+        <v>2</v>
+      </c>
+      <c r="D274" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
+      <c r="A275" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B275" s="2">
+        <v>45632</v>
+      </c>
+      <c r="C275" s="2">
+        <v>1</v>
+      </c>
+      <c r="D275" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
+      <c r="A276" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B276" s="2">
+        <v>45632</v>
+      </c>
+      <c r="C276" s="2">
+        <v>580</v>
+      </c>
+      <c r="D276" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
+      <c r="A277" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B277" s="2">
+        <v>45635</v>
+      </c>
+      <c r="C277" s="2">
+        <v>360</v>
+      </c>
+      <c r="D277" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4">
+      <c r="A278" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B278" s="2">
+        <v>45635</v>
+      </c>
+      <c r="C278" s="2">
+        <v>10</v>
+      </c>
+      <c r="D278" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4">
+      <c r="A279" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B279" s="2">
+        <v>45638</v>
+      </c>
+      <c r="C279" s="2">
+        <v>457</v>
+      </c>
+      <c r="D279" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4">
+      <c r="A280" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B280" s="2">
+        <v>45638</v>
+      </c>
+      <c r="C280" s="2">
+        <v>193</v>
+      </c>
+      <c r="D280" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4">
+      <c r="A281" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B281" s="2">
+        <v>45638</v>
+      </c>
+      <c r="C281" s="2">
+        <v>16</v>
+      </c>
+      <c r="D281" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4">
+      <c r="A282" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B282" s="2">
+        <v>45640</v>
+      </c>
+      <c r="C282" s="2">
+        <v>1</v>
+      </c>
+      <c r="D282" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4">
+      <c r="A283" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B283" s="2">
+        <v>45640</v>
+      </c>
+      <c r="C283" s="2">
+        <v>7</v>
+      </c>
+      <c r="D283" s="2" t="s">
         <v>5</v>
       </c>
     </row>

--- a/reports/For Winter Ending (Prior Year)_Visits.xlsx
+++ b/reports/For Winter Ending (Prior Year)_Visits.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="9">
   <si>
     <t>Resort</t>
   </si>
@@ -28,22 +28,19 @@
     <t>Location</t>
   </si>
   <si>
-    <t>Purgatory</t>
+    <t>Snowbowl</t>
   </si>
   <si>
-    <t>Purgatory Passes</t>
+    <t>Snowbowl Passes</t>
   </si>
   <si>
-    <t>Purgatory Comp Tickets</t>
+    <t>Snowbowl Uplift Tickets</t>
   </si>
   <si>
-    <t>Purgatory Uplift Tickets</t>
+    <t>Snowbowl Comp Tickets</t>
   </si>
   <si>
-    <t>Purgatory Coaster</t>
-  </si>
-  <si>
-    <t>Purgatory Tickets</t>
+    <t>Snowbowl Tickets</t>
   </si>
 </sst>
 </file>
@@ -406,13 +403,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D283"/>
+  <dimension ref="A1:D277"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -434,10 +431,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>45611</v>
+        <v>45604</v>
       </c>
       <c r="C2" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -448,10 +445,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>45612</v>
+        <v>45605</v>
       </c>
       <c r="C3" s="2">
-        <v>129</v>
+        <v>2</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>5</v>
@@ -462,10 +459,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>45613</v>
+        <v>45605</v>
       </c>
       <c r="C4" s="2">
-        <v>7</v>
+        <v>512</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>5</v>
@@ -476,13 +473,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>45614</v>
+        <v>45607</v>
       </c>
       <c r="C5" s="2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -490,13 +487,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>45614</v>
+        <v>45607</v>
       </c>
       <c r="C6" s="2">
-        <v>200</v>
+        <v>103</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -504,10 +501,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="2">
-        <v>45614</v>
+        <v>45608</v>
       </c>
       <c r="C7" s="2">
-        <v>1</v>
+        <v>235</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>5</v>
@@ -518,10 +515,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>45615</v>
+        <v>45611</v>
       </c>
       <c r="C8" s="2">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>5</v>
@@ -532,13 +529,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>45616</v>
+        <v>45612</v>
       </c>
       <c r="C9" s="2">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -546,13 +543,13 @@
         <v>4</v>
       </c>
       <c r="B10" s="2">
-        <v>45617</v>
+        <v>45615</v>
       </c>
       <c r="C10" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -563,10 +560,10 @@
         <v>45618</v>
       </c>
       <c r="C11" s="2">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -574,10 +571,10 @@
         <v>4</v>
       </c>
       <c r="B12" s="2">
-        <v>45620</v>
+        <v>45621</v>
       </c>
       <c r="C12" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>5</v>
@@ -588,13 +585,13 @@
         <v>4</v>
       </c>
       <c r="B13" s="2">
-        <v>45620</v>
+        <v>45621</v>
       </c>
       <c r="C13" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -602,10 +599,10 @@
         <v>4</v>
       </c>
       <c r="B14" s="2">
-        <v>45620</v>
+        <v>45623</v>
       </c>
       <c r="C14" s="2">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>5</v>
@@ -616,10 +613,10 @@
         <v>4</v>
       </c>
       <c r="B15" s="2">
-        <v>45621</v>
+        <v>45624</v>
       </c>
       <c r="C15" s="2">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>5</v>
@@ -630,13 +627,13 @@
         <v>4</v>
       </c>
       <c r="B16" s="2">
-        <v>45623</v>
+        <v>45624</v>
       </c>
       <c r="C16" s="2">
+        <v>824</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -644,13 +641,13 @@
         <v>4</v>
       </c>
       <c r="B17" s="2">
-        <v>45623</v>
+        <v>45626</v>
       </c>
       <c r="C17" s="2">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -658,13 +655,13 @@
         <v>4</v>
       </c>
       <c r="B18" s="2">
-        <v>45624</v>
+        <v>45626</v>
       </c>
       <c r="C18" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -672,13 +669,13 @@
         <v>4</v>
       </c>
       <c r="B19" s="2">
-        <v>45626</v>
+        <v>45627</v>
       </c>
       <c r="C19" s="2">
-        <v>7</v>
+        <v>786</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -689,10 +686,10 @@
         <v>45627</v>
       </c>
       <c r="C20" s="2">
-        <v>1</v>
+        <v>160</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -700,7 +697,7 @@
         <v>4</v>
       </c>
       <c r="B21" s="2">
-        <v>45627</v>
+        <v>45628</v>
       </c>
       <c r="C21" s="2">
         <v>1</v>
@@ -714,13 +711,13 @@
         <v>4</v>
       </c>
       <c r="B22" s="2">
-        <v>45627</v>
+        <v>45629</v>
       </c>
       <c r="C22" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -731,10 +728,10 @@
         <v>45630</v>
       </c>
       <c r="C23" s="2">
-        <v>90</v>
+        <v>485</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -742,13 +739,13 @@
         <v>4</v>
       </c>
       <c r="B24" s="2">
-        <v>45633</v>
+        <v>45630</v>
       </c>
       <c r="C24" s="2">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -756,13 +753,13 @@
         <v>4</v>
       </c>
       <c r="B25" s="2">
-        <v>45633</v>
+        <v>45631</v>
       </c>
       <c r="C25" s="2">
-        <v>295</v>
+        <v>4</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -770,10 +767,10 @@
         <v>4</v>
       </c>
       <c r="B26" s="2">
-        <v>45635</v>
+        <v>45633</v>
       </c>
       <c r="C26" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>5</v>
@@ -784,13 +781,13 @@
         <v>4</v>
       </c>
       <c r="B27" s="2">
-        <v>45636</v>
+        <v>45633</v>
       </c>
       <c r="C27" s="2">
-        <v>135</v>
+        <v>1404</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -798,13 +795,13 @@
         <v>4</v>
       </c>
       <c r="B28" s="2">
-        <v>45637</v>
+        <v>45633</v>
       </c>
       <c r="C28" s="2">
-        <v>514</v>
+        <v>118</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -812,10 +809,10 @@
         <v>4</v>
       </c>
       <c r="B29" s="2">
-        <v>45638</v>
+        <v>45634</v>
       </c>
       <c r="C29" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>5</v>
@@ -826,10 +823,10 @@
         <v>4</v>
       </c>
       <c r="B30" s="2">
-        <v>45638</v>
+        <v>45634</v>
       </c>
       <c r="C30" s="2">
-        <v>1</v>
+        <v>854</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>5</v>
@@ -840,13 +837,13 @@
         <v>4</v>
       </c>
       <c r="B31" s="2">
-        <v>45639</v>
+        <v>45636</v>
       </c>
       <c r="C31" s="2">
-        <v>265</v>
+        <v>2</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -854,13 +851,13 @@
         <v>4</v>
       </c>
       <c r="B32" s="2">
-        <v>45640</v>
+        <v>45636</v>
       </c>
       <c r="C32" s="2">
-        <v>1413</v>
+        <v>0</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -868,10 +865,10 @@
         <v>4</v>
       </c>
       <c r="B33" s="2">
-        <v>45612</v>
+        <v>45637</v>
       </c>
       <c r="C33" s="2">
-        <v>987</v>
+        <v>2</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>5</v>
@@ -882,10 +879,10 @@
         <v>4</v>
       </c>
       <c r="B34" s="2">
-        <v>45613</v>
+        <v>45637</v>
       </c>
       <c r="C34" s="2">
-        <v>7</v>
+        <v>535</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>5</v>
@@ -896,10 +893,10 @@
         <v>4</v>
       </c>
       <c r="B35" s="2">
-        <v>45614</v>
+        <v>45640</v>
       </c>
       <c r="C35" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>5</v>
@@ -910,10 +907,10 @@
         <v>4</v>
       </c>
       <c r="B36" s="2">
-        <v>45615</v>
+        <v>45640</v>
       </c>
       <c r="C36" s="2">
-        <v>167</v>
+        <v>829</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>5</v>
@@ -924,10 +921,10 @@
         <v>4</v>
       </c>
       <c r="B37" s="2">
-        <v>45616</v>
+        <v>45604</v>
       </c>
       <c r="C37" s="2">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>5</v>
@@ -938,7 +935,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="2">
-        <v>45616</v>
+        <v>45606</v>
       </c>
       <c r="C38" s="2">
         <v>1</v>
@@ -952,13 +949,13 @@
         <v>4</v>
       </c>
       <c r="B39" s="2">
-        <v>45617</v>
+        <v>45606</v>
       </c>
       <c r="C39" s="2">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -966,13 +963,13 @@
         <v>4</v>
       </c>
       <c r="B40" s="2">
-        <v>45618</v>
+        <v>45609</v>
       </c>
       <c r="C40" s="2">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -980,13 +977,13 @@
         <v>4</v>
       </c>
       <c r="B41" s="2">
-        <v>45618</v>
+        <v>45610</v>
       </c>
       <c r="C41" s="2">
-        <v>343</v>
+        <v>28</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -994,13 +991,13 @@
         <v>4</v>
       </c>
       <c r="B42" s="2">
-        <v>45619</v>
+        <v>45612</v>
       </c>
       <c r="C42" s="2">
-        <v>85</v>
+        <v>456</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1008,13 +1005,13 @@
         <v>4</v>
       </c>
       <c r="B43" s="2">
-        <v>45620</v>
+        <v>45613</v>
       </c>
       <c r="C43" s="2">
-        <v>2</v>
+        <v>217</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1022,10 +1019,10 @@
         <v>4</v>
       </c>
       <c r="B44" s="2">
-        <v>45620</v>
+        <v>45614</v>
       </c>
       <c r="C44" s="2">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>5</v>
@@ -1036,13 +1033,13 @@
         <v>4</v>
       </c>
       <c r="B45" s="2">
-        <v>45621</v>
+        <v>45614</v>
       </c>
       <c r="C45" s="2">
-        <v>78</v>
+        <v>320</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1050,13 +1047,13 @@
         <v>4</v>
       </c>
       <c r="B46" s="2">
-        <v>45622</v>
+        <v>45615</v>
       </c>
       <c r="C46" s="2">
-        <v>71</v>
+        <v>194</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1064,10 +1061,10 @@
         <v>4</v>
       </c>
       <c r="B47" s="2">
-        <v>45624</v>
+        <v>45616</v>
       </c>
       <c r="C47" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>5</v>
@@ -1078,10 +1075,10 @@
         <v>4</v>
       </c>
       <c r="B48" s="2">
-        <v>45624</v>
+        <v>45616</v>
       </c>
       <c r="C48" s="2">
-        <v>113</v>
+        <v>35</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>6</v>
@@ -1092,13 +1089,13 @@
         <v>4</v>
       </c>
       <c r="B49" s="2">
-        <v>45624</v>
+        <v>45617</v>
       </c>
       <c r="C49" s="2">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1106,10 +1103,10 @@
         <v>4</v>
       </c>
       <c r="B50" s="2">
-        <v>45625</v>
+        <v>45617</v>
       </c>
       <c r="C50" s="2">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>5</v>
@@ -1120,13 +1117,13 @@
         <v>4</v>
       </c>
       <c r="B51" s="2">
-        <v>45626</v>
+        <v>45618</v>
       </c>
       <c r="C51" s="2">
-        <v>410</v>
+        <v>2</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1134,13 +1131,13 @@
         <v>4</v>
       </c>
       <c r="B52" s="2">
-        <v>45627</v>
+        <v>45618</v>
       </c>
       <c r="C52" s="2">
-        <v>3</v>
+        <v>482</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1148,13 +1145,13 @@
         <v>4</v>
       </c>
       <c r="B53" s="2">
-        <v>45629</v>
+        <v>45619</v>
       </c>
       <c r="C53" s="2">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1162,13 +1159,13 @@
         <v>4</v>
       </c>
       <c r="B54" s="2">
-        <v>45632</v>
+        <v>45620</v>
       </c>
       <c r="C54" s="2">
-        <v>113</v>
+        <v>43</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1176,10 +1173,10 @@
         <v>4</v>
       </c>
       <c r="B55" s="2">
-        <v>45633</v>
+        <v>45620</v>
       </c>
       <c r="C55" s="2">
-        <v>3</v>
+        <v>670</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>5</v>
@@ -1190,10 +1187,10 @@
         <v>4</v>
       </c>
       <c r="B56" s="2">
-        <v>45633</v>
+        <v>45621</v>
       </c>
       <c r="C56" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>5</v>
@@ -1204,13 +1201,13 @@
         <v>4</v>
       </c>
       <c r="B57" s="2">
-        <v>45634</v>
+        <v>45621</v>
       </c>
       <c r="C57" s="2">
-        <v>1</v>
+        <v>529</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1218,10 +1215,10 @@
         <v>4</v>
       </c>
       <c r="B58" s="2">
-        <v>45634</v>
+        <v>45622</v>
       </c>
       <c r="C58" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>5</v>
@@ -1232,13 +1229,13 @@
         <v>4</v>
       </c>
       <c r="B59" s="2">
-        <v>45634</v>
+        <v>45623</v>
       </c>
       <c r="C59" s="2">
-        <v>160</v>
+        <v>608</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1246,13 +1243,13 @@
         <v>4</v>
       </c>
       <c r="B60" s="2">
-        <v>45635</v>
+        <v>45624</v>
       </c>
       <c r="C60" s="2">
-        <v>135</v>
+        <v>3</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1260,10 +1257,10 @@
         <v>4</v>
       </c>
       <c r="B61" s="2">
-        <v>45639</v>
+        <v>45625</v>
       </c>
       <c r="C61" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>5</v>
@@ -1274,7 +1271,7 @@
         <v>4</v>
       </c>
       <c r="B62" s="2">
-        <v>45639</v>
+        <v>45625</v>
       </c>
       <c r="C62" s="2">
         <v>1</v>
@@ -1288,10 +1285,10 @@
         <v>4</v>
       </c>
       <c r="B63" s="2">
-        <v>45639</v>
+        <v>45627</v>
       </c>
       <c r="C63" s="2">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>5</v>
@@ -1302,13 +1299,13 @@
         <v>4</v>
       </c>
       <c r="B64" s="2">
-        <v>45640</v>
+        <v>45629</v>
       </c>
       <c r="C64" s="2">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1316,13 +1313,13 @@
         <v>4</v>
       </c>
       <c r="B65" s="2">
-        <v>45604</v>
+        <v>45632</v>
       </c>
       <c r="C65" s="2">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1330,10 +1327,10 @@
         <v>4</v>
       </c>
       <c r="B66" s="2">
-        <v>45605</v>
+        <v>45635</v>
       </c>
       <c r="C66" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>5</v>
@@ -1344,13 +1341,13 @@
         <v>4</v>
       </c>
       <c r="B67" s="2">
-        <v>45606</v>
+        <v>45635</v>
       </c>
       <c r="C67" s="2">
-        <v>127</v>
+        <v>65</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1358,13 +1355,13 @@
         <v>4</v>
       </c>
       <c r="B68" s="2">
-        <v>45612</v>
+        <v>45638</v>
       </c>
       <c r="C68" s="2">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1372,13 +1369,13 @@
         <v>4</v>
       </c>
       <c r="B69" s="2">
-        <v>45613</v>
+        <v>45639</v>
       </c>
       <c r="C69" s="2">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1386,13 +1383,13 @@
         <v>4</v>
       </c>
       <c r="B70" s="2">
-        <v>45615</v>
+        <v>45640</v>
       </c>
       <c r="C70" s="2">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1400,13 +1397,13 @@
         <v>4</v>
       </c>
       <c r="B71" s="2">
-        <v>45615</v>
+        <v>45597</v>
       </c>
       <c r="C71" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1414,13 +1411,13 @@
         <v>4</v>
       </c>
       <c r="B72" s="2">
-        <v>45616</v>
+        <v>45604</v>
       </c>
       <c r="C72" s="2">
-        <v>181</v>
+        <v>18</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1428,10 +1425,10 @@
         <v>4</v>
       </c>
       <c r="B73" s="2">
-        <v>45619</v>
+        <v>45606</v>
       </c>
       <c r="C73" s="2">
-        <v>623</v>
+        <v>3</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>5</v>
@@ -1442,10 +1439,10 @@
         <v>4</v>
       </c>
       <c r="B74" s="2">
-        <v>45619</v>
+        <v>45606</v>
       </c>
       <c r="C74" s="2">
-        <v>8</v>
+        <v>549</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>5</v>
@@ -1456,13 +1453,13 @@
         <v>4</v>
       </c>
       <c r="B75" s="2">
-        <v>45621</v>
+        <v>45606</v>
       </c>
       <c r="C75" s="2">
-        <v>1</v>
+        <v>290</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1470,13 +1467,13 @@
         <v>4</v>
       </c>
       <c r="B76" s="2">
-        <v>45622</v>
+        <v>45607</v>
       </c>
       <c r="C76" s="2">
-        <v>454</v>
+        <v>33</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -1484,13 +1481,13 @@
         <v>4</v>
       </c>
       <c r="B77" s="2">
-        <v>45622</v>
+        <v>45609</v>
       </c>
       <c r="C77" s="2">
-        <v>284</v>
+        <v>186</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1498,13 +1495,13 @@
         <v>4</v>
       </c>
       <c r="B78" s="2">
-        <v>45622</v>
+        <v>45610</v>
       </c>
       <c r="C78" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1512,7 +1509,7 @@
         <v>4</v>
       </c>
       <c r="B79" s="2">
-        <v>45624</v>
+        <v>45612</v>
       </c>
       <c r="C79" s="2">
         <v>1</v>
@@ -1526,13 +1523,13 @@
         <v>4</v>
       </c>
       <c r="B80" s="2">
-        <v>45625</v>
+        <v>45613</v>
       </c>
       <c r="C80" s="2">
-        <v>426</v>
+        <v>1</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -1540,13 +1537,13 @@
         <v>4</v>
       </c>
       <c r="B81" s="2">
-        <v>45625</v>
+        <v>45613</v>
       </c>
       <c r="C81" s="2">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -1554,10 +1551,10 @@
         <v>4</v>
       </c>
       <c r="B82" s="2">
-        <v>45625</v>
+        <v>45615</v>
       </c>
       <c r="C82" s="2">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>5</v>
@@ -1568,10 +1565,10 @@
         <v>4</v>
       </c>
       <c r="B83" s="2">
-        <v>45627</v>
+        <v>45615</v>
       </c>
       <c r="C83" s="2">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>5</v>
@@ -1582,10 +1579,10 @@
         <v>4</v>
       </c>
       <c r="B84" s="2">
-        <v>45628</v>
+        <v>45618</v>
       </c>
       <c r="C84" s="2">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>5</v>
@@ -1596,13 +1593,13 @@
         <v>4</v>
       </c>
       <c r="B85" s="2">
-        <v>45628</v>
+        <v>45619</v>
       </c>
       <c r="C85" s="2">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1610,13 +1607,13 @@
         <v>4</v>
       </c>
       <c r="B86" s="2">
-        <v>45628</v>
+        <v>45619</v>
       </c>
       <c r="C86" s="2">
-        <v>8</v>
+        <v>163</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -1624,10 +1621,10 @@
         <v>4</v>
       </c>
       <c r="B87" s="2">
-        <v>45631</v>
+        <v>45620</v>
       </c>
       <c r="C87" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>5</v>
@@ -1638,13 +1635,13 @@
         <v>4</v>
       </c>
       <c r="B88" s="2">
-        <v>45631</v>
+        <v>45621</v>
       </c>
       <c r="C88" s="2">
-        <v>89</v>
+        <v>33</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -1652,13 +1649,13 @@
         <v>4</v>
       </c>
       <c r="B89" s="2">
-        <v>45634</v>
+        <v>45622</v>
       </c>
       <c r="C89" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1666,10 +1663,10 @@
         <v>4</v>
       </c>
       <c r="B90" s="2">
-        <v>45634</v>
+        <v>45623</v>
       </c>
       <c r="C90" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>5</v>
@@ -1680,13 +1677,13 @@
         <v>4</v>
       </c>
       <c r="B91" s="2">
-        <v>45635</v>
+        <v>45624</v>
       </c>
       <c r="C91" s="2">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -1694,13 +1691,13 @@
         <v>4</v>
       </c>
       <c r="B92" s="2">
-        <v>45636</v>
+        <v>45625</v>
       </c>
       <c r="C92" s="2">
-        <v>98</v>
+        <v>305</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -1708,10 +1705,10 @@
         <v>4</v>
       </c>
       <c r="B93" s="2">
-        <v>45637</v>
+        <v>45626</v>
       </c>
       <c r="C93" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>5</v>
@@ -1722,10 +1719,10 @@
         <v>4</v>
       </c>
       <c r="B94" s="2">
-        <v>45637</v>
+        <v>45626</v>
       </c>
       <c r="C94" s="2">
-        <v>2</v>
+        <v>757</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>5</v>
@@ -1736,13 +1733,13 @@
         <v>4</v>
       </c>
       <c r="B95" s="2">
-        <v>45638</v>
+        <v>45628</v>
       </c>
       <c r="C95" s="2">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -1750,13 +1747,13 @@
         <v>4</v>
       </c>
       <c r="B96" s="2">
-        <v>45638</v>
+        <v>45629</v>
       </c>
       <c r="C96" s="2">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -1764,10 +1761,10 @@
         <v>4</v>
       </c>
       <c r="B97" s="2">
-        <v>45639</v>
+        <v>45629</v>
       </c>
       <c r="C97" s="2">
-        <v>105</v>
+        <v>384</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>5</v>
@@ -1778,10 +1775,10 @@
         <v>4</v>
       </c>
       <c r="B98" s="2">
-        <v>45640</v>
+        <v>45632</v>
       </c>
       <c r="C98" s="2">
-        <v>5</v>
+        <v>893</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>5</v>
@@ -1792,13 +1789,13 @@
         <v>4</v>
       </c>
       <c r="B99" s="2">
-        <v>45606</v>
+        <v>45632</v>
       </c>
       <c r="C99" s="2">
-        <v>5</v>
+        <v>711</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -1806,13 +1803,13 @@
         <v>4</v>
       </c>
       <c r="B100" s="2">
-        <v>45610</v>
+        <v>45633</v>
       </c>
       <c r="C100" s="2">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -1820,13 +1817,13 @@
         <v>4</v>
       </c>
       <c r="B101" s="2">
-        <v>45610</v>
+        <v>45635</v>
       </c>
       <c r="C101" s="2">
-        <v>6</v>
+        <v>504</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -1834,13 +1831,13 @@
         <v>4</v>
       </c>
       <c r="B102" s="2">
-        <v>45612</v>
+        <v>45635</v>
       </c>
       <c r="C102" s="2">
-        <v>5</v>
+        <v>735</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -1848,13 +1845,13 @@
         <v>4</v>
       </c>
       <c r="B103" s="2">
-        <v>45612</v>
+        <v>45636</v>
       </c>
       <c r="C103" s="2">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -1862,13 +1859,13 @@
         <v>4</v>
       </c>
       <c r="B104" s="2">
-        <v>45613</v>
+        <v>45638</v>
       </c>
       <c r="C104" s="2">
-        <v>44</v>
+        <v>714</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -1876,13 +1873,13 @@
         <v>4</v>
       </c>
       <c r="B105" s="2">
-        <v>45614</v>
+        <v>45639</v>
       </c>
       <c r="C105" s="2">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -1890,13 +1887,13 @@
         <v>4</v>
       </c>
       <c r="B106" s="2">
-        <v>45616</v>
+        <v>45604</v>
       </c>
       <c r="C106" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -1904,10 +1901,10 @@
         <v>4</v>
       </c>
       <c r="B107" s="2">
-        <v>45616</v>
+        <v>45604</v>
       </c>
       <c r="C107" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>5</v>
@@ -1918,13 +1915,13 @@
         <v>4</v>
       </c>
       <c r="B108" s="2">
-        <v>45617</v>
+        <v>45604</v>
       </c>
       <c r="C108" s="2">
-        <v>91</v>
+        <v>139</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -1932,13 +1929,13 @@
         <v>4</v>
       </c>
       <c r="B109" s="2">
-        <v>45617</v>
+        <v>45607</v>
       </c>
       <c r="C109" s="2">
-        <v>234</v>
+        <v>473</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -1946,13 +1943,13 @@
         <v>4</v>
       </c>
       <c r="B110" s="2">
-        <v>45618</v>
+        <v>45608</v>
       </c>
       <c r="C110" s="2">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -1960,13 +1957,13 @@
         <v>4</v>
       </c>
       <c r="B111" s="2">
-        <v>45619</v>
+        <v>45610</v>
       </c>
       <c r="C111" s="2">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -1974,13 +1971,13 @@
         <v>4</v>
       </c>
       <c r="B112" s="2">
-        <v>45620</v>
+        <v>45611</v>
       </c>
       <c r="C112" s="2">
-        <v>541</v>
+        <v>0</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -1988,13 +1985,13 @@
         <v>4</v>
       </c>
       <c r="B113" s="2">
-        <v>45621</v>
+        <v>45613</v>
       </c>
       <c r="C113" s="2">
-        <v>224</v>
+        <v>468</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2002,13 +1999,13 @@
         <v>4</v>
       </c>
       <c r="B114" s="2">
-        <v>45621</v>
+        <v>45614</v>
       </c>
       <c r="C114" s="2">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2016,13 +2013,13 @@
         <v>4</v>
       </c>
       <c r="B115" s="2">
-        <v>45622</v>
+        <v>45616</v>
       </c>
       <c r="C115" s="2">
         <v>3</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2030,13 +2027,13 @@
         <v>4</v>
       </c>
       <c r="B116" s="2">
-        <v>45623</v>
+        <v>45617</v>
       </c>
       <c r="C116" s="2">
-        <v>991</v>
+        <v>12</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2044,13 +2041,13 @@
         <v>4</v>
       </c>
       <c r="B117" s="2">
-        <v>45624</v>
+        <v>45618</v>
       </c>
       <c r="C117" s="2">
-        <v>340</v>
+        <v>60</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2058,10 +2055,10 @@
         <v>4</v>
       </c>
       <c r="B118" s="2">
-        <v>45624</v>
+        <v>45619</v>
       </c>
       <c r="C118" s="2">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>5</v>
@@ -2072,13 +2069,13 @@
         <v>4</v>
       </c>
       <c r="B119" s="2">
-        <v>45624</v>
+        <v>45621</v>
       </c>
       <c r="C119" s="2">
-        <v>18</v>
+        <v>158</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2086,10 +2083,10 @@
         <v>4</v>
       </c>
       <c r="B120" s="2">
-        <v>45625</v>
+        <v>45622</v>
       </c>
       <c r="C120" s="2">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>5</v>
@@ -2100,10 +2097,10 @@
         <v>4</v>
       </c>
       <c r="B121" s="2">
-        <v>45626</v>
+        <v>45622</v>
       </c>
       <c r="C121" s="2">
-        <v>1024</v>
+        <v>415</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>5</v>
@@ -2114,13 +2111,13 @@
         <v>4</v>
       </c>
       <c r="B122" s="2">
-        <v>45627</v>
+        <v>45623</v>
       </c>
       <c r="C122" s="2">
-        <v>173</v>
+        <v>3</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2128,10 +2125,10 @@
         <v>4</v>
       </c>
       <c r="B123" s="2">
-        <v>45634</v>
+        <v>45623</v>
       </c>
       <c r="C123" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>5</v>
@@ -2142,10 +2139,10 @@
         <v>4</v>
       </c>
       <c r="B124" s="2">
-        <v>45635</v>
+        <v>45624</v>
       </c>
       <c r="C124" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>5</v>
@@ -2156,13 +2153,13 @@
         <v>4</v>
       </c>
       <c r="B125" s="2">
-        <v>45636</v>
+        <v>45624</v>
       </c>
       <c r="C125" s="2">
-        <v>2</v>
+        <v>326</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2170,7 +2167,7 @@
         <v>4</v>
       </c>
       <c r="B126" s="2">
-        <v>45638</v>
+        <v>45625</v>
       </c>
       <c r="C126" s="2">
         <v>1</v>
@@ -2184,10 +2181,10 @@
         <v>4</v>
       </c>
       <c r="B127" s="2">
-        <v>45638</v>
+        <v>45625</v>
       </c>
       <c r="C127" s="2">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>5</v>
@@ -2198,10 +2195,10 @@
         <v>4</v>
       </c>
       <c r="B128" s="2">
-        <v>45639</v>
+        <v>45625</v>
       </c>
       <c r="C128" s="2">
-        <v>1</v>
+        <v>935</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>5</v>
@@ -2212,13 +2209,13 @@
         <v>4</v>
       </c>
       <c r="B129" s="2">
-        <v>45639</v>
+        <v>45627</v>
       </c>
       <c r="C129" s="2">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2226,10 +2223,10 @@
         <v>4</v>
       </c>
       <c r="B130" s="2">
-        <v>45640</v>
+        <v>45628</v>
       </c>
       <c r="C130" s="2">
-        <v>145</v>
+        <v>388</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>5</v>
@@ -2240,10 +2237,10 @@
         <v>4</v>
       </c>
       <c r="B131" s="2">
-        <v>45601</v>
+        <v>45630</v>
       </c>
       <c r="C131" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>5</v>
@@ -2254,10 +2251,10 @@
         <v>4</v>
       </c>
       <c r="B132" s="2">
-        <v>45604</v>
+        <v>45631</v>
       </c>
       <c r="C132" s="2">
-        <v>1</v>
+        <v>376</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>5</v>
@@ -2268,13 +2265,13 @@
         <v>4</v>
       </c>
       <c r="B133" s="2">
-        <v>45605</v>
+        <v>45633</v>
       </c>
       <c r="C133" s="2">
-        <v>164</v>
+        <v>15</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2282,13 +2279,13 @@
         <v>4</v>
       </c>
       <c r="B134" s="2">
-        <v>45605</v>
+        <v>45636</v>
       </c>
       <c r="C134" s="2">
+        <v>642</v>
+      </c>
+      <c r="D134" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2296,13 +2293,13 @@
         <v>4</v>
       </c>
       <c r="B135" s="2">
-        <v>45612</v>
+        <v>45637</v>
       </c>
       <c r="C135" s="2">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2310,10 +2307,10 @@
         <v>4</v>
       </c>
       <c r="B136" s="2">
-        <v>45613</v>
+        <v>45639</v>
       </c>
       <c r="C136" s="2">
-        <v>769</v>
+        <v>1</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>5</v>
@@ -2324,13 +2321,13 @@
         <v>4</v>
       </c>
       <c r="B137" s="2">
-        <v>45615</v>
+        <v>45639</v>
       </c>
       <c r="C137" s="2">
-        <v>2</v>
+        <v>807</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -2338,13 +2335,13 @@
         <v>4</v>
       </c>
       <c r="B138" s="2">
-        <v>45618</v>
+        <v>45640</v>
       </c>
       <c r="C138" s="2">
-        <v>2</v>
+        <v>192</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -2352,13 +2349,13 @@
         <v>4</v>
       </c>
       <c r="B139" s="2">
-        <v>45619</v>
+        <v>45605</v>
       </c>
       <c r="C139" s="2">
-        <v>2</v>
+        <v>187</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -2366,10 +2363,10 @@
         <v>4</v>
       </c>
       <c r="B140" s="2">
-        <v>45619</v>
+        <v>45606</v>
       </c>
       <c r="C140" s="2">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>5</v>
@@ -2380,10 +2377,10 @@
         <v>4</v>
       </c>
       <c r="B141" s="2">
-        <v>45619</v>
+        <v>45607</v>
       </c>
       <c r="C141" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>5</v>
@@ -2394,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B142" s="2">
-        <v>45620</v>
+        <v>45608</v>
       </c>
       <c r="C142" s="2">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2408,10 +2405,10 @@
         <v>4</v>
       </c>
       <c r="B143" s="2">
-        <v>45622</v>
+        <v>45609</v>
       </c>
       <c r="C143" s="2">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>5</v>
@@ -2422,10 +2419,10 @@
         <v>4</v>
       </c>
       <c r="B144" s="2">
-        <v>45623</v>
+        <v>45609</v>
       </c>
       <c r="C144" s="2">
-        <v>1</v>
+        <v>319</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>5</v>
@@ -2436,10 +2433,10 @@
         <v>4</v>
       </c>
       <c r="B145" s="2">
-        <v>45623</v>
+        <v>45611</v>
       </c>
       <c r="C145" s="2">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>6</v>
@@ -2450,10 +2447,10 @@
         <v>4</v>
       </c>
       <c r="B146" s="2">
-        <v>45624</v>
+        <v>45612</v>
       </c>
       <c r="C146" s="2">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>5</v>
@@ -2464,10 +2461,10 @@
         <v>4</v>
       </c>
       <c r="B147" s="2">
-        <v>45625</v>
+        <v>45612</v>
       </c>
       <c r="C147" s="2">
-        <v>7</v>
+        <v>614</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>5</v>
@@ -2478,10 +2475,10 @@
         <v>4</v>
       </c>
       <c r="B148" s="2">
-        <v>45625</v>
+        <v>45614</v>
       </c>
       <c r="C148" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>5</v>
@@ -2492,10 +2489,10 @@
         <v>4</v>
       </c>
       <c r="B149" s="2">
-        <v>45626</v>
+        <v>45615</v>
       </c>
       <c r="C149" s="2">
-        <v>1</v>
+        <v>247</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>5</v>
@@ -2506,13 +2503,13 @@
         <v>4</v>
       </c>
       <c r="B150" s="2">
-        <v>45626</v>
+        <v>45617</v>
       </c>
       <c r="C150" s="2">
-        <v>297</v>
+        <v>4</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -2520,13 +2517,13 @@
         <v>4</v>
       </c>
       <c r="B151" s="2">
-        <v>45626</v>
+        <v>45620</v>
       </c>
       <c r="C151" s="2">
-        <v>115</v>
+        <v>681</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -2534,10 +2531,10 @@
         <v>4</v>
       </c>
       <c r="B152" s="2">
-        <v>45627</v>
+        <v>45620</v>
       </c>
       <c r="C152" s="2">
-        <v>114</v>
+        <v>1</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>5</v>
@@ -2548,13 +2545,13 @@
         <v>4</v>
       </c>
       <c r="B153" s="2">
-        <v>45628</v>
+        <v>45623</v>
       </c>
       <c r="C153" s="2">
-        <v>1</v>
+        <v>802</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -2562,13 +2559,13 @@
         <v>4</v>
       </c>
       <c r="B154" s="2">
-        <v>45629</v>
+        <v>45624</v>
       </c>
       <c r="C154" s="2">
-        <v>-3</v>
+        <v>156</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -2576,13 +2573,13 @@
         <v>4</v>
       </c>
       <c r="B155" s="2">
-        <v>45629</v>
+        <v>45626</v>
       </c>
       <c r="C155" s="2">
-        <v>21</v>
+        <v>785</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -2590,10 +2587,10 @@
         <v>4</v>
       </c>
       <c r="B156" s="2">
-        <v>45630</v>
+        <v>45627</v>
       </c>
       <c r="C156" s="2">
-        <v>117</v>
+        <v>3</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>5</v>
@@ -2604,13 +2601,13 @@
         <v>4</v>
       </c>
       <c r="B157" s="2">
-        <v>45631</v>
+        <v>45627</v>
       </c>
       <c r="C157" s="2">
+        <v>109</v>
+      </c>
+      <c r="D157" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="D157" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -2618,13 +2615,13 @@
         <v>4</v>
       </c>
       <c r="B158" s="2">
-        <v>45632</v>
+        <v>45629</v>
       </c>
       <c r="C158" s="2">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -2632,13 +2629,13 @@
         <v>4</v>
       </c>
       <c r="B159" s="2">
-        <v>45633</v>
+        <v>45629</v>
       </c>
       <c r="C159" s="2">
-        <v>149</v>
+        <v>455</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -2646,10 +2643,10 @@
         <v>4</v>
       </c>
       <c r="B160" s="2">
-        <v>45633</v>
+        <v>45630</v>
       </c>
       <c r="C160" s="2">
-        <v>1558</v>
+        <v>1</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>5</v>
@@ -2660,13 +2657,13 @@
         <v>4</v>
       </c>
       <c r="B161" s="2">
-        <v>45634</v>
+        <v>45630</v>
       </c>
       <c r="C161" s="2">
-        <v>160</v>
+        <v>34</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -2674,13 +2671,13 @@
         <v>4</v>
       </c>
       <c r="B162" s="2">
-        <v>45634</v>
+        <v>45631</v>
       </c>
       <c r="C162" s="2">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -2688,10 +2685,10 @@
         <v>4</v>
       </c>
       <c r="B163" s="2">
-        <v>45636</v>
+        <v>45632</v>
       </c>
       <c r="C163" s="2">
-        <v>397</v>
+        <v>68</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>5</v>
@@ -2702,13 +2699,13 @@
         <v>4</v>
       </c>
       <c r="B164" s="2">
-        <v>45637</v>
+        <v>45633</v>
       </c>
       <c r="C164" s="2">
-        <v>151</v>
+        <v>6</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -2716,13 +2713,13 @@
         <v>4</v>
       </c>
       <c r="B165" s="2">
-        <v>45637</v>
+        <v>45634</v>
       </c>
       <c r="C165" s="2">
-        <v>4</v>
+        <v>108</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -2730,13 +2727,13 @@
         <v>4</v>
       </c>
       <c r="B166" s="2">
-        <v>45638</v>
+        <v>45635</v>
       </c>
       <c r="C166" s="2">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -2744,10 +2741,10 @@
         <v>4</v>
       </c>
       <c r="B167" s="2">
-        <v>45639</v>
+        <v>45636</v>
       </c>
       <c r="C167" s="2">
-        <v>573</v>
+        <v>4</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>5</v>
@@ -2758,13 +2755,13 @@
         <v>4</v>
       </c>
       <c r="B168" s="2">
-        <v>45640</v>
+        <v>45637</v>
       </c>
       <c r="C168" s="2">
-        <v>570</v>
+        <v>28</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -2772,10 +2769,10 @@
         <v>4</v>
       </c>
       <c r="B169" s="2">
-        <v>45640</v>
+        <v>45638</v>
       </c>
       <c r="C169" s="2">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>5</v>
@@ -2786,10 +2783,10 @@
         <v>4</v>
       </c>
       <c r="B170" s="2">
-        <v>45601</v>
+        <v>45638</v>
       </c>
       <c r="C170" s="2">
-        <v>1</v>
+        <v>514</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>5</v>
@@ -2800,13 +2797,13 @@
         <v>4</v>
       </c>
       <c r="B171" s="2">
-        <v>45604</v>
+        <v>45640</v>
       </c>
       <c r="C171" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -2814,13 +2811,13 @@
         <v>4</v>
       </c>
       <c r="B172" s="2">
-        <v>45605</v>
+        <v>45640</v>
       </c>
       <c r="C172" s="2">
-        <v>58</v>
+        <v>166</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -2828,13 +2825,13 @@
         <v>4</v>
       </c>
       <c r="B173" s="2">
-        <v>45607</v>
+        <v>45605</v>
       </c>
       <c r="C173" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -2842,13 +2839,13 @@
         <v>4</v>
       </c>
       <c r="B174" s="2">
-        <v>45613</v>
+        <v>45605</v>
       </c>
       <c r="C174" s="2">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -2856,10 +2853,10 @@
         <v>4</v>
       </c>
       <c r="B175" s="2">
-        <v>45613</v>
+        <v>45607</v>
       </c>
       <c r="C175" s="2">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>5</v>
@@ -2870,13 +2867,13 @@
         <v>4</v>
       </c>
       <c r="B176" s="2">
-        <v>45614</v>
+        <v>45608</v>
       </c>
       <c r="C176" s="2">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -2884,13 +2881,13 @@
         <v>4</v>
       </c>
       <c r="B177" s="2">
-        <v>45615</v>
+        <v>45608</v>
       </c>
       <c r="C177" s="2">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -2898,13 +2895,13 @@
         <v>4</v>
       </c>
       <c r="B178" s="2">
-        <v>45617</v>
+        <v>45610</v>
       </c>
       <c r="C178" s="2">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -2912,13 +2909,13 @@
         <v>4</v>
       </c>
       <c r="B179" s="2">
-        <v>45619</v>
+        <v>45611</v>
       </c>
       <c r="C179" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -2926,13 +2923,13 @@
         <v>4</v>
       </c>
       <c r="B180" s="2">
-        <v>45620</v>
+        <v>45612</v>
       </c>
       <c r="C180" s="2">
-        <v>245</v>
+        <v>4</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -2940,10 +2937,10 @@
         <v>4</v>
       </c>
       <c r="B181" s="2">
-        <v>45621</v>
+        <v>45613</v>
       </c>
       <c r="C181" s="2">
-        <v>412</v>
+        <v>32</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>5</v>
@@ -2954,7 +2951,7 @@
         <v>4</v>
       </c>
       <c r="B182" s="2">
-        <v>45622</v>
+        <v>45614</v>
       </c>
       <c r="C182" s="2">
         <v>2</v>
@@ -2968,13 +2965,13 @@
         <v>4</v>
       </c>
       <c r="B183" s="2">
-        <v>45623</v>
+        <v>45614</v>
       </c>
       <c r="C183" s="2">
-        <v>349</v>
+        <v>236</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -2982,13 +2979,13 @@
         <v>4</v>
       </c>
       <c r="B184" s="2">
-        <v>45623</v>
+        <v>45614</v>
       </c>
       <c r="C184" s="2">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -2996,10 +2993,10 @@
         <v>4</v>
       </c>
       <c r="B185" s="2">
-        <v>45624</v>
+        <v>45616</v>
       </c>
       <c r="C185" s="2">
-        <v>957</v>
+        <v>33</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>5</v>
@@ -3010,10 +3007,10 @@
         <v>4</v>
       </c>
       <c r="B186" s="2">
-        <v>45625</v>
+        <v>45617</v>
       </c>
       <c r="C186" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>5</v>
@@ -3024,13 +3021,13 @@
         <v>4</v>
       </c>
       <c r="B187" s="2">
-        <v>45626</v>
+        <v>45617</v>
       </c>
       <c r="C187" s="2">
-        <v>7</v>
+        <v>209</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3038,10 +3035,10 @@
         <v>4</v>
       </c>
       <c r="B188" s="2">
-        <v>45627</v>
+        <v>45617</v>
       </c>
       <c r="C188" s="2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>6</v>
@@ -3052,10 +3049,10 @@
         <v>4</v>
       </c>
       <c r="B189" s="2">
-        <v>45627</v>
+        <v>45618</v>
       </c>
       <c r="C189" s="2">
-        <v>1018</v>
+        <v>8</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>5</v>
@@ -3066,10 +3063,10 @@
         <v>4</v>
       </c>
       <c r="B190" s="2">
-        <v>45627</v>
+        <v>45618</v>
       </c>
       <c r="C190" s="2">
-        <v>9</v>
+        <v>770</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>5</v>
@@ -3080,13 +3077,13 @@
         <v>4</v>
       </c>
       <c r="B191" s="2">
-        <v>45628</v>
+        <v>45620</v>
       </c>
       <c r="C191" s="2">
-        <v>88</v>
+        <v>298</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -3094,10 +3091,10 @@
         <v>4</v>
       </c>
       <c r="B192" s="2">
-        <v>45629</v>
+        <v>45621</v>
       </c>
       <c r="C192" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>5</v>
@@ -3108,13 +3105,13 @@
         <v>4</v>
       </c>
       <c r="B193" s="2">
-        <v>45630</v>
+        <v>45621</v>
       </c>
       <c r="C193" s="2">
-        <v>20</v>
+        <v>480</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3122,10 +3119,10 @@
         <v>4</v>
       </c>
       <c r="B194" s="2">
-        <v>45630</v>
+        <v>45623</v>
       </c>
       <c r="C194" s="2">
-        <v>392</v>
+        <v>1</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>5</v>
@@ -3136,10 +3133,10 @@
         <v>4</v>
       </c>
       <c r="B195" s="2">
-        <v>45630</v>
+        <v>45624</v>
       </c>
       <c r="C195" s="2">
-        <v>2</v>
+        <v>583</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>5</v>
@@ -3150,10 +3147,10 @@
         <v>4</v>
       </c>
       <c r="B196" s="2">
-        <v>45630</v>
+        <v>45627</v>
       </c>
       <c r="C196" s="2">
-        <v>2</v>
+        <v>637</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>5</v>
@@ -3164,13 +3161,13 @@
         <v>4</v>
       </c>
       <c r="B197" s="2">
-        <v>45631</v>
+        <v>45628</v>
       </c>
       <c r="C197" s="2">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3178,13 +3175,13 @@
         <v>4</v>
       </c>
       <c r="B198" s="2">
-        <v>45632</v>
+        <v>45631</v>
       </c>
       <c r="C198" s="2">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3192,13 +3189,13 @@
         <v>4</v>
       </c>
       <c r="B199" s="2">
-        <v>45633</v>
+        <v>45634</v>
       </c>
       <c r="C199" s="2">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -3206,13 +3203,13 @@
         <v>4</v>
       </c>
       <c r="B200" s="2">
-        <v>45633</v>
+        <v>45634</v>
       </c>
       <c r="C200" s="2">
-        <v>11</v>
+        <v>93</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3220,10 +3217,10 @@
         <v>4</v>
       </c>
       <c r="B201" s="2">
-        <v>45634</v>
+        <v>45636</v>
       </c>
       <c r="C201" s="2">
-        <v>168</v>
+        <v>39</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>5</v>
@@ -3234,13 +3231,13 @@
         <v>4</v>
       </c>
       <c r="B202" s="2">
-        <v>45636</v>
+        <v>45637</v>
       </c>
       <c r="C202" s="2">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3248,13 +3245,13 @@
         <v>4</v>
       </c>
       <c r="B203" s="2">
-        <v>45636</v>
+        <v>45637</v>
       </c>
       <c r="C203" s="2">
-        <v>6</v>
+        <v>778</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -3262,10 +3259,10 @@
         <v>4</v>
       </c>
       <c r="B204" s="2">
-        <v>45637</v>
+        <v>45639</v>
       </c>
       <c r="C204" s="2">
-        <v>133</v>
+        <v>51</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>5</v>
@@ -3276,10 +3273,10 @@
         <v>4</v>
       </c>
       <c r="B205" s="2">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="C205" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>5</v>
@@ -3307,7 +3304,7 @@
         <v>45640</v>
       </c>
       <c r="C207" s="2">
-        <v>88</v>
+        <v>1649</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>8</v>
@@ -3318,13 +3315,13 @@
         <v>4</v>
       </c>
       <c r="B208" s="2">
-        <v>45602</v>
+        <v>45604</v>
       </c>
       <c r="C208" s="2">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -3332,13 +3329,13 @@
         <v>4</v>
       </c>
       <c r="B209" s="2">
-        <v>45605</v>
+        <v>45604</v>
       </c>
       <c r="C209" s="2">
-        <v>137</v>
+        <v>789</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -3349,10 +3346,10 @@
         <v>45605</v>
       </c>
       <c r="C210" s="2">
-        <v>760</v>
+        <v>237</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -3363,7 +3360,7 @@
         <v>45606</v>
       </c>
       <c r="C211" s="2">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>5</v>
@@ -3374,13 +3371,13 @@
         <v>4</v>
       </c>
       <c r="B212" s="2">
-        <v>45611</v>
+        <v>45607</v>
       </c>
       <c r="C212" s="2">
-        <v>4</v>
+        <v>904</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -3388,13 +3385,13 @@
         <v>4</v>
       </c>
       <c r="B213" s="2">
-        <v>45613</v>
+        <v>45609</v>
       </c>
       <c r="C213" s="2">
-        <v>153</v>
+        <v>1</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -3402,13 +3399,13 @@
         <v>4</v>
       </c>
       <c r="B214" s="2">
-        <v>45614</v>
+        <v>45616</v>
       </c>
       <c r="C214" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -3416,13 +3413,13 @@
         <v>4</v>
       </c>
       <c r="B215" s="2">
-        <v>45614</v>
+        <v>45619</v>
       </c>
       <c r="C215" s="2">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -3430,13 +3427,13 @@
         <v>4</v>
       </c>
       <c r="B216" s="2">
-        <v>45616</v>
+        <v>45622</v>
       </c>
       <c r="C216" s="2">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -3444,13 +3441,13 @@
         <v>4</v>
       </c>
       <c r="B217" s="2">
-        <v>45617</v>
+        <v>45622</v>
       </c>
       <c r="C217" s="2">
-        <v>4</v>
+        <v>131</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -3458,13 +3455,13 @@
         <v>4</v>
       </c>
       <c r="B218" s="2">
-        <v>45619</v>
+        <v>45623</v>
       </c>
       <c r="C218" s="2">
-        <v>224</v>
+        <v>61</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -3472,7 +3469,7 @@
         <v>4</v>
       </c>
       <c r="B219" s="2">
-        <v>45620</v>
+        <v>45625</v>
       </c>
       <c r="C219" s="2">
         <v>2</v>
@@ -3486,13 +3483,13 @@
         <v>4</v>
       </c>
       <c r="B220" s="2">
-        <v>45621</v>
+        <v>45625</v>
       </c>
       <c r="C220" s="2">
-        <v>107</v>
+        <v>162</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -3500,10 +3497,10 @@
         <v>4</v>
       </c>
       <c r="B221" s="2">
-        <v>45623</v>
+        <v>45625</v>
       </c>
       <c r="C221" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>5</v>
@@ -3514,13 +3511,13 @@
         <v>4</v>
       </c>
       <c r="B222" s="2">
-        <v>45623</v>
+        <v>45626</v>
       </c>
       <c r="C222" s="2">
-        <v>18</v>
+        <v>302</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -3528,10 +3525,10 @@
         <v>4</v>
       </c>
       <c r="B223" s="2">
-        <v>45625</v>
+        <v>45627</v>
       </c>
       <c r="C223" s="2">
-        <v>707</v>
+        <v>61</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>5</v>
@@ -3542,10 +3539,10 @@
         <v>4</v>
       </c>
       <c r="B224" s="2">
-        <v>45626</v>
+        <v>45628</v>
       </c>
       <c r="C224" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>5</v>
@@ -3556,13 +3553,13 @@
         <v>4</v>
       </c>
       <c r="B225" s="2">
-        <v>45626</v>
+        <v>45628</v>
       </c>
       <c r="C225" s="2">
-        <v>9</v>
+        <v>476</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -3570,13 +3567,13 @@
         <v>4</v>
       </c>
       <c r="B226" s="2">
-        <v>45626</v>
+        <v>45629</v>
       </c>
       <c r="C226" s="2">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -3584,10 +3581,10 @@
         <v>4</v>
       </c>
       <c r="B227" s="2">
-        <v>45627</v>
+        <v>45630</v>
       </c>
       <c r="C227" s="2">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>5</v>
@@ -3598,10 +3595,10 @@
         <v>4</v>
       </c>
       <c r="B228" s="2">
-        <v>45627</v>
+        <v>45630</v>
       </c>
       <c r="C228" s="2">
-        <v>7</v>
+        <v>416</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>5</v>
@@ -3612,13 +3609,13 @@
         <v>4</v>
       </c>
       <c r="B229" s="2">
-        <v>45628</v>
+        <v>45631</v>
       </c>
       <c r="C229" s="2">
-        <v>337</v>
+        <v>383</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -3626,10 +3623,10 @@
         <v>4</v>
       </c>
       <c r="B230" s="2">
-        <v>45629</v>
+        <v>45632</v>
       </c>
       <c r="C230" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D230" s="2" t="s">
         <v>5</v>
@@ -3640,13 +3637,13 @@
         <v>4</v>
       </c>
       <c r="B231" s="2">
-        <v>45630</v>
+        <v>45632</v>
       </c>
       <c r="C231" s="2">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -3654,13 +3651,13 @@
         <v>4</v>
       </c>
       <c r="B232" s="2">
-        <v>45631</v>
+        <v>45633</v>
       </c>
       <c r="C232" s="2">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -3668,10 +3665,10 @@
         <v>4</v>
       </c>
       <c r="B233" s="2">
-        <v>45631</v>
+        <v>45633</v>
       </c>
       <c r="C233" s="2">
-        <v>417</v>
+        <v>881</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>5</v>
@@ -3682,10 +3679,10 @@
         <v>4</v>
       </c>
       <c r="B234" s="2">
-        <v>45632</v>
+        <v>45634</v>
       </c>
       <c r="C234" s="2">
-        <v>114</v>
+        <v>2</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>5</v>
@@ -3696,13 +3693,13 @@
         <v>4</v>
       </c>
       <c r="B235" s="2">
-        <v>45632</v>
+        <v>45634</v>
       </c>
       <c r="C235" s="2">
-        <v>5</v>
+        <v>945</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -3710,10 +3707,10 @@
         <v>4</v>
       </c>
       <c r="B236" s="2">
-        <v>45633</v>
+        <v>45635</v>
       </c>
       <c r="C236" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D236" s="2" t="s">
         <v>5</v>
@@ -3724,13 +3721,13 @@
         <v>4</v>
       </c>
       <c r="B237" s="2">
-        <v>45634</v>
+        <v>45636</v>
       </c>
       <c r="C237" s="2">
-        <v>59</v>
+        <v>338</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -3738,10 +3735,10 @@
         <v>4</v>
       </c>
       <c r="B238" s="2">
-        <v>45634</v>
+        <v>45638</v>
       </c>
       <c r="C238" s="2">
-        <v>1260</v>
+        <v>2</v>
       </c>
       <c r="D238" s="2" t="s">
         <v>5</v>
@@ -3752,10 +3749,10 @@
         <v>4</v>
       </c>
       <c r="B239" s="2">
-        <v>45635</v>
+        <v>45639</v>
       </c>
       <c r="C239" s="2">
-        <v>84</v>
+        <v>816</v>
       </c>
       <c r="D239" s="2" t="s">
         <v>5</v>
@@ -3766,10 +3763,10 @@
         <v>4</v>
       </c>
       <c r="B240" s="2">
-        <v>45635</v>
+        <v>45640</v>
       </c>
       <c r="C240" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>5</v>
@@ -3780,10 +3777,10 @@
         <v>4</v>
       </c>
       <c r="B241" s="2">
-        <v>45636</v>
+        <v>45640</v>
       </c>
       <c r="C241" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D241" s="2" t="s">
         <v>5</v>
@@ -3794,13 +3791,13 @@
         <v>4</v>
       </c>
       <c r="B242" s="2">
-        <v>45637</v>
+        <v>45605</v>
       </c>
       <c r="C242" s="2">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -3808,13 +3805,13 @@
         <v>4</v>
       </c>
       <c r="B243" s="2">
-        <v>45638</v>
+        <v>45606</v>
       </c>
       <c r="C243" s="2">
-        <v>102</v>
+        <v>211</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -3822,10 +3819,10 @@
         <v>4</v>
       </c>
       <c r="B244" s="2">
-        <v>45640</v>
+        <v>45607</v>
       </c>
       <c r="C244" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>5</v>
@@ -3836,13 +3833,13 @@
         <v>4</v>
       </c>
       <c r="B245" s="2">
-        <v>45640</v>
+        <v>45608</v>
       </c>
       <c r="C245" s="2">
-        <v>129</v>
+        <v>16</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -3850,13 +3847,13 @@
         <v>4</v>
       </c>
       <c r="B246" s="2">
-        <v>45605</v>
+        <v>45609</v>
       </c>
       <c r="C246" s="2">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -3864,10 +3861,10 @@
         <v>4</v>
       </c>
       <c r="B247" s="2">
-        <v>45606</v>
+        <v>45610</v>
       </c>
       <c r="C247" s="2">
-        <v>499</v>
+        <v>1</v>
       </c>
       <c r="D247" s="2" t="s">
         <v>5</v>
@@ -3878,13 +3875,13 @@
         <v>4</v>
       </c>
       <c r="B248" s="2">
-        <v>45606</v>
+        <v>45610</v>
       </c>
       <c r="C248" s="2">
-        <v>117</v>
+        <v>237</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -3892,13 +3889,13 @@
         <v>4</v>
       </c>
       <c r="B249" s="2">
-        <v>45606</v>
+        <v>45612</v>
       </c>
       <c r="C249" s="2">
+        <v>208</v>
+      </c>
+      <c r="D249" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D249" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -3906,13 +3903,13 @@
         <v>4</v>
       </c>
       <c r="B250" s="2">
-        <v>45612</v>
+        <v>45613</v>
       </c>
       <c r="C250" s="2">
-        <v>222</v>
+        <v>3</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -3920,10 +3917,10 @@
         <v>4</v>
       </c>
       <c r="B251" s="2">
-        <v>45612</v>
+        <v>45613</v>
       </c>
       <c r="C251" s="2">
-        <v>14</v>
+        <v>606</v>
       </c>
       <c r="D251" s="2" t="s">
         <v>5</v>
@@ -3934,13 +3931,13 @@
         <v>4</v>
       </c>
       <c r="B252" s="2">
-        <v>45614</v>
+        <v>45615</v>
       </c>
       <c r="C252" s="2">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -3948,10 +3945,10 @@
         <v>4</v>
       </c>
       <c r="B253" s="2">
-        <v>45615</v>
+        <v>45616</v>
       </c>
       <c r="C253" s="2">
-        <v>2</v>
+        <v>317</v>
       </c>
       <c r="D253" s="2" t="s">
         <v>5</v>
@@ -3962,13 +3959,13 @@
         <v>4</v>
       </c>
       <c r="B254" s="2">
-        <v>45615</v>
+        <v>45616</v>
       </c>
       <c r="C254" s="2">
-        <v>36</v>
+        <v>202</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -3976,10 +3973,10 @@
         <v>4</v>
       </c>
       <c r="B255" s="2">
-        <v>45615</v>
+        <v>45619</v>
       </c>
       <c r="C255" s="2">
-        <v>2</v>
+        <v>779</v>
       </c>
       <c r="D255" s="2" t="s">
         <v>5</v>
@@ -3990,13 +3987,13 @@
         <v>4</v>
       </c>
       <c r="B256" s="2">
-        <v>45618</v>
+        <v>45619</v>
       </c>
       <c r="C256" s="2">
-        <v>2</v>
+        <v>719</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -4004,13 +4001,13 @@
         <v>4</v>
       </c>
       <c r="B257" s="2">
-        <v>45619</v>
+        <v>45620</v>
       </c>
       <c r="C257" s="2">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -4018,10 +4015,10 @@
         <v>4</v>
       </c>
       <c r="B258" s="2">
-        <v>45620</v>
+        <v>45622</v>
       </c>
       <c r="C258" s="2">
-        <v>93</v>
+        <v>3</v>
       </c>
       <c r="D258" s="2" t="s">
         <v>5</v>
@@ -4032,13 +4029,13 @@
         <v>4</v>
       </c>
       <c r="B259" s="2">
-        <v>45621</v>
+        <v>45622</v>
       </c>
       <c r="C259" s="2">
-        <v>1</v>
+        <v>560</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -4046,7 +4043,7 @@
         <v>4</v>
       </c>
       <c r="B260" s="2">
-        <v>45621</v>
+        <v>45623</v>
       </c>
       <c r="C260" s="2">
         <v>1</v>
@@ -4060,13 +4057,13 @@
         <v>4</v>
       </c>
       <c r="B261" s="2">
-        <v>45622</v>
+        <v>45623</v>
       </c>
       <c r="C261" s="2">
-        <v>1</v>
+        <v>126</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4074,13 +4071,13 @@
         <v>4</v>
       </c>
       <c r="B262" s="2">
-        <v>45622</v>
+        <v>45625</v>
       </c>
       <c r="C262" s="2">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -4088,13 +4085,13 @@
         <v>4</v>
       </c>
       <c r="B263" s="2">
-        <v>45623</v>
+        <v>45625</v>
       </c>
       <c r="C263" s="2">
-        <v>124</v>
+        <v>1117</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -4102,7 +4099,7 @@
         <v>4</v>
       </c>
       <c r="B264" s="2">
-        <v>45624</v>
+        <v>45626</v>
       </c>
       <c r="C264" s="2">
         <v>3</v>
@@ -4116,13 +4113,13 @@
         <v>4</v>
       </c>
       <c r="B265" s="2">
-        <v>45624</v>
+        <v>45626</v>
       </c>
       <c r="C265" s="2">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4130,10 +4127,10 @@
         <v>4</v>
       </c>
       <c r="B266" s="2">
-        <v>45625</v>
+        <v>45628</v>
       </c>
       <c r="C266" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D266" s="2" t="s">
         <v>5</v>
@@ -4144,13 +4141,13 @@
         <v>4</v>
       </c>
       <c r="B267" s="2">
-        <v>45625</v>
+        <v>45628</v>
       </c>
       <c r="C267" s="2">
-        <v>159</v>
+        <v>33</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4158,13 +4155,13 @@
         <v>4</v>
       </c>
       <c r="B268" s="2">
-        <v>45625</v>
+        <v>45629</v>
       </c>
       <c r="C268" s="2">
-        <v>132</v>
+        <v>4</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -4172,13 +4169,13 @@
         <v>4</v>
       </c>
       <c r="B269" s="2">
-        <v>45625</v>
+        <v>45631</v>
       </c>
       <c r="C269" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -4186,10 +4183,10 @@
         <v>4</v>
       </c>
       <c r="B270" s="2">
-        <v>45626</v>
+        <v>45631</v>
       </c>
       <c r="C270" s="2">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="D270" s="2" t="s">
         <v>5</v>
@@ -4200,13 +4197,13 @@
         <v>4</v>
       </c>
       <c r="B271" s="2">
-        <v>45628</v>
+        <v>45634</v>
       </c>
       <c r="C271" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -4214,10 +4211,10 @@
         <v>4</v>
       </c>
       <c r="B272" s="2">
-        <v>45629</v>
+        <v>45634</v>
       </c>
       <c r="C272" s="2">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>5</v>
@@ -4228,13 +4225,13 @@
         <v>4</v>
       </c>
       <c r="B273" s="2">
-        <v>45629</v>
+        <v>45635</v>
       </c>
       <c r="C273" s="2">
-        <v>368</v>
+        <v>2</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -4242,13 +4239,13 @@
         <v>4</v>
       </c>
       <c r="B274" s="2">
-        <v>45631</v>
+        <v>45636</v>
       </c>
       <c r="C274" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -4256,10 +4253,10 @@
         <v>4</v>
       </c>
       <c r="B275" s="2">
-        <v>45632</v>
+        <v>45637</v>
       </c>
       <c r="C275" s="2">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>5</v>
@@ -4270,13 +4267,13 @@
         <v>4</v>
       </c>
       <c r="B276" s="2">
-        <v>45632</v>
+        <v>45638</v>
       </c>
       <c r="C276" s="2">
-        <v>580</v>
+        <v>29</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -4284,96 +4281,12 @@
         <v>4</v>
       </c>
       <c r="B277" s="2">
-        <v>45635</v>
+        <v>45639</v>
       </c>
       <c r="C277" s="2">
-        <v>360</v>
+        <v>7</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="278" spans="1:4">
-      <c r="A278" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B278" s="2">
-        <v>45635</v>
-      </c>
-      <c r="C278" s="2">
-        <v>10</v>
-      </c>
-      <c r="D278" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="279" spans="1:4">
-      <c r="A279" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B279" s="2">
-        <v>45638</v>
-      </c>
-      <c r="C279" s="2">
-        <v>457</v>
-      </c>
-      <c r="D279" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="280" spans="1:4">
-      <c r="A280" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B280" s="2">
-        <v>45638</v>
-      </c>
-      <c r="C280" s="2">
-        <v>193</v>
-      </c>
-      <c r="D280" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="281" spans="1:4">
-      <c r="A281" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B281" s="2">
-        <v>45638</v>
-      </c>
-      <c r="C281" s="2">
-        <v>16</v>
-      </c>
-      <c r="D281" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="282" spans="1:4">
-      <c r="A282" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B282" s="2">
-        <v>45640</v>
-      </c>
-      <c r="C282" s="2">
-        <v>1</v>
-      </c>
-      <c r="D282" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="283" spans="1:4">
-      <c r="A283" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B283" s="2">
-        <v>45640</v>
-      </c>
-      <c r="C283" s="2">
-        <v>7</v>
-      </c>
-      <c r="D283" s="2" t="s">
         <v>5</v>
       </c>
     </row>
